--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{235BDD39-45A8-432A-82E0-0ABA90E07268}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F14895-3FE7-4D5B-B648-918811FDA515}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3915" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3915" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="DASHBOARD" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$359</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPASSE!$A$1:$H$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="199">
   <si>
     <t>Gerador</t>
   </si>
@@ -621,6 +621,27 @@
   </si>
   <si>
     <t>Dashboard de Faturamento</t>
+  </si>
+  <si>
+    <t>JANEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATL. DERCIO 1 </t>
+  </si>
+  <si>
+    <t>VIGNOLI - JOAQUIM NAB</t>
+  </si>
+  <si>
+    <t>VIGNOLI - VIRGILIO TAVORA</t>
+  </si>
+  <si>
+    <t>CICLO ENERGY</t>
+  </si>
+  <si>
+    <t>JOSÉ RIBAMAR/VALERIA</t>
+  </si>
+  <si>
+    <t>EMÍLIO RIBAS - RU ITAIÇABA, 111</t>
   </si>
 </sst>
 </file>
@@ -663,7 +684,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,12 +694,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,7 +723,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -719,9 +734,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -733,20 +745,20 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4824,7 +4836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G364"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -4838,25 +4850,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8483,7 +8495,7 @@
       <c r="B153" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D153" s="3" t="s">
@@ -10248,7 +10260,7 @@
         <v>0.1</v>
       </c>
       <c r="G226" s="2">
-        <f t="shared" ref="G226:G246" si="7">E226*F226</f>
+        <f t="shared" ref="G226:G289" si="7">E226*F226</f>
         <v>393.93000000000006</v>
       </c>
     </row>
@@ -10732,8 +10744,2840 @@
         <v>380.26400000000001</v>
       </c>
     </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E247" s="2">
+        <v>718.9</v>
+      </c>
+      <c r="F247" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G247" s="2">
+        <f t="shared" si="7"/>
+        <v>71.89</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A248" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E248" s="2">
+        <v>5054.72</v>
+      </c>
+      <c r="F248" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G248" s="2">
+        <f t="shared" si="7"/>
+        <v>505.47200000000004</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A249" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E249" s="2">
+        <v>189.44</v>
+      </c>
+      <c r="F249" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G249" s="2">
+        <f t="shared" si="7"/>
+        <v>18.943999999999999</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A250" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E250" s="2">
+        <v>6490.24</v>
+      </c>
+      <c r="F250" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G250" s="2">
+        <f t="shared" si="7"/>
+        <v>649.024</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E251" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F251" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G251" s="2">
+        <f t="shared" si="7"/>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E252" s="2">
+        <v>0</v>
+      </c>
+      <c r="F252" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G252" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E253" s="2">
+        <v>2245.1</v>
+      </c>
+      <c r="F253" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G253" s="2">
+        <f t="shared" si="7"/>
+        <v>224.51</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E254" s="2">
+        <v>1179.75</v>
+      </c>
+      <c r="F254" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G254" s="2">
+        <f t="shared" si="7"/>
+        <v>117.97500000000001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E255" s="2">
+        <v>107.52</v>
+      </c>
+      <c r="F255" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G255" s="2">
+        <f t="shared" si="7"/>
+        <v>10.752000000000001</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A256" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E256" s="2">
+        <v>1865.5</v>
+      </c>
+      <c r="F256" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G256" s="2">
+        <f t="shared" si="7"/>
+        <v>186.55</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E257" s="2">
+        <v>0</v>
+      </c>
+      <c r="F257" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G257" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A258" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E258" s="2">
+        <v>0</v>
+      </c>
+      <c r="F258" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G258" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E259" s="2">
+        <v>0</v>
+      </c>
+      <c r="F259" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G259" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E260" s="2">
+        <v>0</v>
+      </c>
+      <c r="F260" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G260" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A261" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E261" s="2">
+        <v>0</v>
+      </c>
+      <c r="F261" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G261" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A262" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E262" s="2">
+        <v>0</v>
+      </c>
+      <c r="F262" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G262" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E263" s="2">
+        <v>9835.1299999999992</v>
+      </c>
+      <c r="F263" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G263" s="2">
+        <f t="shared" si="7"/>
+        <v>983.51299999999992</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A264" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E264" s="2">
+        <v>1855.26</v>
+      </c>
+      <c r="F264" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G264" s="2">
+        <f t="shared" si="7"/>
+        <v>185.52600000000001</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A265" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E265" s="2">
+        <v>7585.28</v>
+      </c>
+      <c r="F265" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G265" s="2">
+        <f t="shared" si="7"/>
+        <v>606.82240000000002</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A266" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E266" s="2">
+        <v>7077.12</v>
+      </c>
+      <c r="F266" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G266" s="2">
+        <f t="shared" si="7"/>
+        <v>566.16960000000006</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E267" s="2">
+        <v>2645.76</v>
+      </c>
+      <c r="F267" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G267" s="2">
+        <f t="shared" si="7"/>
+        <v>211.66080000000002</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A268" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E268" s="2">
+        <v>1724.16</v>
+      </c>
+      <c r="F268" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G268" s="2">
+        <f t="shared" si="7"/>
+        <v>137.93280000000001</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A269" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E269" s="2">
+        <v>1739.88</v>
+      </c>
+      <c r="F269" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G269" s="2">
+        <f t="shared" si="7"/>
+        <v>139.19040000000001</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A270" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E270" s="2">
+        <v>2113.56</v>
+      </c>
+      <c r="F270" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G270" s="2">
+        <f t="shared" si="7"/>
+        <v>169.0848</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A271" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E271" s="2">
+        <v>2683.96</v>
+      </c>
+      <c r="F271" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G271" s="2">
+        <f t="shared" si="7"/>
+        <v>214.71680000000001</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A272" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E272" s="2">
+        <v>2682.6</v>
+      </c>
+      <c r="F272" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G272" s="2">
+        <f t="shared" si="7"/>
+        <v>214.608</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A273" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E273" s="2">
+        <v>4448.5600000000004</v>
+      </c>
+      <c r="F273" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G273" s="2">
+        <f t="shared" si="7"/>
+        <v>355.88480000000004</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A274" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E274" s="2">
+        <v>2325.7800000000002</v>
+      </c>
+      <c r="F274" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G274" s="2">
+        <f t="shared" si="7"/>
+        <v>186.06240000000003</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A275" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E275" s="2">
+        <v>3972.24</v>
+      </c>
+      <c r="F275" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G275" s="2">
+        <f t="shared" si="7"/>
+        <v>317.7792</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A276" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E276" s="2">
+        <v>743.16</v>
+      </c>
+      <c r="F276" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G276" s="2">
+        <f t="shared" si="7"/>
+        <v>59.452799999999996</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A277" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E277" s="2">
+        <v>349.8</v>
+      </c>
+      <c r="F277" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G277" s="2">
+        <f t="shared" si="7"/>
+        <v>27.984000000000002</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E278" s="2">
+        <v>1247.54</v>
+      </c>
+      <c r="F278" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G278" s="2">
+        <f t="shared" si="7"/>
+        <v>99.803200000000004</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A279" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E279" s="2">
+        <v>399.31</v>
+      </c>
+      <c r="F279" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G279" s="2">
+        <f t="shared" si="7"/>
+        <v>31.944800000000001</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A280" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E280" s="2">
+        <v>1170.8499999999999</v>
+      </c>
+      <c r="F280" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G280" s="2">
+        <f t="shared" si="7"/>
+        <v>93.667999999999992</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A281" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E281" s="2">
+        <v>1122.6600000000001</v>
+      </c>
+      <c r="F281" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G281" s="2">
+        <f t="shared" si="7"/>
+        <v>89.81280000000001</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E282" s="2">
+        <v>228.69</v>
+      </c>
+      <c r="F282" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G282" s="2">
+        <f t="shared" si="7"/>
+        <v>18.295200000000001</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E283" s="2">
+        <v>90.52</v>
+      </c>
+      <c r="F283" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G283" s="2">
+        <f t="shared" si="7"/>
+        <v>7.2416</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E284" s="2">
+        <v>366.49</v>
+      </c>
+      <c r="F284" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G284" s="2">
+        <f t="shared" si="7"/>
+        <v>29.319200000000002</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A285" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E285" s="2">
+        <v>282.74</v>
+      </c>
+      <c r="F285" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G285" s="2">
+        <f t="shared" si="7"/>
+        <v>22.619200000000003</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A286" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E286" s="2">
+        <v>260.63</v>
+      </c>
+      <c r="F286" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G286" s="2">
+        <f t="shared" si="7"/>
+        <v>20.8504</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A287" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E287" s="2">
+        <v>369.24</v>
+      </c>
+      <c r="F287" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G287" s="2">
+        <f t="shared" si="7"/>
+        <v>29.539200000000001</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A288" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E288" s="2">
+        <v>552.66999999999996</v>
+      </c>
+      <c r="F288" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G288" s="2">
+        <f t="shared" si="7"/>
+        <v>44.2136</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A289" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E289" s="2">
+        <v>651.33000000000004</v>
+      </c>
+      <c r="F289" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G289" s="2">
+        <f t="shared" si="7"/>
+        <v>52.106400000000008</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E290" s="2">
+        <v>1131.08</v>
+      </c>
+      <c r="F290" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G290" s="2">
+        <f t="shared" ref="G290:G364" si="8">E290*F290</f>
+        <v>90.486399999999989</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A291" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E291" s="2">
+        <v>950.39</v>
+      </c>
+      <c r="F291" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G291" s="2">
+        <f t="shared" si="8"/>
+        <v>76.031199999999998</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A292" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E292" s="2">
+        <v>9944.32</v>
+      </c>
+      <c r="F292" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G292" s="2">
+        <f t="shared" si="8"/>
+        <v>497.21600000000001</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A293" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E293" s="2">
+        <v>4992</v>
+      </c>
+      <c r="F293" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G293" s="2">
+        <f t="shared" si="8"/>
+        <v>249.60000000000002</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A294" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E294" s="2">
+        <v>9592.9599999999991</v>
+      </c>
+      <c r="F294" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G294" s="2">
+        <f t="shared" si="8"/>
+        <v>479.64799999999997</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A295" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E295" s="2">
+        <v>2715.7</v>
+      </c>
+      <c r="F295" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G295" s="2">
+        <f t="shared" si="8"/>
+        <v>135.785</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A296" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E296" s="2">
+        <v>0</v>
+      </c>
+      <c r="F296" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G296" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A297" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E297" s="2">
+        <v>3918.08</v>
+      </c>
+      <c r="F297" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G297" s="2">
+        <f t="shared" si="8"/>
+        <v>195.904</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A298" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E298" s="2">
+        <v>3026.56</v>
+      </c>
+      <c r="F298" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G298" s="2">
+        <f t="shared" si="8"/>
+        <v>151.328</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A299" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E299" s="2">
+        <v>2875.52</v>
+      </c>
+      <c r="F299" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G299" s="2">
+        <f t="shared" si="8"/>
+        <v>143.77600000000001</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A300" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E300" s="2">
+        <v>4040.84</v>
+      </c>
+      <c r="F300" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G300" s="2">
+        <f t="shared" si="8"/>
+        <v>202.04200000000003</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A301" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E301" s="2">
+        <v>1638.65</v>
+      </c>
+      <c r="F301" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G301" s="2">
+        <f t="shared" si="8"/>
+        <v>81.932500000000005</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A302" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E302" s="2">
+        <v>4709.76</v>
+      </c>
+      <c r="F302" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G302" s="2">
+        <f t="shared" si="8"/>
+        <v>235.48800000000003</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A303" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E303" s="2">
+        <v>2125.0700000000002</v>
+      </c>
+      <c r="F303" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G303" s="2">
+        <f t="shared" si="8"/>
+        <v>106.25350000000002</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A304" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E304" s="2">
+        <v>11772.8</v>
+      </c>
+      <c r="F304" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G304" s="2">
+        <f t="shared" si="8"/>
+        <v>588.64</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A305" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E305" s="2">
+        <v>4799.3599999999997</v>
+      </c>
+      <c r="F305" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G305" s="2">
+        <f t="shared" si="8"/>
+        <v>239.96799999999999</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A306" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E306" s="2">
+        <v>9351.5499999999993</v>
+      </c>
+      <c r="F306" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G306" s="2">
+        <f t="shared" si="8"/>
+        <v>467.57749999999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A307" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E307" s="2">
+        <v>3016.59</v>
+      </c>
+      <c r="F307" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G307" s="2">
+        <f t="shared" si="8"/>
+        <v>150.82950000000002</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A308" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E308" s="2">
+        <v>997.75</v>
+      </c>
+      <c r="F308" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G308" s="2">
+        <f t="shared" si="8"/>
+        <v>49.887500000000003</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A309" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E309" s="2">
+        <v>577.28</v>
+      </c>
+      <c r="F309" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G309" s="2">
+        <f t="shared" si="8"/>
+        <v>28.864000000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A310" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E310" s="2">
+        <v>1985.1</v>
+      </c>
+      <c r="F310" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G310" s="2">
+        <f t="shared" si="8"/>
+        <v>99.254999999999995</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E311" s="2">
+        <v>592</v>
+      </c>
+      <c r="F311" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G311" s="2">
+        <f t="shared" si="8"/>
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A312" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E312" s="2">
+        <v>5795.2</v>
+      </c>
+      <c r="F312" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G312" s="2">
+        <f t="shared" si="8"/>
+        <v>289.76</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A313" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E313" s="2">
+        <v>4808.32</v>
+      </c>
+      <c r="F313" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G313" s="2">
+        <f t="shared" si="8"/>
+        <v>240.416</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A314" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E314" s="2">
+        <v>748.8</v>
+      </c>
+      <c r="F314" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G314" s="2">
+        <f t="shared" si="8"/>
+        <v>37.44</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A315" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E315" s="2">
+        <v>6457.6</v>
+      </c>
+      <c r="F315" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G315" s="2">
+        <f t="shared" si="8"/>
+        <v>322.88000000000005</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A316" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E316" s="2">
+        <v>0</v>
+      </c>
+      <c r="F316" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G316" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A317" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E317" s="2">
+        <v>975.86</v>
+      </c>
+      <c r="F317" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G317" s="2">
+        <f t="shared" si="8"/>
+        <v>48.793000000000006</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A318" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E318" s="2">
+        <v>931.84</v>
+      </c>
+      <c r="F318" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G318" s="2">
+        <f t="shared" si="8"/>
+        <v>46.592000000000006</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A319" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E319" s="2">
+        <v>6378.24</v>
+      </c>
+      <c r="F319" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G319" s="2">
+        <f t="shared" si="8"/>
+        <v>318.91200000000003</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A320" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E320" s="2">
+        <v>4465.92</v>
+      </c>
+      <c r="F320" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G320" s="2">
+        <f t="shared" si="8"/>
+        <v>223.29600000000002</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A321" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E321" s="2">
+        <v>8159.36</v>
+      </c>
+      <c r="F321" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G321" s="2">
+        <f t="shared" si="8"/>
+        <v>407.96800000000002</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A322" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E322" s="2">
+        <v>5214.8100000000004</v>
+      </c>
+      <c r="F322" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G322" s="2">
+        <f t="shared" si="8"/>
+        <v>417.18480000000005</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A323" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E323" s="2">
+        <v>278.8</v>
+      </c>
+      <c r="F323" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G323" s="2">
+        <f t="shared" si="8"/>
+        <v>22.304000000000002</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A324" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E324" s="2">
+        <v>2493.21</v>
+      </c>
+      <c r="F324" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G324" s="2">
+        <f t="shared" si="8"/>
+        <v>199.45680000000002</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A325" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E325" s="2">
+        <v>346.68</v>
+      </c>
+      <c r="F325" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G325" s="2">
+        <f t="shared" si="8"/>
+        <v>27.734400000000001</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A326" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E326" s="2">
+        <v>1513.08</v>
+      </c>
+      <c r="F326" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G326" s="2">
+        <f t="shared" si="8"/>
+        <v>121.04639999999999</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A327" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E327" s="2">
+        <v>478.44</v>
+      </c>
+      <c r="F327" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G327" s="2">
+        <f t="shared" si="8"/>
+        <v>38.275199999999998</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A328" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E328" s="2">
+        <v>1092.42</v>
+      </c>
+      <c r="F328" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G328" s="2">
+        <f t="shared" si="8"/>
+        <v>87.393600000000006</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A329" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E329" s="2">
+        <v>731.16</v>
+      </c>
+      <c r="F329" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G329" s="2">
+        <f t="shared" si="8"/>
+        <v>58.492799999999995</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A330" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E330" s="2">
+        <v>4804.38</v>
+      </c>
+      <c r="F330" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G330" s="2">
+        <f t="shared" si="8"/>
+        <v>384.35040000000004</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A331" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E331" s="2">
+        <v>1558.26</v>
+      </c>
+      <c r="F331" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G331" s="2">
+        <f t="shared" si="8"/>
+        <v>124.66080000000001</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A332" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E332" s="2">
+        <v>668.58</v>
+      </c>
+      <c r="F332" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G332" s="2">
+        <f t="shared" si="8"/>
+        <v>53.486400000000003</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A333" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E333" s="2">
+        <v>5931.9</v>
+      </c>
+      <c r="F333" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G333" s="2">
+        <f t="shared" si="8"/>
+        <v>474.55199999999996</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A334" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E334" s="2">
+        <v>13848.45</v>
+      </c>
+      <c r="F334" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G334" s="2">
+        <f t="shared" si="8"/>
+        <v>1107.876</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A335" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E335" s="2">
+        <v>349.44</v>
+      </c>
+      <c r="F335" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G335" s="2">
+        <f t="shared" si="8"/>
+        <v>27.955200000000001</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A336" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E336" s="2">
+        <v>4429.1899999999996</v>
+      </c>
+      <c r="F336" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G336" s="2">
+        <f t="shared" si="8"/>
+        <v>354.33519999999999</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A337" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E337" s="2">
+        <v>2655.25</v>
+      </c>
+      <c r="F337" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G337" s="2">
+        <f t="shared" si="8"/>
+        <v>212.42000000000002</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A338" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E338" s="2">
+        <v>11098.88</v>
+      </c>
+      <c r="F338" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G338" s="2">
+        <f t="shared" si="8"/>
+        <v>887.91039999999998</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A339" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E339" s="2">
+        <v>7549.44</v>
+      </c>
+      <c r="F339" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G339" s="2">
+        <f t="shared" si="8"/>
+        <v>603.95519999999999</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A340" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E340" s="2">
+        <v>0</v>
+      </c>
+      <c r="F340" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G340" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A341" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E341" s="2">
+        <v>4457.8</v>
+      </c>
+      <c r="F341" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G341" s="2">
+        <f t="shared" si="8"/>
+        <v>356.62400000000002</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A342" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E342" s="2">
+        <v>0</v>
+      </c>
+      <c r="F342" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G342" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A343" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E343" s="2">
+        <v>1365.12</v>
+      </c>
+      <c r="F343" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G343" s="2">
+        <f t="shared" si="8"/>
+        <v>109.20959999999999</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A344" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E344" s="2">
+        <v>4877.28</v>
+      </c>
+      <c r="F344" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G344" s="2">
+        <f t="shared" si="8"/>
+        <v>390.18239999999997</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A345" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E345" s="2">
+        <v>1555.85</v>
+      </c>
+      <c r="F345" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G345" s="2">
+        <f t="shared" si="8"/>
+        <v>155.58500000000001</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A346" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E346" s="2">
+        <v>4855.1400000000003</v>
+      </c>
+      <c r="F346" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G346" s="2">
+        <f t="shared" si="8"/>
+        <v>485.51400000000007</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A347" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E347" s="2">
+        <v>0</v>
+      </c>
+      <c r="F347" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G347" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A348" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E348" s="2">
+        <v>10177.73</v>
+      </c>
+      <c r="F348" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G348" s="2">
+        <f t="shared" si="8"/>
+        <v>1017.773</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A349" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E349" s="2">
+        <v>2052</v>
+      </c>
+      <c r="F349" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G349" s="2">
+        <f t="shared" si="8"/>
+        <v>205.20000000000002</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A350" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E350" s="2">
+        <v>9938.7000000000007</v>
+      </c>
+      <c r="F350" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G350" s="2">
+        <f t="shared" si="8"/>
+        <v>993.87000000000012</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A351" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E351" s="2">
+        <v>0</v>
+      </c>
+      <c r="F351" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G351" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A352" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E352" s="2">
+        <v>0</v>
+      </c>
+      <c r="F352" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G352" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A353" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E353" s="2">
+        <v>1579.52</v>
+      </c>
+      <c r="F353" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G353" s="2">
+        <f t="shared" si="8"/>
+        <v>157.952</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A354" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E354" s="2">
+        <v>8942.0499999999993</v>
+      </c>
+      <c r="F354" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G354" s="2">
+        <f t="shared" si="8"/>
+        <v>894.20499999999993</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A355" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E355" s="2">
+        <v>3041.28</v>
+      </c>
+      <c r="F355" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G355" s="2">
+        <f t="shared" si="8"/>
+        <v>304.12800000000004</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A356" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E356" s="2">
+        <v>6325.76</v>
+      </c>
+      <c r="F356" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G356" s="2">
+        <f t="shared" si="8"/>
+        <v>632.57600000000002</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A357" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E357" s="2">
+        <v>2908.8</v>
+      </c>
+      <c r="F357" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G357" s="2">
+        <f t="shared" si="8"/>
+        <v>290.88000000000005</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A358" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E358" s="2">
+        <v>8320.0300000000007</v>
+      </c>
+      <c r="F358" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G358" s="2">
+        <f t="shared" si="8"/>
+        <v>832.00300000000016</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A359" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E359" s="2">
+        <v>5274.08</v>
+      </c>
+      <c r="F359" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G359" s="2">
+        <f t="shared" si="8"/>
+        <v>527.40800000000002</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A360" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E360" s="2">
+        <v>0</v>
+      </c>
+      <c r="F360" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G360" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A361" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E361" s="2">
+        <v>1362.44</v>
+      </c>
+      <c r="F361" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G361" s="2">
+        <f t="shared" si="8"/>
+        <v>136.244</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A362" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E362" s="2">
+        <v>4779.0600000000004</v>
+      </c>
+      <c r="F362" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G362" s="2">
+        <f t="shared" si="8"/>
+        <v>477.90600000000006</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A363" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E363" s="2">
+        <v>2309.5</v>
+      </c>
+      <c r="F363" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G363" s="2">
+        <f t="shared" si="8"/>
+        <v>230.95000000000002</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A364" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E364" s="2">
+        <v>4280.76</v>
+      </c>
+      <c r="F364" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G364" s="2">
+        <f t="shared" si="8"/>
+        <v>428.07600000000002</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G246" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G359" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
@@ -10744,533 +13588,533 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>625.29999999999995</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>62.53</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>70.849999999999994</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>491.92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <v>4282.24</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>428.22</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>485.18</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <v>3368.84</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>170.24</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>17.02</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>19.29</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>133.93</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>4209.28</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>420.93</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>476.91</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>3311.44</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>16.899999999999999</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>1.69</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>1.91</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <v>13.3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>103.9</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>10.39</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>11.77</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <v>81.739999999999995</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>2209.35</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>220.94</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <v>250.32</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <v>1738.1</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>216.45</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>21.65</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>24.52</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <v>170.28</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>182.4</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>18.239999999999998</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <v>20.67</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <v>143.49</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>1202.5</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <v>120.25</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>136.24</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <v>946.01</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>1301.1199999999999</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <v>130.11000000000001</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <v>147.41999999999999</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <v>1023.59</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <v>1301.1199999999999</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <v>130.11000000000001</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <v>147.41999999999999</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <v>1023.59</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>3385.3</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <v>338.53</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <v>383.55</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="10">
         <v>2663.22</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <v>2997.06</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <v>299.70999999999998</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <v>339.57</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <v>2357.79</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <v>9098.8799999999992</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <v>909.89</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <v>1030.9000000000001</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="10">
         <v>7158.09</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <v>8613.02</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <v>861.3</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="10">
         <v>975.86</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="10">
         <v>6775.86</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <v>3396.6</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <v>339.66</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <v>384.83</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="10">
         <v>2672.11</v>
       </c>
     </row>
@@ -11291,7 +14135,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>162</v>
       </c>
       <c r="B1" t="s">
@@ -11302,29 +14146,29 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>334716.67832000001</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>25966.215131999994</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>311772.45000000013</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>24783.780699999992</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>162</v>
       </c>
       <c r="B5" t="s">
@@ -11335,101 +14179,101 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>3802.64</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>380.26400000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>1936.44</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>193.64400000000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>41199.668320000012</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>4119.9668320000001</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>58476.01</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>5847.6009999999997</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>129470.60999999997</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>12935.115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>240696.38000000006</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>12034.818999999998</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>26735.55</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>2673.5550000000003</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>51564.23</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>5156.4230000000007</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>92607.600000000049</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>7408.6080000000002</v>
       </c>
     </row>
@@ -11443,19 +14287,19 @@
   <dimension ref="K4:Q4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="4" spans="11:17" ht="36.6" x14ac:dyDescent="0.7">
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,24 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F14895-3FE7-4D5B-B648-918811FDA515}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E01E1C-503D-425F-91F0-AFE00C07651A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3915" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25140" yWindow="-135" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
     <sheet name="REPASSE" sheetId="3" r:id="rId2"/>
-    <sheet name="ORG. GRAF" sheetId="4" r:id="rId3"/>
-    <sheet name="DASHBOARD" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$363</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPASSE!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="194">
   <si>
     <t>Gerador</t>
   </si>
@@ -530,15 +525,6 @@
   </si>
   <si>
     <t>Mês de Competência</t>
-  </si>
-  <si>
-    <t>Rótulos de Linha</t>
-  </si>
-  <si>
-    <t>Soma de Valor a Pagar para Gerador (R$)</t>
-  </si>
-  <si>
-    <t>Soma de Valor da Gestão (R$)</t>
   </si>
   <si>
     <t>GERADOR</t>
@@ -620,9 +606,6 @@
     <t>MARFRAN</t>
   </si>
   <si>
-    <t>Dashboard de Faturamento</t>
-  </si>
-  <si>
     <t>JANEIRO</t>
   </si>
   <si>
@@ -633,9 +616,6 @@
   </si>
   <si>
     <t>VIGNOLI - VIRGILIO TAVORA</t>
-  </si>
-  <si>
-    <t>CICLO ENERGY</t>
   </si>
   <si>
     <t>JOSÉ RIBAMAR/VALERIA</t>
@@ -652,7 +632,7 @@
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -675,27 +655,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FFFFB549"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -723,43 +689,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -783,3772 +737,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>392429</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>78106</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>196215</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>133975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagem 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{235A5C27-E00A-4FB7-AA3D-7AE2CA8CD89C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="392429" y="259081"/>
-          <a:ext cx="2851786" cy="1065519"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Notebook" refreshedDate="46049.656656597224" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="245" xr:uid="{AF3C71DA-463D-49DD-8A61-8133C4D771B8}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G246" sheet="FATURAMENTO Á RECEBER"/>
-  </cacheSource>
-  <cacheFields count="7">
-    <cacheField name="Gerador" numFmtId="0">
-      <sharedItems count="9">
-        <s v="FAZENDA IPU TIJUCA "/>
-        <s v="SUNCE  "/>
-        <s v="TRAJANO SOLAR "/>
-        <s v="SOLARE ENERGIA "/>
-        <s v="SATIER "/>
-        <s v="MAV ENERGIA "/>
-        <s v="SUNTEB GESTÃO "/>
-        <s v="CYCLO ENERGY"/>
-        <s v="ÁGIOS ENERGIA"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Usina" numFmtId="0">
-      <sharedItems count="17">
-        <s v="ALEX USINA PEQUENA "/>
-        <s v="ALEX USINA GRANDE "/>
-        <s v="LUAN MACHADO "/>
-        <s v="MERC. LADEIRA GRANDE "/>
-        <s v="CEPECE4/ IPU (SETEMBRO)"/>
-        <s v="CEPECE 05"/>
-        <s v="GUARARAPES"/>
-        <s v="SUNCE"/>
-        <s v="TRAJANO SOLAR"/>
-        <s v="ITERU "/>
-        <s v="MSAFE"/>
-        <s v="GOLD "/>
-        <s v="SATIER"/>
-        <s v="MAV ENERGIA"/>
-        <s v="SUNTEB GESTÃO"/>
-        <s v="CYCLO ENERGY"/>
-        <s v="ÁGIOS ENERGIA"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Cliente Final" numFmtId="0">
-      <sharedItems count="129">
-        <s v="POLE ALIMENTOS "/>
-        <s v="SANTA CLARA"/>
-        <s v="ATL. OBERDAN (MUDOU RATEIO)"/>
-        <s v="ATL. PACATUBA"/>
-        <s v="ATL. MANUT FGO"/>
-        <s v="ATL. CALIFORNIA"/>
-        <s v="ATL. DERCIO 1"/>
-        <s v="ATL. PACATUBA (MUDOU RATEIO)"/>
-        <s v="ATL VARJOTA 01"/>
-        <s v="ATL SANTA RITA "/>
-        <s v="ATL SUINO SÃO GON 1"/>
-        <s v="ATL FÁTIMA 3"/>
-        <s v="ATL. OBERDAN"/>
-        <s v="CRISTAL AGROPECUARIA"/>
-        <s v="REGINA (YPIOCA) "/>
-        <s v="VIGNOLI - DESEM LEITE ALB."/>
-        <s v="VIGNOLI- JOAQUIM NAB"/>
-        <s v="COND ED MAISON KARINE "/>
-        <s v="RMA - BEIRA MAR (LOJA)"/>
-        <s v="RMA - FLORES"/>
-        <s v="RMA - PARANGABA"/>
-        <s v="RMA - BM ( QUIOSQUE)"/>
-        <s v="RMA - EUSEBIO "/>
-        <s v="VIGNOLI  - BEIRA MAR "/>
-        <s v="VIGNOLI  - SANTOS DUMONT"/>
-        <s v="VIGNOLI  - JONAS IDELFONSO"/>
-        <s v="VIGNOLI  - JULIO IBIAPINA  "/>
-        <s v="VIGNOLI  - SILVIA JATHY"/>
-        <s v="VIVA ZOE - M. TOMASIA"/>
-        <s v="VIVA ZOE - TORRES CAMARA"/>
-        <s v="SERGIO FINGER "/>
-        <s v="EVERLANE VAZ "/>
-        <s v="MANUEL ANDRANDE "/>
-        <s v="SG PROPAG"/>
-        <s v="FER - ALAN SANKEY- (64514639)"/>
-        <s v="FER ALAN SANKEY - (64514679)"/>
-        <s v="FER ALAN SANKEY  - (64514813)"/>
-        <s v="FER ALAN SANKEY -  (64515140)"/>
-        <s v="FERROVIA - ALINE "/>
-        <s v="FERROVIA - EVELMA "/>
-        <s v="FERROVIA  - LEILA 01 "/>
-        <s v="FERROVIA  - LEILA 02"/>
-        <s v="LUIZ CAVALCANTE 01"/>
-        <s v="LUIZ CAVALCANTE 02"/>
-        <s v="ATL.ANTICA VARJOTA"/>
-        <s v="ATL.ANTICA TAMARITA"/>
-        <s v="ATL.ANTICA SANTA RITA"/>
-        <s v="ATL.ANTICA PARACURU 02"/>
-        <s v="ATL.ANTICA JOQUEY"/>
-        <s v="ATL.ANTICA EXP. CARIRI"/>
-        <s v="ATL.ANTICA CASARÃO"/>
-        <s v="ATL.ANTICA CANAVIEIRA"/>
-        <s v=" (SUINO SÃO GONÇALO 1)"/>
-        <s v="ATL (SUINO SÃO GONÇALO 2)"/>
-        <s v="ATL.ANTICA CAMP 1"/>
-        <s v="ATL FATIMA 3 - FLORES"/>
-        <s v="FATIMA 3"/>
-        <s v="ATL (SUINO SÃO BENEDITO)"/>
-        <s v="ATL.ANTICA VARJOTA 3"/>
-        <s v="POSTO SANTA CECILIA "/>
-        <s v="ATL.ANTICA SOL NASCENTE "/>
-        <s v="ATL.ANTICA PARACURU "/>
-        <s v="ATL.ANTICA PARACURU 2"/>
-        <s v="ATL.ANTICA PARACURU 1"/>
-        <s v="NILO DOURADO "/>
-        <s v="MANUT FRANGO 2"/>
-        <s v="ATL.ANTICA GRÁUNA"/>
-        <s v="ATL.ANTICA VARJOTA 2"/>
-        <s v="FOGO 36 - FRED BORGES 185"/>
-        <s v="FOGO 36 - FREI MANSUETO 746"/>
-        <s v="CORTILLE - UC - 60857369"/>
-        <s v="CORTILLE - UC - 60914118"/>
-        <s v="CORTILLE - UC - 60857316"/>
-        <s v="CORTILLE - VIC LEITE 523"/>
-        <s v="OFICÍNA DE EVENTOS - SALA B"/>
-        <s v="OFICÍNA DE EVENTOS -2257"/>
-        <s v="BABBI -  UC 60906548"/>
-        <s v="BABBI UC - 60909661"/>
-        <s v="COND.SONETO - UC  60923658"/>
-        <s v="LA RESERVE "/>
-        <s v="ROSSANO"/>
-        <s v="PADARIA"/>
-        <s v="JOSÉ MARIA "/>
-        <s v="CLETO ROCHA ( alberto magno)"/>
-        <s v="CLETO ROCHA ( Rui barbosa)"/>
-        <s v="NEIDE DA SILVA ( DISTRATO)"/>
-        <s v="MAYLA - NEIDE (DISTRATO)"/>
-        <s v="COND SAN JULIANO"/>
-        <s v="NOBBYS FARDAMENTOS "/>
-        <s v="MIO CAFÉ (DISTRATO)"/>
-        <s v="RMA- ÚLTIMA SATIER"/>
-        <s v="RIOS E FROTA "/>
-        <s v="RAPHAEL RAMON ( ENCERRADO)"/>
-        <s v="COND.START CITY BL 01"/>
-        <s v="COND.START CITY BL 02"/>
-        <s v="ED. PORTA DAS MARES "/>
-        <s v="REG ALIM|  REG 1 PIND."/>
-        <s v="REG ALIM| REG 2 PIND."/>
-        <s v="REG ALIM| ANT. CAMÂRA"/>
-        <s v="REG ALIM| ANT. CAMÂRA 1."/>
-        <s v="REG AGRO| CONVIDA 3"/>
-        <s v="REG AGRO| UIRAPURU 2"/>
-        <s v="REG AGRO| AVELIMA"/>
-        <s v="REG AGRO| UIRAPURU 1"/>
-        <s v="REG AGRO| NILO DOURADO"/>
-        <s v="REG AGRO| SABIÁ"/>
-        <s v="REG AGRO| FRANGO VERDE "/>
-        <s v="VIG| JOAQUIM NAB Nº 175"/>
-        <s v="VIG| JONAS IDELFONSO Nº 170"/>
-        <s v="ATL | RAMADA"/>
-        <s v="ATL | MAURITI "/>
-        <s v="ATL | ADROALDO "/>
-        <s v="ATL |PORTEIRAS "/>
-        <s v="ATL | BAIXO ALEGRE "/>
-        <s v="ATL | CHOROZINHO "/>
-        <s v="ATL | VALE VERDE "/>
-        <s v="ATL | ITAREMA "/>
-        <s v="COND.ED EAST SIDE "/>
-        <s v="MARFRAN 1 "/>
-        <s v="MARFRAN 2"/>
-        <s v="GREENLIFE A - INICIA JUNHO"/>
-        <s v="VIGNOLI "/>
-        <s v="SANTA RITA"/>
-        <s v="ATL. DERCIO 1 - IPU"/>
-        <s v="ATL.ANTICA PARACURU 03"/>
-        <s v="ATLAS IMPORTAÇÕES (GD1)"/>
-        <s v="EMÍLIO RIBAS - OLIVEIRA PAIVA"/>
-        <s v="EMÍLIO RIBAS - RU ITAICABA"/>
-        <s v="EMÍLIO RIBAS - BEZERRA DE MENEZES"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Mês de Competência" numFmtId="0">
-      <sharedItems count="2">
-        <s v="NOVEMBRO"/>
-        <s v="DEZEMBRO"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Valor a Pagar para Gerador (R$)" numFmtId="44">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="13760.54" count="224">
-        <n v="719.55"/>
-        <n v="3411.2"/>
-        <n v="0"/>
-        <n v="1082.64832"/>
-        <n v="1726.95"/>
-        <n v="1540.41"/>
-        <n v="199.04"/>
-        <n v="418.84"/>
-        <n v="218.73"/>
-        <n v="219.7"/>
-        <n v="46.72"/>
-        <n v="31.85"/>
-        <n v="151.68"/>
-        <n v="1828.45"/>
-        <n v="5198.8999999999996"/>
-        <n v="11686.48"/>
-        <n v="2248.5100000000002"/>
-        <n v="7392.64"/>
-        <n v="6910.72"/>
-        <n v="2600.96"/>
-        <n v="1721.6"/>
-        <n v="1824"/>
-        <n v="2100.6"/>
-        <n v="2458.88"/>
-        <n v="2789.36"/>
-        <n v="4679.08"/>
-        <n v="2113.02"/>
-        <n v="3013.2"/>
-        <n v="646.79999999999995"/>
-        <n v="532.62"/>
-        <n v="519.91999999999996"/>
-        <n v="264"/>
-        <n v="1372.8"/>
-        <n v="1143.1199999999999"/>
-        <n v="250.4"/>
-        <n v="99.11"/>
-        <n v="401.67"/>
-        <n v="326.04000000000002"/>
-        <n v="261.3"/>
-        <n v="404.29"/>
-        <n v="605.13"/>
-        <n v="633.15"/>
-        <n v="1238.44"/>
-        <n v="951.06"/>
-        <m/>
-        <n v="9101.44"/>
-        <n v="4949.76"/>
-        <n v="6338.56"/>
-        <n v="2715.05"/>
-        <n v="3175.68"/>
-        <n v="6210.56"/>
-        <n v="261.47000000000003"/>
-        <n v="1418.88"/>
-        <n v="3537.92"/>
-        <n v="3828.82"/>
-        <n v="5204.55"/>
-        <n v="5534.1"/>
-        <n v="4553.58"/>
-        <n v="11651.2"/>
-        <n v="4817.92"/>
-        <n v="9120.7999999999993"/>
-        <n v="3503.72"/>
-        <n v="1077.05"/>
-        <n v="694.4"/>
-        <n v="5792.15"/>
-        <n v="613.12"/>
-        <n v="5693.44"/>
-        <n v="4423.68"/>
-        <n v="811.52"/>
-        <n v="6256"/>
-        <n v="1003.52"/>
-        <n v="1112.96"/>
-        <n v="5863.04"/>
-        <n v="4433.92"/>
-        <n v="7269.76"/>
-        <n v="5134.1499999999996"/>
-        <n v="217.6"/>
-        <n v="2311.25"/>
-        <n v="289.44"/>
-        <n v="2266.38"/>
-        <n v="423.9"/>
-        <n v="204.68"/>
-        <n v="993.06"/>
-        <n v="885.6"/>
-        <n v="460.08"/>
-        <n v="4362.66"/>
-        <n v="119.46"/>
-        <n v="1359.6"/>
-        <n v="624.36"/>
-        <n v="5857.38"/>
-        <n v="12081.84"/>
-        <n v="348.16"/>
-        <n v="2118.35"/>
-        <n v="3017.95"/>
-        <n v="10561.28"/>
-        <n v="1683.84"/>
-        <n v="1457.39"/>
-        <n v="969.2"/>
-        <n v="226.56"/>
-        <n v="646.38"/>
-        <n v="394.2"/>
-        <n v="1846.2"/>
-        <n v="4475.5200000000004"/>
-        <n v="293.52"/>
-        <n v="4923.97"/>
-        <n v="1840.86"/>
-        <n v="10140.799999999999"/>
-        <n v="123.55"/>
-        <n v="974.7"/>
-        <n v="9473.1"/>
-        <n v="2930.4"/>
-        <n v="6302.08"/>
-        <n v="2708.48"/>
-        <n v="10157.950000000001"/>
-        <n v="5359.76"/>
-        <n v="625.29999999999995"/>
-        <n v="4282.24"/>
-        <n v="4209.28"/>
-        <n v="16.899999999999999"/>
-        <n v="170.24"/>
-        <n v="103.9"/>
-        <n v="3385.3"/>
-        <n v="2209.35"/>
-        <n v="216.45"/>
-        <n v="182.4"/>
-        <n v="1202.5"/>
-        <n v="1301.1199999999999"/>
-        <n v="10827.67"/>
-        <n v="1972.89"/>
-        <n v="6993.28"/>
-        <n v="5920.64"/>
-        <n v="2229.7600000000002"/>
-        <n v="1454.72"/>
-        <n v="1762.56"/>
-        <n v="1858.14"/>
-        <n v="2284.8000000000002"/>
-        <n v="2589.44"/>
-        <n v="3970.52"/>
-        <n v="1874.34"/>
-        <n v="3972.24"/>
-        <n v="673.86"/>
-        <n v="525.36"/>
-        <n v="1149.72"/>
-        <n v="361.68"/>
-        <n v="1538.46"/>
-        <n v="1244.0999999999999"/>
-        <n v="221.29"/>
-        <n v="87.6"/>
-        <n v="354.99"/>
-        <n v="272.02"/>
-        <n v="282.74"/>
-        <n v="357.3"/>
-        <n v="534.79"/>
-        <n v="735.66"/>
-        <n v="1094.49"/>
-        <n v="1009.19"/>
-        <n v="2281.6"/>
-        <n v="4554.24"/>
-        <n v="5114.88"/>
-        <n v="2676.7"/>
-        <n v="3339.12"/>
-        <n v="2411.52"/>
-        <n v="1457.28"/>
-        <n v="2136.3200000000002"/>
-        <n v="2017.92"/>
-        <n v="2946.45"/>
-        <n v="3961.98"/>
-        <n v="5862.96"/>
-        <n v="11147.52"/>
-        <n v="4141.4399999999996"/>
-        <n v="9165.65"/>
-        <n v="3073.6"/>
-        <n v="1116.7"/>
-        <n v="606.72"/>
-        <n v="6490.25"/>
-        <n v="636.79999999999995"/>
-        <n v="5264"/>
-        <n v="4232.32"/>
-        <n v="727.04"/>
-        <n v="5751.04"/>
-        <n v="856.32"/>
-        <n v="934.4"/>
-        <n v="5598.72"/>
-        <n v="4103.68"/>
-        <n v="7120.64"/>
-        <n v="4696.79"/>
-        <n v="250.92"/>
-        <n v="2305.63"/>
-        <n v="349.38"/>
-        <n v="2183.7600000000002"/>
-        <n v="348.84"/>
-        <n v="1008.18"/>
-        <n v="753.3"/>
-        <n v="4191.4799999999996"/>
-        <n v="1318.02"/>
-        <n v="547.14"/>
-        <n v="5358.42"/>
-        <n v="13760.54"/>
-        <n v="359.04"/>
-        <n v="8692.35"/>
-        <n v="1257.0999999999999"/>
-        <n v="5552"/>
-        <n v="2752.64"/>
-        <n v="4079.61"/>
-        <n v="2874.88"/>
-        <n v="199.68"/>
-        <n v="3939.3"/>
-        <n v="3676.86"/>
-        <n v="1674.16"/>
-        <n v="4469.04"/>
-        <n v="212.52"/>
-        <n v="1724.76"/>
-        <n v="2077.38"/>
-        <n v="3666.56"/>
-        <n v="169.04"/>
-        <n v="3659.58"/>
-        <n v="6730.75"/>
-        <n v="2997.06"/>
-        <n v="6286.08"/>
-        <n v="2812.8"/>
-        <n v="8613.02"/>
-        <n v="3396.6"/>
-        <n v="1936.44"/>
-        <n v="3802.64"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="% Gestão" numFmtId="10">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.05" maxValue="0.1"/>
-    </cacheField>
-    <cacheField name="Valor da Gestão (R$)" numFmtId="44">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1376.0540000000001" count="222">
-        <n v="71.954999999999998"/>
-        <n v="341.12"/>
-        <n v="0"/>
-        <n v="108.26483200000001"/>
-        <n v="172.69500000000002"/>
-        <n v="154.04100000000003"/>
-        <n v="19.904"/>
-        <n v="41.884"/>
-        <n v="21.873000000000001"/>
-        <n v="21.97"/>
-        <n v="4.6719999999999997"/>
-        <n v="3.1850000000000005"/>
-        <n v="15.168000000000001"/>
-        <n v="182.84500000000003"/>
-        <n v="519.89"/>
-        <n v="1168.6479999999999"/>
-        <n v="224.85100000000003"/>
-        <n v="591.41120000000001"/>
-        <n v="552.85760000000005"/>
-        <n v="208.07680000000002"/>
-        <n v="137.72800000000001"/>
-        <n v="145.92000000000002"/>
-        <n v="168.048"/>
-        <n v="196.71040000000002"/>
-        <n v="223.14880000000002"/>
-        <n v="374.32639999999998"/>
-        <n v="169.04159999999999"/>
-        <n v="241.05599999999998"/>
-        <n v="51.744"/>
-        <n v="42.6096"/>
-        <n v="41.593599999999995"/>
-        <n v="21.12"/>
-        <n v="109.824"/>
-        <n v="91.44959999999999"/>
-        <n v="20.032"/>
-        <n v="7.9287999999999998"/>
-        <n v="32.133600000000001"/>
-        <n v="26.083200000000001"/>
-        <n v="20.904"/>
-        <n v="32.343200000000003"/>
-        <n v="48.410400000000003"/>
-        <n v="50.652000000000001"/>
-        <n v="99.075200000000009"/>
-        <n v="76.084800000000001"/>
-        <n v="455.07200000000006"/>
-        <n v="247.48800000000003"/>
-        <n v="316.92800000000005"/>
-        <n v="135.75250000000003"/>
-        <n v="158.78399999999999"/>
-        <n v="310.52800000000002"/>
-        <n v="13.073500000000003"/>
-        <n v="70.944000000000003"/>
-        <n v="176.89600000000002"/>
-        <n v="191.44100000000003"/>
-        <n v="260.22750000000002"/>
-        <n v="276.70500000000004"/>
-        <n v="227.679"/>
-        <n v="582.56000000000006"/>
-        <n v="240.89600000000002"/>
-        <n v="456.03999999999996"/>
-        <n v="175.18600000000001"/>
-        <n v="53.852499999999999"/>
-        <n v="34.72"/>
-        <n v="289.60750000000002"/>
-        <n v="30.656000000000002"/>
-        <n v="284.67199999999997"/>
-        <n v="221.18400000000003"/>
-        <n v="40.576000000000001"/>
-        <n v="312.8"/>
-        <n v="50.176000000000002"/>
-        <n v="55.648000000000003"/>
-        <n v="293.15199999999999"/>
-        <n v="221.69600000000003"/>
-        <n v="363.48800000000006"/>
-        <n v="513.41499999999996"/>
-        <n v="21.76"/>
-        <n v="231.125"/>
-        <n v="28.944000000000003"/>
-        <n v="226.63800000000003"/>
-        <n v="42.39"/>
-        <n v="20.468000000000004"/>
-        <n v="99.305999999999997"/>
-        <n v="88.56"/>
-        <n v="46.008000000000003"/>
-        <n v="436.26600000000002"/>
-        <n v="135.96"/>
-        <n v="62.436000000000007"/>
-        <n v="585.73800000000006"/>
-        <n v="1208.184"/>
-        <n v="34.816000000000003"/>
-        <n v="211.83500000000001"/>
-        <n v="301.79500000000002"/>
-        <n v="1056.1280000000002"/>
-        <n v="168.38400000000001"/>
-        <n v="145.739"/>
-        <n v="96.920000000000016"/>
-        <n v="22.656000000000002"/>
-        <n v="64.638000000000005"/>
-        <n v="39.42"/>
-        <n v="184.62"/>
-        <n v="447.55200000000008"/>
-        <n v="29.352"/>
-        <n v="492.39700000000005"/>
-        <n v="184.08600000000001"/>
-        <n v="1014.0799999999999"/>
-        <n v="12.355"/>
-        <n v="97.470000000000013"/>
-        <n v="947.31000000000006"/>
-        <n v="293.04000000000002"/>
-        <n v="630.20800000000008"/>
-        <n v="270.84800000000001"/>
-        <n v="1015.7950000000001"/>
-        <n v="535.976"/>
-        <n v="62.53"/>
-        <n v="428.22399999999999"/>
-        <n v="420.928"/>
-        <n v="1.69"/>
-        <n v="17.024000000000001"/>
-        <n v="10.39"/>
-        <n v="338.53000000000003"/>
-        <n v="220.935"/>
-        <n v="21.645"/>
-        <n v="18.240000000000002"/>
-        <n v="120.25"/>
-        <n v="130.11199999999999"/>
-        <n v="1082.7670000000001"/>
-        <n v="197.28900000000002"/>
-        <n v="559.4624"/>
-        <n v="473.65120000000002"/>
-        <n v="178.38080000000002"/>
-        <n v="116.3776"/>
-        <n v="141.00479999999999"/>
-        <n v="148.65120000000002"/>
-        <n v="182.78400000000002"/>
-        <n v="207.15520000000001"/>
-        <n v="317.64159999999998"/>
-        <n v="149.94720000000001"/>
-        <n v="317.7792"/>
-        <n v="53.908799999999999"/>
-        <n v="42.028800000000004"/>
-        <n v="91.97760000000001"/>
-        <n v="28.9344"/>
-        <n v="123.07680000000001"/>
-        <n v="99.527999999999992"/>
-        <n v="17.703199999999999"/>
-        <n v="7.008"/>
-        <n v="28.3992"/>
-        <n v="21.761599999999998"/>
-        <n v="22.619200000000003"/>
-        <n v="28.584000000000003"/>
-        <n v="42.783200000000001"/>
-        <n v="58.852800000000002"/>
-        <n v="87.559200000000004"/>
-        <n v="80.735200000000006"/>
-        <n v="114.08"/>
-        <n v="227.71199999999999"/>
-        <n v="255.74400000000003"/>
-        <n v="133.83500000000001"/>
-        <n v="166.95600000000002"/>
-        <n v="120.57600000000001"/>
-        <n v="72.864000000000004"/>
-        <n v="106.81600000000002"/>
-        <n v="100.89600000000002"/>
-        <n v="147.32249999999999"/>
-        <n v="198.09900000000002"/>
-        <n v="293.14800000000002"/>
-        <n v="557.37600000000009"/>
-        <n v="207.072"/>
-        <n v="458.28250000000003"/>
-        <n v="153.68"/>
-        <n v="55.835000000000008"/>
-        <n v="30.336000000000002"/>
-        <n v="324.51250000000005"/>
-        <n v="31.84"/>
-        <n v="263.2"/>
-        <n v="211.61599999999999"/>
-        <n v="36.351999999999997"/>
-        <n v="287.55200000000002"/>
-        <n v="42.816000000000003"/>
-        <n v="46.72"/>
-        <n v="279.93600000000004"/>
-        <n v="205.18400000000003"/>
-        <n v="356.03200000000004"/>
-        <n v="469.67900000000003"/>
-        <n v="25.091999999999999"/>
-        <n v="230.56300000000002"/>
-        <n v="34.938000000000002"/>
-        <n v="218.37600000000003"/>
-        <n v="34.884"/>
-        <n v="100.818"/>
-        <n v="75.33"/>
-        <n v="419.14799999999997"/>
-        <n v="131.80199999999999"/>
-        <n v="54.713999999999999"/>
-        <n v="535.84199999999998"/>
-        <n v="1376.0540000000001"/>
-        <n v="35.904000000000003"/>
-        <n v="869.23500000000013"/>
-        <n v="125.71"/>
-        <n v="555.20000000000005"/>
-        <n v="275.26400000000001"/>
-        <n v="407.96100000000001"/>
-        <n v="287.488"/>
-        <n v="19.968000000000004"/>
-        <n v="393.93000000000006"/>
-        <n v="367.68600000000004"/>
-        <n v="167.41600000000003"/>
-        <n v="446.904"/>
-        <n v="21.252000000000002"/>
-        <n v="172.476"/>
-        <n v="207.73800000000003"/>
-        <n v="366.65600000000001"/>
-        <n v="16.904"/>
-        <n v="365.95800000000003"/>
-        <n v="673.07500000000005"/>
-        <n v="299.70600000000002"/>
-        <n v="628.60800000000006"/>
-        <n v="281.28000000000003"/>
-        <n v="861.30200000000013"/>
-        <n v="339.66"/>
-        <n v="193.64400000000001"/>
-        <n v="380.26400000000001"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="2027058992"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="245">
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="0.1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="0.1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="3"/>
-    <n v="0.1"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="4"/>
-    <n v="0.1"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="5"/>
-    <n v="0.1"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="6"/>
-    <n v="0.1"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="7"/>
-    <n v="0.1"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="8"/>
-    <n v="0.1"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="9"/>
-    <n v="0.1"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="10"/>
-    <n v="0.1"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="0"/>
-    <x v="11"/>
-    <n v="0.1"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="0"/>
-    <x v="12"/>
-    <n v="0.1"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="12"/>
-    <x v="0"/>
-    <x v="13"/>
-    <n v="0.1"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="13"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="14"/>
-    <x v="0"/>
-    <x v="14"/>
-    <n v="0.1"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="0"/>
-    <x v="14"/>
-    <n v="0.1"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-    <x v="15"/>
-    <x v="0"/>
-    <x v="15"/>
-    <n v="0.1"/>
-    <x v="15"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-    <x v="16"/>
-    <x v="0"/>
-    <x v="16"/>
-    <n v="0.1"/>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="17"/>
-    <x v="0"/>
-    <x v="17"/>
-    <n v="0.08"/>
-    <x v="17"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="18"/>
-    <x v="0"/>
-    <x v="18"/>
-    <n v="0.08"/>
-    <x v="18"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="19"/>
-    <x v="0"/>
-    <x v="19"/>
-    <n v="0.08"/>
-    <x v="19"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="20"/>
-    <x v="0"/>
-    <x v="20"/>
-    <n v="0.08"/>
-    <x v="20"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="21"/>
-    <x v="0"/>
-    <x v="21"/>
-    <n v="0.08"/>
-    <x v="21"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="22"/>
-    <x v="0"/>
-    <x v="22"/>
-    <n v="0.08"/>
-    <x v="22"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="23"/>
-    <x v="0"/>
-    <x v="23"/>
-    <n v="0.08"/>
-    <x v="23"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="24"/>
-    <x v="0"/>
-    <x v="24"/>
-    <n v="0.08"/>
-    <x v="24"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="25"/>
-    <x v="0"/>
-    <x v="25"/>
-    <n v="0.08"/>
-    <x v="25"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="26"/>
-    <x v="0"/>
-    <x v="26"/>
-    <n v="0.08"/>
-    <x v="26"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="27"/>
-    <x v="0"/>
-    <x v="27"/>
-    <n v="0.08"/>
-    <x v="27"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="28"/>
-    <x v="0"/>
-    <x v="28"/>
-    <n v="0.08"/>
-    <x v="28"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="29"/>
-    <x v="0"/>
-    <x v="29"/>
-    <n v="0.08"/>
-    <x v="29"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="30"/>
-    <x v="0"/>
-    <x v="30"/>
-    <n v="0.08"/>
-    <x v="30"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="31"/>
-    <x v="0"/>
-    <x v="31"/>
-    <n v="0.08"/>
-    <x v="31"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="32"/>
-    <x v="0"/>
-    <x v="32"/>
-    <n v="0.08"/>
-    <x v="32"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="33"/>
-    <x v="0"/>
-    <x v="33"/>
-    <n v="0.08"/>
-    <x v="33"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="34"/>
-    <x v="0"/>
-    <x v="34"/>
-    <n v="0.08"/>
-    <x v="34"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="35"/>
-    <x v="0"/>
-    <x v="35"/>
-    <n v="0.08"/>
-    <x v="35"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="36"/>
-    <x v="0"/>
-    <x v="36"/>
-    <n v="0.08"/>
-    <x v="36"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="37"/>
-    <x v="0"/>
-    <x v="37"/>
-    <n v="0.08"/>
-    <x v="37"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="38"/>
-    <x v="0"/>
-    <x v="38"/>
-    <n v="0.08"/>
-    <x v="38"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="39"/>
-    <x v="0"/>
-    <x v="39"/>
-    <n v="0.08"/>
-    <x v="39"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="40"/>
-    <x v="0"/>
-    <x v="40"/>
-    <n v="0.08"/>
-    <x v="40"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="41"/>
-    <x v="0"/>
-    <x v="41"/>
-    <n v="0.08"/>
-    <x v="41"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="42"/>
-    <x v="0"/>
-    <x v="42"/>
-    <n v="0.08"/>
-    <x v="42"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="43"/>
-    <x v="0"/>
-    <x v="43"/>
-    <n v="0.08"/>
-    <x v="43"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="44"/>
-    <x v="0"/>
-    <x v="44"/>
-    <n v="0.05"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="45"/>
-    <x v="0"/>
-    <x v="45"/>
-    <n v="0.05"/>
-    <x v="44"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="46"/>
-    <x v="0"/>
-    <x v="44"/>
-    <n v="0.05"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="47"/>
-    <x v="0"/>
-    <x v="46"/>
-    <n v="0.05"/>
-    <x v="45"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="48"/>
-    <x v="0"/>
-    <x v="47"/>
-    <n v="0.05"/>
-    <x v="46"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="49"/>
-    <x v="0"/>
-    <x v="48"/>
-    <n v="0.05"/>
-    <x v="47"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="50"/>
-    <x v="0"/>
-    <x v="49"/>
-    <n v="0.05"/>
-    <x v="48"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="51"/>
-    <x v="0"/>
-    <x v="50"/>
-    <n v="0.05"/>
-    <x v="49"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="52"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.05"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="53"/>
-    <x v="0"/>
-    <x v="51"/>
-    <n v="0.05"/>
-    <x v="50"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="54"/>
-    <x v="0"/>
-    <x v="52"/>
-    <n v="0.05"/>
-    <x v="51"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="55"/>
-    <x v="0"/>
-    <x v="53"/>
-    <n v="0.05"/>
-    <x v="52"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="56"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.05"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="57"/>
-    <x v="0"/>
-    <x v="54"/>
-    <n v="0.05"/>
-    <x v="53"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="58"/>
-    <x v="0"/>
-    <x v="55"/>
-    <n v="0.05"/>
-    <x v="54"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="59"/>
-    <x v="0"/>
-    <x v="56"/>
-    <n v="0.05"/>
-    <x v="55"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="60"/>
-    <x v="0"/>
-    <x v="57"/>
-    <n v="0.05"/>
-    <x v="56"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="61"/>
-    <x v="0"/>
-    <x v="58"/>
-    <n v="0.05"/>
-    <x v="57"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="62"/>
-    <x v="0"/>
-    <x v="59"/>
-    <n v="0.05"/>
-    <x v="58"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="63"/>
-    <x v="0"/>
-    <x v="60"/>
-    <n v="0.05"/>
-    <x v="59"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="64"/>
-    <x v="0"/>
-    <x v="61"/>
-    <n v="0.05"/>
-    <x v="60"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="65"/>
-    <x v="0"/>
-    <x v="62"/>
-    <n v="0.05"/>
-    <x v="61"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="66"/>
-    <x v="0"/>
-    <x v="63"/>
-    <n v="0.05"/>
-    <x v="62"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="67"/>
-    <x v="0"/>
-    <x v="64"/>
-    <n v="0.05"/>
-    <x v="63"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="68"/>
-    <x v="0"/>
-    <x v="65"/>
-    <n v="0.05"/>
-    <x v="64"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="69"/>
-    <x v="0"/>
-    <x v="66"/>
-    <n v="0.05"/>
-    <x v="65"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="70"/>
-    <x v="0"/>
-    <x v="67"/>
-    <n v="0.05"/>
-    <x v="66"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="71"/>
-    <x v="0"/>
-    <x v="68"/>
-    <n v="0.05"/>
-    <x v="67"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="72"/>
-    <x v="0"/>
-    <x v="69"/>
-    <n v="0.05"/>
-    <x v="68"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="73"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.05"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="74"/>
-    <x v="0"/>
-    <x v="70"/>
-    <n v="0.05"/>
-    <x v="69"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="75"/>
-    <x v="0"/>
-    <x v="71"/>
-    <n v="0.05"/>
-    <x v="70"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="76"/>
-    <x v="0"/>
-    <x v="72"/>
-    <n v="0.05"/>
-    <x v="71"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="77"/>
-    <x v="0"/>
-    <x v="73"/>
-    <n v="0.05"/>
-    <x v="72"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="78"/>
-    <x v="0"/>
-    <x v="74"/>
-    <n v="0.05"/>
-    <x v="73"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="79"/>
-    <x v="0"/>
-    <x v="75"/>
-    <n v="0.1"/>
-    <x v="74"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="80"/>
-    <x v="0"/>
-    <x v="76"/>
-    <n v="0.1"/>
-    <x v="75"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="81"/>
-    <x v="0"/>
-    <x v="77"/>
-    <n v="0.1"/>
-    <x v="76"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="82"/>
-    <x v="0"/>
-    <x v="78"/>
-    <n v="0.1"/>
-    <x v="77"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="83"/>
-    <x v="0"/>
-    <x v="79"/>
-    <n v="0.1"/>
-    <x v="78"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="84"/>
-    <x v="0"/>
-    <x v="80"/>
-    <n v="0.1"/>
-    <x v="79"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="85"/>
-    <x v="0"/>
-    <x v="81"/>
-    <n v="0.1"/>
-    <x v="80"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="86"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="87"/>
-    <x v="0"/>
-    <x v="82"/>
-    <n v="0.1"/>
-    <x v="81"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="88"/>
-    <x v="0"/>
-    <x v="83"/>
-    <n v="0.1"/>
-    <x v="82"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="89"/>
-    <x v="0"/>
-    <x v="84"/>
-    <n v="0.1"/>
-    <x v="83"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="90"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="91"/>
-    <x v="0"/>
-    <x v="85"/>
-    <n v="0.1"/>
-    <x v="84"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="92"/>
-    <x v="0"/>
-    <x v="86"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="93"/>
-    <x v="0"/>
-    <x v="87"/>
-    <n v="0.1"/>
-    <x v="85"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="94"/>
-    <x v="0"/>
-    <x v="88"/>
-    <n v="0.1"/>
-    <x v="86"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="95"/>
-    <x v="0"/>
-    <x v="89"/>
-    <n v="0.1"/>
-    <x v="87"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="96"/>
-    <x v="0"/>
-    <x v="90"/>
-    <n v="0.1"/>
-    <x v="88"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="97"/>
-    <x v="0"/>
-    <x v="91"/>
-    <n v="0.1"/>
-    <x v="89"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="98"/>
-    <x v="0"/>
-    <x v="92"/>
-    <n v="0.1"/>
-    <x v="90"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="99"/>
-    <x v="0"/>
-    <x v="93"/>
-    <n v="0.1"/>
-    <x v="91"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="100"/>
-    <x v="0"/>
-    <x v="94"/>
-    <n v="0.1"/>
-    <x v="92"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="101"/>
-    <x v="0"/>
-    <x v="95"/>
-    <n v="0.1"/>
-    <x v="93"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="102"/>
-    <x v="0"/>
-    <x v="96"/>
-    <n v="0.1"/>
-    <x v="94"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="103"/>
-    <x v="0"/>
-    <x v="97"/>
-    <n v="0.1"/>
-    <x v="95"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="104"/>
-    <x v="0"/>
-    <x v="98"/>
-    <n v="0.1"/>
-    <x v="96"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="105"/>
-    <x v="0"/>
-    <x v="99"/>
-    <n v="0.1"/>
-    <x v="97"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="106"/>
-    <x v="0"/>
-    <x v="100"/>
-    <n v="0.1"/>
-    <x v="98"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="107"/>
-    <x v="0"/>
-    <x v="101"/>
-    <n v="0.1"/>
-    <x v="99"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="108"/>
-    <x v="0"/>
-    <x v="102"/>
-    <n v="0.1"/>
-    <x v="100"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="109"/>
-    <x v="0"/>
-    <x v="103"/>
-    <n v="0.1"/>
-    <x v="101"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="110"/>
-    <x v="0"/>
-    <x v="104"/>
-    <n v="0.1"/>
-    <x v="102"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="111"/>
-    <x v="0"/>
-    <x v="105"/>
-    <n v="0.1"/>
-    <x v="103"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="112"/>
-    <x v="0"/>
-    <x v="106"/>
-    <n v="0.1"/>
-    <x v="104"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="113"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="114"/>
-    <x v="0"/>
-    <x v="107"/>
-    <n v="0.1"/>
-    <x v="105"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="115"/>
-    <x v="0"/>
-    <x v="108"/>
-    <n v="0.1"/>
-    <x v="106"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="116"/>
-    <x v="0"/>
-    <x v="109"/>
-    <n v="0.1"/>
-    <x v="107"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="117"/>
-    <x v="0"/>
-    <x v="110"/>
-    <n v="0.1"/>
-    <x v="108"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="118"/>
-    <x v="0"/>
-    <x v="111"/>
-    <n v="0.1"/>
-    <x v="109"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="119"/>
-    <x v="0"/>
-    <x v="112"/>
-    <n v="0.1"/>
-    <x v="110"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="120"/>
-    <x v="0"/>
-    <x v="113"/>
-    <n v="0.1"/>
-    <x v="111"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="121"/>
-    <x v="0"/>
-    <x v="114"/>
-    <n v="0.1"/>
-    <x v="112"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="115"/>
-    <n v="0.1"/>
-    <x v="113"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="116"/>
-    <n v="0.1"/>
-    <x v="114"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="117"/>
-    <n v="0.1"/>
-    <x v="115"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="122"/>
-    <x v="1"/>
-    <x v="118"/>
-    <n v="0.1"/>
-    <x v="116"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="5"/>
-    <x v="1"/>
-    <x v="119"/>
-    <n v="0.1"/>
-    <x v="117"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="6"/>
-    <x v="1"/>
-    <x v="120"/>
-    <n v="0.1"/>
-    <x v="118"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="123"/>
-    <x v="1"/>
-    <x v="121"/>
-    <n v="0.1"/>
-    <x v="119"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="122"/>
-    <n v="0.1"/>
-    <x v="120"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="8"/>
-    <x v="1"/>
-    <x v="123"/>
-    <n v="0.1"/>
-    <x v="121"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="1"/>
-    <x v="124"/>
-    <n v="0.1"/>
-    <x v="122"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <x v="12"/>
-    <x v="1"/>
-    <x v="125"/>
-    <n v="0.1"/>
-    <x v="123"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="13"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="14"/>
-    <x v="1"/>
-    <x v="126"/>
-    <n v="0.1"/>
-    <x v="124"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="1"/>
-    <x v="126"/>
-    <n v="0.1"/>
-    <x v="124"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-    <x v="15"/>
-    <x v="1"/>
-    <x v="127"/>
-    <n v="0.1"/>
-    <x v="125"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-    <x v="16"/>
-    <x v="1"/>
-    <x v="128"/>
-    <n v="0.1"/>
-    <x v="126"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="17"/>
-    <x v="1"/>
-    <x v="129"/>
-    <n v="0.08"/>
-    <x v="127"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="18"/>
-    <x v="1"/>
-    <x v="130"/>
-    <n v="0.08"/>
-    <x v="128"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="19"/>
-    <x v="1"/>
-    <x v="131"/>
-    <n v="0.08"/>
-    <x v="129"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="20"/>
-    <x v="1"/>
-    <x v="132"/>
-    <n v="0.08"/>
-    <x v="130"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="21"/>
-    <x v="1"/>
-    <x v="133"/>
-    <n v="0.08"/>
-    <x v="131"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="22"/>
-    <x v="1"/>
-    <x v="134"/>
-    <n v="0.08"/>
-    <x v="132"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="23"/>
-    <x v="1"/>
-    <x v="135"/>
-    <n v="0.08"/>
-    <x v="133"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="24"/>
-    <x v="1"/>
-    <x v="136"/>
-    <n v="0.08"/>
-    <x v="134"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="25"/>
-    <x v="1"/>
-    <x v="137"/>
-    <n v="0.08"/>
-    <x v="135"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="26"/>
-    <x v="1"/>
-    <x v="138"/>
-    <n v="0.08"/>
-    <x v="136"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="27"/>
-    <x v="1"/>
-    <x v="139"/>
-    <n v="0.08"/>
-    <x v="137"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="28"/>
-    <x v="1"/>
-    <x v="140"/>
-    <n v="0.08"/>
-    <x v="138"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="29"/>
-    <x v="1"/>
-    <x v="141"/>
-    <n v="0.08"/>
-    <x v="139"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="30"/>
-    <x v="1"/>
-    <x v="142"/>
-    <n v="0.08"/>
-    <x v="140"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="31"/>
-    <x v="1"/>
-    <x v="143"/>
-    <n v="0.08"/>
-    <x v="141"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="32"/>
-    <x v="1"/>
-    <x v="144"/>
-    <n v="0.08"/>
-    <x v="142"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="33"/>
-    <x v="1"/>
-    <x v="145"/>
-    <n v="0.08"/>
-    <x v="143"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="34"/>
-    <x v="1"/>
-    <x v="146"/>
-    <n v="0.08"/>
-    <x v="144"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="35"/>
-    <x v="1"/>
-    <x v="147"/>
-    <n v="0.08"/>
-    <x v="145"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="36"/>
-    <x v="1"/>
-    <x v="148"/>
-    <n v="0.08"/>
-    <x v="146"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="37"/>
-    <x v="1"/>
-    <x v="149"/>
-    <n v="0.08"/>
-    <x v="147"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="38"/>
-    <x v="1"/>
-    <x v="150"/>
-    <n v="0.08"/>
-    <x v="148"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="39"/>
-    <x v="1"/>
-    <x v="151"/>
-    <n v="0.08"/>
-    <x v="149"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="40"/>
-    <x v="1"/>
-    <x v="152"/>
-    <n v="0.08"/>
-    <x v="150"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="41"/>
-    <x v="1"/>
-    <x v="153"/>
-    <n v="0.08"/>
-    <x v="151"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="42"/>
-    <x v="1"/>
-    <x v="154"/>
-    <n v="0.08"/>
-    <x v="152"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-    <x v="43"/>
-    <x v="1"/>
-    <x v="155"/>
-    <n v="0.08"/>
-    <x v="153"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="45"/>
-    <x v="1"/>
-    <x v="156"/>
-    <n v="0.05"/>
-    <x v="154"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="124"/>
-    <x v="1"/>
-    <x v="157"/>
-    <n v="0.05"/>
-    <x v="155"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="48"/>
-    <x v="1"/>
-    <x v="158"/>
-    <n v="0.05"/>
-    <x v="156"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="49"/>
-    <x v="1"/>
-    <x v="159"/>
-    <n v="0.05"/>
-    <x v="157"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="50"/>
-    <x v="1"/>
-    <x v="160"/>
-    <n v="0.05"/>
-    <x v="158"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="51"/>
-    <x v="1"/>
-    <x v="161"/>
-    <n v="0.05"/>
-    <x v="159"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="54"/>
-    <x v="1"/>
-    <x v="162"/>
-    <n v="0.05"/>
-    <x v="160"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="55"/>
-    <x v="1"/>
-    <x v="163"/>
-    <n v="0.05"/>
-    <x v="161"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="57"/>
-    <x v="1"/>
-    <x v="164"/>
-    <n v="0.05"/>
-    <x v="162"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="58"/>
-    <x v="1"/>
-    <x v="165"/>
-    <n v="0.05"/>
-    <x v="163"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="9"/>
-    <x v="59"/>
-    <x v="1"/>
-    <x v="166"/>
-    <n v="0.05"/>
-    <x v="164"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="60"/>
-    <x v="1"/>
-    <x v="167"/>
-    <n v="0.05"/>
-    <x v="165"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="61"/>
-    <x v="1"/>
-    <x v="168"/>
-    <n v="0.05"/>
-    <x v="166"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="62"/>
-    <x v="1"/>
-    <x v="169"/>
-    <n v="0.05"/>
-    <x v="167"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="63"/>
-    <x v="1"/>
-    <x v="170"/>
-    <n v="0.05"/>
-    <x v="168"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="64"/>
-    <x v="1"/>
-    <x v="171"/>
-    <n v="0.05"/>
-    <x v="169"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="65"/>
-    <x v="1"/>
-    <x v="172"/>
-    <n v="0.05"/>
-    <x v="170"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="66"/>
-    <x v="1"/>
-    <x v="173"/>
-    <n v="0.05"/>
-    <x v="171"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="67"/>
-    <x v="1"/>
-    <x v="174"/>
-    <n v="0.05"/>
-    <x v="172"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="68"/>
-    <x v="1"/>
-    <x v="175"/>
-    <n v="0.05"/>
-    <x v="173"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="69"/>
-    <x v="1"/>
-    <x v="176"/>
-    <n v="0.05"/>
-    <x v="174"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="70"/>
-    <x v="1"/>
-    <x v="177"/>
-    <n v="0.05"/>
-    <x v="175"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="71"/>
-    <x v="1"/>
-    <x v="178"/>
-    <n v="0.05"/>
-    <x v="176"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="72"/>
-    <x v="1"/>
-    <x v="179"/>
-    <n v="0.05"/>
-    <x v="177"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="73"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.05"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="74"/>
-    <x v="1"/>
-    <x v="180"/>
-    <n v="0.05"/>
-    <x v="178"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="75"/>
-    <x v="1"/>
-    <x v="181"/>
-    <n v="0.05"/>
-    <x v="179"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="76"/>
-    <x v="1"/>
-    <x v="182"/>
-    <n v="0.05"/>
-    <x v="180"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="77"/>
-    <x v="1"/>
-    <x v="183"/>
-    <n v="0.05"/>
-    <x v="181"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="78"/>
-    <x v="1"/>
-    <x v="184"/>
-    <n v="0.05"/>
-    <x v="182"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="79"/>
-    <x v="1"/>
-    <x v="185"/>
-    <n v="0.1"/>
-    <x v="183"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="80"/>
-    <x v="1"/>
-    <x v="186"/>
-    <n v="0.1"/>
-    <x v="184"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="81"/>
-    <x v="1"/>
-    <x v="187"/>
-    <n v="0.1"/>
-    <x v="185"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="82"/>
-    <x v="1"/>
-    <x v="188"/>
-    <n v="0.1"/>
-    <x v="186"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="83"/>
-    <x v="1"/>
-    <x v="189"/>
-    <n v="0.1"/>
-    <x v="187"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="84"/>
-    <x v="1"/>
-    <x v="190"/>
-    <n v="0.1"/>
-    <x v="188"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="85"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="86"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="87"/>
-    <x v="1"/>
-    <x v="191"/>
-    <n v="0.1"/>
-    <x v="189"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="88"/>
-    <x v="1"/>
-    <x v="192"/>
-    <n v="0.1"/>
-    <x v="190"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="89"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="90"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="91"/>
-    <x v="1"/>
-    <x v="193"/>
-    <n v="0.1"/>
-    <x v="191"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="92"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="93"/>
-    <x v="1"/>
-    <x v="194"/>
-    <n v="0.1"/>
-    <x v="192"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="94"/>
-    <x v="1"/>
-    <x v="195"/>
-    <n v="0.1"/>
-    <x v="193"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="95"/>
-    <x v="1"/>
-    <x v="196"/>
-    <n v="0.1"/>
-    <x v="194"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="96"/>
-    <x v="1"/>
-    <x v="197"/>
-    <n v="0.1"/>
-    <x v="195"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="97"/>
-    <x v="1"/>
-    <x v="198"/>
-    <n v="0.1"/>
-    <x v="196"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="98"/>
-    <x v="1"/>
-    <x v="199"/>
-    <n v="0.1"/>
-    <x v="197"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="99"/>
-    <x v="1"/>
-    <x v="200"/>
-    <n v="0.1"/>
-    <x v="198"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="100"/>
-    <x v="1"/>
-    <x v="201"/>
-    <n v="0.1"/>
-    <x v="199"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="101"/>
-    <x v="1"/>
-    <x v="202"/>
-    <n v="0.1"/>
-    <x v="200"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="102"/>
-    <x v="1"/>
-    <x v="203"/>
-    <n v="0.1"/>
-    <x v="201"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="103"/>
-    <x v="1"/>
-    <x v="204"/>
-    <n v="0.1"/>
-    <x v="202"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="104"/>
-    <x v="1"/>
-    <x v="205"/>
-    <n v="0.1"/>
-    <x v="203"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="105"/>
-    <x v="1"/>
-    <x v="206"/>
-    <n v="0.1"/>
-    <x v="204"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-    <x v="106"/>
-    <x v="1"/>
-    <x v="207"/>
-    <n v="0.1"/>
-    <x v="205"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="107"/>
-    <x v="1"/>
-    <x v="208"/>
-    <n v="0.1"/>
-    <x v="206"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="108"/>
-    <x v="1"/>
-    <x v="209"/>
-    <n v="0.1"/>
-    <x v="207"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="109"/>
-    <x v="1"/>
-    <x v="210"/>
-    <n v="0.1"/>
-    <x v="208"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="110"/>
-    <x v="1"/>
-    <x v="211"/>
-    <n v="0.1"/>
-    <x v="209"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="111"/>
-    <x v="1"/>
-    <x v="212"/>
-    <n v="0.1"/>
-    <x v="210"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="112"/>
-    <x v="1"/>
-    <x v="213"/>
-    <n v="0.1"/>
-    <x v="211"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="113"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="114"/>
-    <x v="1"/>
-    <x v="214"/>
-    <n v="0.1"/>
-    <x v="212"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="115"/>
-    <x v="1"/>
-    <x v="215"/>
-    <n v="0.1"/>
-    <x v="213"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <x v="116"/>
-    <x v="1"/>
-    <x v="216"/>
-    <n v="0.1"/>
-    <x v="214"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="117"/>
-    <x v="1"/>
-    <x v="217"/>
-    <n v="0.1"/>
-    <x v="215"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="118"/>
-    <x v="1"/>
-    <x v="218"/>
-    <n v="0.1"/>
-    <x v="216"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="119"/>
-    <x v="1"/>
-    <x v="219"/>
-    <n v="0.1"/>
-    <x v="217"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="120"/>
-    <x v="1"/>
-    <x v="220"/>
-    <n v="0.1"/>
-    <x v="218"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="14"/>
-    <x v="121"/>
-    <x v="1"/>
-    <x v="221"/>
-    <n v="0.1"/>
-    <x v="219"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="15"/>
-    <x v="125"/>
-    <x v="1"/>
-    <x v="222"/>
-    <n v="0.1"/>
-    <x v="220"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="16"/>
-    <x v="126"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="16"/>
-    <x v="127"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="0.1"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="16"/>
-    <x v="128"/>
-    <x v="1"/>
-    <x v="223"/>
-    <n v="0.1"/>
-    <x v="221"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E3E9762-1CB9-4F87-88F4-E6866E898EE9}" name="Tabela dinâmica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" customListSort="0">
-  <location ref="A1:C3" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="225">
-        <item h="1" x="2"/>
-        <item h="1" x="118"/>
-        <item h="1" x="11"/>
-        <item h="1" x="10"/>
-        <item h="1" x="147"/>
-        <item h="1" x="35"/>
-        <item h="1" x="120"/>
-        <item h="1" x="86"/>
-        <item h="1" x="107"/>
-        <item h="1" x="12"/>
-        <item h="1" x="214"/>
-        <item h="1" x="119"/>
-        <item h="1" x="124"/>
-        <item x="6"/>
-        <item h="1" x="205"/>
-        <item h="1" x="81"/>
-        <item h="1" x="210"/>
-        <item h="1" x="123"/>
-        <item h="1" x="76"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="146"/>
-        <item h="1" x="98"/>
-        <item h="1" x="34"/>
-        <item h="1" x="186"/>
-        <item h="1" x="38"/>
-        <item h="1" x="51"/>
-        <item h="1" x="31"/>
-        <item h="1" x="149"/>
-        <item h="1" x="150"/>
-        <item h="1" x="78"/>
-        <item h="1" x="103"/>
-        <item h="1" x="37"/>
-        <item h="1" x="91"/>
-        <item h="1" x="190"/>
-        <item h="1" x="188"/>
-        <item h="1" x="148"/>
-        <item h="1" x="151"/>
-        <item h="1" x="198"/>
-        <item h="1" x="143"/>
-        <item h="1" x="100"/>
-        <item h="1" x="36"/>
-        <item h="1" x="39"/>
-        <item h="1" x="7"/>
-        <item h="1" x="80"/>
-        <item h="1" x="84"/>
-        <item h="1" x="30"/>
-        <item h="1" x="141"/>
-        <item h="1" x="29"/>
-        <item h="1" x="152"/>
-        <item h="1" x="195"/>
-        <item h="1" x="40"/>
-        <item h="1" x="173"/>
-        <item h="1" x="65"/>
-        <item h="1" x="88"/>
-        <item h="1" x="115"/>
-        <item h="1" x="41"/>
-        <item h="1" x="175"/>
-        <item h="1" x="99"/>
-        <item h="1" x="28"/>
-        <item h="1" x="140"/>
-        <item h="1" x="63"/>
-        <item h="1" x="0"/>
-        <item h="1" x="178"/>
-        <item h="1" x="153"/>
-        <item h="1" x="192"/>
-        <item h="1" x="68"/>
-        <item h="1" x="180"/>
-        <item h="1" x="83"/>
-        <item h="1" x="181"/>
-        <item h="1" x="43"/>
-        <item h="1" x="97"/>
-        <item h="1" x="108"/>
-        <item h="1" x="82"/>
-        <item h="1" x="70"/>
-        <item h="1" x="191"/>
-        <item h="1" x="155"/>
-        <item h="1" x="62"/>
-        <item h="1" x="3"/>
-        <item h="1" x="154"/>
-        <item h="1" x="71"/>
-        <item h="1" x="172"/>
-        <item h="1" x="33"/>
-        <item h="1" x="142"/>
-        <item h="1" x="125"/>
-        <item h="1" x="42"/>
-        <item h="1" x="145"/>
-        <item h="1" x="200"/>
-        <item h="1" x="126"/>
-        <item h="1" x="194"/>
-        <item h="1" x="87"/>
-        <item h="1" x="32"/>
-        <item h="1" x="52"/>
-        <item h="1" x="132"/>
-        <item h="1" x="162"/>
-        <item h="1" x="96"/>
-        <item h="1" x="144"/>
-        <item h="1" x="5"/>
-        <item h="1" x="208"/>
-        <item h="1" x="95"/>
-        <item h="1" x="20"/>
-        <item h="1" x="211"/>
-        <item h="1" x="4"/>
-        <item h="1" x="133"/>
-        <item h="1" x="21"/>
-        <item h="1" x="13"/>
-        <item h="1" x="105"/>
-        <item h="1" x="101"/>
-        <item h="1" x="134"/>
-        <item h="1" x="138"/>
-        <item h="1" x="222"/>
-        <item h="1" x="128"/>
-        <item h="1" x="164"/>
-        <item h="1" x="212"/>
-        <item h="1" x="22"/>
-        <item h="1" x="26"/>
-        <item h="1" x="92"/>
-        <item h="1" x="163"/>
-        <item h="1" x="189"/>
-        <item h="1" x="122"/>
-        <item h="1" x="131"/>
-        <item h="1" x="16"/>
-        <item h="1" x="79"/>
-        <item h="1" x="156"/>
-        <item h="1" x="135"/>
-        <item h="1" x="187"/>
-        <item h="1" x="77"/>
-        <item h="1" x="161"/>
-        <item h="1" x="23"/>
-        <item h="1" x="136"/>
-        <item h="1" x="19"/>
-        <item h="1" x="159"/>
-        <item h="1" x="112"/>
-        <item h="1" x="48"/>
-        <item h="1" x="202"/>
-        <item h="1" x="24"/>
-        <item h="1" x="219"/>
-        <item h="1" x="204"/>
-        <item h="1" x="110"/>
-        <item h="1" x="165"/>
-        <item h="1" x="217"/>
-        <item h="1" x="27"/>
-        <item h="1" x="93"/>
-        <item h="1" x="171"/>
-        <item h="1" x="49"/>
-        <item h="1" x="160"/>
-        <item h="1" x="121"/>
-        <item h="1" x="221"/>
-        <item h="1" x="1"/>
-        <item h="1" x="61"/>
-        <item h="1" x="53"/>
-        <item h="1" x="215"/>
-        <item h="1" x="213"/>
-        <item h="1" x="207"/>
-        <item h="1" x="223"/>
-        <item h="1" x="54"/>
-        <item h="1" x="206"/>
-        <item h="1" x="166"/>
-        <item h="1" x="137"/>
-        <item h="1" x="139"/>
-        <item h="1" x="203"/>
-        <item h="1" x="183"/>
-        <item h="1" x="169"/>
-        <item h="1" x="193"/>
-        <item h="1" x="117"/>
-        <item h="1" x="177"/>
-        <item h="1" x="116"/>
-        <item h="1" x="85"/>
-        <item h="1" x="67"/>
-        <item h="1" x="73"/>
-        <item h="1" x="209"/>
-        <item h="1" x="102"/>
-        <item h="1" x="57"/>
-        <item h="1" x="157"/>
-        <item h="1" x="25"/>
-        <item h="1" x="185"/>
-        <item h="1" x="59"/>
-        <item h="1" x="104"/>
-        <item h="1" x="46"/>
-        <item h="1" x="158"/>
-        <item h="1" x="75"/>
-        <item h="1" x="14"/>
-        <item h="1" x="55"/>
-        <item h="1" x="176"/>
-        <item h="1" x="196"/>
-        <item h="1" x="114"/>
-        <item h="1" x="56"/>
-        <item h="1" x="201"/>
-        <item h="1" x="182"/>
-        <item h="1" x="66"/>
-        <item h="1" x="179"/>
-        <item h="1" x="64"/>
-        <item h="1" x="89"/>
-        <item h="1" x="167"/>
-        <item h="1" x="72"/>
-        <item h="1" x="130"/>
-        <item h="1" x="50"/>
-        <item h="1" x="69"/>
-        <item h="1" x="218"/>
-        <item h="1" x="111"/>
-        <item h="1" x="47"/>
-        <item h="1" x="174"/>
-        <item h="1" x="216"/>
-        <item h="1" x="18"/>
-        <item h="1" x="129"/>
-        <item h="1" x="184"/>
-        <item h="1" x="74"/>
-        <item h="1" x="17"/>
-        <item h="1" x="220"/>
-        <item h="1" x="199"/>
-        <item h="1" x="45"/>
-        <item h="1" x="60"/>
-        <item h="1" x="170"/>
-        <item h="1" x="109"/>
-        <item h="1" x="106"/>
-        <item h="1" x="113"/>
-        <item h="1" x="94"/>
-        <item h="1" x="127"/>
-        <item h="1" x="168"/>
-        <item h="1" x="58"/>
-        <item h="1" x="15"/>
-        <item h="1" x="90"/>
-        <item h="1" x="197"/>
-        <item h="1" x="44"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0">
-      <items count="223">
-        <item x="2"/>
-        <item x="116"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="145"/>
-        <item x="35"/>
-        <item x="118"/>
-        <item x="105"/>
-        <item x="50"/>
-        <item x="12"/>
-        <item x="212"/>
-        <item x="117"/>
-        <item x="144"/>
-        <item x="122"/>
-        <item x="6"/>
-        <item x="203"/>
-        <item x="34"/>
-        <item x="80"/>
-        <item x="38"/>
-        <item x="31"/>
-        <item x="208"/>
-        <item x="121"/>
-        <item x="75"/>
-        <item x="147"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="148"/>
-        <item x="96"/>
-        <item x="184"/>
-        <item x="37"/>
-        <item x="146"/>
-        <item x="149"/>
-        <item x="141"/>
-        <item x="77"/>
-        <item x="101"/>
-        <item x="171"/>
-        <item x="64"/>
-        <item x="173"/>
-        <item x="36"/>
-        <item x="39"/>
-        <item x="62"/>
-        <item x="89"/>
-        <item x="188"/>
-        <item x="186"/>
-        <item x="196"/>
-        <item x="176"/>
-        <item x="98"/>
-        <item x="67"/>
-        <item x="30"/>
-        <item x="7"/>
-        <item x="139"/>
-        <item x="79"/>
-        <item x="29"/>
-        <item x="150"/>
-        <item x="178"/>
-        <item x="83"/>
-        <item x="179"/>
-        <item x="40"/>
-        <item x="69"/>
-        <item x="41"/>
-        <item x="28"/>
-        <item x="61"/>
-        <item x="138"/>
-        <item x="193"/>
-        <item x="70"/>
-        <item x="170"/>
-        <item x="151"/>
-        <item x="86"/>
-        <item x="113"/>
-        <item x="97"/>
-        <item x="51"/>
-        <item x="0"/>
-        <item x="160"/>
-        <item x="190"/>
-        <item x="43"/>
-        <item x="153"/>
-        <item x="152"/>
-        <item x="82"/>
-        <item x="33"/>
-        <item x="140"/>
-        <item x="95"/>
-        <item x="106"/>
-        <item x="42"/>
-        <item x="81"/>
-        <item x="143"/>
-        <item x="189"/>
-        <item x="162"/>
-        <item x="161"/>
-        <item x="3"/>
-        <item x="32"/>
-        <item x="154"/>
-        <item x="130"/>
-        <item x="123"/>
-        <item x="159"/>
-        <item x="142"/>
-        <item x="198"/>
-        <item x="124"/>
-        <item x="192"/>
-        <item x="157"/>
-        <item x="47"/>
-        <item x="85"/>
-        <item x="20"/>
-        <item x="131"/>
-        <item x="94"/>
-        <item x="21"/>
-        <item x="163"/>
-        <item x="132"/>
-        <item x="136"/>
-        <item x="169"/>
-        <item x="5"/>
-        <item x="48"/>
-        <item x="158"/>
-        <item x="206"/>
-        <item x="22"/>
-        <item x="93"/>
-        <item x="26"/>
-        <item x="209"/>
-        <item x="4"/>
-        <item x="60"/>
-        <item x="52"/>
-        <item x="129"/>
-        <item x="133"/>
-        <item x="13"/>
-        <item x="103"/>
-        <item x="99"/>
-        <item x="53"/>
-        <item x="220"/>
-        <item x="23"/>
-        <item x="126"/>
-        <item x="164"/>
-        <item x="181"/>
-        <item x="167"/>
-        <item x="134"/>
-        <item x="210"/>
-        <item x="19"/>
-        <item x="175"/>
-        <item x="90"/>
-        <item x="187"/>
-        <item x="120"/>
-        <item x="66"/>
-        <item x="72"/>
-        <item x="24"/>
-        <item x="16"/>
-        <item x="78"/>
-        <item x="56"/>
-        <item x="155"/>
-        <item x="185"/>
-        <item x="76"/>
-        <item x="58"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="156"/>
-        <item x="54"/>
-        <item x="174"/>
-        <item x="110"/>
-        <item x="200"/>
-        <item x="55"/>
-        <item x="180"/>
-        <item x="217"/>
-        <item x="65"/>
-        <item x="202"/>
-        <item x="177"/>
-        <item x="63"/>
-        <item x="108"/>
-        <item x="165"/>
-        <item x="71"/>
-        <item x="215"/>
-        <item x="91"/>
-        <item x="49"/>
-        <item x="68"/>
-        <item x="46"/>
-        <item x="135"/>
-        <item x="137"/>
-        <item x="172"/>
-        <item x="119"/>
-        <item x="219"/>
-        <item x="1"/>
-        <item x="182"/>
-        <item x="73"/>
-        <item x="213"/>
-        <item x="211"/>
-        <item x="205"/>
-        <item x="25"/>
-        <item x="221"/>
-        <item x="204"/>
-        <item x="201"/>
-        <item x="191"/>
-        <item x="115"/>
-        <item x="114"/>
-        <item x="84"/>
-        <item x="207"/>
-        <item x="100"/>
-        <item x="44"/>
-        <item x="59"/>
-        <item x="168"/>
-        <item x="183"/>
-        <item x="128"/>
-        <item x="102"/>
-        <item x="74"/>
-        <item x="14"/>
-        <item x="194"/>
-        <item x="112"/>
-        <item x="18"/>
-        <item x="199"/>
-        <item x="166"/>
-        <item x="127"/>
-        <item x="57"/>
-        <item x="87"/>
-        <item x="17"/>
-        <item x="216"/>
-        <item x="109"/>
-        <item x="214"/>
-        <item x="218"/>
-        <item x="197"/>
-        <item x="107"/>
-        <item x="104"/>
-        <item x="111"/>
-        <item x="92"/>
-        <item x="125"/>
-        <item x="15"/>
-        <item x="88"/>
-        <item x="195"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Soma de Valor a Pagar para Gerador (R$)" fld="4" baseField="0" baseItem="0" numFmtId="44"/>
-    <dataField name="Soma de Valor da Gestão (R$)" fld="6" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D34789AD-D5B1-4BDB-8870-634F2C2242B1}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" customListSort="0">
-  <location ref="A5:C14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="10">
-        <item sd="0" x="8"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="18">
-        <item sd="0" x="16"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="12"/>
-        <item sd="0" x="7"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="130">
-        <item x="52"/>
-        <item x="57"/>
-        <item x="53"/>
-        <item x="111"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="116"/>
-        <item x="110"/>
-        <item x="109"/>
-        <item x="115"/>
-        <item x="112"/>
-        <item x="11"/>
-        <item x="55"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="123"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="54"/>
-        <item x="51"/>
-        <item x="50"/>
-        <item x="49"/>
-        <item x="66"/>
-        <item x="48"/>
-        <item x="61"/>
-        <item x="47"/>
-        <item x="124"/>
-        <item x="63"/>
-        <item x="62"/>
-        <item x="46"/>
-        <item x="60"/>
-        <item x="45"/>
-        <item x="44"/>
-        <item x="67"/>
-        <item x="58"/>
-        <item x="125"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="17"/>
-        <item x="87"/>
-        <item x="117"/>
-        <item x="78"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="72"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="73"/>
-        <item x="13"/>
-        <item x="95"/>
-        <item x="128"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="31"/>
-        <item x="56"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="35"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="120"/>
-        <item x="82"/>
-        <item x="79"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="32"/>
-        <item x="65"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="86"/>
-        <item x="89"/>
-        <item x="85"/>
-        <item x="64"/>
-        <item x="88"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="81"/>
-        <item x="0"/>
-        <item x="59"/>
-        <item x="92"/>
-        <item x="102"/>
-        <item x="100"/>
-        <item x="106"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="103"/>
-        <item x="101"/>
-        <item x="96"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="97"/>
-        <item x="14"/>
-        <item x="91"/>
-        <item x="18"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="90"/>
-        <item x="80"/>
-        <item x="1"/>
-        <item x="122"/>
-        <item x="30"/>
-        <item x="33"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="121"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="24"/>
-        <item x="27"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="0"/>
-    <field x="1"/>
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Soma de Valor a Pagar para Gerador (R$)" fld="4" baseField="0" baseItem="0" numFmtId="44"/>
-    <dataField name="Soma de Valor da Gestão (R$)" fld="6" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4836,13 +1024,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G364"/>
+  <dimension ref="A1:G363"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -4850,25 +1038,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
@@ -9887,7 +6075,7 @@
       <c r="B211" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" s="3" t="s">
         <v>112</v>
       </c>
       <c r="D211" s="3" t="s">
@@ -10755,7 +6943,7 @@
         <v>6</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E247" s="2">
         <v>718.9</v>
@@ -10779,7 +6967,7 @@
         <v>10</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E248" s="2">
         <v>5054.72</v>
@@ -10803,7 +6991,7 @@
         <v>13</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E249" s="2">
         <v>189.44</v>
@@ -10827,7 +7015,7 @@
         <v>8</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E250" s="2">
         <v>6490.24</v>
@@ -10851,7 +7039,7 @@
         <v>152</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E251" s="2">
         <v>16.899999999999999</v>
@@ -10871,21 +7059,21 @@
       <c r="B252" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C252" s="4" t="s">
+      <c r="C252" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E252" s="2">
-        <v>0</v>
+        <v>283.82</v>
       </c>
       <c r="F252" s="1">
         <v>0.1</v>
       </c>
       <c r="G252" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>28.382000000000001</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -10899,7 +7087,7 @@
         <v>12</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E253" s="2">
         <v>2245.1</v>
@@ -10923,7 +7111,7 @@
         <v>17</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E254" s="2">
         <v>1179.75</v>
@@ -10947,7 +7135,7 @@
         <v>20</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E255" s="2">
         <v>107.52</v>
@@ -10971,7 +7159,7 @@
         <v>21</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E256" s="2">
         <v>1865.5</v>
@@ -10991,11 +7179,11 @@
       <c r="B257" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E257" s="2">
         <v>0</v>
@@ -11015,21 +7203,21 @@
       <c r="B258" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C258" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E258" s="2">
-        <v>0</v>
+        <v>5532.8</v>
       </c>
       <c r="F258" s="1">
         <v>0.1</v>
       </c>
       <c r="G258" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>553.28000000000009</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -11039,21 +7227,21 @@
       <c r="B259" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C259" s="4" t="s">
+      <c r="C259" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E259" s="2">
-        <v>0</v>
+        <v>5532.8</v>
       </c>
       <c r="F259" s="1">
         <v>0.1</v>
       </c>
       <c r="G259" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>553.28000000000009</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,23 +7249,23 @@
         <v>4</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E260" s="2">
-        <v>0</v>
+        <v>3222.03</v>
       </c>
       <c r="F260" s="1">
         <v>0.1</v>
       </c>
       <c r="G260" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>322.20300000000003</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -11085,13 +7273,13 @@
         <v>4</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C261" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E261" s="2">
         <v>0</v>
@@ -11109,13 +7297,13 @@
         <v>4</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C262" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C262" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E262" s="2">
         <v>0</v>
@@ -11139,7 +7327,7 @@
         <v>29</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E263" s="2">
         <v>9835.1299999999992</v>
@@ -11160,10 +7348,10 @@
         <v>28</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E264" s="2">
         <v>1855.26</v>
@@ -11187,7 +7375,7 @@
         <v>33</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E265" s="2">
         <v>7585.28</v>
@@ -11211,7 +7399,7 @@
         <v>34</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E266" s="2">
         <v>7077.12</v>
@@ -11235,7 +7423,7 @@
         <v>35</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E267" s="2">
         <v>2645.76</v>
@@ -11259,7 +7447,7 @@
         <v>36</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E268" s="2">
         <v>1724.16</v>
@@ -11283,7 +7471,7 @@
         <v>37</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E269" s="2">
         <v>1739.88</v>
@@ -11307,7 +7495,7 @@
         <v>38</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E270" s="2">
         <v>2113.56</v>
@@ -11331,7 +7519,7 @@
         <v>39</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E271" s="2">
         <v>2683.96</v>
@@ -11355,7 +7543,7 @@
         <v>40</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E272" s="2">
         <v>2682.6</v>
@@ -11379,7 +7567,7 @@
         <v>41</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E273" s="2">
         <v>4448.5600000000004</v>
@@ -11403,7 +7591,7 @@
         <v>42</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E274" s="2">
         <v>2325.7800000000002</v>
@@ -11427,7 +7615,7 @@
         <v>43</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E275" s="2">
         <v>3972.24</v>
@@ -11451,7 +7639,7 @@
         <v>44</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E276" s="2">
         <v>743.16</v>
@@ -11475,7 +7663,7 @@
         <v>45</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E277" s="2">
         <v>349.8</v>
@@ -11499,7 +7687,7 @@
         <v>46</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E278" s="2">
         <v>1247.54</v>
@@ -11523,7 +7711,7 @@
         <v>47</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E279" s="2">
         <v>399.31</v>
@@ -11547,7 +7735,7 @@
         <v>48</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E280" s="2">
         <v>1170.8499999999999</v>
@@ -11571,7 +7759,7 @@
         <v>49</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E281" s="2">
         <v>1122.6600000000001</v>
@@ -11595,7 +7783,7 @@
         <v>50</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E282" s="2">
         <v>228.69</v>
@@ -11619,7 +7807,7 @@
         <v>51</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E283" s="2">
         <v>90.52</v>
@@ -11643,7 +7831,7 @@
         <v>52</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E284" s="2">
         <v>366.49</v>
@@ -11667,7 +7855,7 @@
         <v>53</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E285" s="2">
         <v>282.74</v>
@@ -11691,7 +7879,7 @@
         <v>54</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E286" s="2">
         <v>260.63</v>
@@ -11715,7 +7903,7 @@
         <v>55</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E287" s="2">
         <v>369.24</v>
@@ -11739,7 +7927,7 @@
         <v>56</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E288" s="2">
         <v>552.66999999999996</v>
@@ -11763,7 +7951,7 @@
         <v>57</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E289" s="2">
         <v>651.33000000000004</v>
@@ -11787,7 +7975,7 @@
         <v>58</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E290" s="2">
         <v>1131.08</v>
@@ -11796,7 +7984,7 @@
         <v>0.08</v>
       </c>
       <c r="G290" s="2">
-        <f t="shared" ref="G290:G364" si="8">E290*F290</f>
+        <f t="shared" ref="G290:G363" si="8">E290*F290</f>
         <v>90.486399999999989</v>
       </c>
     </row>
@@ -11811,7 +7999,7 @@
         <v>59</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E291" s="2">
         <v>950.39</v>
@@ -11835,7 +8023,7 @@
         <v>63</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E292" s="2">
         <v>9944.32</v>
@@ -11859,7 +8047,7 @@
         <v>154</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E293" s="2">
         <v>4992</v>
@@ -11883,7 +8071,7 @@
         <v>66</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E294" s="2">
         <v>9592.9599999999991</v>
@@ -11907,7 +8095,7 @@
         <v>67</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E295" s="2">
         <v>2715.7</v>
@@ -11931,17 +8119,17 @@
         <v>68</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E296" s="2">
-        <v>0</v>
+        <v>3280.64</v>
       </c>
       <c r="F296" s="1">
         <v>0.05</v>
       </c>
       <c r="G296" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>164.03200000000001</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11955,7 +8143,7 @@
         <v>69</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E297" s="2">
         <v>3918.08</v>
@@ -11979,7 +8167,7 @@
         <v>72</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E298" s="2">
         <v>3026.56</v>
@@ -12003,7 +8191,7 @@
         <v>73</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E299" s="2">
         <v>2875.52</v>
@@ -12027,7 +8215,7 @@
         <v>75</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E300" s="2">
         <v>4040.84</v>
@@ -12051,7 +8239,7 @@
         <v>76</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E301" s="2">
         <v>1638.65</v>
@@ -12075,7 +8263,7 @@
         <v>77</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E302" s="2">
         <v>4709.76</v>
@@ -12099,7 +8287,7 @@
         <v>79</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E303" s="2">
         <v>2125.0700000000002</v>
@@ -12123,7 +8311,7 @@
         <v>80</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E304" s="2">
         <v>11772.8</v>
@@ -12147,7 +8335,7 @@
         <v>81</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E305" s="2">
         <v>4799.3599999999997</v>
@@ -12171,7 +8359,7 @@
         <v>82</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E306" s="2">
         <v>9351.5499999999993</v>
@@ -12195,7 +8383,7 @@
         <v>83</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E307" s="2">
         <v>3016.59</v>
@@ -12219,7 +8407,7 @@
         <v>84</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E308" s="2">
         <v>997.75</v>
@@ -12243,7 +8431,7 @@
         <v>85</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E309" s="2">
         <v>577.28</v>
@@ -12267,7 +8455,7 @@
         <v>86</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E310" s="2">
         <v>1985.1</v>
@@ -12291,7 +8479,7 @@
         <v>88</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E311" s="2">
         <v>592</v>
@@ -12315,7 +8503,7 @@
         <v>89</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E312" s="2">
         <v>5795.2</v>
@@ -12339,7 +8527,7 @@
         <v>90</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E313" s="2">
         <v>4808.32</v>
@@ -12363,7 +8551,7 @@
         <v>91</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E314" s="2">
         <v>748.8</v>
@@ -12387,7 +8575,7 @@
         <v>92</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E315" s="2">
         <v>6457.6</v>
@@ -12411,7 +8599,7 @@
         <v>93</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E316" s="2">
         <v>0</v>
@@ -12435,7 +8623,7 @@
         <v>94</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E317" s="2">
         <v>975.86</v>
@@ -12459,7 +8647,7 @@
         <v>95</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E318" s="2">
         <v>931.84</v>
@@ -12483,7 +8671,7 @@
         <v>96</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E319" s="2">
         <v>6378.24</v>
@@ -12507,7 +8695,7 @@
         <v>97</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E320" s="2">
         <v>4465.92</v>
@@ -12531,7 +8719,7 @@
         <v>98</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E321" s="2">
         <v>8159.36</v>
@@ -12555,7 +8743,7 @@
         <v>101</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E322" s="2">
         <v>5214.8100000000004</v>
@@ -12579,7 +8767,7 @@
         <v>102</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E323" s="2">
         <v>278.8</v>
@@ -12603,7 +8791,7 @@
         <v>103</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E324" s="2">
         <v>2493.21</v>
@@ -12627,7 +8815,7 @@
         <v>104</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E325" s="2">
         <v>346.68</v>
@@ -12651,7 +8839,7 @@
         <v>105</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E326" s="2">
         <v>1513.08</v>
@@ -12675,7 +8863,7 @@
         <v>106</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E327" s="2">
         <v>478.44</v>
@@ -12699,7 +8887,7 @@
         <v>109</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E328" s="2">
         <v>1092.42</v>
@@ -12723,7 +8911,7 @@
         <v>110</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E329" s="2">
         <v>731.16</v>
@@ -12747,7 +8935,7 @@
         <v>113</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E330" s="2">
         <v>4804.38</v>
@@ -12771,7 +8959,7 @@
         <v>115</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E331" s="2">
         <v>1558.26</v>
@@ -12795,7 +8983,7 @@
         <v>116</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E332" s="2">
         <v>668.58</v>
@@ -12819,7 +9007,7 @@
         <v>117</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E333" s="2">
         <v>5931.9</v>
@@ -12843,7 +9031,7 @@
         <v>118</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E334" s="2">
         <v>13848.45</v>
@@ -12867,7 +9055,7 @@
         <v>119</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E335" s="2">
         <v>349.44</v>
@@ -12891,7 +9079,7 @@
         <v>120</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E336" s="2">
         <v>4429.1899999999996</v>
@@ -12915,7 +9103,7 @@
         <v>121</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E337" s="2">
         <v>2655.25</v>
@@ -12939,7 +9127,7 @@
         <v>122</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E338" s="2">
         <v>11098.88</v>
@@ -12963,7 +9151,7 @@
         <v>123</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E339" s="2">
         <v>7549.44</v>
@@ -12983,21 +9171,21 @@
       <c r="B340" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C340" s="4" t="s">
+      <c r="C340" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E340" s="2">
-        <v>0</v>
+        <v>4834.82</v>
       </c>
       <c r="F340" s="1">
         <v>0.08</v>
       </c>
       <c r="G340" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>386.78559999999999</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
@@ -13011,17 +9199,17 @@
         <v>125</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E341" s="2">
-        <v>4457.8</v>
+        <v>4457.8100000000004</v>
       </c>
       <c r="F341" s="1">
         <v>0.08</v>
       </c>
       <c r="G341" s="2">
         <f t="shared" si="8"/>
-        <v>356.62400000000002</v>
+        <v>356.62480000000005</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
@@ -13031,21 +9219,21 @@
       <c r="B342" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C342" s="4" t="s">
+      <c r="C342" s="3" t="s">
         <v>126</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E342" s="2">
-        <v>0</v>
+        <v>229.12</v>
       </c>
       <c r="F342" s="1">
         <v>0.08</v>
       </c>
       <c r="G342" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>18.329599999999999</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
@@ -13059,7 +9247,7 @@
         <v>127</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E343" s="2">
         <v>1365.12</v>
@@ -13083,7 +9271,7 @@
         <v>128</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E344" s="2">
         <v>4877.28</v>
@@ -13107,7 +9295,7 @@
         <v>131</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E345" s="2">
         <v>1555.85</v>
@@ -13131,7 +9319,7 @@
         <v>132</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E346" s="2">
         <v>4855.1400000000003</v>
@@ -13151,21 +9339,21 @@
       <c r="B347" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C347" s="4" t="s">
+      <c r="C347" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E347" s="2">
-        <v>0</v>
+        <v>284.58</v>
       </c>
       <c r="F347" s="1">
         <v>0.1</v>
       </c>
       <c r="G347" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>28.457999999999998</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
@@ -13179,7 +9367,7 @@
         <v>134</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E348" s="2">
         <v>10177.73</v>
@@ -13203,7 +9391,7 @@
         <v>135</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E349" s="2">
         <v>2052</v>
@@ -13227,7 +9415,7 @@
         <v>136</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E350" s="2">
         <v>9938.7000000000007</v>
@@ -13247,21 +9435,21 @@
       <c r="B351" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C351" s="4" t="s">
-        <v>137</v>
+      <c r="C351" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E351" s="2">
-        <v>0</v>
+        <v>193.08</v>
       </c>
       <c r="F351" s="1">
         <v>0.1</v>
       </c>
       <c r="G351" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.308000000000003</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
@@ -13271,21 +9459,21 @@
       <c r="B352" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C352" s="4" t="s">
-        <v>138</v>
+      <c r="C352" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E352" s="2">
-        <v>0</v>
+        <v>1579.52</v>
       </c>
       <c r="F352" s="1">
         <v>0.1</v>
       </c>
       <c r="G352" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>157.952</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
@@ -13296,44 +9484,44 @@
         <v>130</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E353" s="2">
-        <v>1579.52</v>
+        <v>8942.0499999999993</v>
       </c>
       <c r="F353" s="1">
         <v>0.1</v>
       </c>
       <c r="G353" s="2">
         <f t="shared" si="8"/>
-        <v>157.952</v>
+        <v>894.20499999999993</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E354" s="2">
-        <v>8942.0499999999993</v>
+        <v>3041.28</v>
       </c>
       <c r="F354" s="1">
         <v>0.1</v>
       </c>
       <c r="G354" s="2">
         <f t="shared" si="8"/>
-        <v>894.20499999999993</v>
+        <v>304.12800000000004</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
@@ -13344,20 +9532,20 @@
         <v>142</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E355" s="2">
-        <v>3041.28</v>
+        <v>6325.76</v>
       </c>
       <c r="F355" s="1">
         <v>0.1</v>
       </c>
       <c r="G355" s="2">
         <f t="shared" si="8"/>
-        <v>304.12800000000004</v>
+        <v>632.57600000000002</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
@@ -13368,20 +9556,20 @@
         <v>142</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E356" s="2">
-        <v>6325.76</v>
+        <v>2908.8</v>
       </c>
       <c r="F356" s="1">
         <v>0.1</v>
       </c>
       <c r="G356" s="2">
         <f t="shared" si="8"/>
-        <v>632.57600000000002</v>
+        <v>290.88000000000005</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
@@ -13392,20 +9580,20 @@
         <v>142</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E357" s="2">
-        <v>2908.8</v>
+        <v>8320.0300000000007</v>
       </c>
       <c r="F357" s="1">
         <v>0.1</v>
       </c>
       <c r="G357" s="2">
         <f t="shared" si="8"/>
-        <v>290.88000000000005</v>
+        <v>832.00300000000016</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
@@ -13416,92 +9604,92 @@
         <v>142</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E358" s="2">
-        <v>8320.0300000000007</v>
+        <v>5274.08</v>
       </c>
       <c r="F358" s="1">
         <v>0.1</v>
       </c>
       <c r="G358" s="2">
         <f t="shared" si="8"/>
-        <v>832.00300000000016</v>
+        <v>527.40800000000002</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E359" s="2">
-        <v>5274.08</v>
+        <v>0</v>
       </c>
       <c r="F359" s="1">
         <v>0.1</v>
       </c>
       <c r="G359" s="2">
         <f t="shared" si="8"/>
-        <v>527.40800000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E360" s="2">
-        <v>0</v>
+        <v>1362.44</v>
       </c>
       <c r="F360" s="1">
         <v>0.1</v>
       </c>
       <c r="G360" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136.244</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E361" s="2">
-        <v>1362.44</v>
+        <v>4779.0600000000004</v>
       </c>
       <c r="F361" s="1">
         <v>0.1</v>
       </c>
       <c r="G361" s="2">
         <f t="shared" si="8"/>
-        <v>136.244</v>
+        <v>477.90600000000006</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
@@ -13512,20 +9700,20 @@
         <v>156</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E362" s="2">
-        <v>4779.0600000000004</v>
+        <v>2309.5</v>
       </c>
       <c r="F362" s="1">
         <v>0.1</v>
       </c>
       <c r="G362" s="2">
         <f t="shared" si="8"/>
-        <v>477.90600000000006</v>
+        <v>230.95000000000002</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
@@ -13536,48 +9724,24 @@
         <v>156</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E363" s="2">
-        <v>2309.5</v>
+        <v>4280.76</v>
       </c>
       <c r="F363" s="1">
         <v>0.1</v>
       </c>
       <c r="G363" s="2">
         <f t="shared" si="8"/>
-        <v>230.95000000000002</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A364" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B364" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C364" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D364" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E364" s="2">
-        <v>4280.76</v>
-      </c>
-      <c r="F364" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="G364" s="2">
-        <f t="shared" si="8"/>
         <v>428.07600000000002</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G359" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G363" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
@@ -13588,533 +9752,533 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="E1" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="F1" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="G1" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="H1" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="11" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="B2" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="C2" s="5" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="D2" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="6">
+        <v>625.29999999999995</v>
+      </c>
+      <c r="F2" s="6">
+        <v>62.53</v>
+      </c>
+      <c r="G2" s="6">
+        <v>70.849999999999994</v>
+      </c>
+      <c r="H2" s="6">
+        <v>491.92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="6">
+        <v>4282.24</v>
+      </c>
+      <c r="F3" s="6">
+        <v>428.22</v>
+      </c>
+      <c r="G3" s="6">
+        <v>485.18</v>
+      </c>
+      <c r="H3" s="6">
+        <v>3368.84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="6">
+        <v>170.24</v>
+      </c>
+      <c r="F4" s="6">
+        <v>17.02</v>
+      </c>
+      <c r="G4" s="6">
+        <v>19.29</v>
+      </c>
+      <c r="H4" s="6">
+        <v>133.93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="10">
-        <v>625.29999999999995</v>
-      </c>
-      <c r="F2" s="10">
-        <v>62.53</v>
-      </c>
-      <c r="G2" s="10">
-        <v>70.849999999999994</v>
-      </c>
-      <c r="H2" s="10">
-        <v>491.92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="D5" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4209.28</v>
+      </c>
+      <c r="F5" s="6">
+        <v>420.93</v>
+      </c>
+      <c r="G5" s="6">
+        <v>476.91</v>
+      </c>
+      <c r="H5" s="6">
+        <v>3311.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" s="10">
-        <v>4282.24</v>
-      </c>
-      <c r="F3" s="10">
-        <v>428.22</v>
-      </c>
-      <c r="G3" s="10">
-        <v>485.18</v>
-      </c>
-      <c r="H3" s="10">
-        <v>3368.84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="D6" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="6">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1.91</v>
+      </c>
+      <c r="H6" s="6">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" s="10">
-        <v>170.24</v>
-      </c>
-      <c r="F4" s="10">
-        <v>17.02</v>
-      </c>
-      <c r="G4" s="10">
-        <v>19.29</v>
-      </c>
-      <c r="H4" s="10">
-        <v>133.93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="6">
+        <v>103.9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>10.39</v>
+      </c>
+      <c r="G7" s="6">
+        <v>11.77</v>
+      </c>
+      <c r="H7" s="6">
+        <v>81.739999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2209.35</v>
+      </c>
+      <c r="F8" s="6">
+        <v>220.94</v>
+      </c>
+      <c r="G8" s="6">
+        <v>250.32</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1738.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="10">
-        <v>4209.28</v>
-      </c>
-      <c r="F5" s="10">
-        <v>420.93</v>
-      </c>
-      <c r="G5" s="10">
-        <v>476.91</v>
-      </c>
-      <c r="H5" s="10">
-        <v>3311.44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="D9" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="6">
+        <v>216.45</v>
+      </c>
+      <c r="F9" s="6">
+        <v>21.65</v>
+      </c>
+      <c r="G9" s="6">
+        <v>24.52</v>
+      </c>
+      <c r="H9" s="6">
+        <v>170.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="6">
+        <v>182.4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>18.239999999999998</v>
+      </c>
+      <c r="G10" s="6">
+        <v>20.67</v>
+      </c>
+      <c r="H10" s="6">
+        <v>143.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="10">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1.69</v>
-      </c>
-      <c r="G6" s="10">
-        <v>1.91</v>
-      </c>
-      <c r="H6" s="10">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="D11" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1202.5</v>
+      </c>
+      <c r="F11" s="6">
+        <v>120.25</v>
+      </c>
+      <c r="G11" s="6">
+        <v>136.24</v>
+      </c>
+      <c r="H11" s="6">
+        <v>946.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C12" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1301.1199999999999</v>
+      </c>
+      <c r="F14" s="6">
+        <v>130.11000000000001</v>
+      </c>
+      <c r="G14" s="6">
+        <v>147.41999999999999</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1023.59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1301.1199999999999</v>
+      </c>
+      <c r="F15" s="6">
+        <v>130.11000000000001</v>
+      </c>
+      <c r="G15" s="6">
+        <v>147.41999999999999</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1023.59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="10">
-        <v>103.9</v>
-      </c>
-      <c r="F7" s="10">
-        <v>10.39</v>
-      </c>
-      <c r="G7" s="10">
-        <v>11.77</v>
-      </c>
-      <c r="H7" s="10">
-        <v>81.739999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" s="10">
-        <v>2209.35</v>
-      </c>
-      <c r="F8" s="10">
-        <v>220.94</v>
-      </c>
-      <c r="G8" s="10">
-        <v>250.32</v>
-      </c>
-      <c r="H8" s="10">
-        <v>1738.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="10">
-        <v>216.45</v>
-      </c>
-      <c r="F9" s="10">
-        <v>21.65</v>
-      </c>
-      <c r="G9" s="10">
-        <v>24.52</v>
-      </c>
-      <c r="H9" s="10">
-        <v>170.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="10">
-        <v>182.4</v>
-      </c>
-      <c r="F10" s="10">
-        <v>18.239999999999998</v>
-      </c>
-      <c r="G10" s="10">
-        <v>20.67</v>
-      </c>
-      <c r="H10" s="10">
-        <v>143.49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1202.5</v>
-      </c>
-      <c r="F11" s="10">
-        <v>120.25</v>
-      </c>
-      <c r="G11" s="10">
-        <v>136.24</v>
-      </c>
-      <c r="H11" s="10">
-        <v>946.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="D16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="6">
+        <v>3385.3</v>
+      </c>
+      <c r="F16" s="6">
+        <v>338.53</v>
+      </c>
+      <c r="G16" s="6">
+        <v>383.55</v>
+      </c>
+      <c r="H16" s="6">
+        <v>2663.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="C17" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2997.06</v>
+      </c>
+      <c r="F17" s="6">
+        <v>299.70999999999998</v>
+      </c>
+      <c r="G17" s="6">
+        <v>339.57</v>
+      </c>
+      <c r="H17" s="6">
+        <v>2357.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1301.1199999999999</v>
-      </c>
-      <c r="F14" s="10">
-        <v>130.11000000000001</v>
-      </c>
-      <c r="G14" s="10">
-        <v>147.41999999999999</v>
-      </c>
-      <c r="H14" s="10">
-        <v>1023.59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1301.1199999999999</v>
-      </c>
-      <c r="F15" s="10">
-        <v>130.11000000000001</v>
-      </c>
-      <c r="G15" s="10">
-        <v>147.41999999999999</v>
-      </c>
-      <c r="H15" s="10">
-        <v>1023.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="10">
-        <v>3385.3</v>
-      </c>
-      <c r="F16" s="10">
-        <v>338.53</v>
-      </c>
-      <c r="G16" s="10">
-        <v>383.55</v>
-      </c>
-      <c r="H16" s="10">
-        <v>2663.22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="D18" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="6">
+        <v>9098.8799999999992</v>
+      </c>
+      <c r="F18" s="6">
+        <v>909.89</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1030.9000000000001</v>
+      </c>
+      <c r="H18" s="6">
+        <v>7158.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="10">
-        <v>2997.06</v>
-      </c>
-      <c r="F17" s="10">
-        <v>299.70999999999998</v>
-      </c>
-      <c r="G17" s="10">
-        <v>339.57</v>
-      </c>
-      <c r="H17" s="10">
-        <v>2357.79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="B19" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="6">
+        <v>8613.02</v>
+      </c>
+      <c r="F19" s="6">
+        <v>861.3</v>
+      </c>
+      <c r="G19" s="6">
+        <v>975.86</v>
+      </c>
+      <c r="H19" s="6">
+        <v>6775.86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" s="10">
-        <v>9098.8799999999992</v>
-      </c>
-      <c r="F18" s="10">
-        <v>909.89</v>
-      </c>
-      <c r="G18" s="10">
-        <v>1030.9000000000001</v>
-      </c>
-      <c r="H18" s="10">
-        <v>7158.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="10">
-        <v>8613.02</v>
-      </c>
-      <c r="F19" s="10">
-        <v>861.3</v>
-      </c>
-      <c r="G19" s="10">
-        <v>975.86</v>
-      </c>
-      <c r="H19" s="10">
-        <v>6775.86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="10">
+      <c r="D20" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="6">
         <v>3396.6</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="6">
         <v>339.66</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="6">
         <v>384.83</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="6">
         <v>2672.11</v>
       </c>
     </row>
@@ -14122,191 +10286,4 @@
   <autoFilter ref="A1:H1" xr:uid="{ECB98000-6C5E-44B6-ACEA-67E04ECC731C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00387D0C-05AA-4DC2-A95D-0F01933D4F85}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="8">
-        <v>334716.67832000001</v>
-      </c>
-      <c r="C2" s="8">
-        <v>25966.215131999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="8">
-        <v>311772.45000000013</v>
-      </c>
-      <c r="C3" s="8">
-        <v>24783.780699999992</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="8">
-        <v>3802.64</v>
-      </c>
-      <c r="C6" s="8">
-        <v>380.26400000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1936.44</v>
-      </c>
-      <c r="C7" s="8">
-        <v>193.64400000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8">
-        <v>41199.668320000012</v>
-      </c>
-      <c r="C8" s="8">
-        <v>4119.9668320000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="8">
-        <v>58476.01</v>
-      </c>
-      <c r="C9" s="8">
-        <v>5847.6009999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="8">
-        <v>129470.60999999997</v>
-      </c>
-      <c r="C10" s="8">
-        <v>12935.115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="8">
-        <v>240696.38000000006</v>
-      </c>
-      <c r="C11" s="8">
-        <v>12034.818999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="8">
-        <v>26735.55</v>
-      </c>
-      <c r="C12" s="8">
-        <v>2673.5550000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" s="8">
-        <v>51564.23</v>
-      </c>
-      <c r="C13" s="8">
-        <v>5156.4230000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="8">
-        <v>92607.600000000049</v>
-      </c>
-      <c r="C14" s="8">
-        <v>7408.6080000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD628134-A9F1-4E6B-BF2F-DFB2119DFCA8}">
-  <dimension ref="K4:Q4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="16384" width="8.88671875" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="11:17" ht="36.6" x14ac:dyDescent="0.7">
-      <c r="K4" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="K4:Q4"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E01E1C-503D-425F-91F0-AFE00C07651A}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{166B2273-78AF-4A1E-A190-0252973D2070}"/>
   <bookViews>
-    <workbookView xWindow="-25140" yWindow="-135" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24705" yWindow="300" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="194">
   <si>
     <t>Gerador</t>
   </si>
@@ -539,10 +539,6 @@
     <t>MÊS DE COMPETÊNCIA</t>
   </si>
   <si>
-    <t>FATURAMENTO 
-CLIENTE FINAL</t>
-  </si>
-  <si>
     <t xml:space="preserve"> DESCONTO GESTÃO </t>
   </si>
   <si>
@@ -622,15 +618,19 @@
   </si>
   <si>
     <t>EMÍLIO RIBAS - RU ITAIÇABA, 111</t>
+  </si>
+  <si>
+    <t>FATURAMENTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -689,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -698,9 +698,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -713,6 +710,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1024,6 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G363"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1038,29 +1044,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1073,18 +1079,18 @@
       <c r="D2" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="10">
         <v>719.55</v>
       </c>
       <c r="F2" s="1">
         <v>0.1</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="10">
         <f>E2*F2</f>
         <v>71.954999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1097,18 +1103,18 @@
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="10">
         <v>3411.2</v>
       </c>
       <c r="F3" s="1">
         <v>0.1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="10">
         <f>E3*F3</f>
         <v>341.12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1121,17 +1127,17 @@
       <c r="D4" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="10">
         <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0.1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1144,18 +1150,18 @@
       <c r="D5" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="10">
         <v>1082.64832</v>
       </c>
       <c r="F5" s="1">
         <v>0.1</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="10">
         <f t="shared" ref="G5:G36" si="0">E5*F5</f>
         <v>108.26483200000001</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1168,18 +1174,18 @@
       <c r="D6" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="10">
         <v>1726.95</v>
       </c>
       <c r="F6" s="1">
         <v>0.1</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
         <v>172.69500000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -1192,18 +1198,18 @@
       <c r="D7" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="10">
         <v>1540.41</v>
       </c>
       <c r="F7" s="1">
         <v>0.1</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="10">
         <f t="shared" si="0"/>
         <v>154.04100000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -1216,18 +1222,18 @@
       <c r="D8" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="10">
         <v>199.04</v>
       </c>
       <c r="F8" s="1">
         <v>0.1</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="10">
         <f t="shared" si="0"/>
         <v>19.904</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1240,18 +1246,18 @@
       <c r="D9" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="10">
         <v>418.84</v>
       </c>
       <c r="F9" s="1">
         <v>0.1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="10">
         <f t="shared" si="0"/>
         <v>41.884</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1264,18 +1270,18 @@
       <c r="D10" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="10">
         <v>0</v>
       </c>
       <c r="F10" s="1">
         <v>0.1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -1288,18 +1294,18 @@
       <c r="D11" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="10">
         <v>218.73</v>
       </c>
       <c r="F11" s="1">
         <v>0.1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="10">
         <f t="shared" si="0"/>
         <v>21.873000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1312,18 +1318,18 @@
       <c r="D12" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="10">
         <v>219.7</v>
       </c>
       <c r="F12" s="1">
         <v>0.1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="10">
         <f t="shared" si="0"/>
         <v>21.97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
@@ -1336,18 +1342,18 @@
       <c r="D13" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="10">
         <v>46.72</v>
       </c>
       <c r="F13" s="1">
         <v>0.1</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="10">
         <f t="shared" si="0"/>
         <v>4.6719999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1360,18 +1366,18 @@
       <c r="D14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="10">
         <v>31.85</v>
       </c>
       <c r="F14" s="1">
         <v>0.1</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
         <v>3.1850000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1384,18 +1390,18 @@
       <c r="D15" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="10">
         <v>151.68</v>
       </c>
       <c r="F15" s="1">
         <v>0.1</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="10">
         <f t="shared" si="0"/>
         <v>15.168000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
@@ -1408,18 +1414,18 @@
       <c r="D16" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="10">
         <v>1828.45</v>
       </c>
       <c r="F16" s="1">
         <v>0.1</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
         <v>182.84500000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1432,18 +1438,18 @@
       <c r="D17" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="10">
         <v>0</v>
       </c>
       <c r="F17" s="1">
         <v>0.1</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1456,18 +1462,18 @@
       <c r="D18" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="10">
         <v>5198.8999999999996</v>
       </c>
       <c r="F18" s="1">
         <v>0.1</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="10">
         <f t="shared" si="0"/>
         <v>519.89</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1480,18 +1486,18 @@
       <c r="D19" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="10">
         <v>5198.8999999999996</v>
       </c>
       <c r="F19" s="1">
         <v>0.1</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="10">
         <f t="shared" si="0"/>
         <v>519.89</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1504,18 +1510,18 @@
       <c r="D20" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="10">
         <v>11686.48</v>
       </c>
       <c r="F20" s="1">
         <v>0.1</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="10">
         <f t="shared" si="0"/>
         <v>1168.6479999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
@@ -1528,18 +1534,18 @@
       <c r="D21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="10">
         <v>2248.5100000000002</v>
       </c>
       <c r="F21" s="1">
         <v>0.1</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="10">
         <f t="shared" si="0"/>
         <v>224.85100000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
@@ -1552,18 +1558,18 @@
       <c r="D22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="10">
         <v>7392.64</v>
       </c>
       <c r="F22" s="1">
         <v>0.08</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="10">
         <f t="shared" si="0"/>
         <v>591.41120000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>31</v>
       </c>
@@ -1576,18 +1582,18 @@
       <c r="D23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="10">
         <v>6910.72</v>
       </c>
       <c r="F23" s="1">
         <v>0.08</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="10">
         <f t="shared" si="0"/>
         <v>552.85760000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
@@ -1600,18 +1606,18 @@
       <c r="D24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="10">
         <v>2600.96</v>
       </c>
       <c r="F24" s="1">
         <v>0.08</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="10">
         <f t="shared" si="0"/>
         <v>208.07680000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
@@ -1624,18 +1630,18 @@
       <c r="D25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="10">
         <v>1721.6</v>
       </c>
       <c r="F25" s="1">
         <v>0.08</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="10">
         <f t="shared" si="0"/>
         <v>137.72800000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
@@ -1648,18 +1654,18 @@
       <c r="D26" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="10">
         <v>1824</v>
       </c>
       <c r="F26" s="1">
         <v>0.08</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="10">
         <f t="shared" si="0"/>
         <v>145.92000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
@@ -1672,18 +1678,18 @@
       <c r="D27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="10">
         <v>2100.6</v>
       </c>
       <c r="F27" s="1">
         <v>0.08</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="10">
         <f t="shared" si="0"/>
         <v>168.048</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
@@ -1696,18 +1702,18 @@
       <c r="D28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="10">
         <v>2458.88</v>
       </c>
       <c r="F28" s="1">
         <v>0.08</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="10">
         <f t="shared" si="0"/>
         <v>196.71040000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
@@ -1720,18 +1726,18 @@
       <c r="D29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="10">
         <v>2789.36</v>
       </c>
       <c r="F29" s="1">
         <v>0.08</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="10">
         <f t="shared" si="0"/>
         <v>223.14880000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
@@ -1744,18 +1750,18 @@
       <c r="D30" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="10">
         <v>4679.08</v>
       </c>
       <c r="F30" s="1">
         <v>0.08</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="10">
         <f t="shared" si="0"/>
         <v>374.32639999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
@@ -1768,18 +1774,18 @@
       <c r="D31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="10">
         <v>2113.02</v>
       </c>
       <c r="F31" s="1">
         <v>0.08</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="10">
         <f t="shared" si="0"/>
         <v>169.04159999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -1792,18 +1798,18 @@
       <c r="D32" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="10">
         <v>3013.2</v>
       </c>
       <c r="F32" s="1">
         <v>0.08</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="10">
         <f t="shared" si="0"/>
         <v>241.05599999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
@@ -1816,18 +1822,18 @@
       <c r="D33" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="10">
         <v>646.79999999999995</v>
       </c>
       <c r="F33" s="1">
         <v>0.08</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="10">
         <f t="shared" si="0"/>
         <v>51.744</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1840,18 +1846,18 @@
       <c r="D34" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="10">
         <v>532.62</v>
       </c>
       <c r="F34" s="1">
         <v>0.08</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="10">
         <f t="shared" si="0"/>
         <v>42.6096</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
@@ -1864,18 +1870,18 @@
       <c r="D35" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="10">
         <v>519.91999999999996</v>
       </c>
       <c r="F35" s="1">
         <v>0.08</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="10">
         <f t="shared" si="0"/>
         <v>41.593599999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>31</v>
       </c>
@@ -1888,18 +1894,18 @@
       <c r="D36" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="10">
         <v>264</v>
       </c>
       <c r="F36" s="1">
         <v>0.08</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="10">
         <f t="shared" si="0"/>
         <v>21.12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
@@ -1912,18 +1918,18 @@
       <c r="D37" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="10">
         <v>1372.8</v>
       </c>
       <c r="F37" s="1">
         <v>0.08</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="10">
         <f t="shared" ref="G37:G68" si="1">E37*F37</f>
         <v>109.824</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1936,18 +1942,18 @@
       <c r="D38" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="10">
         <v>1143.1199999999999</v>
       </c>
       <c r="F38" s="1">
         <v>0.08</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="10">
         <f t="shared" si="1"/>
         <v>91.44959999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1960,18 +1966,18 @@
       <c r="D39" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="10">
         <v>250.4</v>
       </c>
       <c r="F39" s="1">
         <v>0.08</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="10">
         <f t="shared" si="1"/>
         <v>20.032</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1984,18 +1990,18 @@
       <c r="D40" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="10">
         <v>99.11</v>
       </c>
       <c r="F40" s="1">
         <v>0.08</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="10">
         <f t="shared" si="1"/>
         <v>7.9287999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -2008,18 +2014,18 @@
       <c r="D41" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="10">
         <v>401.67</v>
       </c>
       <c r="F41" s="1">
         <v>0.08</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="10">
         <f t="shared" si="1"/>
         <v>32.133600000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -2032,18 +2038,18 @@
       <c r="D42" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="10">
         <v>326.04000000000002</v>
       </c>
       <c r="F42" s="1">
         <v>0.08</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="10">
         <f t="shared" si="1"/>
         <v>26.083200000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -2056,18 +2062,18 @@
       <c r="D43" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="10">
         <v>261.3</v>
       </c>
       <c r="F43" s="1">
         <v>0.08</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="10">
         <f t="shared" si="1"/>
         <v>20.904</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>31</v>
       </c>
@@ -2080,18 +2086,18 @@
       <c r="D44" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="10">
         <v>404.29</v>
       </c>
       <c r="F44" s="1">
         <v>0.08</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="10">
         <f t="shared" si="1"/>
         <v>32.343200000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>31</v>
       </c>
@@ -2104,18 +2110,18 @@
       <c r="D45" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="10">
         <v>605.13</v>
       </c>
       <c r="F45" s="1">
         <v>0.08</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="10">
         <f t="shared" si="1"/>
         <v>48.410400000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>31</v>
       </c>
@@ -2128,18 +2134,18 @@
       <c r="D46" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="10">
         <v>633.15</v>
       </c>
       <c r="F46" s="1">
         <v>0.08</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46" s="10">
         <f t="shared" si="1"/>
         <v>50.652000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>31</v>
       </c>
@@ -2152,18 +2158,18 @@
       <c r="D47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="10">
         <v>1238.44</v>
       </c>
       <c r="F47" s="1">
         <v>0.08</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="10">
         <f t="shared" si="1"/>
         <v>99.075200000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>31</v>
       </c>
@@ -2176,18 +2182,18 @@
       <c r="D48" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="10">
         <v>951.06</v>
       </c>
       <c r="F48" s="1">
         <v>0.08</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="10">
         <f t="shared" si="1"/>
         <v>76.084800000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>60</v>
       </c>
@@ -2200,15 +2206,16 @@
       <c r="D49" s="3" t="s">
         <v>148</v>
       </c>
+      <c r="E49" s="10"/>
       <c r="F49" s="1">
         <v>0.05</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>60</v>
       </c>
@@ -2221,18 +2228,18 @@
       <c r="D50" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="10">
         <v>9101.44</v>
       </c>
       <c r="F50" s="1">
         <v>0.05</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="10">
         <f t="shared" si="1"/>
         <v>455.07200000000006</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>60</v>
       </c>
@@ -2245,15 +2252,16 @@
       <c r="D51" s="3" t="s">
         <v>148</v>
       </c>
+      <c r="E51" s="10"/>
       <c r="F51" s="1">
         <v>0.05</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>60</v>
       </c>
@@ -2266,18 +2274,18 @@
       <c r="D52" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="10">
         <v>4949.76</v>
       </c>
       <c r="F52" s="1">
         <v>0.05</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G52" s="10">
         <f t="shared" si="1"/>
         <v>247.48800000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>60</v>
       </c>
@@ -2290,18 +2298,18 @@
       <c r="D53" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="10">
         <v>6338.56</v>
       </c>
       <c r="F53" s="1">
         <v>0.05</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G53" s="10">
         <f t="shared" si="1"/>
         <v>316.92800000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>60</v>
       </c>
@@ -2314,18 +2322,18 @@
       <c r="D54" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="10">
         <v>2715.05</v>
       </c>
       <c r="F54" s="1">
         <v>0.05</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G54" s="10">
         <f t="shared" si="1"/>
         <v>135.75250000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>60</v>
       </c>
@@ -2338,18 +2346,18 @@
       <c r="D55" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="10">
         <v>3175.68</v>
       </c>
       <c r="F55" s="1">
         <v>0.05</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G55" s="10">
         <f t="shared" si="1"/>
         <v>158.78399999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>60</v>
       </c>
@@ -2362,18 +2370,18 @@
       <c r="D56" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="10">
         <v>6210.56</v>
       </c>
       <c r="F56" s="1">
         <v>0.05</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="10">
         <f t="shared" si="1"/>
         <v>310.52800000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>60</v>
       </c>
@@ -2386,18 +2394,18 @@
       <c r="D57" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="10">
         <v>0</v>
       </c>
       <c r="F57" s="1">
         <v>0.05</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G57" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
@@ -2410,18 +2418,18 @@
       <c r="D58" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="10">
         <v>261.47000000000003</v>
       </c>
       <c r="F58" s="1">
         <v>0.05</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G58" s="10">
         <f t="shared" si="1"/>
         <v>13.073500000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>60</v>
       </c>
@@ -2434,18 +2442,18 @@
       <c r="D59" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="10">
         <v>1418.88</v>
       </c>
       <c r="F59" s="1">
         <v>0.05</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G59" s="10">
         <f t="shared" si="1"/>
         <v>70.944000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
@@ -2458,18 +2466,18 @@
       <c r="D60" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="10">
         <v>3537.92</v>
       </c>
       <c r="F60" s="1">
         <v>0.05</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G60" s="10">
         <f t="shared" si="1"/>
         <v>176.89600000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
@@ -2482,18 +2490,18 @@
       <c r="D61" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="10">
         <v>0</v>
       </c>
       <c r="F61" s="1">
         <v>0.05</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G61" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>60</v>
       </c>
@@ -2506,18 +2514,18 @@
       <c r="D62" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="10">
         <v>3828.82</v>
       </c>
       <c r="F62" s="1">
         <v>0.05</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G62" s="10">
         <f t="shared" si="1"/>
         <v>191.44100000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>60</v>
       </c>
@@ -2530,18 +2538,18 @@
       <c r="D63" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="10">
         <v>5204.55</v>
       </c>
       <c r="F63" s="1">
         <v>0.05</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G63" s="10">
         <f t="shared" si="1"/>
         <v>260.22750000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>60</v>
       </c>
@@ -2554,18 +2562,18 @@
       <c r="D64" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="10">
         <v>5534.1</v>
       </c>
       <c r="F64" s="1">
         <v>0.05</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G64" s="10">
         <f t="shared" si="1"/>
         <v>276.70500000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
@@ -2578,18 +2586,18 @@
       <c r="D65" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="10">
         <v>4553.58</v>
       </c>
       <c r="F65" s="1">
         <v>0.05</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G65" s="10">
         <f t="shared" si="1"/>
         <v>227.679</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>60</v>
       </c>
@@ -2602,18 +2610,18 @@
       <c r="D66" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="10">
         <v>11651.2</v>
       </c>
       <c r="F66" s="1">
         <v>0.05</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G66" s="10">
         <f t="shared" si="1"/>
         <v>582.56000000000006</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>60</v>
       </c>
@@ -2626,18 +2634,18 @@
       <c r="D67" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="10">
         <v>4817.92</v>
       </c>
       <c r="F67" s="1">
         <v>0.05</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G67" s="10">
         <f t="shared" si="1"/>
         <v>240.89600000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>60</v>
       </c>
@@ -2650,18 +2658,18 @@
       <c r="D68" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="10">
         <v>9120.7999999999993</v>
       </c>
       <c r="F68" s="1">
         <v>0.05</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G68" s="10">
         <f t="shared" si="1"/>
         <v>456.03999999999996</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>60</v>
       </c>
@@ -2674,18 +2682,18 @@
       <c r="D69" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="10">
         <v>3503.72</v>
       </c>
       <c r="F69" s="1">
         <v>0.05</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G69" s="10">
         <f t="shared" ref="G69:G96" si="2">E69*F69</f>
         <v>175.18600000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>60</v>
       </c>
@@ -2698,18 +2706,18 @@
       <c r="D70" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="10">
         <v>1077.05</v>
       </c>
       <c r="F70" s="1">
         <v>0.05</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="10">
         <f t="shared" si="2"/>
         <v>53.852499999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>60</v>
       </c>
@@ -2722,18 +2730,18 @@
       <c r="D71" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="10">
         <v>694.4</v>
       </c>
       <c r="F71" s="1">
         <v>0.05</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="10">
         <f t="shared" si="2"/>
         <v>34.72</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>60</v>
       </c>
@@ -2746,18 +2754,18 @@
       <c r="D72" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="10">
         <v>5792.15</v>
       </c>
       <c r="F72" s="1">
         <v>0.05</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G72" s="10">
         <f t="shared" si="2"/>
         <v>289.60750000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>60</v>
       </c>
@@ -2770,18 +2778,18 @@
       <c r="D73" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="10">
         <v>613.12</v>
       </c>
       <c r="F73" s="1">
         <v>0.05</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G73" s="10">
         <f t="shared" si="2"/>
         <v>30.656000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>60</v>
       </c>
@@ -2794,18 +2802,18 @@
       <c r="D74" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="10">
         <v>5693.44</v>
       </c>
       <c r="F74" s="1">
         <v>0.05</v>
       </c>
-      <c r="G74" s="2">
+      <c r="G74" s="10">
         <f t="shared" si="2"/>
         <v>284.67199999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>60</v>
       </c>
@@ -2818,18 +2826,18 @@
       <c r="D75" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="10">
         <v>4423.68</v>
       </c>
       <c r="F75" s="1">
         <v>0.05</v>
       </c>
-      <c r="G75" s="2">
+      <c r="G75" s="10">
         <f t="shared" si="2"/>
         <v>221.18400000000003</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>60</v>
       </c>
@@ -2842,18 +2850,18 @@
       <c r="D76" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="10">
         <v>811.52</v>
       </c>
       <c r="F76" s="1">
         <v>0.05</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G76" s="10">
         <f t="shared" si="2"/>
         <v>40.576000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>60</v>
       </c>
@@ -2866,18 +2874,18 @@
       <c r="D77" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="10">
         <v>6256</v>
       </c>
       <c r="F77" s="1">
         <v>0.05</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G77" s="10">
         <f t="shared" si="2"/>
         <v>312.8</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>60</v>
       </c>
@@ -2890,18 +2898,18 @@
       <c r="D78" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="10">
         <v>0</v>
       </c>
       <c r="F78" s="1">
         <v>0.05</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G78" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>60</v>
       </c>
@@ -2914,18 +2922,18 @@
       <c r="D79" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="10">
         <v>1003.52</v>
       </c>
       <c r="F79" s="1">
         <v>0.05</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G79" s="10">
         <f t="shared" si="2"/>
         <v>50.176000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>60</v>
       </c>
@@ -2938,18 +2946,18 @@
       <c r="D80" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="10">
         <v>1112.96</v>
       </c>
       <c r="F80" s="1">
         <v>0.05</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G80" s="10">
         <f t="shared" si="2"/>
         <v>55.648000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>60</v>
       </c>
@@ -2962,18 +2970,18 @@
       <c r="D81" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="10">
         <v>5863.04</v>
       </c>
       <c r="F81" s="1">
         <v>0.05</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G81" s="10">
         <f t="shared" si="2"/>
         <v>293.15199999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>60</v>
       </c>
@@ -2986,18 +2994,18 @@
       <c r="D82" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="10">
         <v>4433.92</v>
       </c>
       <c r="F82" s="1">
         <v>0.05</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G82" s="10">
         <f t="shared" si="2"/>
         <v>221.69600000000003</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>60</v>
       </c>
@@ -3010,18 +3018,18 @@
       <c r="D83" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="10">
         <v>7269.76</v>
       </c>
       <c r="F83" s="1">
         <v>0.05</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G83" s="10">
         <f t="shared" si="2"/>
         <v>363.48800000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>99</v>
       </c>
@@ -3034,18 +3042,18 @@
       <c r="D84" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="10">
         <v>5134.1499999999996</v>
       </c>
       <c r="F84" s="1">
         <v>0.1</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G84" s="10">
         <f t="shared" si="2"/>
         <v>513.41499999999996</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>99</v>
       </c>
@@ -3058,18 +3066,18 @@
       <c r="D85" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="10">
         <v>217.6</v>
       </c>
       <c r="F85" s="1">
         <v>0.1</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G85" s="10">
         <f t="shared" si="2"/>
         <v>21.76</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>99</v>
       </c>
@@ -3082,18 +3090,18 @@
       <c r="D86" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="10">
         <v>2311.25</v>
       </c>
       <c r="F86" s="1">
         <v>0.1</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G86" s="10">
         <f t="shared" si="2"/>
         <v>231.125</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>99</v>
       </c>
@@ -3106,18 +3114,18 @@
       <c r="D87" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="10">
         <v>289.44</v>
       </c>
       <c r="F87" s="1">
         <v>0.1</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G87" s="10">
         <f t="shared" si="2"/>
         <v>28.944000000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>99</v>
       </c>
@@ -3130,18 +3138,18 @@
       <c r="D88" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="10">
         <v>2266.38</v>
       </c>
       <c r="F88" s="1">
         <v>0.1</v>
       </c>
-      <c r="G88" s="2">
+      <c r="G88" s="10">
         <f t="shared" si="2"/>
         <v>226.63800000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>99</v>
       </c>
@@ -3154,18 +3162,18 @@
       <c r="D89" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="10">
         <v>423.9</v>
       </c>
       <c r="F89" s="1">
         <v>0.1</v>
       </c>
-      <c r="G89" s="2">
+      <c r="G89" s="10">
         <f t="shared" si="2"/>
         <v>42.39</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>99</v>
       </c>
@@ -3178,18 +3186,18 @@
       <c r="D90" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="10">
         <v>204.68</v>
       </c>
       <c r="F90" s="1">
         <v>0.1</v>
       </c>
-      <c r="G90" s="2">
+      <c r="G90" s="10">
         <f t="shared" si="2"/>
         <v>20.468000000000004</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>99</v>
       </c>
@@ -3202,18 +3210,18 @@
       <c r="D91" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="10">
         <v>0</v>
       </c>
       <c r="F91" s="1">
         <v>0.1</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>99</v>
       </c>
@@ -3226,18 +3234,18 @@
       <c r="D92" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="10">
         <v>993.06</v>
       </c>
       <c r="F92" s="1">
         <v>0.1</v>
       </c>
-      <c r="G92" s="2">
+      <c r="G92" s="10">
         <f t="shared" si="2"/>
         <v>99.305999999999997</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>99</v>
       </c>
@@ -3250,18 +3258,18 @@
       <c r="D93" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="10">
         <v>885.6</v>
       </c>
       <c r="F93" s="1">
         <v>0.1</v>
       </c>
-      <c r="G93" s="2">
+      <c r="G93" s="10">
         <f t="shared" si="2"/>
         <v>88.56</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>99</v>
       </c>
@@ -3274,18 +3282,18 @@
       <c r="D94" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="10">
         <v>460.08</v>
       </c>
       <c r="F94" s="1">
         <v>0.1</v>
       </c>
-      <c r="G94" s="2">
+      <c r="G94" s="10">
         <f t="shared" si="2"/>
         <v>46.008000000000003</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>99</v>
       </c>
@@ -3298,18 +3306,18 @@
       <c r="D95" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="10">
         <v>0</v>
       </c>
       <c r="F95" s="1">
         <v>0.1</v>
       </c>
-      <c r="G95" s="2">
+      <c r="G95" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>99</v>
       </c>
@@ -3322,18 +3330,18 @@
       <c r="D96" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="10">
         <v>4362.66</v>
       </c>
       <c r="F96" s="1">
         <v>0.1</v>
       </c>
-      <c r="G96" s="2">
+      <c r="G96" s="10">
         <f t="shared" si="2"/>
         <v>436.26600000000002</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>99</v>
       </c>
@@ -3346,17 +3354,17 @@
       <c r="D97" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="10">
         <v>119.46</v>
       </c>
       <c r="F97" s="1">
         <v>0.1</v>
       </c>
-      <c r="G97" s="2">
+      <c r="G97" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>99</v>
       </c>
@@ -3369,18 +3377,18 @@
       <c r="D98" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="10">
         <v>1359.6</v>
       </c>
       <c r="F98" s="1">
         <v>0.1</v>
       </c>
-      <c r="G98" s="2">
+      <c r="G98" s="10">
         <f t="shared" ref="G98:G129" si="3">E98*F98</f>
         <v>135.96</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>99</v>
       </c>
@@ -3393,18 +3401,18 @@
       <c r="D99" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="10">
         <v>624.36</v>
       </c>
       <c r="F99" s="1">
         <v>0.1</v>
       </c>
-      <c r="G99" s="2">
+      <c r="G99" s="10">
         <f t="shared" si="3"/>
         <v>62.436000000000007</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>99</v>
       </c>
@@ -3417,18 +3425,18 @@
       <c r="D100" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="10">
         <v>5857.38</v>
       </c>
       <c r="F100" s="1">
         <v>0.1</v>
       </c>
-      <c r="G100" s="2">
+      <c r="G100" s="10">
         <f t="shared" si="3"/>
         <v>585.73800000000006</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>99</v>
       </c>
@@ -3441,18 +3449,18 @@
       <c r="D101" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="10">
         <v>12081.84</v>
       </c>
       <c r="F101" s="1">
         <v>0.1</v>
       </c>
-      <c r="G101" s="2">
+      <c r="G101" s="10">
         <f t="shared" si="3"/>
         <v>1208.184</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>99</v>
       </c>
@@ -3465,18 +3473,18 @@
       <c r="D102" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="10">
         <v>348.16</v>
       </c>
       <c r="F102" s="1">
         <v>0.1</v>
       </c>
-      <c r="G102" s="2">
+      <c r="G102" s="10">
         <f t="shared" si="3"/>
         <v>34.816000000000003</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>99</v>
       </c>
@@ -3489,18 +3497,18 @@
       <c r="D103" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="10">
         <v>2118.35</v>
       </c>
       <c r="F103" s="1">
         <v>0.1</v>
       </c>
-      <c r="G103" s="2">
+      <c r="G103" s="10">
         <f t="shared" si="3"/>
         <v>211.83500000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>99</v>
       </c>
@@ -3513,18 +3521,18 @@
       <c r="D104" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="10">
         <v>3017.95</v>
       </c>
       <c r="F104" s="1">
         <v>0.1</v>
       </c>
-      <c r="G104" s="2">
+      <c r="G104" s="10">
         <f t="shared" si="3"/>
         <v>301.79500000000002</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>99</v>
       </c>
@@ -3537,18 +3545,18 @@
       <c r="D105" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E105" s="10">
         <v>10561.28</v>
       </c>
       <c r="F105" s="1">
         <v>0.1</v>
       </c>
-      <c r="G105" s="2">
+      <c r="G105" s="10">
         <f t="shared" si="3"/>
         <v>1056.1280000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>99</v>
       </c>
@@ -3561,18 +3569,18 @@
       <c r="D106" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="10">
         <v>1683.84</v>
       </c>
       <c r="F106" s="1">
         <v>0.1</v>
       </c>
-      <c r="G106" s="2">
+      <c r="G106" s="10">
         <f t="shared" si="3"/>
         <v>168.38400000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>99</v>
       </c>
@@ -3585,18 +3593,18 @@
       <c r="D107" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="10">
         <v>1457.39</v>
       </c>
       <c r="F107" s="1">
         <v>0.1</v>
       </c>
-      <c r="G107" s="2">
+      <c r="G107" s="10">
         <f t="shared" si="3"/>
         <v>145.739</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>99</v>
       </c>
@@ -3609,18 +3617,18 @@
       <c r="D108" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="10">
         <v>969.2</v>
       </c>
       <c r="F108" s="1">
         <v>0.1</v>
       </c>
-      <c r="G108" s="2">
+      <c r="G108" s="10">
         <f t="shared" si="3"/>
         <v>96.920000000000016</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>99</v>
       </c>
@@ -3633,18 +3641,18 @@
       <c r="D109" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="10">
         <v>226.56</v>
       </c>
       <c r="F109" s="1">
         <v>0.1</v>
       </c>
-      <c r="G109" s="2">
+      <c r="G109" s="10">
         <f t="shared" si="3"/>
         <v>22.656000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>99</v>
       </c>
@@ -3657,18 +3665,18 @@
       <c r="D110" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E110" s="10">
         <v>646.38</v>
       </c>
       <c r="F110" s="1">
         <v>0.1</v>
       </c>
-      <c r="G110" s="2">
+      <c r="G110" s="10">
         <f t="shared" si="3"/>
         <v>64.638000000000005</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>99</v>
       </c>
@@ -3681,18 +3689,18 @@
       <c r="D111" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="10">
         <v>394.2</v>
       </c>
       <c r="F111" s="1">
         <v>0.1</v>
       </c>
-      <c r="G111" s="2">
+      <c r="G111" s="10">
         <f t="shared" si="3"/>
         <v>39.42</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>129</v>
       </c>
@@ -3705,18 +3713,18 @@
       <c r="D112" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="10">
         <v>1846.2</v>
       </c>
       <c r="F112" s="1">
         <v>0.1</v>
       </c>
-      <c r="G112" s="2">
+      <c r="G112" s="10">
         <f t="shared" si="3"/>
         <v>184.62</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>129</v>
       </c>
@@ -3729,18 +3737,18 @@
       <c r="D113" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="10">
         <v>4475.5200000000004</v>
       </c>
       <c r="F113" s="1">
         <v>0.1</v>
       </c>
-      <c r="G113" s="2">
+      <c r="G113" s="10">
         <f t="shared" si="3"/>
         <v>447.55200000000008</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>129</v>
       </c>
@@ -3753,18 +3761,18 @@
       <c r="D114" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="10">
         <v>293.52</v>
       </c>
       <c r="F114" s="1">
         <v>0.1</v>
       </c>
-      <c r="G114" s="2">
+      <c r="G114" s="10">
         <f t="shared" si="3"/>
         <v>29.352</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>129</v>
       </c>
@@ -3777,18 +3785,18 @@
       <c r="D115" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="10">
         <v>4923.97</v>
       </c>
       <c r="F115" s="1">
         <v>0.1</v>
       </c>
-      <c r="G115" s="2">
+      <c r="G115" s="10">
         <f t="shared" si="3"/>
         <v>492.39700000000005</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>129</v>
       </c>
@@ -3801,18 +3809,18 @@
       <c r="D116" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="10">
         <v>1840.86</v>
       </c>
       <c r="F116" s="1">
         <v>0.1</v>
       </c>
-      <c r="G116" s="2">
+      <c r="G116" s="10">
         <f t="shared" si="3"/>
         <v>184.08600000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>129</v>
       </c>
@@ -3825,18 +3833,18 @@
       <c r="D117" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="10">
         <v>10140.799999999999</v>
       </c>
       <c r="F117" s="1">
         <v>0.1</v>
       </c>
-      <c r="G117" s="2">
+      <c r="G117" s="10">
         <f t="shared" si="3"/>
         <v>1014.0799999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>129</v>
       </c>
@@ -3849,18 +3857,18 @@
       <c r="D118" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="10">
         <v>0</v>
       </c>
       <c r="F118" s="1">
         <v>0.1</v>
       </c>
-      <c r="G118" s="2">
+      <c r="G118" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>129</v>
       </c>
@@ -3873,18 +3881,18 @@
       <c r="D119" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="10">
         <v>123.55</v>
       </c>
       <c r="F119" s="1">
         <v>0.1</v>
       </c>
-      <c r="G119" s="2">
+      <c r="G119" s="10">
         <f t="shared" si="3"/>
         <v>12.355</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>129</v>
       </c>
@@ -3897,18 +3905,18 @@
       <c r="D120" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E120" s="10">
         <v>974.7</v>
       </c>
       <c r="F120" s="1">
         <v>0.1</v>
       </c>
-      <c r="G120" s="2">
+      <c r="G120" s="10">
         <f t="shared" si="3"/>
         <v>97.470000000000013</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>129</v>
       </c>
@@ -3921,18 +3929,18 @@
       <c r="D121" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="10">
         <v>9473.1</v>
       </c>
       <c r="F121" s="1">
         <v>0.1</v>
       </c>
-      <c r="G121" s="2">
+      <c r="G121" s="10">
         <f t="shared" si="3"/>
         <v>947.31000000000006</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>141</v>
       </c>
@@ -3945,18 +3953,18 @@
       <c r="D122" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E122" s="10">
         <v>2930.4</v>
       </c>
       <c r="F122" s="1">
         <v>0.1</v>
       </c>
-      <c r="G122" s="2">
+      <c r="G122" s="10">
         <f t="shared" si="3"/>
         <v>293.04000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>141</v>
       </c>
@@ -3969,18 +3977,18 @@
       <c r="D123" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E123" s="10">
         <v>6302.08</v>
       </c>
       <c r="F123" s="1">
         <v>0.1</v>
       </c>
-      <c r="G123" s="2">
+      <c r="G123" s="10">
         <f t="shared" si="3"/>
         <v>630.20800000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>141</v>
       </c>
@@ -3993,18 +4001,18 @@
       <c r="D124" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="10">
         <v>2708.48</v>
       </c>
       <c r="F124" s="1">
         <v>0.1</v>
       </c>
-      <c r="G124" s="2">
+      <c r="G124" s="10">
         <f t="shared" si="3"/>
         <v>270.84800000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>141</v>
       </c>
@@ -4017,18 +4025,18 @@
       <c r="D125" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="10">
         <v>10157.950000000001</v>
       </c>
       <c r="F125" s="1">
         <v>0.1</v>
       </c>
-      <c r="G125" s="2">
+      <c r="G125" s="10">
         <f t="shared" si="3"/>
         <v>1015.7950000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>141</v>
       </c>
@@ -4041,18 +4049,18 @@
       <c r="D126" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="10">
         <v>5359.76</v>
       </c>
       <c r="F126" s="1">
         <v>0.1</v>
       </c>
-      <c r="G126" s="2">
+      <c r="G126" s="10">
         <f t="shared" si="3"/>
         <v>535.976</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>4</v>
       </c>
@@ -4065,18 +4073,18 @@
       <c r="D127" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="10">
         <v>625.29999999999995</v>
       </c>
       <c r="F127" s="1">
         <v>0.1</v>
       </c>
-      <c r="G127" s="2">
+      <c r="G127" s="10">
         <f t="shared" si="3"/>
         <v>62.53</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>4</v>
       </c>
@@ -4089,18 +4097,18 @@
       <c r="D128" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="10">
         <v>4282.24</v>
       </c>
       <c r="F128" s="1">
         <v>0.1</v>
       </c>
-      <c r="G128" s="2">
+      <c r="G128" s="10">
         <f t="shared" si="3"/>
         <v>428.22399999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>4</v>
       </c>
@@ -4113,18 +4121,18 @@
       <c r="D129" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="10">
         <v>4209.28</v>
       </c>
       <c r="F129" s="1">
         <v>0.1</v>
       </c>
-      <c r="G129" s="2">
+      <c r="G129" s="10">
         <f t="shared" si="3"/>
         <v>420.928</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>4</v>
       </c>
@@ -4137,18 +4145,18 @@
       <c r="D130" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="10">
         <v>16.899999999999999</v>
       </c>
       <c r="F130" s="1">
         <v>0.1</v>
       </c>
-      <c r="G130" s="2">
+      <c r="G130" s="10">
         <f t="shared" ref="G130:G161" si="4">E130*F130</f>
         <v>1.69</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>4</v>
       </c>
@@ -4161,18 +4169,18 @@
       <c r="D131" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="10">
         <v>170.24</v>
       </c>
       <c r="F131" s="1">
         <v>0.1</v>
       </c>
-      <c r="G131" s="2">
+      <c r="G131" s="10">
         <f t="shared" si="4"/>
         <v>17.024000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>4</v>
       </c>
@@ -4185,18 +4193,18 @@
       <c r="D132" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="10">
         <v>103.9</v>
       </c>
       <c r="F132" s="1">
         <v>0.1</v>
       </c>
-      <c r="G132" s="2">
+      <c r="G132" s="10">
         <f t="shared" si="4"/>
         <v>10.39</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>4</v>
       </c>
@@ -4209,18 +4217,18 @@
       <c r="D133" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="10">
         <v>3385.3</v>
       </c>
       <c r="F133" s="1">
         <v>0.1</v>
       </c>
-      <c r="G133" s="2">
+      <c r="G133" s="10">
         <f t="shared" si="4"/>
         <v>338.53000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>4</v>
       </c>
@@ -4233,18 +4241,18 @@
       <c r="D134" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="10">
         <v>2209.35</v>
       </c>
       <c r="F134" s="1">
         <v>0.1</v>
       </c>
-      <c r="G134" s="2">
+      <c r="G134" s="10">
         <f t="shared" si="4"/>
         <v>220.935</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>4</v>
       </c>
@@ -4257,18 +4265,18 @@
       <c r="D135" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="10">
         <v>216.45</v>
       </c>
       <c r="F135" s="1">
         <v>0.1</v>
       </c>
-      <c r="G135" s="2">
+      <c r="G135" s="10">
         <f t="shared" si="4"/>
         <v>21.645</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>4</v>
       </c>
@@ -4281,18 +4289,18 @@
       <c r="D136" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="10">
         <v>182.4</v>
       </c>
       <c r="F136" s="1">
         <v>0.1</v>
       </c>
-      <c r="G136" s="2">
+      <c r="G136" s="10">
         <f t="shared" si="4"/>
         <v>18.240000000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>4</v>
       </c>
@@ -4305,18 +4313,18 @@
       <c r="D137" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="10">
         <v>1202.5</v>
       </c>
       <c r="F137" s="1">
         <v>0.1</v>
       </c>
-      <c r="G137" s="2">
+      <c r="G137" s="10">
         <f t="shared" si="4"/>
         <v>120.25</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>4</v>
       </c>
@@ -4329,18 +4337,18 @@
       <c r="D138" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="10">
         <v>0</v>
       </c>
       <c r="F138" s="1">
         <v>0.1</v>
       </c>
-      <c r="G138" s="2">
+      <c r="G138" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>4</v>
       </c>
@@ -4353,18 +4361,18 @@
       <c r="D139" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="10">
         <v>1301.1199999999999</v>
       </c>
       <c r="F139" s="1">
         <v>0.1</v>
       </c>
-      <c r="G139" s="2">
+      <c r="G139" s="10">
         <f t="shared" si="4"/>
         <v>130.11199999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>4</v>
       </c>
@@ -4377,18 +4385,18 @@
       <c r="D140" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="10">
         <v>1301.1199999999999</v>
       </c>
       <c r="F140" s="1">
         <v>0.1</v>
       </c>
-      <c r="G140" s="2">
+      <c r="G140" s="10">
         <f t="shared" si="4"/>
         <v>130.11199999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>27</v>
       </c>
@@ -4401,18 +4409,18 @@
       <c r="D141" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="10">
         <v>10827.67</v>
       </c>
       <c r="F141" s="1">
         <v>0.1</v>
       </c>
-      <c r="G141" s="2">
+      <c r="G141" s="10">
         <f t="shared" si="4"/>
         <v>1082.7670000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4425,18 +4433,18 @@
       <c r="D142" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="10">
         <v>1972.89</v>
       </c>
       <c r="F142" s="1">
         <v>0.1</v>
       </c>
-      <c r="G142" s="2">
+      <c r="G142" s="10">
         <f t="shared" si="4"/>
         <v>197.28900000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>31</v>
       </c>
@@ -4449,18 +4457,18 @@
       <c r="D143" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="10">
         <v>6993.28</v>
       </c>
       <c r="F143" s="1">
         <v>0.08</v>
       </c>
-      <c r="G143" s="2">
+      <c r="G143" s="10">
         <f t="shared" si="4"/>
         <v>559.4624</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>31</v>
       </c>
@@ -4473,18 +4481,18 @@
       <c r="D144" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="10">
         <v>5920.64</v>
       </c>
       <c r="F144" s="1">
         <v>0.08</v>
       </c>
-      <c r="G144" s="2">
+      <c r="G144" s="10">
         <f t="shared" si="4"/>
         <v>473.65120000000002</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>31</v>
       </c>
@@ -4497,18 +4505,18 @@
       <c r="D145" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="10">
         <v>2229.7600000000002</v>
       </c>
       <c r="F145" s="1">
         <v>0.08</v>
       </c>
-      <c r="G145" s="2">
+      <c r="G145" s="10">
         <f t="shared" si="4"/>
         <v>178.38080000000002</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>31</v>
       </c>
@@ -4521,18 +4529,18 @@
       <c r="D146" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="10">
         <v>1454.72</v>
       </c>
       <c r="F146" s="1">
         <v>0.08</v>
       </c>
-      <c r="G146" s="2">
+      <c r="G146" s="10">
         <f t="shared" si="4"/>
         <v>116.3776</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>31</v>
       </c>
@@ -4545,18 +4553,18 @@
       <c r="D147" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="10">
         <v>1762.56</v>
       </c>
       <c r="F147" s="1">
         <v>0.08</v>
       </c>
-      <c r="G147" s="2">
+      <c r="G147" s="10">
         <f t="shared" si="4"/>
         <v>141.00479999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>31</v>
       </c>
@@ -4569,18 +4577,18 @@
       <c r="D148" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="10">
         <v>1858.14</v>
       </c>
       <c r="F148" s="1">
         <v>0.08</v>
       </c>
-      <c r="G148" s="2">
+      <c r="G148" s="10">
         <f t="shared" si="4"/>
         <v>148.65120000000002</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>31</v>
       </c>
@@ -4593,18 +4601,18 @@
       <c r="D149" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E149" s="2">
+      <c r="E149" s="10">
         <v>2284.8000000000002</v>
       </c>
       <c r="F149" s="1">
         <v>0.08</v>
       </c>
-      <c r="G149" s="2">
+      <c r="G149" s="10">
         <f t="shared" si="4"/>
         <v>182.78400000000002</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>31</v>
       </c>
@@ -4617,18 +4625,18 @@
       <c r="D150" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E150" s="2">
+      <c r="E150" s="10">
         <v>2589.44</v>
       </c>
       <c r="F150" s="1">
         <v>0.08</v>
       </c>
-      <c r="G150" s="2">
+      <c r="G150" s="10">
         <f t="shared" si="4"/>
         <v>207.15520000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>31</v>
       </c>
@@ -4641,18 +4649,18 @@
       <c r="D151" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="10">
         <v>3970.52</v>
       </c>
       <c r="F151" s="1">
         <v>0.08</v>
       </c>
-      <c r="G151" s="2">
+      <c r="G151" s="10">
         <f t="shared" si="4"/>
         <v>317.64159999999998</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>31</v>
       </c>
@@ -4665,18 +4673,18 @@
       <c r="D152" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="10">
         <v>1874.34</v>
       </c>
       <c r="F152" s="1">
         <v>0.08</v>
       </c>
-      <c r="G152" s="2">
+      <c r="G152" s="10">
         <f t="shared" si="4"/>
         <v>149.94720000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>31</v>
       </c>
@@ -4689,18 +4697,18 @@
       <c r="D153" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E153" s="2">
+      <c r="E153" s="10">
         <v>3972.24</v>
       </c>
       <c r="F153" s="1">
         <v>0.08</v>
       </c>
-      <c r="G153" s="2">
+      <c r="G153" s="10">
         <f t="shared" si="4"/>
         <v>317.7792</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>31</v>
       </c>
@@ -4713,18 +4721,18 @@
       <c r="D154" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="10">
         <v>673.86</v>
       </c>
       <c r="F154" s="1">
         <v>0.08</v>
       </c>
-      <c r="G154" s="2">
+      <c r="G154" s="10">
         <f t="shared" si="4"/>
         <v>53.908799999999999</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>31</v>
       </c>
@@ -4737,18 +4745,18 @@
       <c r="D155" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="10">
         <v>525.36</v>
       </c>
       <c r="F155" s="1">
         <v>0.08</v>
       </c>
-      <c r="G155" s="2">
+      <c r="G155" s="10">
         <f t="shared" si="4"/>
         <v>42.028800000000004</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>31</v>
       </c>
@@ -4761,18 +4769,18 @@
       <c r="D156" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E156" s="2">
+      <c r="E156" s="10">
         <v>1149.72</v>
       </c>
       <c r="F156" s="1">
         <v>0.08</v>
       </c>
-      <c r="G156" s="2">
+      <c r="G156" s="10">
         <f t="shared" si="4"/>
         <v>91.97760000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>31</v>
       </c>
@@ -4785,18 +4793,18 @@
       <c r="D157" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="10">
         <v>361.68</v>
       </c>
       <c r="F157" s="1">
         <v>0.08</v>
       </c>
-      <c r="G157" s="2">
+      <c r="G157" s="10">
         <f t="shared" si="4"/>
         <v>28.9344</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>31</v>
       </c>
@@ -4809,18 +4817,18 @@
       <c r="D158" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="10">
         <v>1538.46</v>
       </c>
       <c r="F158" s="1">
         <v>0.08</v>
       </c>
-      <c r="G158" s="2">
+      <c r="G158" s="10">
         <f t="shared" si="4"/>
         <v>123.07680000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>31</v>
       </c>
@@ -4833,18 +4841,18 @@
       <c r="D159" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="10">
         <v>1244.0999999999999</v>
       </c>
       <c r="F159" s="1">
         <v>0.08</v>
       </c>
-      <c r="G159" s="2">
+      <c r="G159" s="10">
         <f t="shared" si="4"/>
         <v>99.527999999999992</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>31</v>
       </c>
@@ -4857,18 +4865,18 @@
       <c r="D160" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="10">
         <v>221.29</v>
       </c>
       <c r="F160" s="1">
         <v>0.08</v>
       </c>
-      <c r="G160" s="2">
+      <c r="G160" s="10">
         <f t="shared" si="4"/>
         <v>17.703199999999999</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>31</v>
       </c>
@@ -4881,18 +4889,18 @@
       <c r="D161" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="10">
         <v>87.6</v>
       </c>
       <c r="F161" s="1">
         <v>0.08</v>
       </c>
-      <c r="G161" s="2">
+      <c r="G161" s="10">
         <f t="shared" si="4"/>
         <v>7.008</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>31</v>
       </c>
@@ -4905,18 +4913,18 @@
       <c r="D162" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E162" s="2">
+      <c r="E162" s="10">
         <v>354.99</v>
       </c>
       <c r="F162" s="1">
         <v>0.08</v>
       </c>
-      <c r="G162" s="2">
+      <c r="G162" s="10">
         <f t="shared" ref="G162:G193" si="5">E162*F162</f>
         <v>28.3992</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>31</v>
       </c>
@@ -4929,18 +4937,18 @@
       <c r="D163" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E163" s="2">
+      <c r="E163" s="10">
         <v>272.02</v>
       </c>
       <c r="F163" s="1">
         <v>0.08</v>
       </c>
-      <c r="G163" s="2">
+      <c r="G163" s="10">
         <f t="shared" si="5"/>
         <v>21.761599999999998</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>31</v>
       </c>
@@ -4953,18 +4961,18 @@
       <c r="D164" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E164" s="2">
+      <c r="E164" s="10">
         <v>282.74</v>
       </c>
       <c r="F164" s="1">
         <v>0.08</v>
       </c>
-      <c r="G164" s="2">
+      <c r="G164" s="10">
         <f t="shared" si="5"/>
         <v>22.619200000000003</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>31</v>
       </c>
@@ -4977,18 +4985,18 @@
       <c r="D165" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="10">
         <v>357.3</v>
       </c>
       <c r="F165" s="1">
         <v>0.08</v>
       </c>
-      <c r="G165" s="2">
+      <c r="G165" s="10">
         <f t="shared" si="5"/>
         <v>28.584000000000003</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>31</v>
       </c>
@@ -5001,18 +5009,18 @@
       <c r="D166" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E166" s="2">
+      <c r="E166" s="10">
         <v>534.79</v>
       </c>
       <c r="F166" s="1">
         <v>0.08</v>
       </c>
-      <c r="G166" s="2">
+      <c r="G166" s="10">
         <f t="shared" si="5"/>
         <v>42.783200000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>31</v>
       </c>
@@ -5025,18 +5033,18 @@
       <c r="D167" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E167" s="2">
+      <c r="E167" s="10">
         <v>735.66</v>
       </c>
       <c r="F167" s="1">
         <v>0.08</v>
       </c>
-      <c r="G167" s="2">
+      <c r="G167" s="10">
         <f t="shared" si="5"/>
         <v>58.852800000000002</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>31</v>
       </c>
@@ -5049,18 +5057,18 @@
       <c r="D168" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E168" s="2">
+      <c r="E168" s="10">
         <v>1094.49</v>
       </c>
       <c r="F168" s="1">
         <v>0.08</v>
       </c>
-      <c r="G168" s="2">
+      <c r="G168" s="10">
         <f t="shared" si="5"/>
         <v>87.559200000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>31</v>
       </c>
@@ -5073,18 +5081,18 @@
       <c r="D169" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E169" s="2">
+      <c r="E169" s="10">
         <v>1009.19</v>
       </c>
       <c r="F169" s="1">
         <v>0.08</v>
       </c>
-      <c r="G169" s="2">
+      <c r="G169" s="10">
         <f t="shared" si="5"/>
         <v>80.735200000000006</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>60</v>
       </c>
@@ -5097,18 +5105,18 @@
       <c r="D170" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E170" s="2">
+      <c r="E170" s="10">
         <v>2281.6</v>
       </c>
       <c r="F170" s="1">
         <v>0.05</v>
       </c>
-      <c r="G170" s="2">
+      <c r="G170" s="10">
         <f t="shared" si="5"/>
         <v>114.08</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>60</v>
       </c>
@@ -5121,18 +5129,18 @@
       <c r="D171" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E171" s="2">
+      <c r="E171" s="10">
         <v>4554.24</v>
       </c>
       <c r="F171" s="1">
         <v>0.05</v>
       </c>
-      <c r="G171" s="2">
+      <c r="G171" s="10">
         <f t="shared" si="5"/>
         <v>227.71199999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>60</v>
       </c>
@@ -5145,18 +5153,18 @@
       <c r="D172" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="10">
         <v>5114.88</v>
       </c>
       <c r="F172" s="1">
         <v>0.05</v>
       </c>
-      <c r="G172" s="2">
+      <c r="G172" s="10">
         <f t="shared" si="5"/>
         <v>255.74400000000003</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>60</v>
       </c>
@@ -5169,18 +5177,18 @@
       <c r="D173" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E173" s="2">
+      <c r="E173" s="10">
         <v>2676.7</v>
       </c>
       <c r="F173" s="1">
         <v>0.05</v>
       </c>
-      <c r="G173" s="2">
+      <c r="G173" s="10">
         <f t="shared" si="5"/>
         <v>133.83500000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>60</v>
       </c>
@@ -5193,18 +5201,18 @@
       <c r="D174" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E174" s="2">
+      <c r="E174" s="10">
         <v>3339.12</v>
       </c>
       <c r="F174" s="1">
         <v>0.05</v>
       </c>
-      <c r="G174" s="2">
+      <c r="G174" s="10">
         <f t="shared" si="5"/>
         <v>166.95600000000002</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>60</v>
       </c>
@@ -5217,18 +5225,18 @@
       <c r="D175" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E175" s="2">
+      <c r="E175" s="10">
         <v>2411.52</v>
       </c>
       <c r="F175" s="1">
         <v>0.05</v>
       </c>
-      <c r="G175" s="2">
+      <c r="G175" s="10">
         <f t="shared" si="5"/>
         <v>120.57600000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>60</v>
       </c>
@@ -5241,18 +5249,18 @@
       <c r="D176" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E176" s="2">
+      <c r="E176" s="10">
         <v>1457.28</v>
       </c>
       <c r="F176" s="1">
         <v>0.05</v>
       </c>
-      <c r="G176" s="2">
+      <c r="G176" s="10">
         <f t="shared" si="5"/>
         <v>72.864000000000004</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>60</v>
       </c>
@@ -5265,18 +5273,18 @@
       <c r="D177" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="10">
         <v>2136.3200000000002</v>
       </c>
       <c r="F177" s="1">
         <v>0.05</v>
       </c>
-      <c r="G177" s="2">
+      <c r="G177" s="10">
         <f t="shared" si="5"/>
         <v>106.81600000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>60</v>
       </c>
@@ -5289,18 +5297,18 @@
       <c r="D178" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E178" s="2">
+      <c r="E178" s="10">
         <v>2017.92</v>
       </c>
       <c r="F178" s="1">
         <v>0.05</v>
       </c>
-      <c r="G178" s="2">
+      <c r="G178" s="10">
         <f t="shared" si="5"/>
         <v>100.89600000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>60</v>
       </c>
@@ -5313,18 +5321,18 @@
       <c r="D179" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="10">
         <v>2946.45</v>
       </c>
       <c r="F179" s="1">
         <v>0.05</v>
       </c>
-      <c r="G179" s="2">
+      <c r="G179" s="10">
         <f t="shared" si="5"/>
         <v>147.32249999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>60</v>
       </c>
@@ -5337,18 +5345,18 @@
       <c r="D180" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E180" s="2">
+      <c r="E180" s="10">
         <v>3961.98</v>
       </c>
       <c r="F180" s="1">
         <v>0.05</v>
       </c>
-      <c r="G180" s="2">
+      <c r="G180" s="10">
         <f t="shared" si="5"/>
         <v>198.09900000000002</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>60</v>
       </c>
@@ -5361,18 +5369,18 @@
       <c r="D181" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E181" s="2">
+      <c r="E181" s="10">
         <v>5862.96</v>
       </c>
       <c r="F181" s="1">
         <v>0.05</v>
       </c>
-      <c r="G181" s="2">
+      <c r="G181" s="10">
         <f t="shared" si="5"/>
         <v>293.14800000000002</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>60</v>
       </c>
@@ -5385,18 +5393,18 @@
       <c r="D182" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E182" s="2">
+      <c r="E182" s="10">
         <v>11147.52</v>
       </c>
       <c r="F182" s="1">
         <v>0.05</v>
       </c>
-      <c r="G182" s="2">
+      <c r="G182" s="10">
         <f t="shared" si="5"/>
         <v>557.37600000000009</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>60</v>
       </c>
@@ -5409,18 +5417,18 @@
       <c r="D183" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="10">
         <v>4141.4399999999996</v>
       </c>
       <c r="F183" s="1">
         <v>0.05</v>
       </c>
-      <c r="G183" s="2">
+      <c r="G183" s="10">
         <f t="shared" si="5"/>
         <v>207.072</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>60</v>
       </c>
@@ -5433,18 +5441,18 @@
       <c r="D184" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="10">
         <v>9165.65</v>
       </c>
       <c r="F184" s="1">
         <v>0.05</v>
       </c>
-      <c r="G184" s="2">
+      <c r="G184" s="10">
         <f t="shared" si="5"/>
         <v>458.28250000000003</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>60</v>
       </c>
@@ -5457,18 +5465,18 @@
       <c r="D185" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E185" s="2">
+      <c r="E185" s="10">
         <v>3073.6</v>
       </c>
       <c r="F185" s="1">
         <v>0.05</v>
       </c>
-      <c r="G185" s="2">
+      <c r="G185" s="10">
         <f t="shared" si="5"/>
         <v>153.68</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>60</v>
       </c>
@@ -5481,18 +5489,18 @@
       <c r="D186" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="10">
         <v>1116.7</v>
       </c>
       <c r="F186" s="1">
         <v>0.05</v>
       </c>
-      <c r="G186" s="2">
+      <c r="G186" s="10">
         <f t="shared" si="5"/>
         <v>55.835000000000008</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>60</v>
       </c>
@@ -5505,18 +5513,18 @@
       <c r="D187" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="10">
         <v>606.72</v>
       </c>
       <c r="F187" s="1">
         <v>0.05</v>
       </c>
-      <c r="G187" s="2">
+      <c r="G187" s="10">
         <f t="shared" si="5"/>
         <v>30.336000000000002</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>60</v>
       </c>
@@ -5529,18 +5537,18 @@
       <c r="D188" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="10">
         <v>6490.25</v>
       </c>
       <c r="F188" s="1">
         <v>0.05</v>
       </c>
-      <c r="G188" s="2">
+      <c r="G188" s="10">
         <f t="shared" si="5"/>
         <v>324.51250000000005</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>60</v>
       </c>
@@ -5553,18 +5561,18 @@
       <c r="D189" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="10">
         <v>636.79999999999995</v>
       </c>
       <c r="F189" s="1">
         <v>0.05</v>
       </c>
-      <c r="G189" s="2">
+      <c r="G189" s="10">
         <f t="shared" si="5"/>
         <v>31.84</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>60</v>
       </c>
@@ -5577,18 +5585,18 @@
       <c r="D190" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="10">
         <v>5264</v>
       </c>
       <c r="F190" s="1">
         <v>0.05</v>
       </c>
-      <c r="G190" s="2">
+      <c r="G190" s="10">
         <f t="shared" si="5"/>
         <v>263.2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>60</v>
       </c>
@@ -5601,18 +5609,18 @@
       <c r="D191" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E191" s="2">
+      <c r="E191" s="10">
         <v>4232.32</v>
       </c>
       <c r="F191" s="1">
         <v>0.05</v>
       </c>
-      <c r="G191" s="2">
+      <c r="G191" s="10">
         <f t="shared" si="5"/>
         <v>211.61599999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>60</v>
       </c>
@@ -5625,18 +5633,18 @@
       <c r="D192" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E192" s="2">
+      <c r="E192" s="10">
         <v>727.04</v>
       </c>
       <c r="F192" s="1">
         <v>0.05</v>
       </c>
-      <c r="G192" s="2">
+      <c r="G192" s="10">
         <f t="shared" si="5"/>
         <v>36.351999999999997</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>60</v>
       </c>
@@ -5649,18 +5657,18 @@
       <c r="D193" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E193" s="2">
+      <c r="E193" s="10">
         <v>5751.04</v>
       </c>
       <c r="F193" s="1">
         <v>0.05</v>
       </c>
-      <c r="G193" s="2">
+      <c r="G193" s="10">
         <f t="shared" si="5"/>
         <v>287.55200000000002</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>60</v>
       </c>
@@ -5673,18 +5681,18 @@
       <c r="D194" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="10">
         <v>0</v>
       </c>
       <c r="F194" s="1">
         <v>0.05</v>
       </c>
-      <c r="G194" s="2">
+      <c r="G194" s="10">
         <f t="shared" ref="G194:G225" si="6">E194*F194</f>
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>60</v>
       </c>
@@ -5697,18 +5705,18 @@
       <c r="D195" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E195" s="2">
+      <c r="E195" s="10">
         <v>856.32</v>
       </c>
       <c r="F195" s="1">
         <v>0.05</v>
       </c>
-      <c r="G195" s="2">
+      <c r="G195" s="10">
         <f t="shared" si="6"/>
         <v>42.816000000000003</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>60</v>
       </c>
@@ -5721,18 +5729,18 @@
       <c r="D196" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E196" s="2">
+      <c r="E196" s="10">
         <v>934.4</v>
       </c>
       <c r="F196" s="1">
         <v>0.05</v>
       </c>
-      <c r="G196" s="2">
+      <c r="G196" s="10">
         <f t="shared" si="6"/>
         <v>46.72</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>60</v>
       </c>
@@ -5745,18 +5753,18 @@
       <c r="D197" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E197" s="2">
+      <c r="E197" s="10">
         <v>5598.72</v>
       </c>
       <c r="F197" s="1">
         <v>0.05</v>
       </c>
-      <c r="G197" s="2">
+      <c r="G197" s="10">
         <f t="shared" si="6"/>
         <v>279.93600000000004</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>60</v>
       </c>
@@ -5769,18 +5777,18 @@
       <c r="D198" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E198" s="2">
+      <c r="E198" s="10">
         <v>4103.68</v>
       </c>
       <c r="F198" s="1">
         <v>0.05</v>
       </c>
-      <c r="G198" s="2">
+      <c r="G198" s="10">
         <f t="shared" si="6"/>
         <v>205.18400000000003</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>60</v>
       </c>
@@ -5793,18 +5801,18 @@
       <c r="D199" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E199" s="2">
+      <c r="E199" s="10">
         <v>7120.64</v>
       </c>
       <c r="F199" s="1">
         <v>0.05</v>
       </c>
-      <c r="G199" s="2">
+      <c r="G199" s="10">
         <f t="shared" si="6"/>
         <v>356.03200000000004</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>99</v>
       </c>
@@ -5817,18 +5825,18 @@
       <c r="D200" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E200" s="2">
+      <c r="E200" s="10">
         <v>4696.79</v>
       </c>
       <c r="F200" s="1">
         <v>0.1</v>
       </c>
-      <c r="G200" s="2">
+      <c r="G200" s="10">
         <f t="shared" si="6"/>
         <v>469.67900000000003</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>99</v>
       </c>
@@ -5841,18 +5849,18 @@
       <c r="D201" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="10">
         <v>250.92</v>
       </c>
       <c r="F201" s="1">
         <v>0.1</v>
       </c>
-      <c r="G201" s="2">
+      <c r="G201" s="10">
         <f t="shared" si="6"/>
         <v>25.091999999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>99</v>
       </c>
@@ -5865,18 +5873,18 @@
       <c r="D202" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E202" s="2">
+      <c r="E202" s="10">
         <v>2305.63</v>
       </c>
       <c r="F202" s="1">
         <v>0.1</v>
       </c>
-      <c r="G202" s="2">
+      <c r="G202" s="10">
         <f t="shared" si="6"/>
         <v>230.56300000000002</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>99</v>
       </c>
@@ -5889,18 +5897,18 @@
       <c r="D203" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E203" s="2">
+      <c r="E203" s="10">
         <v>349.38</v>
       </c>
       <c r="F203" s="1">
         <v>0.1</v>
       </c>
-      <c r="G203" s="2">
+      <c r="G203" s="10">
         <f t="shared" si="6"/>
         <v>34.938000000000002</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>99</v>
       </c>
@@ -5913,18 +5921,18 @@
       <c r="D204" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E204" s="2">
+      <c r="E204" s="10">
         <v>2183.7600000000002</v>
       </c>
       <c r="F204" s="1">
         <v>0.1</v>
       </c>
-      <c r="G204" s="2">
+      <c r="G204" s="10">
         <f t="shared" si="6"/>
         <v>218.37600000000003</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>99</v>
       </c>
@@ -5937,18 +5945,18 @@
       <c r="D205" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E205" s="2">
+      <c r="E205" s="10">
         <v>348.84</v>
       </c>
       <c r="F205" s="1">
         <v>0.1</v>
       </c>
-      <c r="G205" s="2">
+      <c r="G205" s="10">
         <f t="shared" si="6"/>
         <v>34.884</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>99</v>
       </c>
@@ -5961,18 +5969,18 @@
       <c r="D206" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="10">
         <v>0</v>
       </c>
       <c r="F206" s="1">
         <v>0.1</v>
       </c>
-      <c r="G206" s="2">
+      <c r="G206" s="10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>99</v>
       </c>
@@ -5985,18 +5993,18 @@
       <c r="D207" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E207" s="2">
+      <c r="E207" s="10">
         <v>0</v>
       </c>
       <c r="F207" s="1">
         <v>0.1</v>
       </c>
-      <c r="G207" s="2">
+      <c r="G207" s="10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>99</v>
       </c>
@@ -6009,18 +6017,18 @@
       <c r="D208" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E208" s="2">
+      <c r="E208" s="10">
         <v>1008.18</v>
       </c>
       <c r="F208" s="1">
         <v>0.1</v>
       </c>
-      <c r="G208" s="2">
+      <c r="G208" s="10">
         <f t="shared" si="6"/>
         <v>100.818</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>99</v>
       </c>
@@ -6033,18 +6041,18 @@
       <c r="D209" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E209" s="2">
+      <c r="E209" s="10">
         <v>753.3</v>
       </c>
       <c r="F209" s="1">
         <v>0.1</v>
       </c>
-      <c r="G209" s="2">
+      <c r="G209" s="10">
         <f t="shared" si="6"/>
         <v>75.33</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>99</v>
       </c>
@@ -6057,18 +6065,18 @@
       <c r="D210" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E210" s="2">
+      <c r="E210" s="10">
         <v>0</v>
       </c>
       <c r="F210" s="1">
         <v>0.1</v>
       </c>
-      <c r="G210" s="2">
+      <c r="G210" s="10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>99</v>
       </c>
@@ -6081,18 +6089,18 @@
       <c r="D211" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E211" s="2">
+      <c r="E211" s="10">
         <v>0</v>
       </c>
       <c r="F211" s="1">
         <v>0.1</v>
       </c>
-      <c r="G211" s="2">
+      <c r="G211" s="10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>99</v>
       </c>
@@ -6105,18 +6113,18 @@
       <c r="D212" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="10">
         <v>4191.4799999999996</v>
       </c>
       <c r="F212" s="1">
         <v>0.1</v>
       </c>
-      <c r="G212" s="2">
+      <c r="G212" s="10">
         <f t="shared" si="6"/>
         <v>419.14799999999997</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>99</v>
       </c>
@@ -6129,18 +6137,18 @@
       <c r="D213" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E213" s="2">
+      <c r="E213" s="10">
         <v>0</v>
       </c>
       <c r="F213" s="1">
         <v>0.1</v>
       </c>
-      <c r="G213" s="2">
+      <c r="G213" s="10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>99</v>
       </c>
@@ -6153,18 +6161,18 @@
       <c r="D214" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E214" s="2">
+      <c r="E214" s="10">
         <v>1318.02</v>
       </c>
       <c r="F214" s="1">
         <v>0.1</v>
       </c>
-      <c r="G214" s="2">
+      <c r="G214" s="10">
         <f t="shared" si="6"/>
         <v>131.80199999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>99</v>
       </c>
@@ -6177,18 +6185,18 @@
       <c r="D215" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="10">
         <v>547.14</v>
       </c>
       <c r="F215" s="1">
         <v>0.1</v>
       </c>
-      <c r="G215" s="2">
+      <c r="G215" s="10">
         <f t="shared" si="6"/>
         <v>54.713999999999999</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>99</v>
       </c>
@@ -6201,18 +6209,18 @@
       <c r="D216" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="10">
         <v>5358.42</v>
       </c>
       <c r="F216" s="1">
         <v>0.1</v>
       </c>
-      <c r="G216" s="2">
+      <c r="G216" s="10">
         <f t="shared" si="6"/>
         <v>535.84199999999998</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>99</v>
       </c>
@@ -6225,18 +6233,18 @@
       <c r="D217" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E217" s="2">
+      <c r="E217" s="10">
         <v>13760.54</v>
       </c>
       <c r="F217" s="1">
         <v>0.1</v>
       </c>
-      <c r="G217" s="2">
+      <c r="G217" s="10">
         <f t="shared" si="6"/>
         <v>1376.0540000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>99</v>
       </c>
@@ -6249,18 +6257,18 @@
       <c r="D218" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="10">
         <v>359.04</v>
       </c>
       <c r="F218" s="1">
         <v>0.1</v>
       </c>
-      <c r="G218" s="2">
+      <c r="G218" s="10">
         <f t="shared" si="6"/>
         <v>35.904000000000003</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>99</v>
       </c>
@@ -6273,18 +6281,18 @@
       <c r="D219" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E219" s="2">
+      <c r="E219" s="10">
         <v>8692.35</v>
       </c>
       <c r="F219" s="1">
         <v>0.1</v>
       </c>
-      <c r="G219" s="2">
+      <c r="G219" s="10">
         <f t="shared" si="6"/>
         <v>869.23500000000013</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>99</v>
       </c>
@@ -6297,18 +6305,18 @@
       <c r="D220" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E220" s="2">
+      <c r="E220" s="10">
         <v>1257.0999999999999</v>
       </c>
       <c r="F220" s="1">
         <v>0.1</v>
       </c>
-      <c r="G220" s="2">
+      <c r="G220" s="10">
         <f t="shared" si="6"/>
         <v>125.71</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>99</v>
       </c>
@@ -6321,18 +6329,18 @@
       <c r="D221" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="10">
         <v>5552</v>
       </c>
       <c r="F221" s="1">
         <v>0.1</v>
       </c>
-      <c r="G221" s="2">
+      <c r="G221" s="10">
         <f t="shared" si="6"/>
         <v>555.20000000000005</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>99</v>
       </c>
@@ -6345,18 +6353,18 @@
       <c r="D222" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E222" s="2">
+      <c r="E222" s="10">
         <v>2752.64</v>
       </c>
       <c r="F222" s="1">
         <v>0.1</v>
       </c>
-      <c r="G222" s="2">
+      <c r="G222" s="10">
         <f t="shared" si="6"/>
         <v>275.26400000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>99</v>
       </c>
@@ -6369,18 +6377,18 @@
       <c r="D223" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="10">
         <v>4079.61</v>
       </c>
       <c r="F223" s="1">
         <v>0.1</v>
       </c>
-      <c r="G223" s="2">
+      <c r="G223" s="10">
         <f t="shared" si="6"/>
         <v>407.96100000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>99</v>
       </c>
@@ -6393,18 +6401,18 @@
       <c r="D224" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E224" s="2">
+      <c r="E224" s="10">
         <v>2874.88</v>
       </c>
       <c r="F224" s="1">
         <v>0.1</v>
       </c>
-      <c r="G224" s="2">
+      <c r="G224" s="10">
         <f t="shared" si="6"/>
         <v>287.488</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>99</v>
       </c>
@@ -6417,18 +6425,18 @@
       <c r="D225" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E225" s="2">
+      <c r="E225" s="10">
         <v>199.68</v>
       </c>
       <c r="F225" s="1">
         <v>0.1</v>
       </c>
-      <c r="G225" s="2">
+      <c r="G225" s="10">
         <f t="shared" si="6"/>
         <v>19.968000000000004</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>99</v>
       </c>
@@ -6441,18 +6449,18 @@
       <c r="D226" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E226" s="2">
+      <c r="E226" s="10">
         <v>3939.3</v>
       </c>
       <c r="F226" s="1">
         <v>0.1</v>
       </c>
-      <c r="G226" s="2">
+      <c r="G226" s="10">
         <f t="shared" ref="G226:G289" si="7">E226*F226</f>
         <v>393.93000000000006</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>99</v>
       </c>
@@ -6465,18 +6473,18 @@
       <c r="D227" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E227" s="2">
+      <c r="E227" s="10">
         <v>3676.86</v>
       </c>
       <c r="F227" s="1">
         <v>0.1</v>
       </c>
-      <c r="G227" s="2">
+      <c r="G227" s="10">
         <f t="shared" si="7"/>
         <v>367.68600000000004</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>129</v>
       </c>
@@ -6489,18 +6497,18 @@
       <c r="D228" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E228" s="2">
+      <c r="E228" s="10">
         <v>1674.16</v>
       </c>
       <c r="F228" s="1">
         <v>0.1</v>
       </c>
-      <c r="G228" s="2">
+      <c r="G228" s="10">
         <f t="shared" si="7"/>
         <v>167.41600000000003</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>129</v>
       </c>
@@ -6513,18 +6521,18 @@
       <c r="D229" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E229" s="2">
+      <c r="E229" s="10">
         <v>4469.04</v>
       </c>
       <c r="F229" s="1">
         <v>0.1</v>
       </c>
-      <c r="G229" s="2">
+      <c r="G229" s="10">
         <f t="shared" si="7"/>
         <v>446.904</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>129</v>
       </c>
@@ -6537,18 +6545,18 @@
       <c r="D230" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="10">
         <v>212.52</v>
       </c>
       <c r="F230" s="1">
         <v>0.1</v>
       </c>
-      <c r="G230" s="2">
+      <c r="G230" s="10">
         <f t="shared" si="7"/>
         <v>21.252000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>129</v>
       </c>
@@ -6561,18 +6569,18 @@
       <c r="D231" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E231" s="2">
+      <c r="E231" s="10">
         <v>1724.76</v>
       </c>
       <c r="F231" s="1">
         <v>0.1</v>
       </c>
-      <c r="G231" s="2">
+      <c r="G231" s="10">
         <f t="shared" si="7"/>
         <v>172.476</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>129</v>
       </c>
@@ -6585,18 +6593,18 @@
       <c r="D232" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E232" s="2">
+      <c r="E232" s="10">
         <v>2077.38</v>
       </c>
       <c r="F232" s="1">
         <v>0.1</v>
       </c>
-      <c r="G232" s="2">
+      <c r="G232" s="10">
         <f t="shared" si="7"/>
         <v>207.73800000000003</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>129</v>
       </c>
@@ -6609,18 +6617,18 @@
       <c r="D233" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E233" s="2">
+      <c r="E233" s="10">
         <v>3666.56</v>
       </c>
       <c r="F233" s="1">
         <v>0.1</v>
       </c>
-      <c r="G233" s="2">
+      <c r="G233" s="10">
         <f t="shared" si="7"/>
         <v>366.65600000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>129</v>
       </c>
@@ -6633,18 +6641,18 @@
       <c r="D234" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E234" s="2">
+      <c r="E234" s="10">
         <v>0</v>
       </c>
       <c r="F234" s="1">
         <v>0.1</v>
       </c>
-      <c r="G234" s="2">
+      <c r="G234" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>129</v>
       </c>
@@ -6657,18 +6665,18 @@
       <c r="D235" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="10">
         <v>169.04</v>
       </c>
       <c r="F235" s="1">
         <v>0.1</v>
       </c>
-      <c r="G235" s="2">
+      <c r="G235" s="10">
         <f t="shared" si="7"/>
         <v>16.904</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>129</v>
       </c>
@@ -6681,18 +6689,18 @@
       <c r="D236" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E236" s="2">
+      <c r="E236" s="10">
         <v>3659.58</v>
       </c>
       <c r="F236" s="1">
         <v>0.1</v>
       </c>
-      <c r="G236" s="2">
+      <c r="G236" s="10">
         <f t="shared" si="7"/>
         <v>365.95800000000003</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>129</v>
       </c>
@@ -6705,18 +6713,18 @@
       <c r="D237" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E237" s="2">
+      <c r="E237" s="10">
         <v>6730.75</v>
       </c>
       <c r="F237" s="1">
         <v>0.1</v>
       </c>
-      <c r="G237" s="2">
+      <c r="G237" s="10">
         <f t="shared" si="7"/>
         <v>673.07500000000005</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>141</v>
       </c>
@@ -6729,18 +6737,18 @@
       <c r="D238" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E238" s="2">
+      <c r="E238" s="10">
         <v>2997.06</v>
       </c>
       <c r="F238" s="1">
         <v>0.1</v>
       </c>
-      <c r="G238" s="2">
+      <c r="G238" s="10">
         <f t="shared" si="7"/>
         <v>299.70600000000002</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>141</v>
       </c>
@@ -6753,18 +6761,18 @@
       <c r="D239" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E239" s="2">
+      <c r="E239" s="10">
         <v>6286.08</v>
       </c>
       <c r="F239" s="1">
         <v>0.1</v>
       </c>
-      <c r="G239" s="2">
+      <c r="G239" s="10">
         <f t="shared" si="7"/>
         <v>628.60800000000006</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>141</v>
       </c>
@@ -6777,18 +6785,18 @@
       <c r="D240" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E240" s="2">
+      <c r="E240" s="10">
         <v>2812.8</v>
       </c>
       <c r="F240" s="1">
         <v>0.1</v>
       </c>
-      <c r="G240" s="2">
+      <c r="G240" s="10">
         <f t="shared" si="7"/>
         <v>281.28000000000003</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>141</v>
       </c>
@@ -6801,18 +6809,18 @@
       <c r="D241" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="10">
         <v>8613.02</v>
       </c>
       <c r="F241" s="1">
         <v>0.1</v>
       </c>
-      <c r="G241" s="2">
+      <c r="G241" s="10">
         <f t="shared" si="7"/>
         <v>861.30200000000013</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>141</v>
       </c>
@@ -6825,18 +6833,18 @@
       <c r="D242" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E242" s="2">
+      <c r="E242" s="10">
         <v>3396.6</v>
       </c>
       <c r="F242" s="1">
         <v>0.1</v>
       </c>
-      <c r="G242" s="2">
+      <c r="G242" s="10">
         <f t="shared" si="7"/>
         <v>339.66</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>155</v>
       </c>
@@ -6849,18 +6857,18 @@
       <c r="D243" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="10">
         <v>1936.44</v>
       </c>
       <c r="F243" s="1">
         <v>0.1</v>
       </c>
-      <c r="G243" s="2">
+      <c r="G243" s="10">
         <f t="shared" si="7"/>
         <v>193.64400000000001</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>156</v>
       </c>
@@ -6873,18 +6881,18 @@
       <c r="D244" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="10">
         <v>0</v>
       </c>
       <c r="F244" s="1">
         <v>0.1</v>
       </c>
-      <c r="G244" s="2">
+      <c r="G244" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>156</v>
       </c>
@@ -6897,18 +6905,18 @@
       <c r="D245" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E245" s="2">
+      <c r="E245" s="10">
         <v>0</v>
       </c>
       <c r="F245" s="1">
         <v>0.1</v>
       </c>
-      <c r="G245" s="2">
+      <c r="G245" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>156</v>
       </c>
@@ -6921,13 +6929,13 @@
       <c r="D246" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E246" s="2">
+      <c r="E246" s="10">
         <v>3802.64</v>
       </c>
       <c r="F246" s="1">
         <v>0.1</v>
       </c>
-      <c r="G246" s="2">
+      <c r="G246" s="10">
         <f t="shared" si="7"/>
         <v>380.26400000000001</v>
       </c>
@@ -6943,15 +6951,15 @@
         <v>6</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E247" s="2">
+        <v>187</v>
+      </c>
+      <c r="E247" s="10">
         <v>718.9</v>
       </c>
       <c r="F247" s="1">
         <v>0.1</v>
       </c>
-      <c r="G247" s="2">
+      <c r="G247" s="10">
         <f t="shared" si="7"/>
         <v>71.89</v>
       </c>
@@ -6967,15 +6975,15 @@
         <v>10</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E248" s="2">
+        <v>187</v>
+      </c>
+      <c r="E248" s="10">
         <v>5054.72</v>
       </c>
       <c r="F248" s="1">
         <v>0.1</v>
       </c>
-      <c r="G248" s="2">
+      <c r="G248" s="10">
         <f t="shared" si="7"/>
         <v>505.47200000000004</v>
       </c>
@@ -6991,15 +6999,15 @@
         <v>13</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E249" s="2">
+        <v>187</v>
+      </c>
+      <c r="E249" s="10">
         <v>189.44</v>
       </c>
       <c r="F249" s="1">
         <v>0.1</v>
       </c>
-      <c r="G249" s="2">
+      <c r="G249" s="10">
         <f t="shared" si="7"/>
         <v>18.943999999999999</v>
       </c>
@@ -7015,15 +7023,15 @@
         <v>8</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E250" s="2">
+        <v>187</v>
+      </c>
+      <c r="E250" s="10">
         <v>6490.24</v>
       </c>
       <c r="F250" s="1">
         <v>0.1</v>
       </c>
-      <c r="G250" s="2">
+      <c r="G250" s="10">
         <f t="shared" si="7"/>
         <v>649.024</v>
       </c>
@@ -7039,15 +7047,15 @@
         <v>152</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E251" s="2">
+        <v>187</v>
+      </c>
+      <c r="E251" s="10">
         <v>16.899999999999999</v>
       </c>
       <c r="F251" s="1">
         <v>0.1</v>
       </c>
-      <c r="G251" s="2">
+      <c r="G251" s="10">
         <f t="shared" si="7"/>
         <v>1.69</v>
       </c>
@@ -7063,17 +7071,17 @@
         <v>15</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E252" s="2">
-        <v>283.82</v>
+        <v>187</v>
+      </c>
+      <c r="E252" s="10">
+        <v>293.82</v>
       </c>
       <c r="F252" s="1">
         <v>0.1</v>
       </c>
-      <c r="G252" s="2">
+      <c r="G252" s="10">
         <f t="shared" si="7"/>
-        <v>28.382000000000001</v>
+        <v>29.382000000000001</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -7087,15 +7095,15 @@
         <v>12</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E253" s="2">
+        <v>187</v>
+      </c>
+      <c r="E253" s="10">
         <v>2245.1</v>
       </c>
       <c r="F253" s="1">
         <v>0.1</v>
       </c>
-      <c r="G253" s="2">
+      <c r="G253" s="10">
         <f t="shared" si="7"/>
         <v>224.51</v>
       </c>
@@ -7111,15 +7119,15 @@
         <v>17</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E254" s="2">
+        <v>187</v>
+      </c>
+      <c r="E254" s="10">
         <v>1179.75</v>
       </c>
       <c r="F254" s="1">
         <v>0.1</v>
       </c>
-      <c r="G254" s="2">
+      <c r="G254" s="10">
         <f t="shared" si="7"/>
         <v>117.97500000000001</v>
       </c>
@@ -7135,15 +7143,15 @@
         <v>20</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E255" s="2">
+        <v>187</v>
+      </c>
+      <c r="E255" s="10">
         <v>107.52</v>
       </c>
       <c r="F255" s="1">
         <v>0.1</v>
       </c>
-      <c r="G255" s="2">
+      <c r="G255" s="10">
         <f t="shared" si="7"/>
         <v>10.752000000000001</v>
       </c>
@@ -7159,15 +7167,15 @@
         <v>21</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E256" s="2">
+        <v>187</v>
+      </c>
+      <c r="E256" s="10">
         <v>1865.5</v>
       </c>
       <c r="F256" s="1">
         <v>0.1</v>
       </c>
-      <c r="G256" s="2">
+      <c r="G256" s="10">
         <f t="shared" si="7"/>
         <v>186.55</v>
       </c>
@@ -7183,15 +7191,15 @@
         <v>23</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E257" s="2">
+        <v>187</v>
+      </c>
+      <c r="E257" s="10">
         <v>0</v>
       </c>
       <c r="F257" s="1">
         <v>0.1</v>
       </c>
-      <c r="G257" s="2">
+      <c r="G257" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7207,15 +7215,15 @@
         <v>25</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E258" s="2">
+        <v>187</v>
+      </c>
+      <c r="E258" s="10">
         <v>5532.8</v>
       </c>
       <c r="F258" s="1">
         <v>0.1</v>
       </c>
-      <c r="G258" s="2">
+      <c r="G258" s="10">
         <f t="shared" si="7"/>
         <v>553.28000000000009</v>
       </c>
@@ -7231,15 +7239,15 @@
         <v>25</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E259" s="2">
+        <v>187</v>
+      </c>
+      <c r="E259" s="10">
         <v>5532.8</v>
       </c>
       <c r="F259" s="1">
         <v>0.1</v>
       </c>
-      <c r="G259" s="2">
+      <c r="G259" s="10">
         <f t="shared" si="7"/>
         <v>553.28000000000009</v>
       </c>
@@ -7249,21 +7257,21 @@
         <v>4</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E260" s="2">
+        <v>187</v>
+      </c>
+      <c r="E260" s="10">
         <v>3222.03</v>
       </c>
       <c r="F260" s="1">
         <v>0.1</v>
       </c>
-      <c r="G260" s="2">
+      <c r="G260" s="10">
         <f t="shared" si="7"/>
         <v>322.20300000000003</v>
       </c>
@@ -7273,21 +7281,21 @@
         <v>4</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E261" s="2">
+        <v>187</v>
+      </c>
+      <c r="E261" s="10">
         <v>0</v>
       </c>
       <c r="F261" s="1">
         <v>0.1</v>
       </c>
-      <c r="G261" s="2">
+      <c r="G261" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7297,21 +7305,21 @@
         <v>4</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E262" s="2">
+        <v>187</v>
+      </c>
+      <c r="E262" s="10">
         <v>0</v>
       </c>
       <c r="F262" s="1">
         <v>0.1</v>
       </c>
-      <c r="G262" s="2">
+      <c r="G262" s="10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7327,15 +7335,15 @@
         <v>29</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E263" s="2">
+        <v>187</v>
+      </c>
+      <c r="E263" s="10">
         <v>9835.1299999999992</v>
       </c>
       <c r="F263" s="1">
         <v>0.1</v>
       </c>
-      <c r="G263" s="2">
+      <c r="G263" s="10">
         <f t="shared" si="7"/>
         <v>983.51299999999992</v>
       </c>
@@ -7348,18 +7356,18 @@
         <v>28</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E264" s="2">
+        <v>187</v>
+      </c>
+      <c r="E264" s="10">
         <v>1855.26</v>
       </c>
       <c r="F264" s="1">
         <v>0.1</v>
       </c>
-      <c r="G264" s="2">
+      <c r="G264" s="10">
         <f t="shared" si="7"/>
         <v>185.52600000000001</v>
       </c>
@@ -7375,15 +7383,15 @@
         <v>33</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E265" s="2">
+        <v>187</v>
+      </c>
+      <c r="E265" s="10">
         <v>7585.28</v>
       </c>
       <c r="F265" s="1">
         <v>0.08</v>
       </c>
-      <c r="G265" s="2">
+      <c r="G265" s="10">
         <f t="shared" si="7"/>
         <v>606.82240000000002</v>
       </c>
@@ -7399,15 +7407,15 @@
         <v>34</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E266" s="2">
+        <v>187</v>
+      </c>
+      <c r="E266" s="10">
         <v>7077.12</v>
       </c>
       <c r="F266" s="1">
         <v>0.08</v>
       </c>
-      <c r="G266" s="2">
+      <c r="G266" s="10">
         <f t="shared" si="7"/>
         <v>566.16960000000006</v>
       </c>
@@ -7423,15 +7431,15 @@
         <v>35</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E267" s="2">
+        <v>187</v>
+      </c>
+      <c r="E267" s="10">
         <v>2645.76</v>
       </c>
       <c r="F267" s="1">
         <v>0.08</v>
       </c>
-      <c r="G267" s="2">
+      <c r="G267" s="10">
         <f t="shared" si="7"/>
         <v>211.66080000000002</v>
       </c>
@@ -7447,15 +7455,15 @@
         <v>36</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E268" s="2">
+        <v>187</v>
+      </c>
+      <c r="E268" s="10">
         <v>1724.16</v>
       </c>
       <c r="F268" s="1">
         <v>0.08</v>
       </c>
-      <c r="G268" s="2">
+      <c r="G268" s="10">
         <f t="shared" si="7"/>
         <v>137.93280000000001</v>
       </c>
@@ -7471,15 +7479,15 @@
         <v>37</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E269" s="2">
+        <v>187</v>
+      </c>
+      <c r="E269" s="10">
         <v>1739.88</v>
       </c>
       <c r="F269" s="1">
         <v>0.08</v>
       </c>
-      <c r="G269" s="2">
+      <c r="G269" s="10">
         <f t="shared" si="7"/>
         <v>139.19040000000001</v>
       </c>
@@ -7495,15 +7503,15 @@
         <v>38</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E270" s="2">
+        <v>187</v>
+      </c>
+      <c r="E270" s="10">
         <v>2113.56</v>
       </c>
       <c r="F270" s="1">
         <v>0.08</v>
       </c>
-      <c r="G270" s="2">
+      <c r="G270" s="10">
         <f t="shared" si="7"/>
         <v>169.0848</v>
       </c>
@@ -7519,15 +7527,15 @@
         <v>39</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E271" s="2">
+        <v>187</v>
+      </c>
+      <c r="E271" s="10">
         <v>2683.96</v>
       </c>
       <c r="F271" s="1">
         <v>0.08</v>
       </c>
-      <c r="G271" s="2">
+      <c r="G271" s="10">
         <f t="shared" si="7"/>
         <v>214.71680000000001</v>
       </c>
@@ -7543,15 +7551,15 @@
         <v>40</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E272" s="2">
+        <v>187</v>
+      </c>
+      <c r="E272" s="10">
         <v>2682.6</v>
       </c>
       <c r="F272" s="1">
         <v>0.08</v>
       </c>
-      <c r="G272" s="2">
+      <c r="G272" s="10">
         <f t="shared" si="7"/>
         <v>214.608</v>
       </c>
@@ -7567,15 +7575,15 @@
         <v>41</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E273" s="2">
+        <v>187</v>
+      </c>
+      <c r="E273" s="10">
         <v>4448.5600000000004</v>
       </c>
       <c r="F273" s="1">
         <v>0.08</v>
       </c>
-      <c r="G273" s="2">
+      <c r="G273" s="10">
         <f t="shared" si="7"/>
         <v>355.88480000000004</v>
       </c>
@@ -7591,15 +7599,15 @@
         <v>42</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E274" s="2">
+        <v>187</v>
+      </c>
+      <c r="E274" s="10">
         <v>2325.7800000000002</v>
       </c>
       <c r="F274" s="1">
         <v>0.08</v>
       </c>
-      <c r="G274" s="2">
+      <c r="G274" s="10">
         <f t="shared" si="7"/>
         <v>186.06240000000003</v>
       </c>
@@ -7615,17 +7623,17 @@
         <v>43</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E275" s="2">
-        <v>3972.24</v>
+        <v>187</v>
+      </c>
+      <c r="E275" s="10">
+        <v>0</v>
       </c>
       <c r="F275" s="1">
         <v>0.08</v>
       </c>
-      <c r="G275" s="2">
+      <c r="G275" s="10">
         <f t="shared" si="7"/>
-        <v>317.7792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -7639,15 +7647,15 @@
         <v>44</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E276" s="2">
+        <v>187</v>
+      </c>
+      <c r="E276" s="10">
         <v>743.16</v>
       </c>
       <c r="F276" s="1">
         <v>0.08</v>
       </c>
-      <c r="G276" s="2">
+      <c r="G276" s="10">
         <f t="shared" si="7"/>
         <v>59.452799999999996</v>
       </c>
@@ -7663,15 +7671,15 @@
         <v>45</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E277" s="2">
+        <v>187</v>
+      </c>
+      <c r="E277" s="10">
         <v>349.8</v>
       </c>
       <c r="F277" s="1">
         <v>0.08</v>
       </c>
-      <c r="G277" s="2">
+      <c r="G277" s="10">
         <f t="shared" si="7"/>
         <v>27.984000000000002</v>
       </c>
@@ -7687,15 +7695,15 @@
         <v>46</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E278" s="2">
+        <v>187</v>
+      </c>
+      <c r="E278" s="10">
         <v>1247.54</v>
       </c>
       <c r="F278" s="1">
         <v>0.08</v>
       </c>
-      <c r="G278" s="2">
+      <c r="G278" s="10">
         <f t="shared" si="7"/>
         <v>99.803200000000004</v>
       </c>
@@ -7711,17 +7719,17 @@
         <v>47</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E279" s="2">
-        <v>399.31</v>
+        <v>187</v>
+      </c>
+      <c r="E279" s="10">
+        <v>399.3</v>
       </c>
       <c r="F279" s="1">
         <v>0.08</v>
       </c>
-      <c r="G279" s="2">
+      <c r="G279" s="10">
         <f t="shared" si="7"/>
-        <v>31.944800000000001</v>
+        <v>31.944000000000003</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -7735,17 +7743,17 @@
         <v>48</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E280" s="2">
-        <v>1170.8499999999999</v>
+        <v>187</v>
+      </c>
+      <c r="E280" s="10">
+        <v>1170.8399999999999</v>
       </c>
       <c r="F280" s="1">
         <v>0.08</v>
       </c>
-      <c r="G280" s="2">
+      <c r="G280" s="10">
         <f t="shared" si="7"/>
-        <v>93.667999999999992</v>
+        <v>93.667199999999994</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -7759,15 +7767,15 @@
         <v>49</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E281" s="2">
+        <v>187</v>
+      </c>
+      <c r="E281" s="10">
         <v>1122.6600000000001</v>
       </c>
       <c r="F281" s="1">
         <v>0.08</v>
       </c>
-      <c r="G281" s="2">
+      <c r="G281" s="10">
         <f t="shared" si="7"/>
         <v>89.81280000000001</v>
       </c>
@@ -7783,15 +7791,15 @@
         <v>50</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E282" s="2">
+        <v>187</v>
+      </c>
+      <c r="E282" s="10">
         <v>228.69</v>
       </c>
       <c r="F282" s="1">
         <v>0.08</v>
       </c>
-      <c r="G282" s="2">
+      <c r="G282" s="10">
         <f t="shared" si="7"/>
         <v>18.295200000000001</v>
       </c>
@@ -7807,15 +7815,15 @@
         <v>51</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E283" s="2">
+        <v>187</v>
+      </c>
+      <c r="E283" s="10">
         <v>90.52</v>
       </c>
       <c r="F283" s="1">
         <v>0.08</v>
       </c>
-      <c r="G283" s="2">
+      <c r="G283" s="10">
         <f t="shared" si="7"/>
         <v>7.2416</v>
       </c>
@@ -7831,15 +7839,15 @@
         <v>52</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E284" s="2">
+        <v>187</v>
+      </c>
+      <c r="E284" s="10">
         <v>366.49</v>
       </c>
       <c r="F284" s="1">
         <v>0.08</v>
       </c>
-      <c r="G284" s="2">
+      <c r="G284" s="10">
         <f t="shared" si="7"/>
         <v>29.319200000000002</v>
       </c>
@@ -7855,15 +7863,15 @@
         <v>53</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E285" s="2">
+        <v>187</v>
+      </c>
+      <c r="E285" s="10">
         <v>282.74</v>
       </c>
       <c r="F285" s="1">
         <v>0.08</v>
       </c>
-      <c r="G285" s="2">
+      <c r="G285" s="10">
         <f t="shared" si="7"/>
         <v>22.619200000000003</v>
       </c>
@@ -7879,15 +7887,15 @@
         <v>54</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E286" s="2">
+        <v>187</v>
+      </c>
+      <c r="E286" s="10">
         <v>260.63</v>
       </c>
       <c r="F286" s="1">
         <v>0.08</v>
       </c>
-      <c r="G286" s="2">
+      <c r="G286" s="10">
         <f t="shared" si="7"/>
         <v>20.8504</v>
       </c>
@@ -7903,15 +7911,15 @@
         <v>55</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E287" s="2">
+        <v>187</v>
+      </c>
+      <c r="E287" s="10">
         <v>369.24</v>
       </c>
       <c r="F287" s="1">
         <v>0.08</v>
       </c>
-      <c r="G287" s="2">
+      <c r="G287" s="10">
         <f t="shared" si="7"/>
         <v>29.539200000000001</v>
       </c>
@@ -7927,15 +7935,15 @@
         <v>56</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E288" s="2">
+        <v>187</v>
+      </c>
+      <c r="E288" s="10">
         <v>552.66999999999996</v>
       </c>
       <c r="F288" s="1">
         <v>0.08</v>
       </c>
-      <c r="G288" s="2">
+      <c r="G288" s="10">
         <f t="shared" si="7"/>
         <v>44.2136</v>
       </c>
@@ -7951,15 +7959,15 @@
         <v>57</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E289" s="2">
+        <v>187</v>
+      </c>
+      <c r="E289" s="10">
         <v>651.33000000000004</v>
       </c>
       <c r="F289" s="1">
         <v>0.08</v>
       </c>
-      <c r="G289" s="2">
+      <c r="G289" s="10">
         <f t="shared" si="7"/>
         <v>52.106400000000008</v>
       </c>
@@ -7975,15 +7983,15 @@
         <v>58</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E290" s="2">
+        <v>187</v>
+      </c>
+      <c r="E290" s="10">
         <v>1131.08</v>
       </c>
       <c r="F290" s="1">
         <v>0.08</v>
       </c>
-      <c r="G290" s="2">
+      <c r="G290" s="10">
         <f t="shared" ref="G290:G363" si="8">E290*F290</f>
         <v>90.486399999999989</v>
       </c>
@@ -7999,15 +8007,15 @@
         <v>59</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E291" s="2">
+        <v>187</v>
+      </c>
+      <c r="E291" s="10">
         <v>950.39</v>
       </c>
       <c r="F291" s="1">
         <v>0.08</v>
       </c>
-      <c r="G291" s="2">
+      <c r="G291" s="10">
         <f t="shared" si="8"/>
         <v>76.031199999999998</v>
       </c>
@@ -8023,15 +8031,15 @@
         <v>63</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E292" s="2">
+        <v>187</v>
+      </c>
+      <c r="E292" s="10">
         <v>9944.32</v>
       </c>
       <c r="F292" s="1">
         <v>0.05</v>
       </c>
-      <c r="G292" s="2">
+      <c r="G292" s="10">
         <f t="shared" si="8"/>
         <v>497.21600000000001</v>
       </c>
@@ -8047,15 +8055,15 @@
         <v>154</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E293" s="2">
+        <v>187</v>
+      </c>
+      <c r="E293" s="10">
         <v>4992</v>
       </c>
       <c r="F293" s="1">
         <v>0.05</v>
       </c>
-      <c r="G293" s="2">
+      <c r="G293" s="10">
         <f t="shared" si="8"/>
         <v>249.60000000000002</v>
       </c>
@@ -8071,15 +8079,15 @@
         <v>66</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E294" s="2">
+        <v>187</v>
+      </c>
+      <c r="E294" s="10">
         <v>9592.9599999999991</v>
       </c>
       <c r="F294" s="1">
         <v>0.05</v>
       </c>
-      <c r="G294" s="2">
+      <c r="G294" s="10">
         <f t="shared" si="8"/>
         <v>479.64799999999997</v>
       </c>
@@ -8095,15 +8103,15 @@
         <v>67</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E295" s="2">
+        <v>187</v>
+      </c>
+      <c r="E295" s="10">
         <v>2715.7</v>
       </c>
       <c r="F295" s="1">
         <v>0.05</v>
       </c>
-      <c r="G295" s="2">
+      <c r="G295" s="10">
         <f t="shared" si="8"/>
         <v>135.785</v>
       </c>
@@ -8119,15 +8127,15 @@
         <v>68</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E296" s="2">
+        <v>187</v>
+      </c>
+      <c r="E296" s="10">
         <v>3280.64</v>
       </c>
       <c r="F296" s="1">
         <v>0.05</v>
       </c>
-      <c r="G296" s="2">
+      <c r="G296" s="10">
         <f t="shared" si="8"/>
         <v>164.03200000000001</v>
       </c>
@@ -8143,15 +8151,15 @@
         <v>69</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E297" s="2">
+        <v>187</v>
+      </c>
+      <c r="E297" s="10">
         <v>3918.08</v>
       </c>
       <c r="F297" s="1">
         <v>0.05</v>
       </c>
-      <c r="G297" s="2">
+      <c r="G297" s="10">
         <f t="shared" si="8"/>
         <v>195.904</v>
       </c>
@@ -8167,15 +8175,15 @@
         <v>72</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E298" s="2">
+        <v>187</v>
+      </c>
+      <c r="E298" s="10">
         <v>3026.56</v>
       </c>
       <c r="F298" s="1">
         <v>0.05</v>
       </c>
-      <c r="G298" s="2">
+      <c r="G298" s="10">
         <f t="shared" si="8"/>
         <v>151.328</v>
       </c>
@@ -8191,15 +8199,15 @@
         <v>73</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E299" s="2">
+        <v>187</v>
+      </c>
+      <c r="E299" s="10">
         <v>2875.52</v>
       </c>
       <c r="F299" s="1">
         <v>0.05</v>
       </c>
-      <c r="G299" s="2">
+      <c r="G299" s="10">
         <f t="shared" si="8"/>
         <v>143.77600000000001</v>
       </c>
@@ -8215,15 +8223,15 @@
         <v>75</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E300" s="2">
+        <v>187</v>
+      </c>
+      <c r="E300" s="10">
         <v>4040.84</v>
       </c>
       <c r="F300" s="1">
         <v>0.05</v>
       </c>
-      <c r="G300" s="2">
+      <c r="G300" s="10">
         <f t="shared" si="8"/>
         <v>202.04200000000003</v>
       </c>
@@ -8239,15 +8247,15 @@
         <v>76</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E301" s="2">
+        <v>187</v>
+      </c>
+      <c r="E301" s="10">
         <v>1638.65</v>
       </c>
       <c r="F301" s="1">
         <v>0.05</v>
       </c>
-      <c r="G301" s="2">
+      <c r="G301" s="10">
         <f t="shared" si="8"/>
         <v>81.932500000000005</v>
       </c>
@@ -8263,15 +8271,15 @@
         <v>77</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E302" s="2">
+        <v>187</v>
+      </c>
+      <c r="E302" s="10">
         <v>4709.76</v>
       </c>
       <c r="F302" s="1">
         <v>0.05</v>
       </c>
-      <c r="G302" s="2">
+      <c r="G302" s="10">
         <f t="shared" si="8"/>
         <v>235.48800000000003</v>
       </c>
@@ -8287,15 +8295,15 @@
         <v>79</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E303" s="2">
+        <v>187</v>
+      </c>
+      <c r="E303" s="10">
         <v>2125.0700000000002</v>
       </c>
       <c r="F303" s="1">
         <v>0.05</v>
       </c>
-      <c r="G303" s="2">
+      <c r="G303" s="10">
         <f t="shared" si="8"/>
         <v>106.25350000000002</v>
       </c>
@@ -8311,15 +8319,15 @@
         <v>80</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E304" s="2">
+        <v>187</v>
+      </c>
+      <c r="E304" s="10">
         <v>11772.8</v>
       </c>
       <c r="F304" s="1">
         <v>0.05</v>
       </c>
-      <c r="G304" s="2">
+      <c r="G304" s="10">
         <f t="shared" si="8"/>
         <v>588.64</v>
       </c>
@@ -8335,15 +8343,15 @@
         <v>81</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E305" s="2">
+        <v>187</v>
+      </c>
+      <c r="E305" s="10">
         <v>4799.3599999999997</v>
       </c>
       <c r="F305" s="1">
         <v>0.05</v>
       </c>
-      <c r="G305" s="2">
+      <c r="G305" s="10">
         <f t="shared" si="8"/>
         <v>239.96799999999999</v>
       </c>
@@ -8359,15 +8367,15 @@
         <v>82</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E306" s="2">
+        <v>187</v>
+      </c>
+      <c r="E306" s="10">
         <v>9351.5499999999993</v>
       </c>
       <c r="F306" s="1">
         <v>0.05</v>
       </c>
-      <c r="G306" s="2">
+      <c r="G306" s="10">
         <f t="shared" si="8"/>
         <v>467.57749999999999</v>
       </c>
@@ -8383,15 +8391,15 @@
         <v>83</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E307" s="2">
+        <v>187</v>
+      </c>
+      <c r="E307" s="10">
         <v>3016.59</v>
       </c>
       <c r="F307" s="1">
         <v>0.05</v>
       </c>
-      <c r="G307" s="2">
+      <c r="G307" s="10">
         <f t="shared" si="8"/>
         <v>150.82950000000002</v>
       </c>
@@ -8407,15 +8415,15 @@
         <v>84</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E308" s="2">
+        <v>187</v>
+      </c>
+      <c r="E308" s="10">
         <v>997.75</v>
       </c>
       <c r="F308" s="1">
         <v>0.05</v>
       </c>
-      <c r="G308" s="2">
+      <c r="G308" s="10">
         <f t="shared" si="8"/>
         <v>49.887500000000003</v>
       </c>
@@ -8431,15 +8439,15 @@
         <v>85</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E309" s="2">
+        <v>187</v>
+      </c>
+      <c r="E309" s="10">
         <v>577.28</v>
       </c>
       <c r="F309" s="1">
         <v>0.05</v>
       </c>
-      <c r="G309" s="2">
+      <c r="G309" s="10">
         <f t="shared" si="8"/>
         <v>28.864000000000001</v>
       </c>
@@ -8455,15 +8463,15 @@
         <v>86</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E310" s="2">
+        <v>187</v>
+      </c>
+      <c r="E310" s="10">
         <v>1985.1</v>
       </c>
       <c r="F310" s="1">
         <v>0.05</v>
       </c>
-      <c r="G310" s="2">
+      <c r="G310" s="10">
         <f t="shared" si="8"/>
         <v>99.254999999999995</v>
       </c>
@@ -8479,15 +8487,15 @@
         <v>88</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E311" s="2">
+        <v>187</v>
+      </c>
+      <c r="E311" s="10">
         <v>592</v>
       </c>
       <c r="F311" s="1">
         <v>0.05</v>
       </c>
-      <c r="G311" s="2">
+      <c r="G311" s="10">
         <f t="shared" si="8"/>
         <v>29.6</v>
       </c>
@@ -8503,15 +8511,15 @@
         <v>89</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E312" s="2">
+        <v>187</v>
+      </c>
+      <c r="E312" s="10">
         <v>5795.2</v>
       </c>
       <c r="F312" s="1">
         <v>0.05</v>
       </c>
-      <c r="G312" s="2">
+      <c r="G312" s="10">
         <f t="shared" si="8"/>
         <v>289.76</v>
       </c>
@@ -8527,15 +8535,15 @@
         <v>90</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E313" s="2">
+        <v>187</v>
+      </c>
+      <c r="E313" s="10">
         <v>4808.32</v>
       </c>
       <c r="F313" s="1">
         <v>0.05</v>
       </c>
-      <c r="G313" s="2">
+      <c r="G313" s="10">
         <f t="shared" si="8"/>
         <v>240.416</v>
       </c>
@@ -8551,15 +8559,15 @@
         <v>91</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E314" s="2">
+        <v>187</v>
+      </c>
+      <c r="E314" s="10">
         <v>748.8</v>
       </c>
       <c r="F314" s="1">
         <v>0.05</v>
       </c>
-      <c r="G314" s="2">
+      <c r="G314" s="10">
         <f t="shared" si="8"/>
         <v>37.44</v>
       </c>
@@ -8575,15 +8583,15 @@
         <v>92</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E315" s="2">
+        <v>187</v>
+      </c>
+      <c r="E315" s="10">
         <v>6457.6</v>
       </c>
       <c r="F315" s="1">
         <v>0.05</v>
       </c>
-      <c r="G315" s="2">
+      <c r="G315" s="10">
         <f t="shared" si="8"/>
         <v>322.88000000000005</v>
       </c>
@@ -8599,15 +8607,15 @@
         <v>93</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E316" s="2">
+        <v>187</v>
+      </c>
+      <c r="E316" s="10">
         <v>0</v>
       </c>
       <c r="F316" s="1">
         <v>0.05</v>
       </c>
-      <c r="G316" s="2">
+      <c r="G316" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -8623,15 +8631,15 @@
         <v>94</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E317" s="2">
+        <v>187</v>
+      </c>
+      <c r="E317" s="10">
         <v>975.86</v>
       </c>
       <c r="F317" s="1">
         <v>0.05</v>
       </c>
-      <c r="G317" s="2">
+      <c r="G317" s="10">
         <f t="shared" si="8"/>
         <v>48.793000000000006</v>
       </c>
@@ -8647,15 +8655,15 @@
         <v>95</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E318" s="2">
+        <v>187</v>
+      </c>
+      <c r="E318" s="10">
         <v>931.84</v>
       </c>
       <c r="F318" s="1">
         <v>0.05</v>
       </c>
-      <c r="G318" s="2">
+      <c r="G318" s="10">
         <f t="shared" si="8"/>
         <v>46.592000000000006</v>
       </c>
@@ -8671,15 +8679,15 @@
         <v>96</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E319" s="2">
+        <v>187</v>
+      </c>
+      <c r="E319" s="10">
         <v>6378.24</v>
       </c>
       <c r="F319" s="1">
         <v>0.05</v>
       </c>
-      <c r="G319" s="2">
+      <c r="G319" s="10">
         <f t="shared" si="8"/>
         <v>318.91200000000003</v>
       </c>
@@ -8695,15 +8703,15 @@
         <v>97</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E320" s="2">
+        <v>187</v>
+      </c>
+      <c r="E320" s="10">
         <v>4465.92</v>
       </c>
       <c r="F320" s="1">
         <v>0.05</v>
       </c>
-      <c r="G320" s="2">
+      <c r="G320" s="10">
         <f t="shared" si="8"/>
         <v>223.29600000000002</v>
       </c>
@@ -8719,15 +8727,15 @@
         <v>98</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E321" s="2">
+        <v>187</v>
+      </c>
+      <c r="E321" s="10">
         <v>8159.36</v>
       </c>
       <c r="F321" s="1">
         <v>0.05</v>
       </c>
-      <c r="G321" s="2">
+      <c r="G321" s="10">
         <f t="shared" si="8"/>
         <v>407.96800000000002</v>
       </c>
@@ -8743,15 +8751,15 @@
         <v>101</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E322" s="2">
+        <v>187</v>
+      </c>
+      <c r="E322" s="10">
         <v>5214.8100000000004</v>
       </c>
       <c r="F322" s="1">
         <v>0.08</v>
       </c>
-      <c r="G322" s="2">
+      <c r="G322" s="10">
         <f t="shared" si="8"/>
         <v>417.18480000000005</v>
       </c>
@@ -8767,15 +8775,15 @@
         <v>102</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E323" s="2">
+        <v>187</v>
+      </c>
+      <c r="E323" s="10">
         <v>278.8</v>
       </c>
       <c r="F323" s="1">
         <v>0.08</v>
       </c>
-      <c r="G323" s="2">
+      <c r="G323" s="10">
         <f t="shared" si="8"/>
         <v>22.304000000000002</v>
       </c>
@@ -8791,15 +8799,15 @@
         <v>103</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E324" s="2">
+        <v>187</v>
+      </c>
+      <c r="E324" s="10">
         <v>2493.21</v>
       </c>
       <c r="F324" s="1">
         <v>0.08</v>
       </c>
-      <c r="G324" s="2">
+      <c r="G324" s="10">
         <f t="shared" si="8"/>
         <v>199.45680000000002</v>
       </c>
@@ -8815,15 +8823,15 @@
         <v>104</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E325" s="2">
+        <v>187</v>
+      </c>
+      <c r="E325" s="10">
         <v>346.68</v>
       </c>
       <c r="F325" s="1">
         <v>0.08</v>
       </c>
-      <c r="G325" s="2">
+      <c r="G325" s="10">
         <f t="shared" si="8"/>
         <v>27.734400000000001</v>
       </c>
@@ -8839,15 +8847,15 @@
         <v>105</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E326" s="2">
+        <v>187</v>
+      </c>
+      <c r="E326" s="10">
         <v>1513.08</v>
       </c>
       <c r="F326" s="1">
         <v>0.08</v>
       </c>
-      <c r="G326" s="2">
+      <c r="G326" s="10">
         <f t="shared" si="8"/>
         <v>121.04639999999999</v>
       </c>
@@ -8863,15 +8871,15 @@
         <v>106</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E327" s="2">
+        <v>187</v>
+      </c>
+      <c r="E327" s="10">
         <v>478.44</v>
       </c>
       <c r="F327" s="1">
         <v>0.08</v>
       </c>
-      <c r="G327" s="2">
+      <c r="G327" s="10">
         <f t="shared" si="8"/>
         <v>38.275199999999998</v>
       </c>
@@ -8887,15 +8895,15 @@
         <v>109</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E328" s="2">
+        <v>187</v>
+      </c>
+      <c r="E328" s="10">
         <v>1092.42</v>
       </c>
       <c r="F328" s="1">
         <v>0.08</v>
       </c>
-      <c r="G328" s="2">
+      <c r="G328" s="10">
         <f t="shared" si="8"/>
         <v>87.393600000000006</v>
       </c>
@@ -8911,15 +8919,15 @@
         <v>110</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E329" s="2">
+        <v>187</v>
+      </c>
+      <c r="E329" s="10">
         <v>731.16</v>
       </c>
       <c r="F329" s="1">
         <v>0.08</v>
       </c>
-      <c r="G329" s="2">
+      <c r="G329" s="10">
         <f t="shared" si="8"/>
         <v>58.492799999999995</v>
       </c>
@@ -8935,15 +8943,15 @@
         <v>113</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E330" s="2">
+        <v>187</v>
+      </c>
+      <c r="E330" s="10">
         <v>4804.38</v>
       </c>
       <c r="F330" s="1">
         <v>0.08</v>
       </c>
-      <c r="G330" s="2">
+      <c r="G330" s="10">
         <f t="shared" si="8"/>
         <v>384.35040000000004</v>
       </c>
@@ -8959,15 +8967,15 @@
         <v>115</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E331" s="2">
+        <v>187</v>
+      </c>
+      <c r="E331" s="10">
         <v>1558.26</v>
       </c>
       <c r="F331" s="1">
         <v>0.08</v>
       </c>
-      <c r="G331" s="2">
+      <c r="G331" s="10">
         <f t="shared" si="8"/>
         <v>124.66080000000001</v>
       </c>
@@ -8983,15 +8991,15 @@
         <v>116</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E332" s="2">
+        <v>187</v>
+      </c>
+      <c r="E332" s="10">
         <v>668.58</v>
       </c>
       <c r="F332" s="1">
         <v>0.08</v>
       </c>
-      <c r="G332" s="2">
+      <c r="G332" s="10">
         <f t="shared" si="8"/>
         <v>53.486400000000003</v>
       </c>
@@ -9007,15 +9015,15 @@
         <v>117</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E333" s="2">
+        <v>187</v>
+      </c>
+      <c r="E333" s="10">
         <v>5931.9</v>
       </c>
       <c r="F333" s="1">
         <v>0.08</v>
       </c>
-      <c r="G333" s="2">
+      <c r="G333" s="10">
         <f t="shared" si="8"/>
         <v>474.55199999999996</v>
       </c>
@@ -9031,15 +9039,15 @@
         <v>118</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E334" s="2">
+        <v>187</v>
+      </c>
+      <c r="E334" s="10">
         <v>13848.45</v>
       </c>
       <c r="F334" s="1">
         <v>0.08</v>
       </c>
-      <c r="G334" s="2">
+      <c r="G334" s="10">
         <f t="shared" si="8"/>
         <v>1107.876</v>
       </c>
@@ -9055,15 +9063,15 @@
         <v>119</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E335" s="2">
+        <v>187</v>
+      </c>
+      <c r="E335" s="10">
         <v>349.44</v>
       </c>
       <c r="F335" s="1">
         <v>0.08</v>
       </c>
-      <c r="G335" s="2">
+      <c r="G335" s="10">
         <f t="shared" si="8"/>
         <v>27.955200000000001</v>
       </c>
@@ -9079,15 +9087,15 @@
         <v>120</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E336" s="2">
+        <v>187</v>
+      </c>
+      <c r="E336" s="10">
         <v>4429.1899999999996</v>
       </c>
       <c r="F336" s="1">
         <v>0.08</v>
       </c>
-      <c r="G336" s="2">
+      <c r="G336" s="10">
         <f t="shared" si="8"/>
         <v>354.33519999999999</v>
       </c>
@@ -9103,15 +9111,15 @@
         <v>121</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E337" s="2">
+        <v>187</v>
+      </c>
+      <c r="E337" s="10">
         <v>2655.25</v>
       </c>
       <c r="F337" s="1">
         <v>0.08</v>
       </c>
-      <c r="G337" s="2">
+      <c r="G337" s="10">
         <f t="shared" si="8"/>
         <v>212.42000000000002</v>
       </c>
@@ -9127,15 +9135,15 @@
         <v>122</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E338" s="2">
+        <v>187</v>
+      </c>
+      <c r="E338" s="10">
         <v>11098.88</v>
       </c>
       <c r="F338" s="1">
         <v>0.08</v>
       </c>
-      <c r="G338" s="2">
+      <c r="G338" s="10">
         <f t="shared" si="8"/>
         <v>887.91039999999998</v>
       </c>
@@ -9151,15 +9159,15 @@
         <v>123</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E339" s="2">
+        <v>187</v>
+      </c>
+      <c r="E339" s="10">
         <v>7549.44</v>
       </c>
       <c r="F339" s="1">
         <v>0.08</v>
       </c>
-      <c r="G339" s="2">
+      <c r="G339" s="10">
         <f t="shared" si="8"/>
         <v>603.95519999999999</v>
       </c>
@@ -9175,15 +9183,15 @@
         <v>124</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E340" s="2">
+        <v>187</v>
+      </c>
+      <c r="E340" s="10">
         <v>4834.82</v>
       </c>
       <c r="F340" s="1">
         <v>0.08</v>
       </c>
-      <c r="G340" s="2">
+      <c r="G340" s="10">
         <f t="shared" si="8"/>
         <v>386.78559999999999</v>
       </c>
@@ -9199,15 +9207,15 @@
         <v>125</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E341" s="2">
+        <v>187</v>
+      </c>
+      <c r="E341" s="10">
         <v>4457.8100000000004</v>
       </c>
       <c r="F341" s="1">
         <v>0.08</v>
       </c>
-      <c r="G341" s="2">
+      <c r="G341" s="10">
         <f t="shared" si="8"/>
         <v>356.62480000000005</v>
       </c>
@@ -9223,15 +9231,15 @@
         <v>126</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E342" s="2">
+        <v>187</v>
+      </c>
+      <c r="E342" s="10">
         <v>229.12</v>
       </c>
       <c r="F342" s="1">
         <v>0.08</v>
       </c>
-      <c r="G342" s="2">
+      <c r="G342" s="10">
         <f t="shared" si="8"/>
         <v>18.329599999999999</v>
       </c>
@@ -9247,15 +9255,15 @@
         <v>127</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E343" s="2">
+        <v>187</v>
+      </c>
+      <c r="E343" s="10">
         <v>1365.12</v>
       </c>
       <c r="F343" s="1">
         <v>0.08</v>
       </c>
-      <c r="G343" s="2">
+      <c r="G343" s="10">
         <f t="shared" si="8"/>
         <v>109.20959999999999</v>
       </c>
@@ -9271,15 +9279,15 @@
         <v>128</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E344" s="2">
+        <v>187</v>
+      </c>
+      <c r="E344" s="10">
         <v>4877.28</v>
       </c>
       <c r="F344" s="1">
         <v>0.08</v>
       </c>
-      <c r="G344" s="2">
+      <c r="G344" s="10">
         <f t="shared" si="8"/>
         <v>390.18239999999997</v>
       </c>
@@ -9295,15 +9303,15 @@
         <v>131</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E345" s="2">
+        <v>187</v>
+      </c>
+      <c r="E345" s="10">
         <v>1555.85</v>
       </c>
       <c r="F345" s="1">
         <v>0.1</v>
       </c>
-      <c r="G345" s="2">
+      <c r="G345" s="10">
         <f t="shared" si="8"/>
         <v>155.58500000000001</v>
       </c>
@@ -9319,15 +9327,15 @@
         <v>132</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E346" s="2">
+        <v>187</v>
+      </c>
+      <c r="E346" s="10">
         <v>4855.1400000000003</v>
       </c>
       <c r="F346" s="1">
         <v>0.1</v>
       </c>
-      <c r="G346" s="2">
+      <c r="G346" s="10">
         <f t="shared" si="8"/>
         <v>485.51400000000007</v>
       </c>
@@ -9343,15 +9351,15 @@
         <v>133</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E347" s="2">
+        <v>187</v>
+      </c>
+      <c r="E347" s="10">
         <v>284.58</v>
       </c>
       <c r="F347" s="1">
         <v>0.1</v>
       </c>
-      <c r="G347" s="2">
+      <c r="G347" s="10">
         <f t="shared" si="8"/>
         <v>28.457999999999998</v>
       </c>
@@ -9367,15 +9375,15 @@
         <v>134</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E348" s="2">
+        <v>187</v>
+      </c>
+      <c r="E348" s="10">
         <v>10177.73</v>
       </c>
       <c r="F348" s="1">
         <v>0.1</v>
       </c>
-      <c r="G348" s="2">
+      <c r="G348" s="10">
         <f t="shared" si="8"/>
         <v>1017.773</v>
       </c>
@@ -9391,15 +9399,15 @@
         <v>135</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E349" s="2">
+        <v>187</v>
+      </c>
+      <c r="E349" s="10">
         <v>2052</v>
       </c>
       <c r="F349" s="1">
         <v>0.1</v>
       </c>
-      <c r="G349" s="2">
+      <c r="G349" s="10">
         <f t="shared" si="8"/>
         <v>205.20000000000002</v>
       </c>
@@ -9415,15 +9423,15 @@
         <v>136</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E350" s="2">
+        <v>187</v>
+      </c>
+      <c r="E350" s="10">
         <v>9938.7000000000007</v>
       </c>
       <c r="F350" s="1">
         <v>0.1</v>
       </c>
-      <c r="G350" s="2">
+      <c r="G350" s="10">
         <f t="shared" si="8"/>
         <v>993.87000000000012</v>
       </c>
@@ -9439,15 +9447,15 @@
         <v>138</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E351" s="2">
+        <v>187</v>
+      </c>
+      <c r="E351" s="10">
         <v>193.08</v>
       </c>
       <c r="F351" s="1">
         <v>0.1</v>
       </c>
-      <c r="G351" s="2">
+      <c r="G351" s="10">
         <f t="shared" si="8"/>
         <v>19.308000000000003</v>
       </c>
@@ -9463,15 +9471,15 @@
         <v>139</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E352" s="2">
+        <v>187</v>
+      </c>
+      <c r="E352" s="10">
         <v>1579.52</v>
       </c>
       <c r="F352" s="1">
         <v>0.1</v>
       </c>
-      <c r="G352" s="2">
+      <c r="G352" s="10">
         <f t="shared" si="8"/>
         <v>157.952</v>
       </c>
@@ -9487,15 +9495,15 @@
         <v>140</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E353" s="2">
+        <v>187</v>
+      </c>
+      <c r="E353" s="10">
         <v>8942.0499999999993</v>
       </c>
       <c r="F353" s="1">
         <v>0.1</v>
       </c>
-      <c r="G353" s="2">
+      <c r="G353" s="10">
         <f t="shared" si="8"/>
         <v>894.20499999999993</v>
       </c>
@@ -9511,15 +9519,15 @@
         <v>143</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E354" s="2">
+        <v>187</v>
+      </c>
+      <c r="E354" s="10">
         <v>3041.28</v>
       </c>
       <c r="F354" s="1">
         <v>0.1</v>
       </c>
-      <c r="G354" s="2">
+      <c r="G354" s="10">
         <f t="shared" si="8"/>
         <v>304.12800000000004</v>
       </c>
@@ -9535,15 +9543,15 @@
         <v>144</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E355" s="2">
+        <v>187</v>
+      </c>
+      <c r="E355" s="10">
         <v>6325.76</v>
       </c>
       <c r="F355" s="1">
         <v>0.1</v>
       </c>
-      <c r="G355" s="2">
+      <c r="G355" s="10">
         <f t="shared" si="8"/>
         <v>632.57600000000002</v>
       </c>
@@ -9559,15 +9567,15 @@
         <v>145</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E356" s="2">
+        <v>187</v>
+      </c>
+      <c r="E356" s="10">
         <v>2908.8</v>
       </c>
       <c r="F356" s="1">
         <v>0.1</v>
       </c>
-      <c r="G356" s="2">
+      <c r="G356" s="10">
         <f t="shared" si="8"/>
         <v>290.88000000000005</v>
       </c>
@@ -9583,15 +9591,15 @@
         <v>146</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E357" s="2">
+        <v>187</v>
+      </c>
+      <c r="E357" s="10">
         <v>8320.0300000000007</v>
       </c>
       <c r="F357" s="1">
         <v>0.1</v>
       </c>
-      <c r="G357" s="2">
+      <c r="G357" s="10">
         <f t="shared" si="8"/>
         <v>832.00300000000016</v>
       </c>
@@ -9604,18 +9612,18 @@
         <v>142</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E358" s="2">
+        <v>187</v>
+      </c>
+      <c r="E358" s="10">
         <v>5274.08</v>
       </c>
       <c r="F358" s="1">
         <v>0.1</v>
       </c>
-      <c r="G358" s="2">
+      <c r="G358" s="10">
         <f t="shared" si="8"/>
         <v>527.40800000000002</v>
       </c>
@@ -9631,15 +9639,15 @@
         <v>157</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E359" s="2">
+        <v>187</v>
+      </c>
+      <c r="E359" s="10">
         <v>0</v>
       </c>
       <c r="F359" s="1">
         <v>0.1</v>
       </c>
-      <c r="G359" s="2">
+      <c r="G359" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -9652,18 +9660,18 @@
         <v>155</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E360" s="2">
+        <v>187</v>
+      </c>
+      <c r="E360" s="10">
         <v>1362.44</v>
       </c>
       <c r="F360" s="1">
         <v>0.1</v>
       </c>
-      <c r="G360" s="2">
+      <c r="G360" s="10">
         <f t="shared" si="8"/>
         <v>136.244</v>
       </c>
@@ -9679,15 +9687,15 @@
         <v>158</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E361" s="2">
+        <v>187</v>
+      </c>
+      <c r="E361" s="10">
         <v>4779.0600000000004</v>
       </c>
       <c r="F361" s="1">
         <v>0.1</v>
       </c>
-      <c r="G361" s="2">
+      <c r="G361" s="10">
         <f t="shared" si="8"/>
         <v>477.90600000000006</v>
       </c>
@@ -9700,18 +9708,18 @@
         <v>156</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E362" s="2">
+        <v>187</v>
+      </c>
+      <c r="E362" s="10">
         <v>2309.5</v>
       </c>
       <c r="F362" s="1">
         <v>0.1</v>
       </c>
-      <c r="G362" s="2">
+      <c r="G362" s="10">
         <f t="shared" si="8"/>
         <v>230.95000000000002</v>
       </c>
@@ -9727,21 +9735,27 @@
         <v>160</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E363" s="2">
+        <v>187</v>
+      </c>
+      <c r="E363" s="10">
         <v>4280.76</v>
       </c>
       <c r="F363" s="1">
         <v>0.1</v>
       </c>
-      <c r="G363" s="2">
+      <c r="G363" s="10">
         <f t="shared" si="8"/>
         <v>428.07600000000002</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G363" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G363" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="JANEIRO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
@@ -9749,7 +9763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB98000-6C5E-44B6-ACEA-67E04ECC731C}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -9762,64 +9776,66 @@
     <col min="8" max="8" width="15.44140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="7" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="12">
+        <v>625.29999999999995</v>
+      </c>
+      <c r="F2" s="12">
+        <f>E2*0.1</f>
+        <v>62.53</v>
+      </c>
+      <c r="G2" s="12">
+        <f>E2*0.1133</f>
+        <v>70.846489999999989</v>
+      </c>
+      <c r="H2" s="12">
+        <v>491.92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="6">
-        <v>625.29999999999995</v>
-      </c>
-      <c r="F2" s="6">
-        <v>62.53</v>
-      </c>
-      <c r="G2" s="6">
-        <v>70.849999999999994</v>
-      </c>
-      <c r="H2" s="6">
-        <v>491.92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>10</v>
@@ -9827,25 +9843,28 @@
       <c r="D3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="12">
         <v>4282.24</v>
       </c>
-      <c r="F3" s="6">
-        <v>428.22</v>
-      </c>
-      <c r="G3" s="6">
-        <v>485.18</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="F3" s="12">
+        <f t="shared" ref="F3:F20" si="0">E3*0.1</f>
+        <v>428.22399999999999</v>
+      </c>
+      <c r="G3" s="12">
+        <f t="shared" ref="G3:G20" si="1">E3*0.1133</f>
+        <v>485.17779199999995</v>
+      </c>
+      <c r="H3" s="12">
         <v>3368.84</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>13</v>
@@ -9853,77 +9872,83 @@
       <c r="D4" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="12">
         <v>170.24</v>
       </c>
-      <c r="F4" s="6">
-        <v>17.02</v>
-      </c>
-      <c r="G4" s="6">
-        <v>19.29</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="F4" s="12">
+        <f t="shared" si="0"/>
+        <v>17.024000000000001</v>
+      </c>
+      <c r="G4" s="12">
+        <f t="shared" si="1"/>
+        <v>19.288192000000002</v>
+      </c>
+      <c r="H4" s="12">
         <v>133.93</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="12">
+        <v>4209.28</v>
+      </c>
+      <c r="F5" s="12">
+        <f t="shared" si="0"/>
+        <v>420.928</v>
+      </c>
+      <c r="G5" s="12">
+        <f t="shared" si="1"/>
+        <v>476.91142399999995</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3311.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="6">
-        <v>4209.28</v>
-      </c>
-      <c r="F5" s="6">
-        <v>420.93</v>
-      </c>
-      <c r="G5" s="6">
-        <v>476.91</v>
-      </c>
-      <c r="H5" s="6">
-        <v>3311.44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="12">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="shared" si="0"/>
+        <v>1.69</v>
+      </c>
+      <c r="G6" s="12">
+        <f t="shared" si="1"/>
+        <v>1.9147699999999999</v>
+      </c>
+      <c r="H6" s="12">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="6">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1.69</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1.91</v>
-      </c>
-      <c r="H6" s="6">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>15</v>
@@ -9931,25 +9956,27 @@
       <c r="D7" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="12">
         <v>103.9</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="12">
+        <f t="shared" si="0"/>
         <v>10.39</v>
       </c>
-      <c r="G7" s="6">
-        <v>11.77</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G7" s="12">
+        <f t="shared" si="1"/>
+        <v>11.77187</v>
+      </c>
+      <c r="H7" s="12">
         <v>81.739999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>12</v>
@@ -9957,51 +9984,55 @@
       <c r="D8" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="12">
         <v>2209.35</v>
       </c>
-      <c r="F8" s="6">
-        <v>220.94</v>
-      </c>
-      <c r="G8" s="6">
-        <v>250.32</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="F8" s="12">
+        <f t="shared" si="0"/>
+        <v>220.935</v>
+      </c>
+      <c r="G8" s="12">
+        <f t="shared" si="1"/>
+        <v>250.31935499999997</v>
+      </c>
+      <c r="H8" s="12">
         <v>1738.1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>178</v>
-      </c>
       <c r="D9" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="12">
         <v>216.45</v>
       </c>
-      <c r="F9" s="6">
-        <v>21.65</v>
-      </c>
-      <c r="G9" s="6">
-        <v>24.52</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="F9" s="12">
+        <f t="shared" si="0"/>
+        <v>21.645</v>
+      </c>
+      <c r="G9" s="12">
+        <f t="shared" si="1"/>
+        <v>24.523784999999997</v>
+      </c>
+      <c r="H9" s="12">
         <v>170.28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
@@ -10009,155 +10040,163 @@
       <c r="D10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="12">
         <v>182.4</v>
       </c>
-      <c r="F10" s="6">
-        <v>18.239999999999998</v>
-      </c>
-      <c r="G10" s="6">
-        <v>20.67</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>18.240000000000002</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="1"/>
+        <v>20.66592</v>
+      </c>
+      <c r="H10" s="12">
         <v>143.49</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1202.5</v>
+      </c>
+      <c r="F11" s="12">
+        <f t="shared" si="0"/>
+        <v>120.25</v>
+      </c>
+      <c r="G11" s="12">
+        <f t="shared" si="1"/>
+        <v>136.24324999999999</v>
+      </c>
+      <c r="H11" s="12">
+        <v>946.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1202.5</v>
-      </c>
-      <c r="F11" s="6">
-        <v>120.25</v>
-      </c>
-      <c r="G11" s="6">
-        <v>136.24</v>
-      </c>
-      <c r="H11" s="6">
-        <v>946.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="5" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>183</v>
-      </c>
       <c r="C13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="12">
         <v>1301.1199999999999</v>
       </c>
-      <c r="F14" s="6">
-        <v>130.11000000000001</v>
-      </c>
-      <c r="G14" s="6">
-        <v>147.41999999999999</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="F14" s="12">
+        <f t="shared" si="0"/>
+        <v>130.11199999999999</v>
+      </c>
+      <c r="G14" s="12">
+        <f t="shared" si="1"/>
+        <v>147.41689599999998</v>
+      </c>
+      <c r="H14" s="12">
         <v>1023.59</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1301.1199999999999</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="0"/>
+        <v>130.11199999999999</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>147.41689599999998</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1023.59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1301.1199999999999</v>
-      </c>
-      <c r="F15" s="6">
-        <v>130.11000000000001</v>
-      </c>
-      <c r="G15" s="6">
-        <v>147.41999999999999</v>
-      </c>
-      <c r="H15" s="6">
-        <v>1023.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>15</v>
@@ -10165,16 +10204,18 @@
       <c r="D16" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="12">
         <v>3385.3</v>
       </c>
-      <c r="F16" s="6">
-        <v>338.53</v>
-      </c>
-      <c r="G16" s="6">
-        <v>383.55</v>
-      </c>
-      <c r="H16" s="6">
+      <c r="F16" s="12">
+        <f t="shared" si="0"/>
+        <v>338.53000000000003</v>
+      </c>
+      <c r="G16" s="12">
+        <f t="shared" si="1"/>
+        <v>383.55448999999999</v>
+      </c>
+      <c r="H16" s="12">
         <v>2663.22</v>
       </c>
     </row>
@@ -10183,7 +10224,7 @@
         <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>143</v>
@@ -10191,16 +10232,18 @@
       <c r="D17" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="12">
         <v>2997.06</v>
       </c>
-      <c r="F17" s="6">
-        <v>299.70999999999998</v>
-      </c>
-      <c r="G17" s="6">
-        <v>339.57</v>
-      </c>
-      <c r="H17" s="6">
+      <c r="F17" s="12">
+        <f t="shared" si="0"/>
+        <v>299.70600000000002</v>
+      </c>
+      <c r="G17" s="12">
+        <f t="shared" si="1"/>
+        <v>339.56689799999998</v>
+      </c>
+      <c r="H17" s="12">
         <v>2357.79</v>
       </c>
     </row>
@@ -10209,24 +10252,26 @@
         <v>142</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>187</v>
-      </c>
       <c r="D18" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="12">
         <v>9098.8799999999992</v>
       </c>
-      <c r="F18" s="6">
-        <v>909.89</v>
-      </c>
-      <c r="G18" s="6">
-        <v>1030.9000000000001</v>
-      </c>
-      <c r="H18" s="6">
+      <c r="F18" s="12">
+        <f t="shared" si="0"/>
+        <v>909.88799999999992</v>
+      </c>
+      <c r="G18" s="12">
+        <f t="shared" si="1"/>
+        <v>1030.903104</v>
+      </c>
+      <c r="H18" s="12">
         <v>7158.09</v>
       </c>
     </row>
@@ -10235,7 +10280,7 @@
         <v>142</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>146</v>
@@ -10243,16 +10288,18 @@
       <c r="D19" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="12">
         <v>8613.02</v>
       </c>
-      <c r="F19" s="6">
-        <v>861.3</v>
-      </c>
-      <c r="G19" s="6">
-        <v>975.86</v>
-      </c>
-      <c r="H19" s="6">
+      <c r="F19" s="12">
+        <f t="shared" si="0"/>
+        <v>861.30200000000013</v>
+      </c>
+      <c r="G19" s="12">
+        <f t="shared" si="1"/>
+        <v>975.85516600000005</v>
+      </c>
+      <c r="H19" s="12">
         <v>6775.86</v>
       </c>
     </row>
@@ -10261,7 +10308,7 @@
         <v>142</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>147</v>
@@ -10269,16 +10316,18 @@
       <c r="D20" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="12">
         <v>3396.6</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="12">
+        <f t="shared" si="0"/>
         <v>339.66</v>
       </c>
-      <c r="G20" s="6">
-        <v>384.83</v>
-      </c>
-      <c r="H20" s="6">
+      <c r="G20" s="12">
+        <f t="shared" si="1"/>
+        <v>384.83477999999997</v>
+      </c>
+      <c r="H20" s="12">
         <v>2672.11</v>
       </c>
     </row>

--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{166B2273-78AF-4A1E-A190-0252973D2070}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0DB018C-28A0-4B66-BF42-3206F6CDF863}"/>
   <bookViews>
-    <workbookView xWindow="-24705" yWindow="300" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="-1815" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="192">
   <si>
     <t>Gerador</t>
   </si>
@@ -485,9 +485,6 @@
     <t xml:space="preserve">VIGNOLI </t>
   </si>
   <si>
-    <t>NOVEMBRO</t>
-  </si>
-  <si>
     <t>Valor a Pagar para Gerador (R$)</t>
   </si>
   <si>
@@ -600,9 +597,6 @@
   </si>
   <si>
     <t>MARFRAN</t>
-  </si>
-  <si>
-    <t>JANEIRO</t>
   </si>
   <si>
     <t xml:space="preserve">ATL. DERCIO 1 </t>
@@ -689,7 +683,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -718,6 +712,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1029,7 +1026,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G363"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1054,19 +1050,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1076,8 +1072,8 @@
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>148</v>
+      <c r="D2" s="14">
+        <v>45962</v>
       </c>
       <c r="E2" s="10">
         <v>719.55</v>
@@ -1090,7 +1086,7 @@
         <v>71.954999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1100,8 +1096,8 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>148</v>
+      <c r="D3" s="14">
+        <v>45962</v>
       </c>
       <c r="E3" s="10">
         <v>3411.2</v>
@@ -1114,7 +1110,7 @@
         <v>341.12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1124,8 +1120,8 @@
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>148</v>
+      <c r="D4" s="14">
+        <v>45962</v>
       </c>
       <c r="E4" s="10">
         <v>0</v>
@@ -1137,7 +1133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1147,8 +1143,8 @@
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>148</v>
+      <c r="D5" s="14">
+        <v>45962</v>
       </c>
       <c r="E5" s="10">
         <v>1082.64832</v>
@@ -1161,7 +1157,7 @@
         <v>108.26483200000001</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1171,8 +1167,8 @@
       <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>148</v>
+      <c r="D6" s="14">
+        <v>45962</v>
       </c>
       <c r="E6" s="10">
         <v>1726.95</v>
@@ -1185,7 +1181,7 @@
         <v>172.69500000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -1195,8 +1191,8 @@
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>148</v>
+      <c r="D7" s="14">
+        <v>45962</v>
       </c>
       <c r="E7" s="10">
         <v>1540.41</v>
@@ -1209,7 +1205,7 @@
         <v>154.04100000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -1219,8 +1215,8 @@
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>148</v>
+      <c r="D8" s="14">
+        <v>45962</v>
       </c>
       <c r="E8" s="10">
         <v>199.04</v>
@@ -1233,7 +1229,7 @@
         <v>19.904</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1243,8 +1239,8 @@
       <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>148</v>
+      <c r="D9" s="14">
+        <v>45962</v>
       </c>
       <c r="E9" s="10">
         <v>418.84</v>
@@ -1257,7 +1253,7 @@
         <v>41.884</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1267,8 +1263,8 @@
       <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>148</v>
+      <c r="D10" s="14">
+        <v>45962</v>
       </c>
       <c r="E10" s="10">
         <v>0</v>
@@ -1281,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -1291,8 +1287,8 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>148</v>
+      <c r="D11" s="14">
+        <v>45962</v>
       </c>
       <c r="E11" s="10">
         <v>218.73</v>
@@ -1305,7 +1301,7 @@
         <v>21.873000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1315,8 +1311,8 @@
       <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>148</v>
+      <c r="D12" s="14">
+        <v>45962</v>
       </c>
       <c r="E12" s="10">
         <v>219.7</v>
@@ -1329,7 +1325,7 @@
         <v>21.97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
@@ -1339,8 +1335,8 @@
       <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>148</v>
+      <c r="D13" s="14">
+        <v>45962</v>
       </c>
       <c r="E13" s="10">
         <v>46.72</v>
@@ -1353,7 +1349,7 @@
         <v>4.6719999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1363,8 +1359,8 @@
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>148</v>
+      <c r="D14" s="14">
+        <v>45962</v>
       </c>
       <c r="E14" s="10">
         <v>31.85</v>
@@ -1377,7 +1373,7 @@
         <v>3.1850000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1387,8 +1383,8 @@
       <c r="C15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>148</v>
+      <c r="D15" s="14">
+        <v>45962</v>
       </c>
       <c r="E15" s="10">
         <v>151.68</v>
@@ -1401,7 +1397,7 @@
         <v>15.168000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
@@ -1411,8 +1407,8 @@
       <c r="C16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>148</v>
+      <c r="D16" s="14">
+        <v>45962</v>
       </c>
       <c r="E16" s="10">
         <v>1828.45</v>
@@ -1425,7 +1421,7 @@
         <v>182.84500000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1435,8 +1431,8 @@
       <c r="C17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>148</v>
+      <c r="D17" s="14">
+        <v>45962</v>
       </c>
       <c r="E17" s="10">
         <v>0</v>
@@ -1449,7 +1445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1459,8 +1455,8 @@
       <c r="C18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>148</v>
+      <c r="D18" s="14">
+        <v>45962</v>
       </c>
       <c r="E18" s="10">
         <v>5198.8999999999996</v>
@@ -1473,7 +1469,7 @@
         <v>519.89</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -1483,8 +1479,8 @@
       <c r="C19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>148</v>
+      <c r="D19" s="14">
+        <v>45962</v>
       </c>
       <c r="E19" s="10">
         <v>5198.8999999999996</v>
@@ -1497,7 +1493,7 @@
         <v>519.89</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1507,8 +1503,8 @@
       <c r="C20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>148</v>
+      <c r="D20" s="14">
+        <v>45962</v>
       </c>
       <c r="E20" s="10">
         <v>11686.48</v>
@@ -1521,7 +1517,7 @@
         <v>1168.6479999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
@@ -1531,8 +1527,8 @@
       <c r="C21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>148</v>
+      <c r="D21" s="14">
+        <v>45962</v>
       </c>
       <c r="E21" s="10">
         <v>2248.5100000000002</v>
@@ -1545,7 +1541,7 @@
         <v>224.85100000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
@@ -1555,8 +1551,8 @@
       <c r="C22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>148</v>
+      <c r="D22" s="14">
+        <v>45962</v>
       </c>
       <c r="E22" s="10">
         <v>7392.64</v>
@@ -1569,7 +1565,7 @@
         <v>591.41120000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>31</v>
       </c>
@@ -1579,8 +1575,8 @@
       <c r="C23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>148</v>
+      <c r="D23" s="14">
+        <v>45962</v>
       </c>
       <c r="E23" s="10">
         <v>6910.72</v>
@@ -1593,7 +1589,7 @@
         <v>552.85760000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
@@ -1603,8 +1599,8 @@
       <c r="C24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>148</v>
+      <c r="D24" s="14">
+        <v>45962</v>
       </c>
       <c r="E24" s="10">
         <v>2600.96</v>
@@ -1617,7 +1613,7 @@
         <v>208.07680000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
@@ -1627,8 +1623,8 @@
       <c r="C25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>148</v>
+      <c r="D25" s="14">
+        <v>45962</v>
       </c>
       <c r="E25" s="10">
         <v>1721.6</v>
@@ -1641,7 +1637,7 @@
         <v>137.72800000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
@@ -1651,8 +1647,8 @@
       <c r="C26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>148</v>
+      <c r="D26" s="14">
+        <v>45962</v>
       </c>
       <c r="E26" s="10">
         <v>1824</v>
@@ -1665,7 +1661,7 @@
         <v>145.92000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
@@ -1675,8 +1671,8 @@
       <c r="C27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>148</v>
+      <c r="D27" s="14">
+        <v>45962</v>
       </c>
       <c r="E27" s="10">
         <v>2100.6</v>
@@ -1689,7 +1685,7 @@
         <v>168.048</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
@@ -1699,8 +1695,8 @@
       <c r="C28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>148</v>
+      <c r="D28" s="14">
+        <v>45962</v>
       </c>
       <c r="E28" s="10">
         <v>2458.88</v>
@@ -1713,7 +1709,7 @@
         <v>196.71040000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
@@ -1723,8 +1719,8 @@
       <c r="C29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>148</v>
+      <c r="D29" s="14">
+        <v>45962</v>
       </c>
       <c r="E29" s="10">
         <v>2789.36</v>
@@ -1737,7 +1733,7 @@
         <v>223.14880000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
@@ -1747,8 +1743,8 @@
       <c r="C30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>148</v>
+      <c r="D30" s="14">
+        <v>45962</v>
       </c>
       <c r="E30" s="10">
         <v>4679.08</v>
@@ -1761,7 +1757,7 @@
         <v>374.32639999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
@@ -1771,8 +1767,8 @@
       <c r="C31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>148</v>
+      <c r="D31" s="14">
+        <v>45962</v>
       </c>
       <c r="E31" s="10">
         <v>2113.02</v>
@@ -1785,7 +1781,7 @@
         <v>169.04159999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -1795,8 +1791,8 @@
       <c r="C32" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>148</v>
+      <c r="D32" s="14">
+        <v>45962</v>
       </c>
       <c r="E32" s="10">
         <v>3013.2</v>
@@ -1809,7 +1805,7 @@
         <v>241.05599999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
@@ -1819,8 +1815,8 @@
       <c r="C33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>148</v>
+      <c r="D33" s="14">
+        <v>45962</v>
       </c>
       <c r="E33" s="10">
         <v>646.79999999999995</v>
@@ -1833,7 +1829,7 @@
         <v>51.744</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1843,8 +1839,8 @@
       <c r="C34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>148</v>
+      <c r="D34" s="14">
+        <v>45962</v>
       </c>
       <c r="E34" s="10">
         <v>532.62</v>
@@ -1857,7 +1853,7 @@
         <v>42.6096</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
@@ -1867,8 +1863,8 @@
       <c r="C35" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>148</v>
+      <c r="D35" s="14">
+        <v>45962</v>
       </c>
       <c r="E35" s="10">
         <v>519.91999999999996</v>
@@ -1881,7 +1877,7 @@
         <v>41.593599999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>31</v>
       </c>
@@ -1891,8 +1887,8 @@
       <c r="C36" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>148</v>
+      <c r="D36" s="14">
+        <v>45962</v>
       </c>
       <c r="E36" s="10">
         <v>264</v>
@@ -1905,7 +1901,7 @@
         <v>21.12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
@@ -1915,8 +1911,8 @@
       <c r="C37" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>148</v>
+      <c r="D37" s="14">
+        <v>45962</v>
       </c>
       <c r="E37" s="10">
         <v>1372.8</v>
@@ -1929,7 +1925,7 @@
         <v>109.824</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1939,8 +1935,8 @@
       <c r="C38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>148</v>
+      <c r="D38" s="14">
+        <v>45962</v>
       </c>
       <c r="E38" s="10">
         <v>1143.1199999999999</v>
@@ -1953,7 +1949,7 @@
         <v>91.44959999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1963,8 +1959,8 @@
       <c r="C39" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>148</v>
+      <c r="D39" s="14">
+        <v>45962</v>
       </c>
       <c r="E39" s="10">
         <v>250.4</v>
@@ -1977,7 +1973,7 @@
         <v>20.032</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1987,8 +1983,8 @@
       <c r="C40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>148</v>
+      <c r="D40" s="14">
+        <v>45962</v>
       </c>
       <c r="E40" s="10">
         <v>99.11</v>
@@ -2001,7 +1997,7 @@
         <v>7.9287999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -2011,8 +2007,8 @@
       <c r="C41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>148</v>
+      <c r="D41" s="14">
+        <v>45962</v>
       </c>
       <c r="E41" s="10">
         <v>401.67</v>
@@ -2025,7 +2021,7 @@
         <v>32.133600000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -2035,8 +2031,8 @@
       <c r="C42" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>148</v>
+      <c r="D42" s="14">
+        <v>45962</v>
       </c>
       <c r="E42" s="10">
         <v>326.04000000000002</v>
@@ -2049,7 +2045,7 @@
         <v>26.083200000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -2059,8 +2055,8 @@
       <c r="C43" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>148</v>
+      <c r="D43" s="14">
+        <v>45962</v>
       </c>
       <c r="E43" s="10">
         <v>261.3</v>
@@ -2073,7 +2069,7 @@
         <v>20.904</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>31</v>
       </c>
@@ -2083,8 +2079,8 @@
       <c r="C44" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>148</v>
+      <c r="D44" s="14">
+        <v>45962</v>
       </c>
       <c r="E44" s="10">
         <v>404.29</v>
@@ -2097,7 +2093,7 @@
         <v>32.343200000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>31</v>
       </c>
@@ -2107,8 +2103,8 @@
       <c r="C45" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>148</v>
+      <c r="D45" s="14">
+        <v>45962</v>
       </c>
       <c r="E45" s="10">
         <v>605.13</v>
@@ -2121,7 +2117,7 @@
         <v>48.410400000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>31</v>
       </c>
@@ -2131,8 +2127,8 @@
       <c r="C46" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>148</v>
+      <c r="D46" s="14">
+        <v>45962</v>
       </c>
       <c r="E46" s="10">
         <v>633.15</v>
@@ -2145,7 +2141,7 @@
         <v>50.652000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>31</v>
       </c>
@@ -2155,8 +2151,8 @@
       <c r="C47" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>148</v>
+      <c r="D47" s="14">
+        <v>45962</v>
       </c>
       <c r="E47" s="10">
         <v>1238.44</v>
@@ -2169,7 +2165,7 @@
         <v>99.075200000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>31</v>
       </c>
@@ -2179,8 +2175,8 @@
       <c r="C48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>148</v>
+      <c r="D48" s="14">
+        <v>45962</v>
       </c>
       <c r="E48" s="10">
         <v>951.06</v>
@@ -2193,7 +2189,7 @@
         <v>76.084800000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>60</v>
       </c>
@@ -2203,8 +2199,8 @@
       <c r="C49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>148</v>
+      <c r="D49" s="14">
+        <v>45962</v>
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="1">
@@ -2215,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>60</v>
       </c>
@@ -2225,8 +2221,8 @@
       <c r="C50" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>148</v>
+      <c r="D50" s="14">
+        <v>45962</v>
       </c>
       <c r="E50" s="10">
         <v>9101.44</v>
@@ -2239,7 +2235,7 @@
         <v>455.07200000000006</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>60</v>
       </c>
@@ -2249,8 +2245,8 @@
       <c r="C51" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>148</v>
+      <c r="D51" s="14">
+        <v>45962</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="1">
@@ -2261,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>60</v>
       </c>
@@ -2271,8 +2267,8 @@
       <c r="C52" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>148</v>
+      <c r="D52" s="14">
+        <v>45962</v>
       </c>
       <c r="E52" s="10">
         <v>4949.76</v>
@@ -2285,7 +2281,7 @@
         <v>247.48800000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2291,8 @@
       <c r="C53" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>148</v>
+      <c r="D53" s="14">
+        <v>45962</v>
       </c>
       <c r="E53" s="10">
         <v>6338.56</v>
@@ -2309,7 +2305,7 @@
         <v>316.92800000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>60</v>
       </c>
@@ -2319,8 +2315,8 @@
       <c r="C54" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>148</v>
+      <c r="D54" s="14">
+        <v>45962</v>
       </c>
       <c r="E54" s="10">
         <v>2715.05</v>
@@ -2333,7 +2329,7 @@
         <v>135.75250000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>60</v>
       </c>
@@ -2343,8 +2339,8 @@
       <c r="C55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>148</v>
+      <c r="D55" s="14">
+        <v>45962</v>
       </c>
       <c r="E55" s="10">
         <v>3175.68</v>
@@ -2357,7 +2353,7 @@
         <v>158.78399999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>60</v>
       </c>
@@ -2367,8 +2363,8 @@
       <c r="C56" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>148</v>
+      <c r="D56" s="14">
+        <v>45962</v>
       </c>
       <c r="E56" s="10">
         <v>6210.56</v>
@@ -2381,7 +2377,7 @@
         <v>310.52800000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>60</v>
       </c>
@@ -2391,8 +2387,8 @@
       <c r="C57" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>148</v>
+      <c r="D57" s="14">
+        <v>45962</v>
       </c>
       <c r="E57" s="10">
         <v>0</v>
@@ -2405,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
@@ -2415,8 +2411,8 @@
       <c r="C58" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>148</v>
+      <c r="D58" s="14">
+        <v>45962</v>
       </c>
       <c r="E58" s="10">
         <v>261.47000000000003</v>
@@ -2429,7 +2425,7 @@
         <v>13.073500000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>60</v>
       </c>
@@ -2439,8 +2435,8 @@
       <c r="C59" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>148</v>
+      <c r="D59" s="14">
+        <v>45962</v>
       </c>
       <c r="E59" s="10">
         <v>1418.88</v>
@@ -2453,7 +2449,7 @@
         <v>70.944000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
@@ -2463,8 +2459,8 @@
       <c r="C60" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>148</v>
+      <c r="D60" s="14">
+        <v>45962</v>
       </c>
       <c r="E60" s="10">
         <v>3537.92</v>
@@ -2477,7 +2473,7 @@
         <v>176.89600000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
@@ -2487,8 +2483,8 @@
       <c r="C61" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>148</v>
+      <c r="D61" s="14">
+        <v>45962</v>
       </c>
       <c r="E61" s="10">
         <v>0</v>
@@ -2501,7 +2497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>60</v>
       </c>
@@ -2511,8 +2507,8 @@
       <c r="C62" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>148</v>
+      <c r="D62" s="14">
+        <v>45962</v>
       </c>
       <c r="E62" s="10">
         <v>3828.82</v>
@@ -2525,7 +2521,7 @@
         <v>191.44100000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>60</v>
       </c>
@@ -2535,8 +2531,8 @@
       <c r="C63" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>148</v>
+      <c r="D63" s="14">
+        <v>45962</v>
       </c>
       <c r="E63" s="10">
         <v>5204.55</v>
@@ -2549,7 +2545,7 @@
         <v>260.22750000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>60</v>
       </c>
@@ -2559,8 +2555,8 @@
       <c r="C64" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>148</v>
+      <c r="D64" s="14">
+        <v>45962</v>
       </c>
       <c r="E64" s="10">
         <v>5534.1</v>
@@ -2573,7 +2569,7 @@
         <v>276.70500000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
@@ -2583,8 +2579,8 @@
       <c r="C65" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>148</v>
+      <c r="D65" s="14">
+        <v>45962</v>
       </c>
       <c r="E65" s="10">
         <v>4553.58</v>
@@ -2597,7 +2593,7 @@
         <v>227.679</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>60</v>
       </c>
@@ -2607,8 +2603,8 @@
       <c r="C66" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>148</v>
+      <c r="D66" s="14">
+        <v>45962</v>
       </c>
       <c r="E66" s="10">
         <v>11651.2</v>
@@ -2621,7 +2617,7 @@
         <v>582.56000000000006</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>60</v>
       </c>
@@ -2631,8 +2627,8 @@
       <c r="C67" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>148</v>
+      <c r="D67" s="14">
+        <v>45962</v>
       </c>
       <c r="E67" s="10">
         <v>4817.92</v>
@@ -2645,7 +2641,7 @@
         <v>240.89600000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>60</v>
       </c>
@@ -2655,8 +2651,8 @@
       <c r="C68" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>148</v>
+      <c r="D68" s="14">
+        <v>45962</v>
       </c>
       <c r="E68" s="10">
         <v>9120.7999999999993</v>
@@ -2669,7 +2665,7 @@
         <v>456.03999999999996</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>60</v>
       </c>
@@ -2679,8 +2675,8 @@
       <c r="C69" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>148</v>
+      <c r="D69" s="14">
+        <v>45962</v>
       </c>
       <c r="E69" s="10">
         <v>3503.72</v>
@@ -2693,7 +2689,7 @@
         <v>175.18600000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>60</v>
       </c>
@@ -2703,8 +2699,8 @@
       <c r="C70" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>148</v>
+      <c r="D70" s="14">
+        <v>45962</v>
       </c>
       <c r="E70" s="10">
         <v>1077.05</v>
@@ -2717,7 +2713,7 @@
         <v>53.852499999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>60</v>
       </c>
@@ -2727,8 +2723,8 @@
       <c r="C71" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>148</v>
+      <c r="D71" s="14">
+        <v>45962</v>
       </c>
       <c r="E71" s="10">
         <v>694.4</v>
@@ -2741,7 +2737,7 @@
         <v>34.72</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>60</v>
       </c>
@@ -2751,8 +2747,8 @@
       <c r="C72" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>148</v>
+      <c r="D72" s="14">
+        <v>45962</v>
       </c>
       <c r="E72" s="10">
         <v>5792.15</v>
@@ -2765,7 +2761,7 @@
         <v>289.60750000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>60</v>
       </c>
@@ -2775,8 +2771,8 @@
       <c r="C73" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>148</v>
+      <c r="D73" s="14">
+        <v>45962</v>
       </c>
       <c r="E73" s="10">
         <v>613.12</v>
@@ -2789,7 +2785,7 @@
         <v>30.656000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>60</v>
       </c>
@@ -2799,8 +2795,8 @@
       <c r="C74" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>148</v>
+      <c r="D74" s="14">
+        <v>45962</v>
       </c>
       <c r="E74" s="10">
         <v>5693.44</v>
@@ -2813,7 +2809,7 @@
         <v>284.67199999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>60</v>
       </c>
@@ -2823,8 +2819,8 @@
       <c r="C75" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>148</v>
+      <c r="D75" s="14">
+        <v>45962</v>
       </c>
       <c r="E75" s="10">
         <v>4423.68</v>
@@ -2837,7 +2833,7 @@
         <v>221.18400000000003</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>60</v>
       </c>
@@ -2847,8 +2843,8 @@
       <c r="C76" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>148</v>
+      <c r="D76" s="14">
+        <v>45962</v>
       </c>
       <c r="E76" s="10">
         <v>811.52</v>
@@ -2861,7 +2857,7 @@
         <v>40.576000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>60</v>
       </c>
@@ -2871,8 +2867,8 @@
       <c r="C77" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>148</v>
+      <c r="D77" s="14">
+        <v>45962</v>
       </c>
       <c r="E77" s="10">
         <v>6256</v>
@@ -2885,7 +2881,7 @@
         <v>312.8</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>60</v>
       </c>
@@ -2895,8 +2891,8 @@
       <c r="C78" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>148</v>
+      <c r="D78" s="14">
+        <v>45962</v>
       </c>
       <c r="E78" s="10">
         <v>0</v>
@@ -2909,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>60</v>
       </c>
@@ -2919,8 +2915,8 @@
       <c r="C79" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>148</v>
+      <c r="D79" s="14">
+        <v>45962</v>
       </c>
       <c r="E79" s="10">
         <v>1003.52</v>
@@ -2933,7 +2929,7 @@
         <v>50.176000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>60</v>
       </c>
@@ -2943,8 +2939,8 @@
       <c r="C80" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>148</v>
+      <c r="D80" s="14">
+        <v>45962</v>
       </c>
       <c r="E80" s="10">
         <v>1112.96</v>
@@ -2957,7 +2953,7 @@
         <v>55.648000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>60</v>
       </c>
@@ -2967,8 +2963,8 @@
       <c r="C81" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>148</v>
+      <c r="D81" s="14">
+        <v>45962</v>
       </c>
       <c r="E81" s="10">
         <v>5863.04</v>
@@ -2981,7 +2977,7 @@
         <v>293.15199999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>60</v>
       </c>
@@ -2991,8 +2987,8 @@
       <c r="C82" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>148</v>
+      <c r="D82" s="14">
+        <v>45962</v>
       </c>
       <c r="E82" s="10">
         <v>4433.92</v>
@@ -3005,7 +3001,7 @@
         <v>221.69600000000003</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>60</v>
       </c>
@@ -3015,8 +3011,8 @@
       <c r="C83" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>148</v>
+      <c r="D83" s="14">
+        <v>45962</v>
       </c>
       <c r="E83" s="10">
         <v>7269.76</v>
@@ -3029,7 +3025,7 @@
         <v>363.48800000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>99</v>
       </c>
@@ -3039,8 +3035,8 @@
       <c r="C84" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>148</v>
+      <c r="D84" s="14">
+        <v>45962</v>
       </c>
       <c r="E84" s="10">
         <v>5134.1499999999996</v>
@@ -3053,7 +3049,7 @@
         <v>513.41499999999996</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>99</v>
       </c>
@@ -3063,8 +3059,8 @@
       <c r="C85" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>148</v>
+      <c r="D85" s="14">
+        <v>45962</v>
       </c>
       <c r="E85" s="10">
         <v>217.6</v>
@@ -3077,7 +3073,7 @@
         <v>21.76</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>99</v>
       </c>
@@ -3087,8 +3083,8 @@
       <c r="C86" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>148</v>
+      <c r="D86" s="14">
+        <v>45962</v>
       </c>
       <c r="E86" s="10">
         <v>2311.25</v>
@@ -3101,7 +3097,7 @@
         <v>231.125</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>99</v>
       </c>
@@ -3111,8 +3107,8 @@
       <c r="C87" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>148</v>
+      <c r="D87" s="14">
+        <v>45962</v>
       </c>
       <c r="E87" s="10">
         <v>289.44</v>
@@ -3125,7 +3121,7 @@
         <v>28.944000000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>99</v>
       </c>
@@ -3135,8 +3131,8 @@
       <c r="C88" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>148</v>
+      <c r="D88" s="14">
+        <v>45962</v>
       </c>
       <c r="E88" s="10">
         <v>2266.38</v>
@@ -3149,7 +3145,7 @@
         <v>226.63800000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>99</v>
       </c>
@@ -3159,8 +3155,8 @@
       <c r="C89" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>148</v>
+      <c r="D89" s="14">
+        <v>45962</v>
       </c>
       <c r="E89" s="10">
         <v>423.9</v>
@@ -3173,7 +3169,7 @@
         <v>42.39</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>99</v>
       </c>
@@ -3183,8 +3179,8 @@
       <c r="C90" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>148</v>
+      <c r="D90" s="14">
+        <v>45962</v>
       </c>
       <c r="E90" s="10">
         <v>204.68</v>
@@ -3197,7 +3193,7 @@
         <v>20.468000000000004</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>99</v>
       </c>
@@ -3207,8 +3203,8 @@
       <c r="C91" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>148</v>
+      <c r="D91" s="14">
+        <v>45962</v>
       </c>
       <c r="E91" s="10">
         <v>0</v>
@@ -3221,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>99</v>
       </c>
@@ -3231,8 +3227,8 @@
       <c r="C92" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>148</v>
+      <c r="D92" s="14">
+        <v>45962</v>
       </c>
       <c r="E92" s="10">
         <v>993.06</v>
@@ -3245,7 +3241,7 @@
         <v>99.305999999999997</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>99</v>
       </c>
@@ -3255,8 +3251,8 @@
       <c r="C93" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>148</v>
+      <c r="D93" s="14">
+        <v>45962</v>
       </c>
       <c r="E93" s="10">
         <v>885.6</v>
@@ -3269,7 +3265,7 @@
         <v>88.56</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>99</v>
       </c>
@@ -3279,8 +3275,8 @@
       <c r="C94" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>148</v>
+      <c r="D94" s="14">
+        <v>45962</v>
       </c>
       <c r="E94" s="10">
         <v>460.08</v>
@@ -3293,7 +3289,7 @@
         <v>46.008000000000003</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>99</v>
       </c>
@@ -3303,8 +3299,8 @@
       <c r="C95" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>148</v>
+      <c r="D95" s="14">
+        <v>45962</v>
       </c>
       <c r="E95" s="10">
         <v>0</v>
@@ -3317,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>99</v>
       </c>
@@ -3327,8 +3323,8 @@
       <c r="C96" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>148</v>
+      <c r="D96" s="14">
+        <v>45962</v>
       </c>
       <c r="E96" s="10">
         <v>4362.66</v>
@@ -3341,7 +3337,7 @@
         <v>436.26600000000002</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>99</v>
       </c>
@@ -3351,8 +3347,8 @@
       <c r="C97" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>148</v>
+      <c r="D97" s="14">
+        <v>45962</v>
       </c>
       <c r="E97" s="10">
         <v>119.46</v>
@@ -3364,7 +3360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>99</v>
       </c>
@@ -3374,8 +3370,8 @@
       <c r="C98" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>148</v>
+      <c r="D98" s="14">
+        <v>45962</v>
       </c>
       <c r="E98" s="10">
         <v>1359.6</v>
@@ -3388,7 +3384,7 @@
         <v>135.96</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>99</v>
       </c>
@@ -3398,8 +3394,8 @@
       <c r="C99" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>148</v>
+      <c r="D99" s="14">
+        <v>45962</v>
       </c>
       <c r="E99" s="10">
         <v>624.36</v>
@@ -3412,7 +3408,7 @@
         <v>62.436000000000007</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>99</v>
       </c>
@@ -3422,8 +3418,8 @@
       <c r="C100" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>148</v>
+      <c r="D100" s="14">
+        <v>45962</v>
       </c>
       <c r="E100" s="10">
         <v>5857.38</v>
@@ -3436,7 +3432,7 @@
         <v>585.73800000000006</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>99</v>
       </c>
@@ -3446,8 +3442,8 @@
       <c r="C101" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>148</v>
+      <c r="D101" s="14">
+        <v>45962</v>
       </c>
       <c r="E101" s="10">
         <v>12081.84</v>
@@ -3460,7 +3456,7 @@
         <v>1208.184</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>99</v>
       </c>
@@ -3470,8 +3466,8 @@
       <c r="C102" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>148</v>
+      <c r="D102" s="14">
+        <v>45962</v>
       </c>
       <c r="E102" s="10">
         <v>348.16</v>
@@ -3484,7 +3480,7 @@
         <v>34.816000000000003</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>99</v>
       </c>
@@ -3494,8 +3490,8 @@
       <c r="C103" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>148</v>
+      <c r="D103" s="14">
+        <v>45962</v>
       </c>
       <c r="E103" s="10">
         <v>2118.35</v>
@@ -3508,7 +3504,7 @@
         <v>211.83500000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>99</v>
       </c>
@@ -3518,8 +3514,8 @@
       <c r="C104" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>148</v>
+      <c r="D104" s="14">
+        <v>45962</v>
       </c>
       <c r="E104" s="10">
         <v>3017.95</v>
@@ -3532,7 +3528,7 @@
         <v>301.79500000000002</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>99</v>
       </c>
@@ -3542,8 +3538,8 @@
       <c r="C105" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>148</v>
+      <c r="D105" s="14">
+        <v>45962</v>
       </c>
       <c r="E105" s="10">
         <v>10561.28</v>
@@ -3556,7 +3552,7 @@
         <v>1056.1280000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>99</v>
       </c>
@@ -3566,8 +3562,8 @@
       <c r="C106" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>148</v>
+      <c r="D106" s="14">
+        <v>45962</v>
       </c>
       <c r="E106" s="10">
         <v>1683.84</v>
@@ -3580,7 +3576,7 @@
         <v>168.38400000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>99</v>
       </c>
@@ -3590,8 +3586,8 @@
       <c r="C107" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>148</v>
+      <c r="D107" s="14">
+        <v>45962</v>
       </c>
       <c r="E107" s="10">
         <v>1457.39</v>
@@ -3604,7 +3600,7 @@
         <v>145.739</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>99</v>
       </c>
@@ -3614,8 +3610,8 @@
       <c r="C108" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>148</v>
+      <c r="D108" s="14">
+        <v>45962</v>
       </c>
       <c r="E108" s="10">
         <v>969.2</v>
@@ -3628,7 +3624,7 @@
         <v>96.920000000000016</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>99</v>
       </c>
@@ -3638,8 +3634,8 @@
       <c r="C109" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>148</v>
+      <c r="D109" s="14">
+        <v>45962</v>
       </c>
       <c r="E109" s="10">
         <v>226.56</v>
@@ -3652,7 +3648,7 @@
         <v>22.656000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>99</v>
       </c>
@@ -3662,8 +3658,8 @@
       <c r="C110" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>148</v>
+      <c r="D110" s="14">
+        <v>45962</v>
       </c>
       <c r="E110" s="10">
         <v>646.38</v>
@@ -3676,7 +3672,7 @@
         <v>64.638000000000005</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>99</v>
       </c>
@@ -3686,8 +3682,8 @@
       <c r="C111" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>148</v>
+      <c r="D111" s="14">
+        <v>45962</v>
       </c>
       <c r="E111" s="10">
         <v>394.2</v>
@@ -3700,7 +3696,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>129</v>
       </c>
@@ -3710,8 +3706,8 @@
       <c r="C112" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>148</v>
+      <c r="D112" s="14">
+        <v>45962</v>
       </c>
       <c r="E112" s="10">
         <v>1846.2</v>
@@ -3724,7 +3720,7 @@
         <v>184.62</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>129</v>
       </c>
@@ -3734,8 +3730,8 @@
       <c r="C113" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>148</v>
+      <c r="D113" s="14">
+        <v>45962</v>
       </c>
       <c r="E113" s="10">
         <v>4475.5200000000004</v>
@@ -3748,7 +3744,7 @@
         <v>447.55200000000008</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>129</v>
       </c>
@@ -3758,8 +3754,8 @@
       <c r="C114" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>148</v>
+      <c r="D114" s="14">
+        <v>45962</v>
       </c>
       <c r="E114" s="10">
         <v>293.52</v>
@@ -3772,7 +3768,7 @@
         <v>29.352</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>129</v>
       </c>
@@ -3782,8 +3778,8 @@
       <c r="C115" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>148</v>
+      <c r="D115" s="14">
+        <v>45962</v>
       </c>
       <c r="E115" s="10">
         <v>4923.97</v>
@@ -3796,7 +3792,7 @@
         <v>492.39700000000005</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>129</v>
       </c>
@@ -3806,8 +3802,8 @@
       <c r="C116" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>148</v>
+      <c r="D116" s="14">
+        <v>45962</v>
       </c>
       <c r="E116" s="10">
         <v>1840.86</v>
@@ -3820,7 +3816,7 @@
         <v>184.08600000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>129</v>
       </c>
@@ -3830,8 +3826,8 @@
       <c r="C117" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>148</v>
+      <c r="D117" s="14">
+        <v>45962</v>
       </c>
       <c r="E117" s="10">
         <v>10140.799999999999</v>
@@ -3844,7 +3840,7 @@
         <v>1014.0799999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>129</v>
       </c>
@@ -3854,8 +3850,8 @@
       <c r="C118" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>148</v>
+      <c r="D118" s="14">
+        <v>45962</v>
       </c>
       <c r="E118" s="10">
         <v>0</v>
@@ -3868,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>129</v>
       </c>
@@ -3878,8 +3874,8 @@
       <c r="C119" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>148</v>
+      <c r="D119" s="14">
+        <v>45962</v>
       </c>
       <c r="E119" s="10">
         <v>123.55</v>
@@ -3892,7 +3888,7 @@
         <v>12.355</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>129</v>
       </c>
@@ -3902,8 +3898,8 @@
       <c r="C120" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>148</v>
+      <c r="D120" s="14">
+        <v>45962</v>
       </c>
       <c r="E120" s="10">
         <v>974.7</v>
@@ -3916,7 +3912,7 @@
         <v>97.470000000000013</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>129</v>
       </c>
@@ -3926,8 +3922,8 @@
       <c r="C121" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>148</v>
+      <c r="D121" s="14">
+        <v>45962</v>
       </c>
       <c r="E121" s="10">
         <v>9473.1</v>
@@ -3940,7 +3936,7 @@
         <v>947.31000000000006</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>141</v>
       </c>
@@ -3950,8 +3946,8 @@
       <c r="C122" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>148</v>
+      <c r="D122" s="14">
+        <v>45962</v>
       </c>
       <c r="E122" s="10">
         <v>2930.4</v>
@@ -3964,7 +3960,7 @@
         <v>293.04000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>141</v>
       </c>
@@ -3974,8 +3970,8 @@
       <c r="C123" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>148</v>
+      <c r="D123" s="14">
+        <v>45962</v>
       </c>
       <c r="E123" s="10">
         <v>6302.08</v>
@@ -3988,7 +3984,7 @@
         <v>630.20800000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>141</v>
       </c>
@@ -3998,8 +3994,8 @@
       <c r="C124" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>148</v>
+      <c r="D124" s="14">
+        <v>45962</v>
       </c>
       <c r="E124" s="10">
         <v>2708.48</v>
@@ -4012,7 +4008,7 @@
         <v>270.84800000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>141</v>
       </c>
@@ -4022,8 +4018,8 @@
       <c r="C125" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>148</v>
+      <c r="D125" s="14">
+        <v>45962</v>
       </c>
       <c r="E125" s="10">
         <v>10157.950000000001</v>
@@ -4036,7 +4032,7 @@
         <v>1015.7950000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>141</v>
       </c>
@@ -4046,8 +4042,8 @@
       <c r="C126" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>148</v>
+      <c r="D126" s="14">
+        <v>45962</v>
       </c>
       <c r="E126" s="10">
         <v>5359.76</v>
@@ -4060,7 +4056,7 @@
         <v>535.976</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>4</v>
       </c>
@@ -4070,8 +4066,8 @@
       <c r="C127" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>151</v>
+      <c r="D127" s="14">
+        <v>45992</v>
       </c>
       <c r="E127" s="10">
         <v>625.29999999999995</v>
@@ -4084,7 +4080,7 @@
         <v>62.53</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>4</v>
       </c>
@@ -4094,8 +4090,8 @@
       <c r="C128" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>151</v>
+      <c r="D128" s="14">
+        <v>45992</v>
       </c>
       <c r="E128" s="10">
         <v>4282.24</v>
@@ -4108,7 +4104,7 @@
         <v>428.22399999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>4</v>
       </c>
@@ -4118,8 +4114,8 @@
       <c r="C129" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>151</v>
+      <c r="D129" s="14">
+        <v>45992</v>
       </c>
       <c r="E129" s="10">
         <v>4209.28</v>
@@ -4132,7 +4128,7 @@
         <v>420.928</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>4</v>
       </c>
@@ -4140,10 +4136,10 @@
         <v>11</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D130" s="3" t="s">
         <v>151</v>
+      </c>
+      <c r="D130" s="14">
+        <v>45992</v>
       </c>
       <c r="E130" s="10">
         <v>16.899999999999999</v>
@@ -4156,7 +4152,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>4</v>
       </c>
@@ -4166,8 +4162,8 @@
       <c r="C131" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>151</v>
+      <c r="D131" s="14">
+        <v>45992</v>
       </c>
       <c r="E131" s="10">
         <v>170.24</v>
@@ -4180,7 +4176,7 @@
         <v>17.024000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>4</v>
       </c>
@@ -4190,8 +4186,8 @@
       <c r="C132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>151</v>
+      <c r="D132" s="14">
+        <v>45992</v>
       </c>
       <c r="E132" s="10">
         <v>103.9</v>
@@ -4204,7 +4200,7 @@
         <v>10.39</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>4</v>
       </c>
@@ -4212,10 +4208,10 @@
         <v>14</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="D133" s="14">
+        <v>45992</v>
       </c>
       <c r="E133" s="10">
         <v>3385.3</v>
@@ -4228,7 +4224,7 @@
         <v>338.53000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>4</v>
       </c>
@@ -4238,8 +4234,8 @@
       <c r="C134" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>151</v>
+      <c r="D134" s="14">
+        <v>45992</v>
       </c>
       <c r="E134" s="10">
         <v>2209.35</v>
@@ -4252,7 +4248,7 @@
         <v>220.935</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>4</v>
       </c>
@@ -4262,8 +4258,8 @@
       <c r="C135" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>151</v>
+      <c r="D135" s="14">
+        <v>45992</v>
       </c>
       <c r="E135" s="10">
         <v>216.45</v>
@@ -4276,7 +4272,7 @@
         <v>21.645</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>4</v>
       </c>
@@ -4286,8 +4282,8 @@
       <c r="C136" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>151</v>
+      <c r="D136" s="14">
+        <v>45992</v>
       </c>
       <c r="E136" s="10">
         <v>182.4</v>
@@ -4300,7 +4296,7 @@
         <v>18.240000000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>4</v>
       </c>
@@ -4310,8 +4306,8 @@
       <c r="C137" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>151</v>
+      <c r="D137" s="14">
+        <v>45992</v>
       </c>
       <c r="E137" s="10">
         <v>1202.5</v>
@@ -4324,7 +4320,7 @@
         <v>120.25</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>4</v>
       </c>
@@ -4334,8 +4330,8 @@
       <c r="C138" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D138" s="3" t="s">
-        <v>151</v>
+      <c r="D138" s="14">
+        <v>45992</v>
       </c>
       <c r="E138" s="10">
         <v>0</v>
@@ -4348,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>4</v>
       </c>
@@ -4358,8 +4354,8 @@
       <c r="C139" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>151</v>
+      <c r="D139" s="14">
+        <v>45992</v>
       </c>
       <c r="E139" s="10">
         <v>1301.1199999999999</v>
@@ -4372,7 +4368,7 @@
         <v>130.11199999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>4</v>
       </c>
@@ -4382,8 +4378,8 @@
       <c r="C140" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D140" s="3" t="s">
-        <v>151</v>
+      <c r="D140" s="14">
+        <v>45992</v>
       </c>
       <c r="E140" s="10">
         <v>1301.1199999999999</v>
@@ -4396,7 +4392,7 @@
         <v>130.11199999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>27</v>
       </c>
@@ -4406,8 +4402,8 @@
       <c r="C141" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>151</v>
+      <c r="D141" s="14">
+        <v>45992</v>
       </c>
       <c r="E141" s="10">
         <v>10827.67</v>
@@ -4420,7 +4416,7 @@
         <v>1082.7670000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>27</v>
       </c>
@@ -4430,8 +4426,8 @@
       <c r="C142" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>151</v>
+      <c r="D142" s="14">
+        <v>45992</v>
       </c>
       <c r="E142" s="10">
         <v>1972.89</v>
@@ -4444,7 +4440,7 @@
         <v>197.28900000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>31</v>
       </c>
@@ -4454,8 +4450,8 @@
       <c r="C143" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>151</v>
+      <c r="D143" s="14">
+        <v>45992</v>
       </c>
       <c r="E143" s="10">
         <v>6993.28</v>
@@ -4468,7 +4464,7 @@
         <v>559.4624</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>31</v>
       </c>
@@ -4478,8 +4474,8 @@
       <c r="C144" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D144" s="3" t="s">
-        <v>151</v>
+      <c r="D144" s="14">
+        <v>45992</v>
       </c>
       <c r="E144" s="10">
         <v>5920.64</v>
@@ -4492,7 +4488,7 @@
         <v>473.65120000000002</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>31</v>
       </c>
@@ -4502,8 +4498,8 @@
       <c r="C145" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>151</v>
+      <c r="D145" s="14">
+        <v>45992</v>
       </c>
       <c r="E145" s="10">
         <v>2229.7600000000002</v>
@@ -4516,7 +4512,7 @@
         <v>178.38080000000002</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>31</v>
       </c>
@@ -4526,8 +4522,8 @@
       <c r="C146" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>151</v>
+      <c r="D146" s="14">
+        <v>45992</v>
       </c>
       <c r="E146" s="10">
         <v>1454.72</v>
@@ -4540,7 +4536,7 @@
         <v>116.3776</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>31</v>
       </c>
@@ -4550,8 +4546,8 @@
       <c r="C147" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>151</v>
+      <c r="D147" s="14">
+        <v>45992</v>
       </c>
       <c r="E147" s="10">
         <v>1762.56</v>
@@ -4564,7 +4560,7 @@
         <v>141.00479999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>31</v>
       </c>
@@ -4574,8 +4570,8 @@
       <c r="C148" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>151</v>
+      <c r="D148" s="14">
+        <v>45992</v>
       </c>
       <c r="E148" s="10">
         <v>1858.14</v>
@@ -4588,7 +4584,7 @@
         <v>148.65120000000002</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>31</v>
       </c>
@@ -4598,8 +4594,8 @@
       <c r="C149" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D149" s="3" t="s">
-        <v>151</v>
+      <c r="D149" s="14">
+        <v>45992</v>
       </c>
       <c r="E149" s="10">
         <v>2284.8000000000002</v>
@@ -4612,7 +4608,7 @@
         <v>182.78400000000002</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>31</v>
       </c>
@@ -4622,8 +4618,8 @@
       <c r="C150" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>151</v>
+      <c r="D150" s="14">
+        <v>45992</v>
       </c>
       <c r="E150" s="10">
         <v>2589.44</v>
@@ -4636,7 +4632,7 @@
         <v>207.15520000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>31</v>
       </c>
@@ -4646,8 +4642,8 @@
       <c r="C151" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D151" s="3" t="s">
-        <v>151</v>
+      <c r="D151" s="14">
+        <v>45992</v>
       </c>
       <c r="E151" s="10">
         <v>3970.52</v>
@@ -4660,7 +4656,7 @@
         <v>317.64159999999998</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>31</v>
       </c>
@@ -4670,8 +4666,8 @@
       <c r="C152" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>151</v>
+      <c r="D152" s="14">
+        <v>45992</v>
       </c>
       <c r="E152" s="10">
         <v>1874.34</v>
@@ -4684,7 +4680,7 @@
         <v>149.94720000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>31</v>
       </c>
@@ -4694,8 +4690,8 @@
       <c r="C153" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D153" s="3" t="s">
-        <v>151</v>
+      <c r="D153" s="14">
+        <v>45992</v>
       </c>
       <c r="E153" s="10">
         <v>3972.24</v>
@@ -4708,7 +4704,7 @@
         <v>317.7792</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>31</v>
       </c>
@@ -4718,8 +4714,8 @@
       <c r="C154" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>151</v>
+      <c r="D154" s="14">
+        <v>45992</v>
       </c>
       <c r="E154" s="10">
         <v>673.86</v>
@@ -4732,7 +4728,7 @@
         <v>53.908799999999999</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>31</v>
       </c>
@@ -4742,8 +4738,8 @@
       <c r="C155" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>151</v>
+      <c r="D155" s="14">
+        <v>45992</v>
       </c>
       <c r="E155" s="10">
         <v>525.36</v>
@@ -4756,7 +4752,7 @@
         <v>42.028800000000004</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>31</v>
       </c>
@@ -4766,8 +4762,8 @@
       <c r="C156" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>151</v>
+      <c r="D156" s="14">
+        <v>45992</v>
       </c>
       <c r="E156" s="10">
         <v>1149.72</v>
@@ -4780,7 +4776,7 @@
         <v>91.97760000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>31</v>
       </c>
@@ -4790,8 +4786,8 @@
       <c r="C157" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>151</v>
+      <c r="D157" s="14">
+        <v>45992</v>
       </c>
       <c r="E157" s="10">
         <v>361.68</v>
@@ -4804,7 +4800,7 @@
         <v>28.9344</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>31</v>
       </c>
@@ -4814,8 +4810,8 @@
       <c r="C158" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>151</v>
+      <c r="D158" s="14">
+        <v>45992</v>
       </c>
       <c r="E158" s="10">
         <v>1538.46</v>
@@ -4828,7 +4824,7 @@
         <v>123.07680000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>31</v>
       </c>
@@ -4838,8 +4834,8 @@
       <c r="C159" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>151</v>
+      <c r="D159" s="14">
+        <v>45992</v>
       </c>
       <c r="E159" s="10">
         <v>1244.0999999999999</v>
@@ -4852,7 +4848,7 @@
         <v>99.527999999999992</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>31</v>
       </c>
@@ -4862,8 +4858,8 @@
       <c r="C160" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>151</v>
+      <c r="D160" s="14">
+        <v>45992</v>
       </c>
       <c r="E160" s="10">
         <v>221.29</v>
@@ -4876,7 +4872,7 @@
         <v>17.703199999999999</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>31</v>
       </c>
@@ -4886,8 +4882,8 @@
       <c r="C161" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>151</v>
+      <c r="D161" s="14">
+        <v>45992</v>
       </c>
       <c r="E161" s="10">
         <v>87.6</v>
@@ -4900,7 +4896,7 @@
         <v>7.008</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>31</v>
       </c>
@@ -4910,8 +4906,8 @@
       <c r="C162" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D162" s="3" t="s">
-        <v>151</v>
+      <c r="D162" s="14">
+        <v>45992</v>
       </c>
       <c r="E162" s="10">
         <v>354.99</v>
@@ -4924,7 +4920,7 @@
         <v>28.3992</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>31</v>
       </c>
@@ -4934,8 +4930,8 @@
       <c r="C163" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>151</v>
+      <c r="D163" s="14">
+        <v>45992</v>
       </c>
       <c r="E163" s="10">
         <v>272.02</v>
@@ -4948,7 +4944,7 @@
         <v>21.761599999999998</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>31</v>
       </c>
@@ -4958,8 +4954,8 @@
       <c r="C164" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D164" s="3" t="s">
-        <v>151</v>
+      <c r="D164" s="14">
+        <v>45992</v>
       </c>
       <c r="E164" s="10">
         <v>282.74</v>
@@ -4972,7 +4968,7 @@
         <v>22.619200000000003</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>31</v>
       </c>
@@ -4982,8 +4978,8 @@
       <c r="C165" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D165" s="3" t="s">
-        <v>151</v>
+      <c r="D165" s="14">
+        <v>45992</v>
       </c>
       <c r="E165" s="10">
         <v>357.3</v>
@@ -4996,7 +4992,7 @@
         <v>28.584000000000003</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>31</v>
       </c>
@@ -5006,8 +5002,8 @@
       <c r="C166" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>151</v>
+      <c r="D166" s="14">
+        <v>45992</v>
       </c>
       <c r="E166" s="10">
         <v>534.79</v>
@@ -5020,7 +5016,7 @@
         <v>42.783200000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>31</v>
       </c>
@@ -5030,8 +5026,8 @@
       <c r="C167" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>151</v>
+      <c r="D167" s="14">
+        <v>45992</v>
       </c>
       <c r="E167" s="10">
         <v>735.66</v>
@@ -5044,7 +5040,7 @@
         <v>58.852800000000002</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>31</v>
       </c>
@@ -5054,8 +5050,8 @@
       <c r="C168" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>151</v>
+      <c r="D168" s="14">
+        <v>45992</v>
       </c>
       <c r="E168" s="10">
         <v>1094.49</v>
@@ -5068,7 +5064,7 @@
         <v>87.559200000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>31</v>
       </c>
@@ -5078,8 +5074,8 @@
       <c r="C169" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>151</v>
+      <c r="D169" s="14">
+        <v>45992</v>
       </c>
       <c r="E169" s="10">
         <v>1009.19</v>
@@ -5092,7 +5088,7 @@
         <v>80.735200000000006</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>60</v>
       </c>
@@ -5102,8 +5098,8 @@
       <c r="C170" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>151</v>
+      <c r="D170" s="14">
+        <v>45992</v>
       </c>
       <c r="E170" s="10">
         <v>2281.6</v>
@@ -5116,7 +5112,7 @@
         <v>114.08</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>60</v>
       </c>
@@ -5124,10 +5120,10 @@
         <v>61</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
+      </c>
+      <c r="D171" s="14">
+        <v>45992</v>
       </c>
       <c r="E171" s="10">
         <v>4554.24</v>
@@ -5140,7 +5136,7 @@
         <v>227.71199999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>60</v>
       </c>
@@ -5150,8 +5146,8 @@
       <c r="C172" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>151</v>
+      <c r="D172" s="14">
+        <v>45992</v>
       </c>
       <c r="E172" s="10">
         <v>5114.88</v>
@@ -5164,7 +5160,7 @@
         <v>255.74400000000003</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>60</v>
       </c>
@@ -5174,8 +5170,8 @@
       <c r="C173" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>151</v>
+      <c r="D173" s="14">
+        <v>45992</v>
       </c>
       <c r="E173" s="10">
         <v>2676.7</v>
@@ -5188,7 +5184,7 @@
         <v>133.83500000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>60</v>
       </c>
@@ -5198,8 +5194,8 @@
       <c r="C174" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>151</v>
+      <c r="D174" s="14">
+        <v>45992</v>
       </c>
       <c r="E174" s="10">
         <v>3339.12</v>
@@ -5212,7 +5208,7 @@
         <v>166.95600000000002</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>60</v>
       </c>
@@ -5222,8 +5218,8 @@
       <c r="C175" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D175" s="3" t="s">
-        <v>151</v>
+      <c r="D175" s="14">
+        <v>45992</v>
       </c>
       <c r="E175" s="10">
         <v>2411.52</v>
@@ -5236,7 +5232,7 @@
         <v>120.57600000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>60</v>
       </c>
@@ -5246,8 +5242,8 @@
       <c r="C176" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D176" s="3" t="s">
-        <v>151</v>
+      <c r="D176" s="14">
+        <v>45992</v>
       </c>
       <c r="E176" s="10">
         <v>1457.28</v>
@@ -5260,7 +5256,7 @@
         <v>72.864000000000004</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>60</v>
       </c>
@@ -5270,8 +5266,8 @@
       <c r="C177" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D177" s="3" t="s">
-        <v>151</v>
+      <c r="D177" s="14">
+        <v>45992</v>
       </c>
       <c r="E177" s="10">
         <v>2136.3200000000002</v>
@@ -5284,7 +5280,7 @@
         <v>106.81600000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>60</v>
       </c>
@@ -5294,8 +5290,8 @@
       <c r="C178" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D178" s="3" t="s">
-        <v>151</v>
+      <c r="D178" s="14">
+        <v>45992</v>
       </c>
       <c r="E178" s="10">
         <v>2017.92</v>
@@ -5308,7 +5304,7 @@
         <v>100.89600000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>60</v>
       </c>
@@ -5318,8 +5314,8 @@
       <c r="C179" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D179" s="3" t="s">
-        <v>151</v>
+      <c r="D179" s="14">
+        <v>45992</v>
       </c>
       <c r="E179" s="10">
         <v>2946.45</v>
@@ -5332,7 +5328,7 @@
         <v>147.32249999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>60</v>
       </c>
@@ -5342,8 +5338,8 @@
       <c r="C180" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D180" s="3" t="s">
-        <v>151</v>
+      <c r="D180" s="14">
+        <v>45992</v>
       </c>
       <c r="E180" s="10">
         <v>3961.98</v>
@@ -5356,7 +5352,7 @@
         <v>198.09900000000002</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>60</v>
       </c>
@@ -5366,8 +5362,8 @@
       <c r="C181" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>151</v>
+      <c r="D181" s="14">
+        <v>45992</v>
       </c>
       <c r="E181" s="10">
         <v>5862.96</v>
@@ -5380,7 +5376,7 @@
         <v>293.14800000000002</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>60</v>
       </c>
@@ -5390,8 +5386,8 @@
       <c r="C182" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D182" s="3" t="s">
-        <v>151</v>
+      <c r="D182" s="14">
+        <v>45992</v>
       </c>
       <c r="E182" s="10">
         <v>11147.52</v>
@@ -5404,7 +5400,7 @@
         <v>557.37600000000009</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>60</v>
       </c>
@@ -5414,8 +5410,8 @@
       <c r="C183" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>151</v>
+      <c r="D183" s="14">
+        <v>45992</v>
       </c>
       <c r="E183" s="10">
         <v>4141.4399999999996</v>
@@ -5428,7 +5424,7 @@
         <v>207.072</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>60</v>
       </c>
@@ -5438,8 +5434,8 @@
       <c r="C184" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D184" s="3" t="s">
-        <v>151</v>
+      <c r="D184" s="14">
+        <v>45992</v>
       </c>
       <c r="E184" s="10">
         <v>9165.65</v>
@@ -5452,7 +5448,7 @@
         <v>458.28250000000003</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>60</v>
       </c>
@@ -5462,8 +5458,8 @@
       <c r="C185" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D185" s="3" t="s">
-        <v>151</v>
+      <c r="D185" s="14">
+        <v>45992</v>
       </c>
       <c r="E185" s="10">
         <v>3073.6</v>
@@ -5476,7 +5472,7 @@
         <v>153.68</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>60</v>
       </c>
@@ -5486,8 +5482,8 @@
       <c r="C186" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D186" s="3" t="s">
-        <v>151</v>
+      <c r="D186" s="14">
+        <v>45992</v>
       </c>
       <c r="E186" s="10">
         <v>1116.7</v>
@@ -5500,7 +5496,7 @@
         <v>55.835000000000008</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>60</v>
       </c>
@@ -5510,8 +5506,8 @@
       <c r="C187" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>151</v>
+      <c r="D187" s="14">
+        <v>45992</v>
       </c>
       <c r="E187" s="10">
         <v>606.72</v>
@@ -5524,7 +5520,7 @@
         <v>30.336000000000002</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>60</v>
       </c>
@@ -5534,8 +5530,8 @@
       <c r="C188" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D188" s="3" t="s">
-        <v>151</v>
+      <c r="D188" s="14">
+        <v>45992</v>
       </c>
       <c r="E188" s="10">
         <v>6490.25</v>
@@ -5548,7 +5544,7 @@
         <v>324.51250000000005</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>60</v>
       </c>
@@ -5558,8 +5554,8 @@
       <c r="C189" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>151</v>
+      <c r="D189" s="14">
+        <v>45992</v>
       </c>
       <c r="E189" s="10">
         <v>636.79999999999995</v>
@@ -5572,7 +5568,7 @@
         <v>31.84</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>60</v>
       </c>
@@ -5582,8 +5578,8 @@
       <c r="C190" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D190" s="3" t="s">
-        <v>151</v>
+      <c r="D190" s="14">
+        <v>45992</v>
       </c>
       <c r="E190" s="10">
         <v>5264</v>
@@ -5596,7 +5592,7 @@
         <v>263.2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>60</v>
       </c>
@@ -5606,8 +5602,8 @@
       <c r="C191" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D191" s="3" t="s">
-        <v>151</v>
+      <c r="D191" s="14">
+        <v>45992</v>
       </c>
       <c r="E191" s="10">
         <v>4232.32</v>
@@ -5620,7 +5616,7 @@
         <v>211.61599999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>60</v>
       </c>
@@ -5630,8 +5626,8 @@
       <c r="C192" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>151</v>
+      <c r="D192" s="14">
+        <v>45992</v>
       </c>
       <c r="E192" s="10">
         <v>727.04</v>
@@ -5644,7 +5640,7 @@
         <v>36.351999999999997</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>60</v>
       </c>
@@ -5654,8 +5650,8 @@
       <c r="C193" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D193" s="3" t="s">
-        <v>151</v>
+      <c r="D193" s="14">
+        <v>45992</v>
       </c>
       <c r="E193" s="10">
         <v>5751.04</v>
@@ -5668,7 +5664,7 @@
         <v>287.55200000000002</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>60</v>
       </c>
@@ -5678,8 +5674,8 @@
       <c r="C194" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D194" s="3" t="s">
-        <v>151</v>
+      <c r="D194" s="14">
+        <v>45992</v>
       </c>
       <c r="E194" s="10">
         <v>0</v>
@@ -5692,7 +5688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>60</v>
       </c>
@@ -5702,8 +5698,8 @@
       <c r="C195" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D195" s="3" t="s">
-        <v>151</v>
+      <c r="D195" s="14">
+        <v>45992</v>
       </c>
       <c r="E195" s="10">
         <v>856.32</v>
@@ -5716,7 +5712,7 @@
         <v>42.816000000000003</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>60</v>
       </c>
@@ -5726,8 +5722,8 @@
       <c r="C196" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>151</v>
+      <c r="D196" s="14">
+        <v>45992</v>
       </c>
       <c r="E196" s="10">
         <v>934.4</v>
@@ -5740,7 +5736,7 @@
         <v>46.72</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>60</v>
       </c>
@@ -5750,8 +5746,8 @@
       <c r="C197" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D197" s="3" t="s">
-        <v>151</v>
+      <c r="D197" s="14">
+        <v>45992</v>
       </c>
       <c r="E197" s="10">
         <v>5598.72</v>
@@ -5764,7 +5760,7 @@
         <v>279.93600000000004</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>60</v>
       </c>
@@ -5774,8 +5770,8 @@
       <c r="C198" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D198" s="3" t="s">
-        <v>151</v>
+      <c r="D198" s="14">
+        <v>45992</v>
       </c>
       <c r="E198" s="10">
         <v>4103.68</v>
@@ -5788,7 +5784,7 @@
         <v>205.18400000000003</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>60</v>
       </c>
@@ -5798,8 +5794,8 @@
       <c r="C199" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D199" s="3" t="s">
-        <v>151</v>
+      <c r="D199" s="14">
+        <v>45992</v>
       </c>
       <c r="E199" s="10">
         <v>7120.64</v>
@@ -5812,7 +5808,7 @@
         <v>356.03200000000004</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>99</v>
       </c>
@@ -5822,8 +5818,8 @@
       <c r="C200" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D200" s="3" t="s">
-        <v>151</v>
+      <c r="D200" s="14">
+        <v>45992</v>
       </c>
       <c r="E200" s="10">
         <v>4696.79</v>
@@ -5836,7 +5832,7 @@
         <v>469.67900000000003</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>99</v>
       </c>
@@ -5846,8 +5842,8 @@
       <c r="C201" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D201" s="3" t="s">
-        <v>151</v>
+      <c r="D201" s="14">
+        <v>45992</v>
       </c>
       <c r="E201" s="10">
         <v>250.92</v>
@@ -5860,7 +5856,7 @@
         <v>25.091999999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>99</v>
       </c>
@@ -5870,8 +5866,8 @@
       <c r="C202" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D202" s="3" t="s">
-        <v>151</v>
+      <c r="D202" s="14">
+        <v>45992</v>
       </c>
       <c r="E202" s="10">
         <v>2305.63</v>
@@ -5884,7 +5880,7 @@
         <v>230.56300000000002</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>99</v>
       </c>
@@ -5894,8 +5890,8 @@
       <c r="C203" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D203" s="3" t="s">
-        <v>151</v>
+      <c r="D203" s="14">
+        <v>45992</v>
       </c>
       <c r="E203" s="10">
         <v>349.38</v>
@@ -5908,7 +5904,7 @@
         <v>34.938000000000002</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>99</v>
       </c>
@@ -5918,8 +5914,8 @@
       <c r="C204" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D204" s="3" t="s">
-        <v>151</v>
+      <c r="D204" s="14">
+        <v>45992</v>
       </c>
       <c r="E204" s="10">
         <v>2183.7600000000002</v>
@@ -5932,7 +5928,7 @@
         <v>218.37600000000003</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>99</v>
       </c>
@@ -5942,8 +5938,8 @@
       <c r="C205" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D205" s="3" t="s">
-        <v>151</v>
+      <c r="D205" s="14">
+        <v>45992</v>
       </c>
       <c r="E205" s="10">
         <v>348.84</v>
@@ -5956,7 +5952,7 @@
         <v>34.884</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>99</v>
       </c>
@@ -5966,8 +5962,8 @@
       <c r="C206" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>151</v>
+      <c r="D206" s="14">
+        <v>45992</v>
       </c>
       <c r="E206" s="10">
         <v>0</v>
@@ -5980,7 +5976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>99</v>
       </c>
@@ -5990,8 +5986,8 @@
       <c r="C207" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D207" s="3" t="s">
-        <v>151</v>
+      <c r="D207" s="14">
+        <v>45992</v>
       </c>
       <c r="E207" s="10">
         <v>0</v>
@@ -6004,7 +6000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>99</v>
       </c>
@@ -6014,8 +6010,8 @@
       <c r="C208" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D208" s="3" t="s">
-        <v>151</v>
+      <c r="D208" s="14">
+        <v>45992</v>
       </c>
       <c r="E208" s="10">
         <v>1008.18</v>
@@ -6028,7 +6024,7 @@
         <v>100.818</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>99</v>
       </c>
@@ -6038,8 +6034,8 @@
       <c r="C209" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D209" s="3" t="s">
-        <v>151</v>
+      <c r="D209" s="14">
+        <v>45992</v>
       </c>
       <c r="E209" s="10">
         <v>753.3</v>
@@ -6052,7 +6048,7 @@
         <v>75.33</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>99</v>
       </c>
@@ -6062,8 +6058,8 @@
       <c r="C210" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D210" s="3" t="s">
-        <v>151</v>
+      <c r="D210" s="14">
+        <v>45992</v>
       </c>
       <c r="E210" s="10">
         <v>0</v>
@@ -6076,7 +6072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>99</v>
       </c>
@@ -6086,8 +6082,8 @@
       <c r="C211" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D211" s="3" t="s">
-        <v>151</v>
+      <c r="D211" s="14">
+        <v>45992</v>
       </c>
       <c r="E211" s="10">
         <v>0</v>
@@ -6100,7 +6096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>99</v>
       </c>
@@ -6110,8 +6106,8 @@
       <c r="C212" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D212" s="3" t="s">
-        <v>151</v>
+      <c r="D212" s="14">
+        <v>45992</v>
       </c>
       <c r="E212" s="10">
         <v>4191.4799999999996</v>
@@ -6124,7 +6120,7 @@
         <v>419.14799999999997</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>99</v>
       </c>
@@ -6134,8 +6130,8 @@
       <c r="C213" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D213" s="3" t="s">
-        <v>151</v>
+      <c r="D213" s="14">
+        <v>45992</v>
       </c>
       <c r="E213" s="10">
         <v>0</v>
@@ -6148,7 +6144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>99</v>
       </c>
@@ -6158,8 +6154,8 @@
       <c r="C214" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D214" s="3" t="s">
-        <v>151</v>
+      <c r="D214" s="14">
+        <v>45992</v>
       </c>
       <c r="E214" s="10">
         <v>1318.02</v>
@@ -6172,7 +6168,7 @@
         <v>131.80199999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>99</v>
       </c>
@@ -6182,8 +6178,8 @@
       <c r="C215" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D215" s="3" t="s">
-        <v>151</v>
+      <c r="D215" s="14">
+        <v>45992</v>
       </c>
       <c r="E215" s="10">
         <v>547.14</v>
@@ -6196,7 +6192,7 @@
         <v>54.713999999999999</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>99</v>
       </c>
@@ -6206,8 +6202,8 @@
       <c r="C216" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D216" s="3" t="s">
-        <v>151</v>
+      <c r="D216" s="14">
+        <v>45992</v>
       </c>
       <c r="E216" s="10">
         <v>5358.42</v>
@@ -6220,7 +6216,7 @@
         <v>535.84199999999998</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>99</v>
       </c>
@@ -6230,8 +6226,8 @@
       <c r="C217" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D217" s="3" t="s">
-        <v>151</v>
+      <c r="D217" s="14">
+        <v>45992</v>
       </c>
       <c r="E217" s="10">
         <v>13760.54</v>
@@ -6244,7 +6240,7 @@
         <v>1376.0540000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>99</v>
       </c>
@@ -6254,8 +6250,8 @@
       <c r="C218" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D218" s="3" t="s">
-        <v>151</v>
+      <c r="D218" s="14">
+        <v>45992</v>
       </c>
       <c r="E218" s="10">
         <v>359.04</v>
@@ -6268,7 +6264,7 @@
         <v>35.904000000000003</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>99</v>
       </c>
@@ -6278,8 +6274,8 @@
       <c r="C219" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D219" s="3" t="s">
-        <v>151</v>
+      <c r="D219" s="14">
+        <v>45992</v>
       </c>
       <c r="E219" s="10">
         <v>8692.35</v>
@@ -6292,7 +6288,7 @@
         <v>869.23500000000013</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>99</v>
       </c>
@@ -6302,8 +6298,8 @@
       <c r="C220" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D220" s="3" t="s">
-        <v>151</v>
+      <c r="D220" s="14">
+        <v>45992</v>
       </c>
       <c r="E220" s="10">
         <v>1257.0999999999999</v>
@@ -6316,7 +6312,7 @@
         <v>125.71</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>99</v>
       </c>
@@ -6326,8 +6322,8 @@
       <c r="C221" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D221" s="3" t="s">
-        <v>151</v>
+      <c r="D221" s="14">
+        <v>45992</v>
       </c>
       <c r="E221" s="10">
         <v>5552</v>
@@ -6340,7 +6336,7 @@
         <v>555.20000000000005</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>99</v>
       </c>
@@ -6350,8 +6346,8 @@
       <c r="C222" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D222" s="3" t="s">
-        <v>151</v>
+      <c r="D222" s="14">
+        <v>45992</v>
       </c>
       <c r="E222" s="10">
         <v>2752.64</v>
@@ -6364,7 +6360,7 @@
         <v>275.26400000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>99</v>
       </c>
@@ -6374,8 +6370,8 @@
       <c r="C223" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D223" s="3" t="s">
-        <v>151</v>
+      <c r="D223" s="14">
+        <v>45992</v>
       </c>
       <c r="E223" s="10">
         <v>4079.61</v>
@@ -6388,7 +6384,7 @@
         <v>407.96100000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>99</v>
       </c>
@@ -6398,8 +6394,8 @@
       <c r="C224" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D224" s="3" t="s">
-        <v>151</v>
+      <c r="D224" s="14">
+        <v>45992</v>
       </c>
       <c r="E224" s="10">
         <v>2874.88</v>
@@ -6412,7 +6408,7 @@
         <v>287.488</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>99</v>
       </c>
@@ -6422,8 +6418,8 @@
       <c r="C225" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D225" s="3" t="s">
-        <v>151</v>
+      <c r="D225" s="14">
+        <v>45992</v>
       </c>
       <c r="E225" s="10">
         <v>199.68</v>
@@ -6436,7 +6432,7 @@
         <v>19.968000000000004</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>99</v>
       </c>
@@ -6446,8 +6442,8 @@
       <c r="C226" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D226" s="3" t="s">
-        <v>151</v>
+      <c r="D226" s="14">
+        <v>45992</v>
       </c>
       <c r="E226" s="10">
         <v>3939.3</v>
@@ -6460,7 +6456,7 @@
         <v>393.93000000000006</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>99</v>
       </c>
@@ -6470,8 +6466,8 @@
       <c r="C227" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D227" s="3" t="s">
-        <v>151</v>
+      <c r="D227" s="14">
+        <v>45992</v>
       </c>
       <c r="E227" s="10">
         <v>3676.86</v>
@@ -6484,7 +6480,7 @@
         <v>367.68600000000004</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>129</v>
       </c>
@@ -6494,8 +6490,8 @@
       <c r="C228" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D228" s="3" t="s">
-        <v>151</v>
+      <c r="D228" s="14">
+        <v>45992</v>
       </c>
       <c r="E228" s="10">
         <v>1674.16</v>
@@ -6508,7 +6504,7 @@
         <v>167.41600000000003</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>129</v>
       </c>
@@ -6518,8 +6514,8 @@
       <c r="C229" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D229" s="3" t="s">
-        <v>151</v>
+      <c r="D229" s="14">
+        <v>45992</v>
       </c>
       <c r="E229" s="10">
         <v>4469.04</v>
@@ -6532,7 +6528,7 @@
         <v>446.904</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>129</v>
       </c>
@@ -6542,8 +6538,8 @@
       <c r="C230" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D230" s="3" t="s">
-        <v>151</v>
+      <c r="D230" s="14">
+        <v>45992</v>
       </c>
       <c r="E230" s="10">
         <v>212.52</v>
@@ -6556,7 +6552,7 @@
         <v>21.252000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>129</v>
       </c>
@@ -6566,8 +6562,8 @@
       <c r="C231" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>151</v>
+      <c r="D231" s="14">
+        <v>45992</v>
       </c>
       <c r="E231" s="10">
         <v>1724.76</v>
@@ -6580,7 +6576,7 @@
         <v>172.476</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>129</v>
       </c>
@@ -6590,8 +6586,8 @@
       <c r="C232" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D232" s="3" t="s">
-        <v>151</v>
+      <c r="D232" s="14">
+        <v>45992</v>
       </c>
       <c r="E232" s="10">
         <v>2077.38</v>
@@ -6604,7 +6600,7 @@
         <v>207.73800000000003</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>129</v>
       </c>
@@ -6614,8 +6610,8 @@
       <c r="C233" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>151</v>
+      <c r="D233" s="14">
+        <v>45992</v>
       </c>
       <c r="E233" s="10">
         <v>3666.56</v>
@@ -6628,7 +6624,7 @@
         <v>366.65600000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>129</v>
       </c>
@@ -6638,8 +6634,8 @@
       <c r="C234" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>151</v>
+      <c r="D234" s="14">
+        <v>45992</v>
       </c>
       <c r="E234" s="10">
         <v>0</v>
@@ -6652,7 +6648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>129</v>
       </c>
@@ -6662,8 +6658,8 @@
       <c r="C235" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D235" s="3" t="s">
-        <v>151</v>
+      <c r="D235" s="14">
+        <v>45992</v>
       </c>
       <c r="E235" s="10">
         <v>169.04</v>
@@ -6676,7 +6672,7 @@
         <v>16.904</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>129</v>
       </c>
@@ -6686,8 +6682,8 @@
       <c r="C236" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D236" s="3" t="s">
-        <v>151</v>
+      <c r="D236" s="14">
+        <v>45992</v>
       </c>
       <c r="E236" s="10">
         <v>3659.58</v>
@@ -6700,7 +6696,7 @@
         <v>365.95800000000003</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>129</v>
       </c>
@@ -6710,8 +6706,8 @@
       <c r="C237" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>151</v>
+      <c r="D237" s="14">
+        <v>45992</v>
       </c>
       <c r="E237" s="10">
         <v>6730.75</v>
@@ -6724,7 +6720,7 @@
         <v>673.07500000000005</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>141</v>
       </c>
@@ -6734,8 +6730,8 @@
       <c r="C238" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>151</v>
+      <c r="D238" s="14">
+        <v>45992</v>
       </c>
       <c r="E238" s="10">
         <v>2997.06</v>
@@ -6748,7 +6744,7 @@
         <v>299.70600000000002</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>141</v>
       </c>
@@ -6758,8 +6754,8 @@
       <c r="C239" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D239" s="3" t="s">
-        <v>151</v>
+      <c r="D239" s="14">
+        <v>45992</v>
       </c>
       <c r="E239" s="10">
         <v>6286.08</v>
@@ -6772,7 +6768,7 @@
         <v>628.60800000000006</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>141</v>
       </c>
@@ -6782,8 +6778,8 @@
       <c r="C240" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D240" s="3" t="s">
-        <v>151</v>
+      <c r="D240" s="14">
+        <v>45992</v>
       </c>
       <c r="E240" s="10">
         <v>2812.8</v>
@@ -6796,7 +6792,7 @@
         <v>281.28000000000003</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>141</v>
       </c>
@@ -6806,8 +6802,8 @@
       <c r="C241" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>151</v>
+      <c r="D241" s="14">
+        <v>45992</v>
       </c>
       <c r="E241" s="10">
         <v>8613.02</v>
@@ -6820,7 +6816,7 @@
         <v>861.30200000000013</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>141</v>
       </c>
@@ -6830,8 +6826,8 @@
       <c r="C242" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>151</v>
+      <c r="D242" s="14">
+        <v>45992</v>
       </c>
       <c r="E242" s="10">
         <v>3396.6</v>
@@ -6844,18 +6840,18 @@
         <v>339.66</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
+      </c>
+      <c r="D243" s="14">
+        <v>45992</v>
       </c>
       <c r="E243" s="10">
         <v>1936.44</v>
@@ -6868,18 +6864,18 @@
         <v>193.64400000000001</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
+      </c>
+      <c r="D244" s="14">
+        <v>45992</v>
       </c>
       <c r="E244" s="10">
         <v>0</v>
@@ -6892,18 +6888,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
+      </c>
+      <c r="D245" s="14">
+        <v>45992</v>
       </c>
       <c r="E245" s="10">
         <v>0</v>
@@ -6916,18 +6912,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
+      </c>
+      <c r="D246" s="14">
+        <v>45992</v>
       </c>
       <c r="E246" s="10">
         <v>3802.64</v>
@@ -6950,8 +6946,8 @@
       <c r="C247" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D247" s="3" t="s">
-        <v>187</v>
+      <c r="D247" s="14">
+        <v>46023</v>
       </c>
       <c r="E247" s="10">
         <v>718.9</v>
@@ -6974,8 +6970,8 @@
       <c r="C248" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>187</v>
+      <c r="D248" s="14">
+        <v>46023</v>
       </c>
       <c r="E248" s="10">
         <v>5054.72</v>
@@ -6998,8 +6994,8 @@
       <c r="C249" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>187</v>
+      <c r="D249" s="14">
+        <v>46023</v>
       </c>
       <c r="E249" s="10">
         <v>189.44</v>
@@ -7022,8 +7018,8 @@
       <c r="C250" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D250" s="3" t="s">
-        <v>187</v>
+      <c r="D250" s="14">
+        <v>46023</v>
       </c>
       <c r="E250" s="10">
         <v>6490.24</v>
@@ -7044,10 +7040,10 @@
         <v>11</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>187</v>
+        <v>151</v>
+      </c>
+      <c r="D251" s="14">
+        <v>46023</v>
       </c>
       <c r="E251" s="10">
         <v>16.899999999999999</v>
@@ -7070,8 +7066,8 @@
       <c r="C252" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D252" s="3" t="s">
-        <v>187</v>
+      <c r="D252" s="14">
+        <v>46023</v>
       </c>
       <c r="E252" s="10">
         <v>293.82</v>
@@ -7094,8 +7090,8 @@
       <c r="C253" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D253" s="3" t="s">
-        <v>187</v>
+      <c r="D253" s="14">
+        <v>46023</v>
       </c>
       <c r="E253" s="10">
         <v>2245.1</v>
@@ -7118,8 +7114,8 @@
       <c r="C254" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D254" s="3" t="s">
-        <v>187</v>
+      <c r="D254" s="14">
+        <v>46023</v>
       </c>
       <c r="E254" s="10">
         <v>1179.75</v>
@@ -7142,8 +7138,8 @@
       <c r="C255" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D255" s="3" t="s">
-        <v>187</v>
+      <c r="D255" s="14">
+        <v>46023</v>
       </c>
       <c r="E255" s="10">
         <v>107.52</v>
@@ -7166,8 +7162,8 @@
       <c r="C256" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D256" s="3" t="s">
-        <v>187</v>
+      <c r="D256" s="14">
+        <v>46023</v>
       </c>
       <c r="E256" s="10">
         <v>1865.5</v>
@@ -7190,8 +7186,8 @@
       <c r="C257" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D257" s="3" t="s">
-        <v>187</v>
+      <c r="D257" s="14">
+        <v>46023</v>
       </c>
       <c r="E257" s="10">
         <v>0</v>
@@ -7214,8 +7210,8 @@
       <c r="C258" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D258" s="3" t="s">
-        <v>187</v>
+      <c r="D258" s="14">
+        <v>46023</v>
       </c>
       <c r="E258" s="10">
         <v>5532.8</v>
@@ -7238,8 +7234,8 @@
       <c r="C259" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D259" s="3" t="s">
-        <v>187</v>
+      <c r="D259" s="14">
+        <v>46023</v>
       </c>
       <c r="E259" s="10">
         <v>5532.8</v>
@@ -7257,13 +7253,13 @@
         <v>4</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
+      </c>
+      <c r="D260" s="14">
+        <v>46023</v>
       </c>
       <c r="E260" s="10">
         <v>3222.03</v>
@@ -7281,13 +7277,13 @@
         <v>4</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D261" s="3" t="s">
-        <v>187</v>
+      <c r="D261" s="14">
+        <v>46023</v>
       </c>
       <c r="E261" s="10">
         <v>0</v>
@@ -7305,13 +7301,13 @@
         <v>4</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D262" s="3" t="s">
-        <v>187</v>
+      <c r="D262" s="14">
+        <v>46023</v>
       </c>
       <c r="E262" s="10">
         <v>0</v>
@@ -7334,8 +7330,8 @@
       <c r="C263" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D263" s="3" t="s">
-        <v>187</v>
+      <c r="D263" s="14">
+        <v>46023</v>
       </c>
       <c r="E263" s="10">
         <v>9835.1299999999992</v>
@@ -7356,10 +7352,10 @@
         <v>28</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D264" s="3" t="s">
         <v>187</v>
+      </c>
+      <c r="D264" s="14">
+        <v>46023</v>
       </c>
       <c r="E264" s="10">
         <v>1855.26</v>
@@ -7382,8 +7378,8 @@
       <c r="C265" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D265" s="3" t="s">
-        <v>187</v>
+      <c r="D265" s="14">
+        <v>46023</v>
       </c>
       <c r="E265" s="10">
         <v>7585.28</v>
@@ -7406,8 +7402,8 @@
       <c r="C266" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D266" s="3" t="s">
-        <v>187</v>
+      <c r="D266" s="14">
+        <v>46023</v>
       </c>
       <c r="E266" s="10">
         <v>7077.12</v>
@@ -7430,8 +7426,8 @@
       <c r="C267" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D267" s="3" t="s">
-        <v>187</v>
+      <c r="D267" s="14">
+        <v>46023</v>
       </c>
       <c r="E267" s="10">
         <v>2645.76</v>
@@ -7454,8 +7450,8 @@
       <c r="C268" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D268" s="3" t="s">
-        <v>187</v>
+      <c r="D268" s="14">
+        <v>46023</v>
       </c>
       <c r="E268" s="10">
         <v>1724.16</v>
@@ -7478,8 +7474,8 @@
       <c r="C269" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D269" s="3" t="s">
-        <v>187</v>
+      <c r="D269" s="14">
+        <v>46023</v>
       </c>
       <c r="E269" s="10">
         <v>1739.88</v>
@@ -7502,8 +7498,8 @@
       <c r="C270" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D270" s="3" t="s">
-        <v>187</v>
+      <c r="D270" s="14">
+        <v>46023</v>
       </c>
       <c r="E270" s="10">
         <v>2113.56</v>
@@ -7526,8 +7522,8 @@
       <c r="C271" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D271" s="3" t="s">
-        <v>187</v>
+      <c r="D271" s="14">
+        <v>46023</v>
       </c>
       <c r="E271" s="10">
         <v>2683.96</v>
@@ -7550,8 +7546,8 @@
       <c r="C272" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D272" s="3" t="s">
-        <v>187</v>
+      <c r="D272" s="14">
+        <v>46023</v>
       </c>
       <c r="E272" s="10">
         <v>2682.6</v>
@@ -7574,8 +7570,8 @@
       <c r="C273" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D273" s="3" t="s">
-        <v>187</v>
+      <c r="D273" s="14">
+        <v>46023</v>
       </c>
       <c r="E273" s="10">
         <v>4448.5600000000004</v>
@@ -7598,8 +7594,8 @@
       <c r="C274" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D274" s="3" t="s">
-        <v>187</v>
+      <c r="D274" s="14">
+        <v>46023</v>
       </c>
       <c r="E274" s="10">
         <v>2325.7800000000002</v>
@@ -7622,8 +7618,8 @@
       <c r="C275" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D275" s="3" t="s">
-        <v>187</v>
+      <c r="D275" s="14">
+        <v>46023</v>
       </c>
       <c r="E275" s="10">
         <v>0</v>
@@ -7646,8 +7642,8 @@
       <c r="C276" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D276" s="3" t="s">
-        <v>187</v>
+      <c r="D276" s="14">
+        <v>46023</v>
       </c>
       <c r="E276" s="10">
         <v>743.16</v>
@@ -7670,8 +7666,8 @@
       <c r="C277" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D277" s="3" t="s">
-        <v>187</v>
+      <c r="D277" s="14">
+        <v>46023</v>
       </c>
       <c r="E277" s="10">
         <v>349.8</v>
@@ -7694,8 +7690,8 @@
       <c r="C278" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D278" s="3" t="s">
-        <v>187</v>
+      <c r="D278" s="14">
+        <v>46023</v>
       </c>
       <c r="E278" s="10">
         <v>1247.54</v>
@@ -7718,8 +7714,8 @@
       <c r="C279" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D279" s="3" t="s">
-        <v>187</v>
+      <c r="D279" s="14">
+        <v>46023</v>
       </c>
       <c r="E279" s="10">
         <v>399.3</v>
@@ -7742,8 +7738,8 @@
       <c r="C280" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D280" s="3" t="s">
-        <v>187</v>
+      <c r="D280" s="14">
+        <v>46023</v>
       </c>
       <c r="E280" s="10">
         <v>1170.8399999999999</v>
@@ -7766,8 +7762,8 @@
       <c r="C281" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D281" s="3" t="s">
-        <v>187</v>
+      <c r="D281" s="14">
+        <v>46023</v>
       </c>
       <c r="E281" s="10">
         <v>1122.6600000000001</v>
@@ -7790,8 +7786,8 @@
       <c r="C282" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D282" s="3" t="s">
-        <v>187</v>
+      <c r="D282" s="14">
+        <v>46023</v>
       </c>
       <c r="E282" s="10">
         <v>228.69</v>
@@ -7814,8 +7810,8 @@
       <c r="C283" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D283" s="3" t="s">
-        <v>187</v>
+      <c r="D283" s="14">
+        <v>46023</v>
       </c>
       <c r="E283" s="10">
         <v>90.52</v>
@@ -7838,8 +7834,8 @@
       <c r="C284" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D284" s="3" t="s">
-        <v>187</v>
+      <c r="D284" s="14">
+        <v>46023</v>
       </c>
       <c r="E284" s="10">
         <v>366.49</v>
@@ -7862,8 +7858,8 @@
       <c r="C285" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D285" s="3" t="s">
-        <v>187</v>
+      <c r="D285" s="14">
+        <v>46023</v>
       </c>
       <c r="E285" s="10">
         <v>282.74</v>
@@ -7886,8 +7882,8 @@
       <c r="C286" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D286" s="3" t="s">
-        <v>187</v>
+      <c r="D286" s="14">
+        <v>46023</v>
       </c>
       <c r="E286" s="10">
         <v>260.63</v>
@@ -7910,8 +7906,8 @@
       <c r="C287" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D287" s="3" t="s">
-        <v>187</v>
+      <c r="D287" s="14">
+        <v>46023</v>
       </c>
       <c r="E287" s="10">
         <v>369.24</v>
@@ -7934,8 +7930,8 @@
       <c r="C288" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D288" s="3" t="s">
-        <v>187</v>
+      <c r="D288" s="14">
+        <v>46023</v>
       </c>
       <c r="E288" s="10">
         <v>552.66999999999996</v>
@@ -7958,8 +7954,8 @@
       <c r="C289" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D289" s="3" t="s">
-        <v>187</v>
+      <c r="D289" s="14">
+        <v>46023</v>
       </c>
       <c r="E289" s="10">
         <v>651.33000000000004</v>
@@ -7982,8 +7978,8 @@
       <c r="C290" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D290" s="3" t="s">
-        <v>187</v>
+      <c r="D290" s="14">
+        <v>46023</v>
       </c>
       <c r="E290" s="10">
         <v>1131.08</v>
@@ -8006,8 +8002,8 @@
       <c r="C291" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D291" s="3" t="s">
-        <v>187</v>
+      <c r="D291" s="14">
+        <v>46023</v>
       </c>
       <c r="E291" s="10">
         <v>950.39</v>
@@ -8030,8 +8026,8 @@
       <c r="C292" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D292" s="3" t="s">
-        <v>187</v>
+      <c r="D292" s="14">
+        <v>46023</v>
       </c>
       <c r="E292" s="10">
         <v>9944.32</v>
@@ -8052,10 +8048,10 @@
         <v>61</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>187</v>
+        <v>153</v>
+      </c>
+      <c r="D293" s="14">
+        <v>46023</v>
       </c>
       <c r="E293" s="10">
         <v>4992</v>
@@ -8078,8 +8074,8 @@
       <c r="C294" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D294" s="3" t="s">
-        <v>187</v>
+      <c r="D294" s="14">
+        <v>46023</v>
       </c>
       <c r="E294" s="10">
         <v>9592.9599999999991</v>
@@ -8102,8 +8098,8 @@
       <c r="C295" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D295" s="3" t="s">
-        <v>187</v>
+      <c r="D295" s="14">
+        <v>46023</v>
       </c>
       <c r="E295" s="10">
         <v>2715.7</v>
@@ -8126,8 +8122,8 @@
       <c r="C296" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D296" s="3" t="s">
-        <v>187</v>
+      <c r="D296" s="14">
+        <v>46023</v>
       </c>
       <c r="E296" s="10">
         <v>3280.64</v>
@@ -8150,8 +8146,8 @@
       <c r="C297" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D297" s="3" t="s">
-        <v>187</v>
+      <c r="D297" s="14">
+        <v>46023</v>
       </c>
       <c r="E297" s="10">
         <v>3918.08</v>
@@ -8174,8 +8170,8 @@
       <c r="C298" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D298" s="3" t="s">
-        <v>187</v>
+      <c r="D298" s="14">
+        <v>46023</v>
       </c>
       <c r="E298" s="10">
         <v>3026.56</v>
@@ -8198,8 +8194,8 @@
       <c r="C299" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D299" s="3" t="s">
-        <v>187</v>
+      <c r="D299" s="14">
+        <v>46023</v>
       </c>
       <c r="E299" s="10">
         <v>2875.52</v>
@@ -8222,8 +8218,8 @@
       <c r="C300" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D300" s="3" t="s">
-        <v>187</v>
+      <c r="D300" s="14">
+        <v>46023</v>
       </c>
       <c r="E300" s="10">
         <v>4040.84</v>
@@ -8246,8 +8242,8 @@
       <c r="C301" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D301" s="3" t="s">
-        <v>187</v>
+      <c r="D301" s="14">
+        <v>46023</v>
       </c>
       <c r="E301" s="10">
         <v>1638.65</v>
@@ -8270,8 +8266,8 @@
       <c r="C302" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D302" s="3" t="s">
-        <v>187</v>
+      <c r="D302" s="14">
+        <v>46023</v>
       </c>
       <c r="E302" s="10">
         <v>4709.76</v>
@@ -8294,8 +8290,8 @@
       <c r="C303" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D303" s="3" t="s">
-        <v>187</v>
+      <c r="D303" s="14">
+        <v>46023</v>
       </c>
       <c r="E303" s="10">
         <v>2125.0700000000002</v>
@@ -8318,8 +8314,8 @@
       <c r="C304" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D304" s="3" t="s">
-        <v>187</v>
+      <c r="D304" s="14">
+        <v>46023</v>
       </c>
       <c r="E304" s="10">
         <v>11772.8</v>
@@ -8342,8 +8338,8 @@
       <c r="C305" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D305" s="3" t="s">
-        <v>187</v>
+      <c r="D305" s="14">
+        <v>46023</v>
       </c>
       <c r="E305" s="10">
         <v>4799.3599999999997</v>
@@ -8366,8 +8362,8 @@
       <c r="C306" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D306" s="3" t="s">
-        <v>187</v>
+      <c r="D306" s="14">
+        <v>46023</v>
       </c>
       <c r="E306" s="10">
         <v>9351.5499999999993</v>
@@ -8390,8 +8386,8 @@
       <c r="C307" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D307" s="3" t="s">
-        <v>187</v>
+      <c r="D307" s="14">
+        <v>46023</v>
       </c>
       <c r="E307" s="10">
         <v>3016.59</v>
@@ -8414,8 +8410,8 @@
       <c r="C308" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D308" s="3" t="s">
-        <v>187</v>
+      <c r="D308" s="14">
+        <v>46023</v>
       </c>
       <c r="E308" s="10">
         <v>997.75</v>
@@ -8438,8 +8434,8 @@
       <c r="C309" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D309" s="3" t="s">
-        <v>187</v>
+      <c r="D309" s="14">
+        <v>46023</v>
       </c>
       <c r="E309" s="10">
         <v>577.28</v>
@@ -8462,8 +8458,8 @@
       <c r="C310" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D310" s="3" t="s">
-        <v>187</v>
+      <c r="D310" s="14">
+        <v>46023</v>
       </c>
       <c r="E310" s="10">
         <v>1985.1</v>
@@ -8486,8 +8482,8 @@
       <c r="C311" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D311" s="3" t="s">
-        <v>187</v>
+      <c r="D311" s="14">
+        <v>46023</v>
       </c>
       <c r="E311" s="10">
         <v>592</v>
@@ -8510,8 +8506,8 @@
       <c r="C312" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D312" s="3" t="s">
-        <v>187</v>
+      <c r="D312" s="14">
+        <v>46023</v>
       </c>
       <c r="E312" s="10">
         <v>5795.2</v>
@@ -8534,8 +8530,8 @@
       <c r="C313" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D313" s="3" t="s">
-        <v>187</v>
+      <c r="D313" s="14">
+        <v>46023</v>
       </c>
       <c r="E313" s="10">
         <v>4808.32</v>
@@ -8558,8 +8554,8 @@
       <c r="C314" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D314" s="3" t="s">
-        <v>187</v>
+      <c r="D314" s="14">
+        <v>46023</v>
       </c>
       <c r="E314" s="10">
         <v>748.8</v>
@@ -8582,8 +8578,8 @@
       <c r="C315" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D315" s="3" t="s">
-        <v>187</v>
+      <c r="D315" s="14">
+        <v>46023</v>
       </c>
       <c r="E315" s="10">
         <v>6457.6</v>
@@ -8606,8 +8602,8 @@
       <c r="C316" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D316" s="3" t="s">
-        <v>187</v>
+      <c r="D316" s="14">
+        <v>46023</v>
       </c>
       <c r="E316" s="10">
         <v>0</v>
@@ -8630,8 +8626,8 @@
       <c r="C317" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D317" s="3" t="s">
-        <v>187</v>
+      <c r="D317" s="14">
+        <v>46023</v>
       </c>
       <c r="E317" s="10">
         <v>975.86</v>
@@ -8654,8 +8650,8 @@
       <c r="C318" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D318" s="3" t="s">
-        <v>187</v>
+      <c r="D318" s="14">
+        <v>46023</v>
       </c>
       <c r="E318" s="10">
         <v>931.84</v>
@@ -8678,8 +8674,8 @@
       <c r="C319" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D319" s="3" t="s">
-        <v>187</v>
+      <c r="D319" s="14">
+        <v>46023</v>
       </c>
       <c r="E319" s="10">
         <v>6378.24</v>
@@ -8702,8 +8698,8 @@
       <c r="C320" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D320" s="3" t="s">
-        <v>187</v>
+      <c r="D320" s="14">
+        <v>46023</v>
       </c>
       <c r="E320" s="10">
         <v>4465.92</v>
@@ -8726,8 +8722,8 @@
       <c r="C321" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D321" s="3" t="s">
-        <v>187</v>
+      <c r="D321" s="14">
+        <v>46023</v>
       </c>
       <c r="E321" s="10">
         <v>8159.36</v>
@@ -8750,8 +8746,8 @@
       <c r="C322" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D322" s="3" t="s">
-        <v>187</v>
+      <c r="D322" s="14">
+        <v>46023</v>
       </c>
       <c r="E322" s="10">
         <v>5214.8100000000004</v>
@@ -8774,8 +8770,8 @@
       <c r="C323" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D323" s="3" t="s">
-        <v>187</v>
+      <c r="D323" s="14">
+        <v>46023</v>
       </c>
       <c r="E323" s="10">
         <v>278.8</v>
@@ -8798,8 +8794,8 @@
       <c r="C324" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D324" s="3" t="s">
-        <v>187</v>
+      <c r="D324" s="14">
+        <v>46023</v>
       </c>
       <c r="E324" s="10">
         <v>2493.21</v>
@@ -8822,8 +8818,8 @@
       <c r="C325" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D325" s="3" t="s">
-        <v>187</v>
+      <c r="D325" s="14">
+        <v>46023</v>
       </c>
       <c r="E325" s="10">
         <v>346.68</v>
@@ -8846,8 +8842,8 @@
       <c r="C326" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D326" s="3" t="s">
-        <v>187</v>
+      <c r="D326" s="14">
+        <v>46023</v>
       </c>
       <c r="E326" s="10">
         <v>1513.08</v>
@@ -8870,8 +8866,8 @@
       <c r="C327" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D327" s="3" t="s">
-        <v>187</v>
+      <c r="D327" s="14">
+        <v>46023</v>
       </c>
       <c r="E327" s="10">
         <v>478.44</v>
@@ -8894,8 +8890,8 @@
       <c r="C328" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D328" s="3" t="s">
-        <v>187</v>
+      <c r="D328" s="14">
+        <v>46023</v>
       </c>
       <c r="E328" s="10">
         <v>1092.42</v>
@@ -8918,8 +8914,8 @@
       <c r="C329" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D329" s="3" t="s">
-        <v>187</v>
+      <c r="D329" s="14">
+        <v>46023</v>
       </c>
       <c r="E329" s="10">
         <v>731.16</v>
@@ -8942,8 +8938,8 @@
       <c r="C330" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D330" s="3" t="s">
-        <v>187</v>
+      <c r="D330" s="14">
+        <v>46023</v>
       </c>
       <c r="E330" s="10">
         <v>4804.38</v>
@@ -8966,8 +8962,8 @@
       <c r="C331" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D331" s="3" t="s">
-        <v>187</v>
+      <c r="D331" s="14">
+        <v>46023</v>
       </c>
       <c r="E331" s="10">
         <v>1558.26</v>
@@ -8990,8 +8986,8 @@
       <c r="C332" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D332" s="3" t="s">
-        <v>187</v>
+      <c r="D332" s="14">
+        <v>46023</v>
       </c>
       <c r="E332" s="10">
         <v>668.58</v>
@@ -9014,8 +9010,8 @@
       <c r="C333" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D333" s="3" t="s">
-        <v>187</v>
+      <c r="D333" s="14">
+        <v>46023</v>
       </c>
       <c r="E333" s="10">
         <v>5931.9</v>
@@ -9038,8 +9034,8 @@
       <c r="C334" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D334" s="3" t="s">
-        <v>187</v>
+      <c r="D334" s="14">
+        <v>46023</v>
       </c>
       <c r="E334" s="10">
         <v>13848.45</v>
@@ -9062,8 +9058,8 @@
       <c r="C335" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D335" s="3" t="s">
-        <v>187</v>
+      <c r="D335" s="14">
+        <v>46023</v>
       </c>
       <c r="E335" s="10">
         <v>349.44</v>
@@ -9086,8 +9082,8 @@
       <c r="C336" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D336" s="3" t="s">
-        <v>187</v>
+      <c r="D336" s="14">
+        <v>46023</v>
       </c>
       <c r="E336" s="10">
         <v>4429.1899999999996</v>
@@ -9110,8 +9106,8 @@
       <c r="C337" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D337" s="3" t="s">
-        <v>187</v>
+      <c r="D337" s="14">
+        <v>46023</v>
       </c>
       <c r="E337" s="10">
         <v>2655.25</v>
@@ -9134,8 +9130,8 @@
       <c r="C338" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D338" s="3" t="s">
-        <v>187</v>
+      <c r="D338" s="14">
+        <v>46023</v>
       </c>
       <c r="E338" s="10">
         <v>11098.88</v>
@@ -9158,8 +9154,8 @@
       <c r="C339" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D339" s="3" t="s">
-        <v>187</v>
+      <c r="D339" s="14">
+        <v>46023</v>
       </c>
       <c r="E339" s="10">
         <v>7549.44</v>
@@ -9182,8 +9178,8 @@
       <c r="C340" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D340" s="3" t="s">
-        <v>187</v>
+      <c r="D340" s="14">
+        <v>46023</v>
       </c>
       <c r="E340" s="10">
         <v>4834.82</v>
@@ -9206,8 +9202,8 @@
       <c r="C341" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D341" s="3" t="s">
-        <v>187</v>
+      <c r="D341" s="14">
+        <v>46023</v>
       </c>
       <c r="E341" s="10">
         <v>4457.8100000000004</v>
@@ -9230,8 +9226,8 @@
       <c r="C342" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D342" s="3" t="s">
-        <v>187</v>
+      <c r="D342" s="14">
+        <v>46023</v>
       </c>
       <c r="E342" s="10">
         <v>229.12</v>
@@ -9254,8 +9250,8 @@
       <c r="C343" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D343" s="3" t="s">
-        <v>187</v>
+      <c r="D343" s="14">
+        <v>46023</v>
       </c>
       <c r="E343" s="10">
         <v>1365.12</v>
@@ -9278,8 +9274,8 @@
       <c r="C344" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D344" s="3" t="s">
-        <v>187</v>
+      <c r="D344" s="14">
+        <v>46023</v>
       </c>
       <c r="E344" s="10">
         <v>4877.28</v>
@@ -9302,8 +9298,8 @@
       <c r="C345" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D345" s="3" t="s">
-        <v>187</v>
+      <c r="D345" s="14">
+        <v>46023</v>
       </c>
       <c r="E345" s="10">
         <v>1555.85</v>
@@ -9326,8 +9322,8 @@
       <c r="C346" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D346" s="3" t="s">
-        <v>187</v>
+      <c r="D346" s="14">
+        <v>46023</v>
       </c>
       <c r="E346" s="10">
         <v>4855.1400000000003</v>
@@ -9350,8 +9346,8 @@
       <c r="C347" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D347" s="3" t="s">
-        <v>187</v>
+      <c r="D347" s="14">
+        <v>46023</v>
       </c>
       <c r="E347" s="10">
         <v>284.58</v>
@@ -9374,8 +9370,8 @@
       <c r="C348" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D348" s="3" t="s">
-        <v>187</v>
+      <c r="D348" s="14">
+        <v>46023</v>
       </c>
       <c r="E348" s="10">
         <v>10177.73</v>
@@ -9398,8 +9394,8 @@
       <c r="C349" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D349" s="3" t="s">
-        <v>187</v>
+      <c r="D349" s="14">
+        <v>46023</v>
       </c>
       <c r="E349" s="10">
         <v>2052</v>
@@ -9422,8 +9418,8 @@
       <c r="C350" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D350" s="3" t="s">
-        <v>187</v>
+      <c r="D350" s="14">
+        <v>46023</v>
       </c>
       <c r="E350" s="10">
         <v>9938.7000000000007</v>
@@ -9446,8 +9442,8 @@
       <c r="C351" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D351" s="3" t="s">
-        <v>187</v>
+      <c r="D351" s="14">
+        <v>46023</v>
       </c>
       <c r="E351" s="10">
         <v>193.08</v>
@@ -9470,8 +9466,8 @@
       <c r="C352" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D352" s="3" t="s">
-        <v>187</v>
+      <c r="D352" s="14">
+        <v>46023</v>
       </c>
       <c r="E352" s="10">
         <v>1579.52</v>
@@ -9494,8 +9490,8 @@
       <c r="C353" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D353" s="3" t="s">
-        <v>187</v>
+      <c r="D353" s="14">
+        <v>46023</v>
       </c>
       <c r="E353" s="10">
         <v>8942.0499999999993</v>
@@ -9518,8 +9514,8 @@
       <c r="C354" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D354" s="3" t="s">
-        <v>187</v>
+      <c r="D354" s="14">
+        <v>46023</v>
       </c>
       <c r="E354" s="10">
         <v>3041.28</v>
@@ -9542,8 +9538,8 @@
       <c r="C355" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D355" s="3" t="s">
-        <v>187</v>
+      <c r="D355" s="14">
+        <v>46023</v>
       </c>
       <c r="E355" s="10">
         <v>6325.76</v>
@@ -9566,8 +9562,8 @@
       <c r="C356" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D356" s="3" t="s">
-        <v>187</v>
+      <c r="D356" s="14">
+        <v>46023</v>
       </c>
       <c r="E356" s="10">
         <v>2908.8</v>
@@ -9590,8 +9586,8 @@
       <c r="C357" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D357" s="3" t="s">
-        <v>187</v>
+      <c r="D357" s="14">
+        <v>46023</v>
       </c>
       <c r="E357" s="10">
         <v>8320.0300000000007</v>
@@ -9612,10 +9608,10 @@
         <v>142</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D358" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="D358" s="14">
+        <v>46023</v>
       </c>
       <c r="E358" s="10">
         <v>5274.08</v>
@@ -9630,16 +9626,16 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D359" s="3" t="s">
-        <v>187</v>
+        <v>156</v>
+      </c>
+      <c r="D359" s="14">
+        <v>46023</v>
       </c>
       <c r="E359" s="10">
         <v>0</v>
@@ -9654,16 +9650,16 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D360" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
+      </c>
+      <c r="D360" s="14">
+        <v>46023</v>
       </c>
       <c r="E360" s="10">
         <v>1362.44</v>
@@ -9678,16 +9674,16 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D361" s="3" t="s">
-        <v>187</v>
+        <v>157</v>
+      </c>
+      <c r="D361" s="14">
+        <v>46023</v>
       </c>
       <c r="E361" s="10">
         <v>4779.0600000000004</v>
@@ -9702,16 +9698,16 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D362" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
+      </c>
+      <c r="D362" s="14">
+        <v>46023</v>
       </c>
       <c r="E362" s="10">
         <v>2309.5</v>
@@ -9726,16 +9722,16 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D363" s="3" t="s">
-        <v>187</v>
+        <v>159</v>
+      </c>
+      <c r="D363" s="14">
+        <v>46023</v>
       </c>
       <c r="E363" s="10">
         <v>4280.76</v>
@@ -9749,13 +9745,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G363" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="JANEIRO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G363" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
@@ -9778,42 +9768,42 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E2" s="12">
         <v>625.29999999999995</v>
@@ -9832,16 +9822,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E3" s="12">
         <v>4282.24</v>
@@ -9861,16 +9851,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4" s="12">
         <v>170.24</v>
@@ -9889,16 +9879,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="12">
         <v>4209.28</v>
@@ -9917,16 +9907,16 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="12">
         <v>16.899999999999999</v>
@@ -9945,16 +9935,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E7" s="12">
         <v>103.9</v>
@@ -9973,16 +9963,16 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E8" s="12">
         <v>2209.35</v>
@@ -10001,16 +9991,16 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>177</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E9" s="12">
         <v>216.45</v>
@@ -10029,16 +10019,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E10" s="12">
         <v>182.4</v>
@@ -10057,16 +10047,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" s="12">
         <v>1202.5</v>
@@ -10085,16 +10075,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
@@ -10106,21 +10096,21 @@
         <v>0</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E13" s="13">
         <v>0</v>
@@ -10132,21 +10122,21 @@
         <v>0</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E14" s="12">
         <v>1301.1199999999999</v>
@@ -10165,16 +10155,16 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E15" s="12">
         <v>1301.1199999999999</v>
@@ -10193,16 +10183,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E16" s="12">
         <v>3385.3</v>
@@ -10224,13 +10214,13 @@
         <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>143</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="12">
         <v>2997.06</v>
@@ -10252,13 +10242,13 @@
         <v>142</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E18" s="12">
         <v>9098.8799999999992</v>
@@ -10280,13 +10270,13 @@
         <v>142</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>146</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E19" s="12">
         <v>8613.02</v>
@@ -10308,13 +10298,13 @@
         <v>142</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>147</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E20" s="12">
         <v>3396.6</v>

--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0DB018C-28A0-4B66-BF42-3206F6CDF863}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBB36703-CEBD-40D7-9152-E3B93D518BEC}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="-1815" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26220" yWindow="180" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="197">
   <si>
     <t>Gerador</t>
   </si>
@@ -615,6 +615,21 @@
   </si>
   <si>
     <t>FATURAMENTO</t>
+  </si>
+  <si>
+    <t>REG ALIM| ANT. CAMÂRA 1</t>
+  </si>
+  <si>
+    <t>PRP BELTÃO</t>
+  </si>
+  <si>
+    <t>PROENGENHARIA</t>
+  </si>
+  <si>
+    <t>EMÍLIO RIBAS - B. STUDART, 722</t>
+  </si>
+  <si>
+    <t>EMÍLIO RIBAS - ITAIÇABA, 95</t>
   </si>
 </sst>
 </file>
@@ -626,7 +641,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,6 +660,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -683,7 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -717,6 +739,7 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1026,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G363"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -7988,7 +8011,7 @@
         <v>0.08</v>
       </c>
       <c r="G290" s="10">
-        <f t="shared" ref="G290:G363" si="8">E290*F290</f>
+        <f t="shared" ref="G290:G480" si="8">E290*F290</f>
         <v>90.486399999999989</v>
       </c>
     </row>
@@ -9742,6 +9765,2812 @@
       <c r="G363" s="10">
         <f t="shared" si="8"/>
         <v>428.07600000000002</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A364" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D364" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E364" s="2">
+        <v>626.6</v>
+      </c>
+      <c r="F364" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G364" s="2">
+        <f t="shared" si="8"/>
+        <v>62.660000000000004</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A365" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D365" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E365" s="2">
+        <v>4315.5200000000004</v>
+      </c>
+      <c r="F365" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G365" s="2">
+        <f t="shared" si="8"/>
+        <v>431.55200000000008</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A366" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D366" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E366" s="2">
+        <v>5454.08</v>
+      </c>
+      <c r="F366" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G366" s="2">
+        <f t="shared" si="8"/>
+        <v>545.40800000000002</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A367" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D367" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E367" s="2">
+        <v>184.32</v>
+      </c>
+      <c r="F367" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G367" s="2">
+        <f t="shared" si="8"/>
+        <v>18.431999999999999</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A368" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D368" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E368" s="2">
+        <v>174.72</v>
+      </c>
+      <c r="F368" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G368" s="2">
+        <f t="shared" si="8"/>
+        <v>17.472000000000001</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A369" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D369" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E369" s="2">
+        <v>127.64</v>
+      </c>
+      <c r="F369" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G369" s="2">
+        <f t="shared" si="8"/>
+        <v>12.764000000000001</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A370" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D370" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E370" s="2">
+        <v>2487.5500000000002</v>
+      </c>
+      <c r="F370" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G370" s="2">
+        <f t="shared" si="8"/>
+        <v>248.75500000000002</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A371" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D371" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E371" s="2">
+        <v>361.4</v>
+      </c>
+      <c r="F371" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G371" s="2">
+        <f t="shared" si="8"/>
+        <v>36.14</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A372" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D372" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E372" s="2">
+        <v>192.64</v>
+      </c>
+      <c r="F372" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G372" s="2">
+        <f t="shared" si="8"/>
+        <v>19.263999999999999</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A373" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D373" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E373" s="2">
+        <v>1267.5</v>
+      </c>
+      <c r="F373" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G373" s="2">
+        <f t="shared" si="8"/>
+        <v>126.75</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A374" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D374" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E374" s="2">
+        <v>755.52</v>
+      </c>
+      <c r="F374" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G374" s="2">
+        <f t="shared" si="8"/>
+        <v>75.552000000000007</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A375" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D375" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E375" s="2">
+        <v>755.52</v>
+      </c>
+      <c r="F375" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G375" s="2">
+        <f t="shared" si="8"/>
+        <v>75.552000000000007</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A376" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D376" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E376" s="2">
+        <v>3357.01</v>
+      </c>
+      <c r="F376" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G376" s="2">
+        <f t="shared" si="8"/>
+        <v>335.70100000000002</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A377" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D377" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E377" s="2">
+        <v>0</v>
+      </c>
+      <c r="F377" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G377" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A378" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D378" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E378" s="2">
+        <v>0</v>
+      </c>
+      <c r="F378" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G378" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A379" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D379" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E379" s="2">
+        <v>10079.08</v>
+      </c>
+      <c r="F379" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G379" s="2">
+        <f t="shared" si="8"/>
+        <v>1007.908</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A380" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D380" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E380" s="2">
+        <v>1901.28</v>
+      </c>
+      <c r="F380" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G380" s="2">
+        <f t="shared" si="8"/>
+        <v>190.12800000000001</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A381" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D381" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E381" s="2">
+        <v>6842.88</v>
+      </c>
+      <c r="F381" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G381" s="2">
+        <f t="shared" si="8"/>
+        <v>547.43039999999996</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A382" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D382" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E382" s="2">
+        <v>6220.16</v>
+      </c>
+      <c r="F382" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G382" s="2">
+        <f t="shared" si="8"/>
+        <v>497.61279999999999</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A383" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D383" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E383" s="2">
+        <v>2459.52</v>
+      </c>
+      <c r="F383" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G383" s="2">
+        <f t="shared" si="8"/>
+        <v>196.76160000000002</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A384" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D384" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E384" s="2">
+        <v>1810.56</v>
+      </c>
+      <c r="F384" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G384" s="2">
+        <f t="shared" si="8"/>
+        <v>144.84479999999999</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A385" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D385" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E385" s="2">
+        <v>1495.31</v>
+      </c>
+      <c r="F385" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G385" s="2">
+        <f t="shared" si="8"/>
+        <v>119.62479999999999</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A386" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D386" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E386" s="2">
+        <v>1866.24</v>
+      </c>
+      <c r="F386" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G386" s="2">
+        <f t="shared" si="8"/>
+        <v>149.29920000000001</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A387" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D387" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E387" s="2">
+        <v>2345.3200000000002</v>
+      </c>
+      <c r="F387" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G387" s="2">
+        <f t="shared" si="8"/>
+        <v>187.62560000000002</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A388" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D388" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E388" s="2">
+        <v>2425.56</v>
+      </c>
+      <c r="F388" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G388" s="2">
+        <f t="shared" si="8"/>
+        <v>194.04480000000001</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A389" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D389" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E389" s="2">
+        <v>4287.3999999999996</v>
+      </c>
+      <c r="F389" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G389" s="2">
+        <f t="shared" si="8"/>
+        <v>342.99199999999996</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A390" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D390" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E390" s="2">
+        <v>1947.38</v>
+      </c>
+      <c r="F390" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G390" s="2">
+        <f t="shared" si="8"/>
+        <v>155.79040000000001</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A391" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D391" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E391" s="2">
+        <v>3093.66</v>
+      </c>
+      <c r="F391" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G391" s="2">
+        <f t="shared" si="8"/>
+        <v>247.49279999999999</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A392" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D392" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E392" s="2">
+        <v>685.08</v>
+      </c>
+      <c r="F392" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G392" s="2">
+        <f t="shared" si="8"/>
+        <v>54.806400000000004</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A393" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D393" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E393" s="2">
+        <v>497.64</v>
+      </c>
+      <c r="F393" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G393" s="2">
+        <f t="shared" si="8"/>
+        <v>39.811199999999999</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A394" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D394" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E394" s="2">
+        <v>1008.35</v>
+      </c>
+      <c r="F394" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G394" s="2">
+        <f t="shared" si="8"/>
+        <v>80.668000000000006</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A395" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D395" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E395" s="2">
+        <v>318.77999999999997</v>
+      </c>
+      <c r="F395" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G395" s="2">
+        <f t="shared" si="8"/>
+        <v>25.502399999999998</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A396" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D396" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E396" s="2">
+        <v>1603.8</v>
+      </c>
+      <c r="F396" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G396" s="2">
+        <f t="shared" si="8"/>
+        <v>128.304</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A397" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D397" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E397" s="2">
+        <v>1215.06</v>
+      </c>
+      <c r="F397" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G397" s="2">
+        <f t="shared" si="8"/>
+        <v>97.204799999999992</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A398" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D398" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E398" s="2">
+        <v>199.81</v>
+      </c>
+      <c r="F398" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G398" s="2">
+        <f t="shared" si="8"/>
+        <v>15.9848</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A399" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D399" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E399" s="2">
+        <v>79.09</v>
+      </c>
+      <c r="F399" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G399" s="2">
+        <f t="shared" si="8"/>
+        <v>6.3272000000000004</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A400" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D400" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E400" s="2">
+        <v>320.89999999999998</v>
+      </c>
+      <c r="F400" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G400" s="2">
+        <f t="shared" si="8"/>
+        <v>25.671999999999997</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A401" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D401" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E401" s="2">
+        <v>274.02999999999997</v>
+      </c>
+      <c r="F401" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G401" s="2">
+        <f t="shared" si="8"/>
+        <v>21.9224</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A402" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B402" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D402" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E402" s="2">
+        <v>229.14</v>
+      </c>
+      <c r="F402" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G402" s="2">
+        <f t="shared" si="8"/>
+        <v>18.331199999999999</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A403" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D403" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E403" s="2">
+        <v>322.61</v>
+      </c>
+      <c r="F403" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G403" s="2">
+        <f t="shared" si="8"/>
+        <v>25.808800000000002</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A404" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C404" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D404" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E404" s="2">
+        <v>482.88</v>
+      </c>
+      <c r="F404" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G404" s="2">
+        <f t="shared" si="8"/>
+        <v>38.630400000000002</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A405" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B405" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C405" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D405" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E405" s="2">
+        <v>410.03</v>
+      </c>
+      <c r="F405" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G405" s="2">
+        <f t="shared" si="8"/>
+        <v>32.802399999999999</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A406" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D406" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E406" s="2">
+        <v>988.24</v>
+      </c>
+      <c r="F406" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G406" s="2">
+        <f t="shared" si="8"/>
+        <v>79.059200000000004</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A407" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D407" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E407" s="2">
+        <v>830.37</v>
+      </c>
+      <c r="F407" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G407" s="2">
+        <f t="shared" si="8"/>
+        <v>66.429600000000008</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A408" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B408" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C408" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D408" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E408" s="2">
+        <v>1961.6</v>
+      </c>
+      <c r="F408" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G408" s="2">
+        <f t="shared" si="8"/>
+        <v>98.08</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A409" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D409" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E409" s="2">
+        <v>4604.16</v>
+      </c>
+      <c r="F409" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G409" s="2">
+        <f t="shared" si="8"/>
+        <v>230.208</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D410" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E410" s="2">
+        <v>5347.84</v>
+      </c>
+      <c r="F410" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G410" s="2">
+        <f t="shared" si="8"/>
+        <v>267.392</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A411" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D411" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E411" s="2">
+        <v>2611.0500000000002</v>
+      </c>
+      <c r="F411" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G411" s="2">
+        <f t="shared" si="8"/>
+        <v>130.55250000000001</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A412" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D412" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E412" s="2">
+        <v>3539.84</v>
+      </c>
+      <c r="F412" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G412" s="2">
+        <f t="shared" si="8"/>
+        <v>176.99200000000002</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A413" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D413" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E413" s="2">
+        <v>6405.12</v>
+      </c>
+      <c r="F413" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G413" s="2">
+        <f t="shared" si="8"/>
+        <v>320.25600000000003</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A414" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D414" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E414" s="2">
+        <v>1567.36</v>
+      </c>
+      <c r="F414" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G414" s="2">
+        <f t="shared" si="8"/>
+        <v>78.367999999999995</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A415" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D415" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E415" s="2">
+        <v>2112.64</v>
+      </c>
+      <c r="F415" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G415" s="2">
+        <f t="shared" si="8"/>
+        <v>105.63200000000001</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A416" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D416" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E416" s="2">
+        <v>2399.36</v>
+      </c>
+      <c r="F416" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G416" s="2">
+        <f t="shared" si="8"/>
+        <v>119.96800000000002</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D417" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E417" s="2">
+        <v>2827.5</v>
+      </c>
+      <c r="F417" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G417" s="2">
+        <f t="shared" si="8"/>
+        <v>141.375</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D418" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E418" s="2">
+        <v>4155.3599999999997</v>
+      </c>
+      <c r="F418" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G418" s="2">
+        <f t="shared" si="8"/>
+        <v>207.768</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D419" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E419" s="2">
+        <v>7307.47</v>
+      </c>
+      <c r="F419" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G419" s="2">
+        <f t="shared" si="8"/>
+        <v>365.37350000000004</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D420" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E420" s="2">
+        <v>11358.39</v>
+      </c>
+      <c r="F420" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G420" s="2">
+        <f t="shared" si="8"/>
+        <v>567.91949999999997</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A421" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B421" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C421" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D421" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E421" s="2">
+        <v>5845.76</v>
+      </c>
+      <c r="F421" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G421" s="2">
+        <f t="shared" si="8"/>
+        <v>292.28800000000001</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A422" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B422" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D422" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E422" s="2">
+        <v>8762</v>
+      </c>
+      <c r="F422" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G422" s="2">
+        <f t="shared" si="8"/>
+        <v>438.1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A423" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B423" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D423" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E423" s="2">
+        <v>2979.86</v>
+      </c>
+      <c r="F423" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G423" s="2">
+        <f t="shared" si="8"/>
+        <v>148.99300000000002</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A424" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B424" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D424" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E424" s="2">
+        <v>786.5</v>
+      </c>
+      <c r="F424" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G424" s="2">
+        <f t="shared" si="8"/>
+        <v>39.325000000000003</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A425" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D425" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E425" s="2">
+        <v>570.24</v>
+      </c>
+      <c r="F425" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G425" s="2">
+        <f t="shared" si="8"/>
+        <v>28.512</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A426" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B426" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C426" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D426" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E426" s="2">
+        <v>6068.4</v>
+      </c>
+      <c r="F426" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G426" s="2">
+        <f t="shared" si="8"/>
+        <v>303.42</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A427" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D427" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E427" s="2">
+        <v>387.84</v>
+      </c>
+      <c r="F427" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G427" s="2">
+        <f t="shared" si="8"/>
+        <v>19.391999999999999</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A428" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D428" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E428" s="2">
+        <v>4712.32</v>
+      </c>
+      <c r="F428" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G428" s="2">
+        <f t="shared" si="8"/>
+        <v>235.61599999999999</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A429" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D429" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E429" s="2">
+        <v>1905.92</v>
+      </c>
+      <c r="F429" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G429" s="2">
+        <f t="shared" si="8"/>
+        <v>95.296000000000006</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A430" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D430" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E430" s="2">
+        <v>0</v>
+      </c>
+      <c r="F430" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G430" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A431" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B431" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D431" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E431" s="2">
+        <v>6552.32</v>
+      </c>
+      <c r="F431" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G431" s="2">
+        <f t="shared" si="8"/>
+        <v>327.61599999999999</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A432" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B432" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D432" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E432" s="2">
+        <v>0</v>
+      </c>
+      <c r="F432" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G432" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A433" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D433" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E433" s="2">
+        <v>1137.92</v>
+      </c>
+      <c r="F433" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G433" s="2">
+        <f t="shared" si="8"/>
+        <v>56.896000000000008</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A434" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D434" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E434" s="2">
+        <v>922.88</v>
+      </c>
+      <c r="F434" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G434" s="2">
+        <f t="shared" si="8"/>
+        <v>46.144000000000005</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A435" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D435" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E435" s="2">
+        <v>5616.64</v>
+      </c>
+      <c r="F435" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G435" s="2">
+        <f t="shared" si="8"/>
+        <v>280.83200000000005</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A436" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D436" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E436" s="2">
+        <v>4409.6000000000004</v>
+      </c>
+      <c r="F436" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G436" s="2">
+        <f t="shared" si="8"/>
+        <v>220.48000000000002</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A437" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D437" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E437" s="2">
+        <v>7367.68</v>
+      </c>
+      <c r="F437" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G437" s="2">
+        <f t="shared" si="8"/>
+        <v>368.38400000000001</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A438" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D438" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E438" s="2">
+        <v>5273.88</v>
+      </c>
+      <c r="F438" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G438" s="2">
+        <f t="shared" si="8"/>
+        <v>421.91040000000004</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A439" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D439" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E439" s="2">
+        <v>270.64</v>
+      </c>
+      <c r="F439" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G439" s="2">
+        <f t="shared" si="8"/>
+        <v>21.651199999999999</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A440" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D440" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E440" s="2">
+        <v>313.2</v>
+      </c>
+      <c r="F440" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G440" s="2">
+        <f t="shared" si="8"/>
+        <v>25.056000000000001</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A441" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D441" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E441" s="15">
+        <v>1618.92</v>
+      </c>
+      <c r="F441" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G441" s="15">
+        <v>250.56</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A442" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D442" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E442" s="15">
+        <v>331.56</v>
+      </c>
+      <c r="F442" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G442" s="15">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A443" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C443" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D443" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E443" s="2">
+        <v>960.12</v>
+      </c>
+      <c r="F443" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G443" s="2">
+        <f t="shared" si="8"/>
+        <v>76.809600000000003</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A444" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C444" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D444" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E444" s="2">
+        <v>1138.5</v>
+      </c>
+      <c r="F444" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G444" s="2">
+        <f t="shared" si="8"/>
+        <v>91.08</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A445" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D445" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E445" s="2">
+        <v>4310.28</v>
+      </c>
+      <c r="F445" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G445" s="2">
+        <f t="shared" si="8"/>
+        <v>344.82239999999996</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A446" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B446" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D446" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E446" s="2">
+        <v>1353.66</v>
+      </c>
+      <c r="F446" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G446" s="2">
+        <f t="shared" si="8"/>
+        <v>108.29280000000001</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A447" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D447" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E447" s="2">
+        <v>604.55999999999995</v>
+      </c>
+      <c r="F447" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G447" s="2">
+        <f t="shared" si="8"/>
+        <v>48.364799999999995</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A448" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D448" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E448" s="2">
+        <v>6772.89</v>
+      </c>
+      <c r="F448" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G448" s="2">
+        <f t="shared" si="8"/>
+        <v>541.83120000000008</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A449" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D449" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E449" s="2">
+        <v>13658.21</v>
+      </c>
+      <c r="F449" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G449" s="2">
+        <f t="shared" si="8"/>
+        <v>1092.6568</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A450" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D450" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E450" s="2">
+        <v>349.44</v>
+      </c>
+      <c r="F450" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G450" s="2">
+        <f t="shared" si="8"/>
+        <v>27.955200000000001</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A451" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D451" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E451" s="2">
+        <v>8040.41</v>
+      </c>
+      <c r="F451" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G451" s="2">
+        <f t="shared" si="8"/>
+        <v>643.2328</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A452" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B452" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D452" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E452" s="2">
+        <v>3814.85</v>
+      </c>
+      <c r="F452" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G452" s="2">
+        <f t="shared" si="8"/>
+        <v>305.18799999999999</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A453" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B453" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D453" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E453" s="2">
+        <v>6478.72</v>
+      </c>
+      <c r="F453" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G453" s="2">
+        <f t="shared" si="8"/>
+        <v>518.29759999999999</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A454" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B454" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D454" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E454" s="2">
+        <v>3061.76</v>
+      </c>
+      <c r="F454" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G454" s="2">
+        <f t="shared" si="8"/>
+        <v>244.94080000000002</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A455" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B455" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D455" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E455" s="2">
+        <v>787.78</v>
+      </c>
+      <c r="F455" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G455" s="2">
+        <f t="shared" si="8"/>
+        <v>63.022399999999998</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A456" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D456" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E456" s="2">
+        <v>1643.57</v>
+      </c>
+      <c r="F456" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G456" s="2">
+        <f t="shared" si="8"/>
+        <v>131.48560000000001</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A457" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D457" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E457" s="2">
+        <v>231.04</v>
+      </c>
+      <c r="F457" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G457" s="2">
+        <f t="shared" si="8"/>
+        <v>18.4832</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A458" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B458" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D458" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E458" s="2">
+        <v>1409.94</v>
+      </c>
+      <c r="F458" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G458" s="2">
+        <f t="shared" si="8"/>
+        <v>112.79520000000001</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A459" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B459" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D459" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E459" s="2">
+        <v>3066.66</v>
+      </c>
+      <c r="F459" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G459" s="2">
+        <f t="shared" si="8"/>
+        <v>245.33279999999999</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A460" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B460" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D460" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E460" s="2">
+        <v>1352.16</v>
+      </c>
+      <c r="F460" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G460" s="2">
+        <f t="shared" si="8"/>
+        <v>135.21600000000001</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A461" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D461" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E461" s="2">
+        <v>4244.3999999999996</v>
+      </c>
+      <c r="F461" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G461" s="2">
+        <f t="shared" si="8"/>
+        <v>424.44</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A462" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B462" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D462" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E462" s="2">
+        <v>146.19</v>
+      </c>
+      <c r="F462" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G462" s="2">
+        <f t="shared" si="8"/>
+        <v>14.619</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A463" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B463" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D463" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E463" s="2">
+        <v>1091.3399999999999</v>
+      </c>
+      <c r="F463" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G463" s="2">
+        <f t="shared" si="8"/>
+        <v>109.134</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A464" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B464" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D464" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E464" s="2">
+        <v>2074.6799999999998</v>
+      </c>
+      <c r="F464" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G464" s="2">
+        <f t="shared" si="8"/>
+        <v>207.46799999999999</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A465" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B465" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D465" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E465" s="2">
+        <v>3632.58</v>
+      </c>
+      <c r="F465" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G465" s="2">
+        <f t="shared" si="8"/>
+        <v>363.25800000000004</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A466" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B466" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D466" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E466" s="2">
+        <v>174.14</v>
+      </c>
+      <c r="F466" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G466" s="2">
+        <f t="shared" si="8"/>
+        <v>17.413999999999998</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A467" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D467" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E467" s="2">
+        <v>2767.2</v>
+      </c>
+      <c r="F467" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G467" s="2">
+        <f t="shared" si="8"/>
+        <v>276.71999999999997</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A468" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B468" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D468" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E468" s="2">
+        <v>6815.25</v>
+      </c>
+      <c r="F468" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G468" s="2">
+        <f t="shared" si="8"/>
+        <v>681.52500000000009</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A469" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D469" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E469" s="2">
+        <v>3063.06</v>
+      </c>
+      <c r="F469" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G469" s="2">
+        <f t="shared" si="8"/>
+        <v>306.30599999999998</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A470" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D470" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E470" s="2">
+        <v>5968</v>
+      </c>
+      <c r="F470" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G470" s="2">
+        <f t="shared" si="8"/>
+        <v>596.80000000000007</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A471" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D471" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E471" s="2">
+        <v>2787.2</v>
+      </c>
+      <c r="F471" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G471" s="2">
+        <f t="shared" si="8"/>
+        <v>278.71999999999997</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A472" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D472" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E472" s="2">
+        <v>7560.67</v>
+      </c>
+      <c r="F472" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G472" s="2">
+        <f t="shared" si="8"/>
+        <v>756.06700000000001</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A473" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D473" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E473" s="2">
+        <v>5180.92</v>
+      </c>
+      <c r="F473" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G473" s="2">
+        <f t="shared" si="8"/>
+        <v>518.09199999999998</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A474" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D474" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E474" s="2">
+        <v>1225.6199999999999</v>
+      </c>
+      <c r="F474" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G474" s="2">
+        <f t="shared" si="8"/>
+        <v>122.562</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A475" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D475" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E475" s="2">
+        <v>986.7</v>
+      </c>
+      <c r="F475" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G475" s="2">
+        <f t="shared" si="8"/>
+        <v>98.670000000000016</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A476" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D476" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E476" s="2">
+        <v>4329.6000000000004</v>
+      </c>
+      <c r="F476" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G476" s="2">
+        <f t="shared" si="8"/>
+        <v>432.96000000000004</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A477" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D477" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E477" s="2">
+        <v>2218.2600000000002</v>
+      </c>
+      <c r="F477" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G477" s="2">
+        <f t="shared" si="8"/>
+        <v>221.82600000000002</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A478" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D478" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E478" s="2">
+        <v>4206.84</v>
+      </c>
+      <c r="F478" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G478" s="2">
+        <f t="shared" si="8"/>
+        <v>420.68400000000003</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A479" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D479" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E479" s="2">
+        <v>1262.25</v>
+      </c>
+      <c r="F479" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G479" s="2">
+        <f t="shared" si="8"/>
+        <v>126.22500000000001</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A480" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D480" s="14">
+        <v>46054</v>
+      </c>
+      <c r="E480" s="2">
+        <v>3221.14</v>
+      </c>
+      <c r="F480" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G480" s="2">
+        <f t="shared" si="8"/>
+        <v>322.11400000000003</v>
       </c>
     </row>
   </sheetData>

--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBB36703-CEBD-40D7-9152-E3B93D518BEC}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{427AF409-E69C-4426-8BF0-A8FD00BB7B1B}"/>
   <bookViews>
-    <workbookView xWindow="-26220" yWindow="180" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3915" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="213">
   <si>
     <t>Gerador</t>
   </si>
@@ -630,6 +630,54 @@
   </si>
   <si>
     <t>EMÍLIO RIBAS - ITAIÇABA, 95</t>
+  </si>
+  <si>
+    <t>ATL. VARJOTA 1</t>
+  </si>
+  <si>
+    <t>CAPELOS | 01 | GUSTAVO HENRIQUE</t>
+  </si>
+  <si>
+    <t>CAPELOS | 02 | CAPELO CURSOS</t>
+  </si>
+  <si>
+    <t>CRISTAL | MAIOR - TEMPORÁRIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF </t>
+  </si>
+  <si>
+    <t>LF 4º USINA</t>
+  </si>
+  <si>
+    <t>EMILIO | 06 | 13 DE MAIO</t>
+  </si>
+  <si>
+    <t>LAPEZI</t>
+  </si>
+  <si>
+    <t>CRISTAL | SUINO SÃO GONÇALO 1</t>
+  </si>
+  <si>
+    <t>LUIZ RAMOS</t>
+  </si>
+  <si>
+    <t>LP DIGITAL</t>
+  </si>
+  <si>
+    <t>LOURIVAL SILVA</t>
+  </si>
+  <si>
+    <t>COND. EDIFICIO PARANOA</t>
+  </si>
+  <si>
+    <t>RMA | 06 | PARQUE MANIBURA</t>
+  </si>
+  <si>
+    <t>WELTER</t>
+  </si>
+  <si>
+    <t>ESSENCIAL COMERCIO</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G480"/>
+  <dimension ref="A1:G608"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -8011,7 +8059,7 @@
         <v>0.08</v>
       </c>
       <c r="G290" s="10">
-        <f t="shared" ref="G290:G480" si="8">E290*F290</f>
+        <f t="shared" ref="G290:G546" si="8">E290*F290</f>
         <v>90.486399999999989</v>
       </c>
     </row>
@@ -12571,6 +12619,3078 @@
       <c r="G480" s="2">
         <f t="shared" si="8"/>
         <v>322.11400000000003</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A481" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B481" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D481" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E481" s="2">
+        <v>676.65</v>
+      </c>
+      <c r="F481" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G481" s="2">
+        <f t="shared" si="8"/>
+        <v>67.665000000000006</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A482" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D482" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E482" s="2">
+        <v>0</v>
+      </c>
+      <c r="F482" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G482" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A483" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C483" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D483" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E483" s="2">
+        <v>185.6</v>
+      </c>
+      <c r="F483" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G483" s="2">
+        <f t="shared" si="8"/>
+        <v>18.559999999999999</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A484" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D484" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E484" s="2">
+        <v>5142.3999999999996</v>
+      </c>
+      <c r="F484" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G484" s="2">
+        <f t="shared" si="8"/>
+        <v>514.24</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A485" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D485" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E485" s="2">
+        <v>187.52</v>
+      </c>
+      <c r="F485" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G485" s="2">
+        <f t="shared" si="8"/>
+        <v>18.752000000000002</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A486" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D486" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E486" s="2">
+        <v>209.63</v>
+      </c>
+      <c r="F486" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G486" s="2">
+        <f t="shared" si="8"/>
+        <v>20.963000000000001</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A487" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D487" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E487" s="2">
+        <v>2172.9499999999998</v>
+      </c>
+      <c r="F487" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G487" s="2">
+        <f t="shared" si="8"/>
+        <v>217.29499999999999</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A488" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D488" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E488" s="2">
+        <v>325</v>
+      </c>
+      <c r="F488" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G488" s="2">
+        <f t="shared" si="8"/>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A489" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D489" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E489" s="2">
+        <v>151.68</v>
+      </c>
+      <c r="F489" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G489" s="2">
+        <f t="shared" si="8"/>
+        <v>15.168000000000001</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A490" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C490" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D490" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E490" s="2">
+        <v>1510.91</v>
+      </c>
+      <c r="F490" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G490" s="2">
+        <f t="shared" si="8"/>
+        <v>151.09100000000001</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A491" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D491" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E491" s="2">
+        <v>0</v>
+      </c>
+      <c r="F491" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G491" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A492" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D492" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E492" s="2">
+        <v>0</v>
+      </c>
+      <c r="F492" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G492" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A493" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D493" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E493" s="2">
+        <v>11971.84</v>
+      </c>
+      <c r="F493" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G493" s="2">
+        <f t="shared" si="8"/>
+        <v>1197.184</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A494" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D494" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E494" s="2">
+        <v>1503.12</v>
+      </c>
+      <c r="F494" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G494" s="2">
+        <f t="shared" si="8"/>
+        <v>150.31199999999998</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A495" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C495" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D495" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E495" s="2">
+        <v>0</v>
+      </c>
+      <c r="F495" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G495" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A496" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D496" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E496" s="2">
+        <v>550.89</v>
+      </c>
+      <c r="F496" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G496" s="2">
+        <f t="shared" si="8"/>
+        <v>55.088999999999999</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A497" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D497" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E497" s="2">
+        <v>14073.16</v>
+      </c>
+      <c r="F497" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G497" s="2">
+        <f t="shared" si="8"/>
+        <v>1407.316</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A498" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D498" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E498" s="2">
+        <v>10802.48</v>
+      </c>
+      <c r="F498" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G498" s="2">
+        <f t="shared" si="8"/>
+        <v>1080.248</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A499" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D499" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E499" s="2">
+        <v>6222.72</v>
+      </c>
+      <c r="F499" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G499" s="2">
+        <f t="shared" si="8"/>
+        <v>497.81760000000003</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A500" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D500" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E500" s="2">
+        <v>5454.72</v>
+      </c>
+      <c r="F500" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G500" s="2">
+        <f t="shared" si="8"/>
+        <v>436.37760000000003</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A501" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D501" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E501" s="2">
+        <v>2471.04</v>
+      </c>
+      <c r="F501" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G501" s="2">
+        <f t="shared" si="8"/>
+        <v>197.6832</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A502" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D502" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E502" s="2">
+        <v>1660.16</v>
+      </c>
+      <c r="F502" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G502" s="2">
+        <f t="shared" si="8"/>
+        <v>132.81280000000001</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A503" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B503" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D503" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E503" s="2">
+        <v>1310.1199999999999</v>
+      </c>
+      <c r="F503" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G503" s="2">
+        <f t="shared" si="8"/>
+        <v>104.80959999999999</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A504" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D504" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E504" s="2">
+        <v>1885.14</v>
+      </c>
+      <c r="F504" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G504" s="2">
+        <f t="shared" si="8"/>
+        <v>150.81120000000001</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A505" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D505" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E505" s="2">
+        <v>2368.44</v>
+      </c>
+      <c r="F505" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G505" s="2">
+        <f t="shared" si="8"/>
+        <v>189.4752</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A506" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D506" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E506" s="2">
+        <v>2335.12</v>
+      </c>
+      <c r="F506" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G506" s="2">
+        <f t="shared" si="8"/>
+        <v>186.80959999999999</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A507" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B507" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D507" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E507" s="2">
+        <v>3909.32</v>
+      </c>
+      <c r="F507" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G507" s="2">
+        <f t="shared" si="8"/>
+        <v>312.74560000000002</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A508" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B508" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D508" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E508" s="2">
+        <v>1645.09</v>
+      </c>
+      <c r="F508" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G508" s="2">
+        <f t="shared" si="8"/>
+        <v>131.60720000000001</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A509" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B509" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C509" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D509" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E509" s="2">
+        <v>2914.92</v>
+      </c>
+      <c r="F509" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G509" s="2">
+        <f t="shared" si="8"/>
+        <v>233.1936</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A510" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B510" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C510" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D510" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E510" s="2">
+        <v>586.08000000000004</v>
+      </c>
+      <c r="F510" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G510" s="2">
+        <f t="shared" si="8"/>
+        <v>46.886400000000002</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A511" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B511" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C511" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D511" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E511" s="2">
+        <v>420.42</v>
+      </c>
+      <c r="F511" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G511" s="2">
+        <f t="shared" si="8"/>
+        <v>33.633600000000001</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A512" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B512" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C512" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D512" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E512" s="2">
+        <v>916.56</v>
+      </c>
+      <c r="F512" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G512" s="2">
+        <f t="shared" si="8"/>
+        <v>73.324799999999996</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A513" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B513" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C513" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D513" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E513" s="2">
+        <v>311.52</v>
+      </c>
+      <c r="F513" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G513" s="2">
+        <f t="shared" si="8"/>
+        <v>24.921599999999998</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A514" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B514" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C514" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D514" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E514" s="2">
+        <v>1805.1</v>
+      </c>
+      <c r="F514" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G514" s="2">
+        <f t="shared" si="8"/>
+        <v>144.40799999999999</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A515" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B515" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D515" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E515" s="2">
+        <v>1135.8599999999999</v>
+      </c>
+      <c r="F515" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G515" s="2">
+        <f t="shared" si="8"/>
+        <v>90.868799999999993</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A516" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B516" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C516" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D516" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E516" s="2">
+        <v>177.11</v>
+      </c>
+      <c r="F516" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G516" s="2">
+        <f t="shared" si="8"/>
+        <v>14.168800000000001</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A517" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B517" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C517" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D517" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E517" s="2">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="F517" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G517" s="2">
+        <f t="shared" si="8"/>
+        <v>5.6079999999999997</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A518" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D518" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E518" s="2">
+        <v>284.11</v>
+      </c>
+      <c r="F518" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G518" s="2">
+        <f t="shared" si="8"/>
+        <v>22.728800000000003</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A519" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D519" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E519" s="2">
+        <v>247.9</v>
+      </c>
+      <c r="F519" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G519" s="2">
+        <f t="shared" si="8"/>
+        <v>19.832000000000001</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A520" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D520" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E520" s="2">
+        <v>251.25</v>
+      </c>
+      <c r="F520" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G520" s="2">
+        <f t="shared" si="8"/>
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A521" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D521" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E521" s="2">
+        <v>285.95</v>
+      </c>
+      <c r="F521" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G521" s="2">
+        <f t="shared" si="8"/>
+        <v>22.876000000000001</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A522" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D522" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E522" s="2">
+        <v>428</v>
+      </c>
+      <c r="F522" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G522" s="2">
+        <f t="shared" si="8"/>
+        <v>34.24</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A523" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B523" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C523" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D523" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E523" s="2">
+        <v>363.43</v>
+      </c>
+      <c r="F523" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G523" s="2">
+        <f t="shared" si="8"/>
+        <v>29.074400000000001</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A524" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B524" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C524" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D524" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E524" s="2">
+        <v>875.95</v>
+      </c>
+      <c r="F524" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G524" s="2">
+        <f t="shared" si="8"/>
+        <v>70.076000000000008</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A525" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B525" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D525" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E525" s="2">
+        <v>736.01</v>
+      </c>
+      <c r="F525" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G525" s="2">
+        <f t="shared" si="8"/>
+        <v>58.880800000000001</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A526" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B526" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C526" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D526" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E526" s="2">
+        <v>5889.92</v>
+      </c>
+      <c r="F526" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G526" s="2">
+        <f t="shared" si="8"/>
+        <v>294.49600000000004</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A527" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B527" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D527" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E527" s="2">
+        <v>4887.68</v>
+      </c>
+      <c r="F527" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G527" s="2">
+        <f t="shared" si="8"/>
+        <v>244.38400000000001</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A528" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B528" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D528" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E528" s="2">
+        <v>5600.64</v>
+      </c>
+      <c r="F528" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G528" s="2">
+        <f t="shared" si="8"/>
+        <v>280.03200000000004</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A529" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B529" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D529" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E529" s="2">
+        <v>2445.3000000000002</v>
+      </c>
+      <c r="F529" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G529" s="2">
+        <f t="shared" si="8"/>
+        <v>122.26500000000001</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A530" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B530" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C530" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D530" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E530" s="2">
+        <v>0</v>
+      </c>
+      <c r="F530" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G530" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A531" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B531" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D531" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E531" s="2">
+        <v>615.67999999999995</v>
+      </c>
+      <c r="F531" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G531" s="2">
+        <f t="shared" si="8"/>
+        <v>30.783999999999999</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A532" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B532" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D532" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E532" s="2">
+        <v>2802.56</v>
+      </c>
+      <c r="F532" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G532" s="2">
+        <f t="shared" si="8"/>
+        <v>140.12800000000001</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A533" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B533" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D533" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E533" s="2">
+        <v>2850.56</v>
+      </c>
+      <c r="F533" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G533" s="2">
+        <f t="shared" si="8"/>
+        <v>142.52799999999999</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A534" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B534" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C534" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D534" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E534" s="2">
+        <v>4378.24</v>
+      </c>
+      <c r="F534" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G534" s="2">
+        <f t="shared" si="8"/>
+        <v>218.91200000000001</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A535" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B535" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D535" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E535" s="2">
+        <v>2827.5</v>
+      </c>
+      <c r="F535" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G535" s="2">
+        <f t="shared" si="8"/>
+        <v>141.375</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A536" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B536" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C536" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D536" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E536" s="2">
+        <v>4138.2</v>
+      </c>
+      <c r="F536" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G536" s="2">
+        <f t="shared" si="8"/>
+        <v>206.91</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A537" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B537" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D537" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E537" s="2">
+        <v>3001.49</v>
+      </c>
+      <c r="F537" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G537" s="2">
+        <f t="shared" si="8"/>
+        <v>150.0745</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A538" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B538" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D538" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E538" s="2">
+        <v>9388.7999999999993</v>
+      </c>
+      <c r="F538" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G538" s="2">
+        <f t="shared" si="8"/>
+        <v>469.44</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A539" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B539" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D539" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E539" s="2">
+        <v>4853.12</v>
+      </c>
+      <c r="F539" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G539" s="2">
+        <f t="shared" si="8"/>
+        <v>242.65600000000001</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A540" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B540" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D540" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E540" s="2">
+        <v>9245.6</v>
+      </c>
+      <c r="F540" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G540" s="2">
+        <f t="shared" si="8"/>
+        <v>462.28000000000003</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A541" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B541" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D541" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E541" s="2">
+        <v>2468.71</v>
+      </c>
+      <c r="F541" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G541" s="2">
+        <f t="shared" si="8"/>
+        <v>123.4355</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A542" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D542" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E542" s="2">
+        <v>860.6</v>
+      </c>
+      <c r="F542" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G542" s="2">
+        <f t="shared" si="8"/>
+        <v>43.03</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A543" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D543" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E543" s="2">
+        <v>585.6</v>
+      </c>
+      <c r="F543" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G543" s="2">
+        <f t="shared" si="8"/>
+        <v>29.28</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A544" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D544" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E544" s="2">
+        <v>2148.9</v>
+      </c>
+      <c r="F544" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G544" s="2">
+        <f t="shared" si="8"/>
+        <v>107.44500000000001</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A545" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D545" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E545" s="2">
+        <v>624.64</v>
+      </c>
+      <c r="F545" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G545" s="2">
+        <f t="shared" si="8"/>
+        <v>31.231999999999999</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A546" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B546" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C546" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D546" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E546" s="2">
+        <v>4987.5200000000004</v>
+      </c>
+      <c r="F546" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G546" s="2">
+        <f t="shared" si="8"/>
+        <v>249.37600000000003</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A547" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D547" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E547" s="2">
+        <v>1856.64</v>
+      </c>
+      <c r="F547" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G547" s="2">
+        <f t="shared" ref="G547:G608" si="9">E547*F547</f>
+        <v>92.832000000000008</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A548" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B548" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D548" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E548" s="2">
+        <v>0</v>
+      </c>
+      <c r="F548" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G548" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A549" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D549" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E549" s="2">
+        <v>6663.04</v>
+      </c>
+      <c r="F549" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G549" s="2">
+        <f t="shared" si="9"/>
+        <v>333.15200000000004</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A550" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D550" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E550" s="2">
+        <v>0</v>
+      </c>
+      <c r="F550" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G550" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A551" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B551" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D551" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E551" s="2">
+        <v>917.12</v>
+      </c>
+      <c r="F551" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G551" s="2">
+        <f t="shared" si="9"/>
+        <v>45.856000000000002</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A552" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D552" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E552" s="2">
+        <v>940.8</v>
+      </c>
+      <c r="F552" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G552" s="2">
+        <f t="shared" si="9"/>
+        <v>47.04</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A553" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D553" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E553" s="2">
+        <v>5932.16</v>
+      </c>
+      <c r="F553" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G553" s="2">
+        <f t="shared" si="9"/>
+        <v>296.608</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A554" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D554" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E554" s="2">
+        <v>4609.92</v>
+      </c>
+      <c r="F554" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G554" s="2">
+        <f t="shared" si="9"/>
+        <v>230.49600000000001</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A555" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D555" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E555" s="2">
+        <v>6851.2</v>
+      </c>
+      <c r="F555" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G555" s="2">
+        <f t="shared" si="9"/>
+        <v>342.56</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A556" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D556" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E556" s="2">
+        <v>5569.81</v>
+      </c>
+      <c r="F556" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G556" s="2">
+        <f t="shared" si="9"/>
+        <v>445.58480000000003</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A557" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D557" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E557" s="2">
+        <v>305.32</v>
+      </c>
+      <c r="F557" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G557" s="2">
+        <f t="shared" si="9"/>
+        <v>24.425599999999999</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A558" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B558" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D558" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E558" s="2">
+        <v>249.48</v>
+      </c>
+      <c r="F558" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G558" s="2">
+        <f t="shared" si="9"/>
+        <v>19.958400000000001</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A559" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D559" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E559" s="2">
+        <v>1409.4</v>
+      </c>
+      <c r="F559" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G559" s="2">
+        <f t="shared" si="9"/>
+        <v>112.75200000000001</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A560" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B560" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C560" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D560" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E560" s="2">
+        <v>279.18</v>
+      </c>
+      <c r="F560" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G560" s="2">
+        <f t="shared" si="9"/>
+        <v>22.334400000000002</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A561" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D561" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E561" s="2">
+        <v>981.18</v>
+      </c>
+      <c r="F561" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G561" s="2">
+        <f t="shared" si="9"/>
+        <v>78.494399999999999</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A562" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D562" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E562" s="2">
+        <v>1016.4</v>
+      </c>
+      <c r="F562" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G562" s="2">
+        <f t="shared" si="9"/>
+        <v>81.311999999999998</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A563" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D563" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E563" s="2">
+        <v>4044.06</v>
+      </c>
+      <c r="F563" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G563" s="2">
+        <f t="shared" si="9"/>
+        <v>323.52480000000003</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A564" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D564" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E564" s="2">
+        <v>1316.04</v>
+      </c>
+      <c r="F564" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G564" s="2">
+        <f t="shared" si="9"/>
+        <v>105.28319999999999</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A565" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B565" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D565" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E565" s="2">
+        <v>564.29999999999995</v>
+      </c>
+      <c r="F565" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G565" s="2">
+        <f t="shared" si="9"/>
+        <v>45.143999999999998</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A566" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D566" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E566" s="2">
+        <v>5664.53</v>
+      </c>
+      <c r="F566" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G566" s="2">
+        <f t="shared" si="9"/>
+        <v>453.16239999999999</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A567" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D567" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E567" s="2">
+        <v>9674.32</v>
+      </c>
+      <c r="F567" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G567" s="2">
+        <f t="shared" si="9"/>
+        <v>773.94560000000001</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A568" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D568" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E568" s="2">
+        <v>314.88</v>
+      </c>
+      <c r="F568" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G568" s="2">
+        <f t="shared" si="9"/>
+        <v>25.1904</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A569" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D569" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E569" s="2">
+        <v>3840.85</v>
+      </c>
+      <c r="F569" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G569" s="2">
+        <f t="shared" si="9"/>
+        <v>307.26799999999997</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A570" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B570" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D570" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E570" s="2">
+        <v>2729.35</v>
+      </c>
+      <c r="F570" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G570" s="2">
+        <f t="shared" si="9"/>
+        <v>218.34799999999998</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A571" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D571" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E571" s="2">
+        <v>5610.24</v>
+      </c>
+      <c r="F571" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G571" s="2">
+        <f t="shared" si="9"/>
+        <v>448.81919999999997</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A572" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B572" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D572" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E572" s="2">
+        <v>3144.96</v>
+      </c>
+      <c r="F572" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G572" s="2">
+        <f t="shared" si="9"/>
+        <v>251.5968</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A573" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D573" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E573" s="2">
+        <v>3826.5</v>
+      </c>
+      <c r="F573" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G573" s="2">
+        <f t="shared" si="9"/>
+        <v>306.12</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A574" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D574" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E574" s="2">
+        <v>6804.98</v>
+      </c>
+      <c r="F574" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G574" s="2">
+        <f t="shared" si="9"/>
+        <v>544.39839999999992</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A575" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D575" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E575" s="2">
+        <v>228.48</v>
+      </c>
+      <c r="F575" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G575" s="2">
+        <f t="shared" si="9"/>
+        <v>18.278400000000001</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A576" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B576" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D576" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E576" s="2">
+        <v>2014.2</v>
+      </c>
+      <c r="F576" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G576" s="2">
+        <f t="shared" si="9"/>
+        <v>161.136</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A577" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D577" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E577" s="2">
+        <v>4732.5600000000004</v>
+      </c>
+      <c r="F577" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G577" s="2">
+        <f t="shared" si="9"/>
+        <v>378.60480000000001</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A578" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D578" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E578" s="2">
+        <v>1338.66</v>
+      </c>
+      <c r="F578" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G578" s="2">
+        <f t="shared" si="9"/>
+        <v>133.86600000000001</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A579" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D579" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E579" s="2">
+        <v>4317.84</v>
+      </c>
+      <c r="F579" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G579" s="2">
+        <f t="shared" si="9"/>
+        <v>431.78400000000005</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A580" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D580" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E580" s="2">
+        <v>231.66</v>
+      </c>
+      <c r="F580" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G580" s="2">
+        <f t="shared" si="9"/>
+        <v>23.166</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D581" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E581" s="2">
+        <v>6507</v>
+      </c>
+      <c r="F581" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G581" s="2">
+        <f t="shared" si="9"/>
+        <v>650.70000000000005</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A582" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D582" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E582" s="2">
+        <v>1543.32</v>
+      </c>
+      <c r="F582" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G582" s="2">
+        <f t="shared" si="9"/>
+        <v>154.33199999999999</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A583" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D583" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E583" s="2">
+        <v>5139.18</v>
+      </c>
+      <c r="F583" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G583" s="2">
+        <f t="shared" si="9"/>
+        <v>513.91800000000001</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A584" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B584" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D584" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E584" s="2">
+        <v>163.38999999999999</v>
+      </c>
+      <c r="F584" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G584" s="2">
+        <f t="shared" si="9"/>
+        <v>16.338999999999999</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A585" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D585" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E585" s="2">
+        <v>910.08</v>
+      </c>
+      <c r="F585" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G585" s="2">
+        <f t="shared" si="9"/>
+        <v>91.00800000000001</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A586" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B586" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D586" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E586" s="2">
+        <v>5931.25</v>
+      </c>
+      <c r="F586" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G586" s="2">
+        <f t="shared" si="9"/>
+        <v>593.125</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A587" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D587" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E587" s="2">
+        <v>759.04</v>
+      </c>
+      <c r="F587" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G587" s="2">
+        <f t="shared" si="9"/>
+        <v>75.903999999999996</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A588" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B588" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D588" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E588" s="2">
+        <v>760.96</v>
+      </c>
+      <c r="F588" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G588" s="2">
+        <f t="shared" si="9"/>
+        <v>76.096000000000004</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A589" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D589" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E589" s="2">
+        <v>2874.96</v>
+      </c>
+      <c r="F589" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G589" s="2">
+        <f t="shared" si="9"/>
+        <v>287.49600000000004</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A590" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B590" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D590" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E590" s="2">
+        <v>6006.4</v>
+      </c>
+      <c r="F590" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G590" s="2">
+        <f t="shared" si="9"/>
+        <v>600.64</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A591" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D591" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E591" s="2">
+        <v>2908.8</v>
+      </c>
+      <c r="F591" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G591" s="2">
+        <f t="shared" si="9"/>
+        <v>290.88000000000005</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A592" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D592" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E592" s="2">
+        <v>6004.99</v>
+      </c>
+      <c r="F592" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G592" s="2">
+        <f t="shared" si="9"/>
+        <v>600.49900000000002</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A593" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D593" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E593" s="2">
+        <v>5360.44</v>
+      </c>
+      <c r="F593" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G593" s="2">
+        <f t="shared" si="9"/>
+        <v>536.04399999999998</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A594" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B594" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D594" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E594" s="2">
+        <v>570.9</v>
+      </c>
+      <c r="F594" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G594" s="2">
+        <f t="shared" si="9"/>
+        <v>57.09</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A595" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B595" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D595" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E595" s="2">
+        <v>675.84</v>
+      </c>
+      <c r="F595" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G595" s="2">
+        <f t="shared" si="9"/>
+        <v>67.584000000000003</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A596" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B596" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D596" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E596" s="2">
+        <v>3957.47</v>
+      </c>
+      <c r="F596" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G596" s="2">
+        <f t="shared" si="9"/>
+        <v>395.74700000000001</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A597" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D597" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E597" s="2">
+        <v>2106.7199999999998</v>
+      </c>
+      <c r="F597" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G597" s="2">
+        <f t="shared" si="9"/>
+        <v>210.672</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A598" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B598" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D598" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E598" s="2">
+        <v>3508.67</v>
+      </c>
+      <c r="F598" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G598" s="2">
+        <f t="shared" si="9"/>
+        <v>350.86700000000002</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A599" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D599" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E599" s="2">
+        <v>11852.88</v>
+      </c>
+      <c r="F599" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G599" s="2">
+        <f t="shared" si="9"/>
+        <v>1185.288</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A600" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B600" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D600" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E600" s="2">
+        <v>1225.4000000000001</v>
+      </c>
+      <c r="F600" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G600" s="2">
+        <f t="shared" si="9"/>
+        <v>122.54000000000002</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A601" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B601" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C601" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D601" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E601" s="2">
+        <v>2880.9</v>
+      </c>
+      <c r="F601" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G601" s="2">
+        <f t="shared" si="9"/>
+        <v>288.09000000000003</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A602" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B602" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D602" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E602" s="2">
+        <v>3156.78</v>
+      </c>
+      <c r="F602" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G602" s="2">
+        <f t="shared" si="9"/>
+        <v>315.67800000000005</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A603" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D603" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E603" s="2">
+        <v>2847.65</v>
+      </c>
+      <c r="F603" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G603" s="2">
+        <f t="shared" si="9"/>
+        <v>284.76500000000004</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A604" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B604" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D604" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E604" s="2">
+        <v>513.36</v>
+      </c>
+      <c r="F604" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G604" s="2">
+        <f t="shared" si="9"/>
+        <v>51.336000000000006</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A605" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B605" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D605" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E605" s="2">
+        <v>487.32</v>
+      </c>
+      <c r="F605" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G605" s="2">
+        <f t="shared" si="9"/>
+        <v>48.731999999999999</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A606" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B606" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C606" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D606" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E606" s="2">
+        <v>357.72</v>
+      </c>
+      <c r="F606" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G606" s="2">
+        <f t="shared" si="9"/>
+        <v>35.772000000000006</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A607" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B607" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D607" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E607" s="2">
+        <v>0</v>
+      </c>
+      <c r="F607" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G607" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A608" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B608" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D608" s="14">
+        <v>46082</v>
+      </c>
+      <c r="E608" s="2">
+        <v>3075.2</v>
+      </c>
+      <c r="F608" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G608" s="2">
+        <f t="shared" si="9"/>
+        <v>307.52</v>
       </c>
     </row>
   </sheetData>

--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{427AF409-E69C-4426-8BF0-A8FD00BB7B1B}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50AC3BA7-87A0-44F8-817D-8B1B969ADFA3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3915" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26880" yWindow="-2415" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$363</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">REPASSE!$A$1:$H$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="231">
   <si>
     <t>Gerador</t>
   </si>
@@ -678,6 +678,60 @@
   </si>
   <si>
     <t>ESSENCIAL COMERCIO</t>
+  </si>
+  <si>
+    <t>LAVCON LAVANDERIA</t>
+  </si>
+  <si>
+    <t>P5 RESTAURANTE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JARDEL</t>
+  </si>
+  <si>
+    <t>MAXSTER | 01 | COM ALI (B71)</t>
+  </si>
+  <si>
+    <t>MAXSTER | 02 | MAXSTER LAN</t>
+  </si>
+  <si>
+    <t>MAXSTER | 03 | LORENA PIN</t>
+  </si>
+  <si>
+    <t>FIP SOARES</t>
+  </si>
+  <si>
+    <t>ZON | 01 | POSTO IGUATEMI</t>
+  </si>
+  <si>
+    <t>LF 1ª E 2ª USINA</t>
+  </si>
+  <si>
+    <t>LF 3ª USINA</t>
+  </si>
+  <si>
+    <t>LF 5ª USINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILIO | 06 | 13 DE MAIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIGNOLI | 02 | JOAQUIM NA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZON | 03 | POSTO JAGUARIBE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZON | 05 | POSTO MORADA NOVA  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZON | 06 | PÁTIO SOL POENTE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZON | 02 | POSTO VILA III </t>
+  </si>
+  <si>
+    <t>CRISTAL | SUINO SÃO GONÇALO 2</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G608"/>
+  <dimension ref="A1:G749"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -14225,7 +14279,7 @@
         <v>0.05</v>
       </c>
       <c r="G547" s="2">
-        <f t="shared" ref="G547:G608" si="9">E547*F547</f>
+        <f t="shared" ref="G547:G749" si="9">E547*F547</f>
         <v>92.832000000000008</v>
       </c>
     </row>
@@ -15691,6 +15745,3390 @@
       <c r="G608" s="2">
         <f t="shared" si="9"/>
         <v>307.52</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A609" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D609" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E609" s="2">
+        <v>653.25</v>
+      </c>
+      <c r="F609" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G609" s="2">
+        <f t="shared" si="9"/>
+        <v>65.325000000000003</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A610" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D610" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E610" s="2">
+        <v>3565.44</v>
+      </c>
+      <c r="F610" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G610" s="2">
+        <f t="shared" si="9"/>
+        <v>356.54400000000004</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A611" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D611" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E611" s="2">
+        <v>161.91999999999999</v>
+      </c>
+      <c r="F611" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G611" s="2">
+        <f t="shared" si="9"/>
+        <v>16.192</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A612" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D612" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E612" s="2">
+        <v>6184.32</v>
+      </c>
+      <c r="F612" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G612" s="2">
+        <f t="shared" si="9"/>
+        <v>618.43200000000002</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A613" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D613" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E613" s="2">
+        <v>281.60000000000002</v>
+      </c>
+      <c r="F613" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G613" s="2">
+        <f t="shared" si="9"/>
+        <v>28.160000000000004</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A614" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B614" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D614" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E614" s="2">
+        <v>1561.37</v>
+      </c>
+      <c r="F614" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G614" s="2">
+        <f t="shared" si="9"/>
+        <v>156.137</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A615" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B615" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D615" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E615" s="2">
+        <v>2096.2800000000002</v>
+      </c>
+      <c r="F615" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G615" s="2">
+        <f t="shared" si="9"/>
+        <v>209.62800000000004</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A616" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B616" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D616" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E616" s="2">
+        <v>0</v>
+      </c>
+      <c r="F616" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G616" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A617" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D617" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E617" s="2">
+        <v>133.12</v>
+      </c>
+      <c r="F617" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G617" s="2">
+        <f t="shared" si="9"/>
+        <v>13.312000000000001</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A618" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D618" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E618" s="2">
+        <v>979.05</v>
+      </c>
+      <c r="F618" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G618" s="2">
+        <f t="shared" si="9"/>
+        <v>97.905000000000001</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A619" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D619" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E619" s="2">
+        <v>0</v>
+      </c>
+      <c r="F619" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G619" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A620" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D620" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E620" s="2">
+        <v>472.96</v>
+      </c>
+      <c r="F620" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G620" s="2">
+        <f t="shared" si="9"/>
+        <v>47.295999999999999</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A621" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D621" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E621" s="2">
+        <v>3357.01</v>
+      </c>
+      <c r="F621" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G621" s="2">
+        <f t="shared" si="9"/>
+        <v>335.70100000000002</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A622" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D622" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E622" s="2">
+        <v>447.82</v>
+      </c>
+      <c r="F622" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G622" s="2">
+        <f t="shared" si="9"/>
+        <v>44.782000000000004</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A623" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D623" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E623" s="2">
+        <v>377.5</v>
+      </c>
+      <c r="F623" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G623" s="2">
+        <f t="shared" si="9"/>
+        <v>37.75</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A624" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D624" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E624" s="2">
+        <v>1573</v>
+      </c>
+      <c r="F624" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G624" s="2">
+        <f t="shared" si="9"/>
+        <v>157.30000000000001</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A625" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D625" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E625" s="2">
+        <v>10945.28</v>
+      </c>
+      <c r="F625" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G625" s="2">
+        <f t="shared" si="9"/>
+        <v>1094.528</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A626" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D626" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E626" s="2">
+        <v>7285.12</v>
+      </c>
+      <c r="F626" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G626" s="2">
+        <f t="shared" si="9"/>
+        <v>582.80960000000005</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A627" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D627" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E627" s="2">
+        <v>6700.16</v>
+      </c>
+      <c r="F627" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G627" s="2">
+        <f t="shared" si="9"/>
+        <v>536.01279999999997</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A628" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D628" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E628" s="2">
+        <v>2391.04</v>
+      </c>
+      <c r="F628" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G628" s="2">
+        <f t="shared" si="9"/>
+        <v>191.28319999999999</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A629" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D629" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E629" s="2">
+        <v>1857.28</v>
+      </c>
+      <c r="F629" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G629" s="2">
+        <f t="shared" si="9"/>
+        <v>148.58240000000001</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A630" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D630" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E630" s="2">
+        <v>1399.35</v>
+      </c>
+      <c r="F630" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G630" s="2">
+        <f t="shared" si="9"/>
+        <v>111.94799999999999</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A631" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D631" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E631" s="2">
+        <v>2278.8000000000002</v>
+      </c>
+      <c r="F631" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G631" s="2">
+        <f t="shared" si="9"/>
+        <v>182.30400000000003</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A632" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D632" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E632" s="2">
+        <v>1739.42</v>
+      </c>
+      <c r="F632" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G632" s="2">
+        <f t="shared" si="9"/>
+        <v>139.15360000000001</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A633" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D633" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E633" s="2">
+        <v>2821.32</v>
+      </c>
+      <c r="F633" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G633" s="2">
+        <f t="shared" si="9"/>
+        <v>225.7056</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A634" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D634" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E634" s="2">
+        <v>4675</v>
+      </c>
+      <c r="F634" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G634" s="2">
+        <f t="shared" si="9"/>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A635" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D635" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E635" s="2">
+        <v>1594.88</v>
+      </c>
+      <c r="F635" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G635" s="2">
+        <f t="shared" si="9"/>
+        <v>127.59040000000002</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A636" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D636" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E636" s="2">
+        <v>2121.8000000000002</v>
+      </c>
+      <c r="F636" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G636" s="2">
+        <f t="shared" si="9"/>
+        <v>169.74400000000003</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A637" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D637" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E637" s="2">
+        <v>723.36</v>
+      </c>
+      <c r="F637" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G637" s="2">
+        <f t="shared" si="9"/>
+        <v>57.8688</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A638" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D638" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E638" s="2">
+        <v>432.96</v>
+      </c>
+      <c r="F638" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G638" s="2">
+        <f t="shared" si="9"/>
+        <v>34.636800000000001</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A639" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D639" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E639" s="2">
+        <v>1620.06</v>
+      </c>
+      <c r="F639" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G639" s="2">
+        <f t="shared" si="9"/>
+        <v>129.60480000000001</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A640" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D640" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E640" s="2">
+        <v>361.02</v>
+      </c>
+      <c r="F640" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G640" s="2">
+        <f t="shared" si="9"/>
+        <v>28.881599999999999</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A641" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D641" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E641" s="2">
+        <v>1712.69</v>
+      </c>
+      <c r="F641" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G641" s="2">
+        <f t="shared" si="9"/>
+        <v>137.01520000000002</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A642" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D642" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E642" s="2">
+        <v>1321.98</v>
+      </c>
+      <c r="F642" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G642" s="2">
+        <f t="shared" si="9"/>
+        <v>105.75840000000001</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A643" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D643" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E643" s="2">
+        <v>172.22</v>
+      </c>
+      <c r="F643" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G643" s="2">
+        <f t="shared" si="9"/>
+        <v>13.7776</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A644" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D644" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E644" s="2">
+        <v>68.17</v>
+      </c>
+      <c r="F644" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G644" s="2">
+        <f t="shared" si="9"/>
+        <v>5.4536000000000007</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A645" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D645" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E645" s="2">
+        <v>276.27</v>
+      </c>
+      <c r="F645" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G645" s="2">
+        <f t="shared" si="9"/>
+        <v>22.101599999999998</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A646" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D646" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E646" s="2">
+        <v>224.24</v>
+      </c>
+      <c r="F646" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G646" s="2">
+        <f t="shared" si="9"/>
+        <v>17.9392</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A647" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D647" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E647" s="2">
+        <v>224.76</v>
+      </c>
+      <c r="F647" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G647" s="2">
+        <f t="shared" si="9"/>
+        <v>17.980799999999999</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A648" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D648" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E648" s="2">
+        <v>278.05</v>
+      </c>
+      <c r="F648" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G648" s="2">
+        <f t="shared" si="9"/>
+        <v>22.244</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A649" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D649" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E649" s="2">
+        <v>416.19</v>
+      </c>
+      <c r="F649" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G649" s="2">
+        <f t="shared" si="9"/>
+        <v>33.295200000000001</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A650" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D650" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E650" s="2">
+        <v>353.4</v>
+      </c>
+      <c r="F650" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G650" s="2">
+        <f t="shared" si="9"/>
+        <v>28.271999999999998</v>
+      </c>
+    </row>
+    <row r="651" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A651" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D651" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E651" s="2">
+        <v>851.77</v>
+      </c>
+      <c r="F651" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G651" s="2">
+        <f t="shared" si="9"/>
+        <v>68.141599999999997</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A652" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D652" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E652" s="2">
+        <v>715.7</v>
+      </c>
+      <c r="F652" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G652" s="2">
+        <f t="shared" si="9"/>
+        <v>57.256000000000007</v>
+      </c>
+    </row>
+    <row r="653" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A653" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D653" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E653" s="2">
+        <v>4282.88</v>
+      </c>
+      <c r="F653" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G653" s="2">
+        <f t="shared" si="9"/>
+        <v>214.14400000000001</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A654" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D654" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E654" s="2">
+        <v>4791.04</v>
+      </c>
+      <c r="F654" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G654" s="2">
+        <f t="shared" si="9"/>
+        <v>239.55200000000002</v>
+      </c>
+    </row>
+    <row r="655" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A655" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D655" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E655" s="2">
+        <v>4240.0600000000004</v>
+      </c>
+      <c r="F655" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G655" s="2">
+        <f t="shared" si="9"/>
+        <v>212.00300000000004</v>
+      </c>
+    </row>
+    <row r="656" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A656" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D656" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E656" s="2">
+        <v>2706.6</v>
+      </c>
+      <c r="F656" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G656" s="2">
+        <f t="shared" si="9"/>
+        <v>135.33000000000001</v>
+      </c>
+    </row>
+    <row r="657" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A657" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D657" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E657" s="2">
+        <v>3251.2</v>
+      </c>
+      <c r="F657" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G657" s="2">
+        <f t="shared" si="9"/>
+        <v>162.56</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A658" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D658" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E658" s="2">
+        <v>9420.16</v>
+      </c>
+      <c r="F658" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G658" s="2">
+        <f t="shared" si="9"/>
+        <v>471.00800000000004</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A659" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D659" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E659" s="2">
+        <v>1646.72</v>
+      </c>
+      <c r="F659" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G659" s="2">
+        <f t="shared" si="9"/>
+        <v>82.336000000000013</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A660" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D660" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E660" s="2">
+        <v>2197.7600000000002</v>
+      </c>
+      <c r="F660" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G660" s="2">
+        <f t="shared" si="9"/>
+        <v>109.88800000000002</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A661" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D661" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E661" s="2">
+        <v>2795.52</v>
+      </c>
+      <c r="F661" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G661" s="2">
+        <f t="shared" si="9"/>
+        <v>139.77600000000001</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A662" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D662" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E662" s="2">
+        <v>2925</v>
+      </c>
+      <c r="F662" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G662" s="2">
+        <f t="shared" si="9"/>
+        <v>146.25</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A663" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D663" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E663" s="2">
+        <v>4482.72</v>
+      </c>
+      <c r="F663" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G663" s="2">
+        <f t="shared" si="9"/>
+        <v>224.13600000000002</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A664" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D664" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E664" s="2">
+        <v>4971.46</v>
+      </c>
+      <c r="F664" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G664" s="2">
+        <f t="shared" si="9"/>
+        <v>248.57300000000001</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A665" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D665" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E665" s="2">
+        <v>10542.18</v>
+      </c>
+      <c r="F665" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G665" s="2">
+        <f t="shared" si="9"/>
+        <v>527.10900000000004</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A666" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D666" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E666" s="2">
+        <v>4873.72</v>
+      </c>
+      <c r="F666" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G666" s="2">
+        <f t="shared" si="9"/>
+        <v>243.68600000000004</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A667" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D667" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E667" s="2">
+        <v>8358.1</v>
+      </c>
+      <c r="F667" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G667" s="2">
+        <f t="shared" si="9"/>
+        <v>417.90500000000003</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A668" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D668" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E668" s="2">
+        <v>2790.06</v>
+      </c>
+      <c r="F668" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G668" s="2">
+        <f t="shared" si="9"/>
+        <v>139.50300000000001</v>
+      </c>
+    </row>
+    <row r="669" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A669" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D669" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E669" s="2">
+        <v>938.6</v>
+      </c>
+      <c r="F669" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G669" s="2">
+        <f t="shared" si="9"/>
+        <v>46.930000000000007</v>
+      </c>
+    </row>
+    <row r="670" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A670" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D670" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E670" s="2">
+        <v>582.4</v>
+      </c>
+      <c r="F670" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G670" s="2">
+        <f t="shared" si="9"/>
+        <v>29.12</v>
+      </c>
+    </row>
+    <row r="671" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A671" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D671" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E671" s="2">
+        <v>5688.15</v>
+      </c>
+      <c r="F671" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G671" s="2">
+        <f t="shared" si="9"/>
+        <v>284.40749999999997</v>
+      </c>
+    </row>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A672" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D672" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E672" s="2">
+        <v>470.4</v>
+      </c>
+      <c r="F672" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G672" s="2">
+        <f t="shared" si="9"/>
+        <v>23.52</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A673" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D673" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E673" s="2">
+        <v>4646.72</v>
+      </c>
+      <c r="F673" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G673" s="2">
+        <f t="shared" si="9"/>
+        <v>232.33600000000001</v>
+      </c>
+    </row>
+    <row r="674" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A674" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D674" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E674" s="2">
+        <v>1564.16</v>
+      </c>
+      <c r="F674" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G674" s="2">
+        <f t="shared" si="9"/>
+        <v>78.208000000000013</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A675" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D675" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E675" s="2">
+        <v>0</v>
+      </c>
+      <c r="F675" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G675" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A676" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D676" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E676" s="2">
+        <v>10446.719999999999</v>
+      </c>
+      <c r="F676" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G676" s="2">
+        <f t="shared" si="9"/>
+        <v>522.33600000000001</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A677" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D677" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E677" s="2">
+        <v>0</v>
+      </c>
+      <c r="F677" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G677" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A678" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D678" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E678" s="2">
+        <v>952.32</v>
+      </c>
+      <c r="F678" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G678" s="2">
+        <f t="shared" si="9"/>
+        <v>47.616000000000007</v>
+      </c>
+    </row>
+    <row r="679" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A679" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D679" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E679" s="2">
+        <v>787.84</v>
+      </c>
+      <c r="F679" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G679" s="2">
+        <f t="shared" si="9"/>
+        <v>39.392000000000003</v>
+      </c>
+    </row>
+    <row r="680" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A680" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D680" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E680" s="2">
+        <v>6469.12</v>
+      </c>
+      <c r="F680" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G680" s="2">
+        <f t="shared" si="9"/>
+        <v>323.45600000000002</v>
+      </c>
+    </row>
+    <row r="681" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A681" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D681" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E681" s="2">
+        <v>4987.5200000000004</v>
+      </c>
+      <c r="F681" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G681" s="2">
+        <f t="shared" si="9"/>
+        <v>249.37600000000003</v>
+      </c>
+    </row>
+    <row r="682" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A682" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D682" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E682" s="2">
+        <v>8300.7999999999993</v>
+      </c>
+      <c r="F682" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G682" s="2">
+        <f t="shared" si="9"/>
+        <v>415.03999999999996</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A683" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D683" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E683" s="2">
+        <v>5346.58</v>
+      </c>
+      <c r="F683" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G683" s="2">
+        <f t="shared" si="9"/>
+        <v>427.72640000000001</v>
+      </c>
+    </row>
+    <row r="684" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A684" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D684" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E684" s="2">
+        <v>318.92</v>
+      </c>
+      <c r="F684" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G684" s="2">
+        <f t="shared" si="9"/>
+        <v>25.5136</v>
+      </c>
+    </row>
+    <row r="685" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A685" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B685" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D685" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E685" s="2">
+        <v>331.56</v>
+      </c>
+      <c r="F685" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G685" s="2">
+        <f t="shared" si="9"/>
+        <v>26.524799999999999</v>
+      </c>
+    </row>
+    <row r="686" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A686" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B686" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D686" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E686" s="2">
+        <v>1719.36</v>
+      </c>
+      <c r="F686" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G686" s="2">
+        <f t="shared" si="9"/>
+        <v>137.5488</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A687" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B687" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D687" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E687" s="2">
+        <v>435.24</v>
+      </c>
+      <c r="F687" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G687" s="2">
+        <f t="shared" si="9"/>
+        <v>34.819200000000002</v>
+      </c>
+    </row>
+    <row r="688" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A688" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D688" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E688" s="2">
+        <v>1096.2</v>
+      </c>
+      <c r="F688" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G688" s="2">
+        <f t="shared" si="9"/>
+        <v>87.696000000000012</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A689" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B689" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D689" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E689" s="2">
+        <v>955.68</v>
+      </c>
+      <c r="F689" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G689" s="2">
+        <f t="shared" si="9"/>
+        <v>76.454399999999993</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A690" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B690" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D690" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E690" s="2">
+        <v>4895.1000000000004</v>
+      </c>
+      <c r="F690" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G690" s="2">
+        <f t="shared" si="9"/>
+        <v>391.60800000000006</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A691" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B691" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D691" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E691" s="2">
+        <v>1412.86</v>
+      </c>
+      <c r="F691" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G691" s="2">
+        <f t="shared" si="9"/>
+        <v>113.02879999999999</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A692" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D692" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E692" s="2">
+        <v>674.52</v>
+      </c>
+      <c r="F692" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G692" s="2">
+        <f t="shared" si="9"/>
+        <v>53.961599999999997</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A693" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B693" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D693" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E693" s="2">
+        <v>6469.91</v>
+      </c>
+      <c r="F693" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G693" s="2">
+        <f t="shared" si="9"/>
+        <v>517.59280000000001</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A694" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D694" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E694" s="2">
+        <v>12170.92</v>
+      </c>
+      <c r="F694" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G694" s="2">
+        <f t="shared" si="9"/>
+        <v>973.67360000000008</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A695" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D695" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E695" s="2">
+        <v>360.96</v>
+      </c>
+      <c r="F695" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G695" s="2">
+        <f t="shared" si="9"/>
+        <v>28.876799999999999</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A696" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D696" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E696" s="2">
+        <v>5806.44</v>
+      </c>
+      <c r="F696" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G696" s="2">
+        <f t="shared" si="9"/>
+        <v>464.51519999999999</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A697" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D697" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E697" s="2">
+        <v>2795.65</v>
+      </c>
+      <c r="F697" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G697" s="2">
+        <f t="shared" si="9"/>
+        <v>223.65200000000002</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A698" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D698" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E698" s="2">
+        <v>6864</v>
+      </c>
+      <c r="F698" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G698" s="2">
+        <f t="shared" si="9"/>
+        <v>549.12</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A699" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D699" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E699" s="2">
+        <v>3170.56</v>
+      </c>
+      <c r="F699" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G699" s="2">
+        <f t="shared" si="9"/>
+        <v>253.6448</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A700" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D700" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E700" s="2">
+        <v>822.73</v>
+      </c>
+      <c r="F700" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G700" s="2">
+        <f t="shared" si="9"/>
+        <v>65.818399999999997</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A701" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D701" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E701" s="2">
+        <v>1482.85</v>
+      </c>
+      <c r="F701" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G701" s="2">
+        <f t="shared" si="9"/>
+        <v>118.628</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A702" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D702" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E702" s="2">
+        <v>206.72</v>
+      </c>
+      <c r="F702" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G702" s="2">
+        <f t="shared" si="9"/>
+        <v>16.537600000000001</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A703" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D703" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E703" s="2">
+        <v>463.86</v>
+      </c>
+      <c r="F703" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G703" s="2">
+        <f t="shared" si="9"/>
+        <v>37.108800000000002</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A704" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D704" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E704" s="2">
+        <v>1807.92</v>
+      </c>
+      <c r="F704" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G704" s="2">
+        <f t="shared" si="9"/>
+        <v>144.6336</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A705" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D705" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E705" s="2">
+        <v>1177.44</v>
+      </c>
+      <c r="F705" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G705" s="2">
+        <f t="shared" si="9"/>
+        <v>94.1952</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A706" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D706" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E706" s="2">
+        <v>4796.8</v>
+      </c>
+      <c r="F706" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G706" s="2">
+        <f t="shared" si="9"/>
+        <v>383.74400000000003</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A707" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D707" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E707" s="2">
+        <v>0</v>
+      </c>
+      <c r="F707" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G707" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A708" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D708" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E708" s="2">
+        <v>1237.43</v>
+      </c>
+      <c r="F708" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G708" s="2">
+        <f t="shared" si="9"/>
+        <v>123.74300000000001</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A709" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B709" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D709" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E709" s="2">
+        <v>4902.12</v>
+      </c>
+      <c r="F709" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G709" s="2">
+        <f t="shared" si="9"/>
+        <v>490.21199999999999</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A710" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D710" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E710" s="2">
+        <v>181.12</v>
+      </c>
+      <c r="F710" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G710" s="2">
+        <f t="shared" si="9"/>
+        <v>18.112000000000002</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A711" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B711" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D711" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E711" s="2">
+        <v>4026.78</v>
+      </c>
+      <c r="F711" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G711" s="2">
+        <f t="shared" si="9"/>
+        <v>402.67800000000005</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A712" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D712" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E712" s="2">
+        <v>2026.08</v>
+      </c>
+      <c r="F712" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G712" s="2">
+        <f t="shared" si="9"/>
+        <v>202.608</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A713" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B713" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D713" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E713" s="2">
+        <v>4347.54</v>
+      </c>
+      <c r="F713" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G713" s="2">
+        <f t="shared" si="9"/>
+        <v>434.75400000000002</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A714" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D714" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E714" s="2">
+        <v>170.1</v>
+      </c>
+      <c r="F714" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G714" s="2">
+        <f t="shared" si="9"/>
+        <v>17.010000000000002</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A715" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B715" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D715" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E715" s="2">
+        <v>3041.92</v>
+      </c>
+      <c r="F715" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G715" s="2">
+        <f t="shared" si="9"/>
+        <v>304.19200000000001</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A716" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B716" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D716" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E716" s="2">
+        <v>6876.35</v>
+      </c>
+      <c r="F716" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G716" s="2">
+        <f t="shared" si="9"/>
+        <v>687.6350000000001</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A717" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D717" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E717" s="2">
+        <v>731.52</v>
+      </c>
+      <c r="F717" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G717" s="2">
+        <f t="shared" si="9"/>
+        <v>73.152000000000001</v>
+      </c>
+    </row>
+    <row r="718" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A718" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D718" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E718" s="2">
+        <v>706.56</v>
+      </c>
+      <c r="F718" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G718" s="2">
+        <f t="shared" si="9"/>
+        <v>70.655999999999992</v>
+      </c>
+    </row>
+    <row r="719" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A719" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B719" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D719" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E719" s="2">
+        <v>1995.52</v>
+      </c>
+      <c r="F719" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G719" s="2">
+        <f t="shared" si="9"/>
+        <v>199.55200000000002</v>
+      </c>
+    </row>
+    <row r="720" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A720" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B720" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D720" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E720" s="2">
+        <v>1859.84</v>
+      </c>
+      <c r="F720" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G720" s="2">
+        <f t="shared" si="9"/>
+        <v>185.98400000000001</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A721" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B721" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D721" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E721" s="2">
+        <v>0</v>
+      </c>
+      <c r="F721" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G721" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A722" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B722" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D722" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E722" s="2">
+        <v>3391.74</v>
+      </c>
+      <c r="F722" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G722" s="2">
+        <f t="shared" si="9"/>
+        <v>339.17399999999998</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A723" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B723" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D723" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E723" s="2">
+        <v>5936.64</v>
+      </c>
+      <c r="F723" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G723" s="2">
+        <f t="shared" si="9"/>
+        <v>593.6640000000001</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A724" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D724" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E724" s="2">
+        <v>2789.76</v>
+      </c>
+      <c r="F724" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G724" s="2">
+        <f t="shared" si="9"/>
+        <v>278.97600000000006</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A725" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D725" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E725" s="2">
+        <v>7542.53</v>
+      </c>
+      <c r="F725" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G725" s="2">
+        <f t="shared" si="9"/>
+        <v>754.25300000000004</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A726" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B726" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D726" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E726" s="2">
+        <v>0</v>
+      </c>
+      <c r="F726" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G726" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A727" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B727" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D727" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E727" s="2">
+        <v>110.88</v>
+      </c>
+      <c r="F727" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G727" s="2">
+        <f t="shared" si="9"/>
+        <v>11.088000000000001</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A728" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D728" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E728" s="2">
+        <v>1069</v>
+      </c>
+      <c r="F728" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G728" s="2">
+        <f t="shared" si="9"/>
+        <v>106.9</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A729" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B729" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D729" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E729" s="2">
+        <v>5043.9399999999996</v>
+      </c>
+      <c r="F729" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G729" s="2">
+        <f t="shared" si="9"/>
+        <v>504.39400000000001</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A730" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B730" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D730" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E730" s="2">
+        <v>2777.28</v>
+      </c>
+      <c r="F730" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G730" s="2">
+        <f t="shared" si="9"/>
+        <v>277.72800000000001</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A731" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B731" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D731" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E731" s="2">
+        <v>3386.68</v>
+      </c>
+      <c r="F731" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G731" s="2">
+        <f t="shared" si="9"/>
+        <v>338.66800000000001</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A732" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B732" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D732" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E732" s="2">
+        <v>0</v>
+      </c>
+      <c r="F732" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G732" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A733" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B733" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D733" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E733" s="2">
+        <v>0</v>
+      </c>
+      <c r="F733" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G733" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A734" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B734" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D734" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E734" s="2">
+        <v>11486.44</v>
+      </c>
+      <c r="F734" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G734" s="2">
+        <f t="shared" si="9"/>
+        <v>1148.644</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A735" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B735" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C735" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D735" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E735" s="2">
+        <v>853.1</v>
+      </c>
+      <c r="F735" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G735" s="2">
+        <f t="shared" si="9"/>
+        <v>85.31</v>
+      </c>
+    </row>
+    <row r="736" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A736" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B736" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D736" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E736" s="2">
+        <v>3838.45</v>
+      </c>
+      <c r="F736" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G736" s="2">
+        <f t="shared" si="9"/>
+        <v>383.84500000000003</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A737" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B737" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C737" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D737" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E737" s="2">
+        <v>3309.9</v>
+      </c>
+      <c r="F737" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G737" s="2">
+        <f t="shared" si="9"/>
+        <v>330.99</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A738" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B738" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D738" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E738" s="2">
+        <v>5301.96</v>
+      </c>
+      <c r="F738" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G738" s="2">
+        <f t="shared" si="9"/>
+        <v>530.19600000000003</v>
+      </c>
+    </row>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A739" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B739" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D739" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E739" s="2">
+        <v>378.88</v>
+      </c>
+      <c r="F739" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G739" s="2">
+        <f t="shared" si="9"/>
+        <v>37.887999999999998</v>
+      </c>
+    </row>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A740" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B740" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D740" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E740" s="2">
+        <v>2480.13</v>
+      </c>
+      <c r="F740" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G740" s="2">
+        <f t="shared" si="9"/>
+        <v>248.01300000000003</v>
+      </c>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A741" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B741" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D741" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E741" s="2">
+        <v>473.6</v>
+      </c>
+      <c r="F741" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G741" s="2">
+        <f t="shared" si="9"/>
+        <v>47.360000000000007</v>
+      </c>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A742" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B742" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D742" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E742" s="2">
+        <v>2779.36</v>
+      </c>
+      <c r="F742" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G742" s="2">
+        <f t="shared" si="9"/>
+        <v>277.93600000000004</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A743" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B743" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D743" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E743" s="2">
+        <v>0</v>
+      </c>
+      <c r="F743" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G743" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A744" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B744" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D744" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E744" s="2">
+        <v>1861.6</v>
+      </c>
+      <c r="F744" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G744" s="2">
+        <f t="shared" si="9"/>
+        <v>186.16</v>
+      </c>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A745" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B745" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D745" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E745" s="2">
+        <v>688.2</v>
+      </c>
+      <c r="F745" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G745" s="2">
+        <f t="shared" si="9"/>
+        <v>68.820000000000007</v>
+      </c>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A746" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B746" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D746" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E746" s="2">
+        <v>451.36</v>
+      </c>
+      <c r="F746" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G746" s="2">
+        <f t="shared" si="9"/>
+        <v>45.136000000000003</v>
+      </c>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A747" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B747" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D747" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E747" s="2">
+        <v>406.56</v>
+      </c>
+      <c r="F747" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G747" s="2">
+        <f t="shared" si="9"/>
+        <v>40.656000000000006</v>
+      </c>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A748" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B748" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D748" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E748" s="2">
+        <v>5407.64</v>
+      </c>
+      <c r="F748" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G748" s="2">
+        <f t="shared" si="9"/>
+        <v>540.76400000000001</v>
+      </c>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A749" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B749" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D749" s="14">
+        <v>46113</v>
+      </c>
+      <c r="E749" s="2">
+        <v>3180.8</v>
+      </c>
+      <c r="F749" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G749" s="2">
+        <f t="shared" si="9"/>
+        <v>318.08000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A53F14-10DF-4883-8171-5B560E98EBB9}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81558D05-BE6A-4B33-9D46-E77397144D81}"/>
   <bookViews>
-    <workbookView xWindow="-25245" yWindow="675" windowWidth="19410" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23400" yWindow="600" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$1195</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3133" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3589" uniqueCount="279">
   <si>
     <t>Gerador</t>
   </si>
@@ -842,6 +842,39 @@
   <si>
     <t>VIGNOLI | 09 | SILVA JATAHY</t>
   </si>
+  <si>
+    <t>CORTILLE |04| UC 60857316</t>
+  </si>
+  <si>
+    <t>PONZA FRUTOS DO MAR</t>
+  </si>
+  <si>
+    <t>OFICÍNA |01| - SALA B</t>
+  </si>
+  <si>
+    <t>OFICÍNA |02| -2257</t>
+  </si>
+  <si>
+    <t>BABBI |01|UC 60906548</t>
+  </si>
+  <si>
+    <t>BABBI |02|UC 60909661</t>
+  </si>
+  <si>
+    <t>SOLARE (DARIO)</t>
+  </si>
+  <si>
+    <t>ATL DERCIO 1</t>
+  </si>
+  <si>
+    <t>YOTO COZINHA NIKKEI</t>
+  </si>
+  <si>
+    <t>SUNTEB ENERGIA</t>
+  </si>
+  <si>
+    <t>REG AGRO | COLINA</t>
+  </si>
 </sst>
 </file>
 
@@ -909,7 +942,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -932,6 +965,11 @@
     </xf>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1241,7 +1279,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1043"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G1195"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -19221,7 +19260,7 @@
         <v>318.08000000000004</v>
       </c>
     </row>
-    <row r="750" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" s="3" t="s">
         <v>4</v>
       </c>
@@ -19245,7 +19284,7 @@
         <v>64.61</v>
       </c>
     </row>
-    <row r="751" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" s="3" t="s">
         <v>4</v>
       </c>
@@ -19269,7 +19308,7 @@
         <v>377.66399999999999</v>
       </c>
     </row>
-    <row r="752" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" s="3" t="s">
         <v>4</v>
       </c>
@@ -19293,7 +19332,7 @@
         <v>16.896000000000001</v>
       </c>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" s="3" t="s">
         <v>4</v>
       </c>
@@ -19317,7 +19356,7 @@
         <v>510.46400000000006</v>
       </c>
     </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" s="3" t="s">
         <v>4</v>
       </c>
@@ -19341,7 +19380,7 @@
         <v>21.632000000000001</v>
       </c>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" s="3" t="s">
         <v>4</v>
       </c>
@@ -19365,7 +19404,7 @@
         <v>18.658000000000001</v>
       </c>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="3" t="s">
         <v>4</v>
       </c>
@@ -19389,7 +19428,7 @@
         <v>135.83599999999998</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
         <v>4</v>
       </c>
@@ -19413,7 +19452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" s="3" t="s">
         <v>4</v>
       </c>
@@ -19437,7 +19476,7 @@
         <v>1.655</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" s="3" t="s">
         <v>4</v>
       </c>
@@ -19461,7 +19500,7 @@
         <v>134.47900000000001</v>
       </c>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
         <v>4</v>
       </c>
@@ -19485,7 +19524,7 @@
         <v>470.78400000000005</v>
       </c>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" s="3" t="s">
         <v>4</v>
       </c>
@@ -19509,7 +19548,7 @@
         <v>78.144000000000005</v>
       </c>
     </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="3" t="s">
         <v>4</v>
       </c>
@@ -19533,7 +19572,7 @@
         <v>92.436000000000007</v>
       </c>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" s="3" t="s">
         <v>4</v>
       </c>
@@ -19557,7 +19596,7 @@
         <v>318.92200000000003</v>
       </c>
     </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" s="3" t="s">
         <v>27</v>
       </c>
@@ -19581,7 +19620,7 @@
         <v>1119.2120000000002</v>
       </c>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765" s="3" t="s">
         <v>31</v>
       </c>
@@ -19605,7 +19644,7 @@
         <v>528.12800000000004</v>
       </c>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" s="3" t="s">
         <v>31</v>
       </c>
@@ -19629,7 +19668,7 @@
         <v>437.09440000000001</v>
       </c>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" s="3" t="s">
         <v>31</v>
       </c>
@@ -19653,7 +19692,7 @@
         <v>199.01439999999999</v>
       </c>
     </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
         <v>31</v>
       </c>
@@ -19677,7 +19716,7 @@
         <v>146.2784</v>
       </c>
     </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
         <v>31</v>
       </c>
@@ -19701,7 +19740,7 @@
         <v>96.66879999999999</v>
       </c>
     </row>
-    <row r="770" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
         <v>31</v>
       </c>
@@ -19725,7 +19764,7 @@
         <v>49.816000000000003</v>
       </c>
     </row>
-    <row r="771" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
         <v>31</v>
       </c>
@@ -19749,7 +19788,7 @@
         <v>93.978400000000008</v>
       </c>
     </row>
-    <row r="772" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
         <v>31</v>
       </c>
@@ -19773,7 +19812,7 @@
         <v>208.56960000000001</v>
       </c>
     </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
         <v>31</v>
       </c>
@@ -19797,7 +19836,7 @@
         <v>351.85919999999999</v>
       </c>
     </row>
-    <row r="774" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
         <v>31</v>
       </c>
@@ -19821,7 +19860,7 @@
         <v>109.1944</v>
       </c>
     </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
         <v>31</v>
       </c>
@@ -19845,7 +19884,7 @@
         <v>143.52160000000001</v>
       </c>
     </row>
-    <row r="776" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
         <v>31</v>
       </c>
@@ -19869,7 +19908,7 @@
         <v>45.196800000000003</v>
       </c>
     </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
         <v>31</v>
       </c>
@@ -19893,7 +19932,7 @@
         <v>36.590400000000002</v>
       </c>
     </row>
-    <row r="778" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
         <v>31</v>
       </c>
@@ -19917,7 +19956,7 @@
         <v>94.925600000000003</v>
       </c>
     </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" s="3" t="s">
         <v>31</v>
       </c>
@@ -19941,7 +19980,7 @@
         <v>29.937600000000003</v>
       </c>
     </row>
-    <row r="780" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780" s="3" t="s">
         <v>31</v>
       </c>
@@ -19965,7 +20004,7 @@
         <v>138.17680000000001</v>
       </c>
     </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
         <v>31</v>
       </c>
@@ -19989,7 +20028,7 @@
         <v>83.582399999999993</v>
       </c>
     </row>
-    <row r="782" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
         <v>31</v>
       </c>
@@ -20013,7 +20052,7 @@
         <v>19.588800000000003</v>
       </c>
     </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
         <v>31</v>
       </c>
@@ -20037,7 +20076,7 @@
         <v>8.7904</v>
       </c>
     </row>
-    <row r="784" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="3" t="s">
         <v>31</v>
       </c>
@@ -20061,7 +20100,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="785" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" s="3" t="s">
         <v>31</v>
       </c>
@@ -20085,7 +20124,7 @@
         <v>16.508800000000001</v>
       </c>
     </row>
-    <row r="786" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" s="3" t="s">
         <v>31</v>
       </c>
@@ -20109,7 +20148,7 @@
         <v>16.9376</v>
       </c>
     </row>
-    <row r="787" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787" s="3" t="s">
         <v>31</v>
       </c>
@@ -20133,7 +20172,7 @@
         <v>21.386399999999998</v>
       </c>
     </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A788" s="3" t="s">
         <v>31</v>
       </c>
@@ -20157,7 +20196,7 @@
         <v>41.003999999999998</v>
       </c>
     </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A789" s="3" t="s">
         <v>31</v>
       </c>
@@ -20181,7 +20220,7 @@
         <v>37.305599999999998</v>
       </c>
     </row>
-    <row r="790" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A790" s="3" t="s">
         <v>31</v>
       </c>
@@ -20205,7 +20244,7 @@
         <v>90.921599999999998</v>
       </c>
     </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A791" s="3" t="s">
         <v>31</v>
       </c>
@@ -20229,7 +20268,7 @@
         <v>81.84</v>
       </c>
     </row>
-    <row r="792" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A792" s="3" t="s">
         <v>60</v>
       </c>
@@ -20253,7 +20292,7 @@
         <v>201.85599999999999</v>
       </c>
     </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A793" s="3" t="s">
         <v>60</v>
       </c>
@@ -20277,7 +20316,7 @@
         <v>246.14400000000001</v>
       </c>
     </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A794" s="3" t="s">
         <v>60</v>
       </c>
@@ -20301,7 +20340,7 @@
         <v>162.34000000000003</v>
       </c>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A795" s="3" t="s">
         <v>60</v>
       </c>
@@ -20325,7 +20364,7 @@
         <v>128.96</v>
       </c>
     </row>
-    <row r="796" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A796" s="3" t="s">
         <v>60</v>
       </c>
@@ -20349,7 +20388,7 @@
         <v>175.39200000000002</v>
       </c>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A797" s="3" t="s">
         <v>60</v>
       </c>
@@ -20373,7 +20412,7 @@
         <v>66.463999999999999</v>
       </c>
     </row>
-    <row r="798" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A798" s="3" t="s">
         <v>60</v>
       </c>
@@ -20397,7 +20436,7 @@
         <v>56.448000000000008</v>
       </c>
     </row>
-    <row r="799" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A799" s="3" t="s">
         <v>60</v>
       </c>
@@ -20421,7 +20460,7 @@
         <v>170.208</v>
       </c>
     </row>
-    <row r="800" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A800" s="3" t="s">
         <v>60</v>
       </c>
@@ -20445,7 +20484,7 @@
         <v>183.00800000000001</v>
       </c>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A801" s="3" t="s">
         <v>60</v>
       </c>
@@ -20469,7 +20508,7 @@
         <v>67.567499999999995</v>
       </c>
     </row>
-    <row r="802" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A802" s="3" t="s">
         <v>60</v>
       </c>
@@ -20493,7 +20532,7 @@
         <v>210.441</v>
       </c>
     </row>
-    <row r="803" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A803" s="3" t="s">
         <v>60</v>
       </c>
@@ -20517,7 +20556,7 @@
         <v>264.74299999999999</v>
       </c>
     </row>
-    <row r="804" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A804" s="3" t="s">
         <v>60</v>
       </c>
@@ -20541,7 +20580,7 @@
         <v>446.44250000000005</v>
       </c>
     </row>
-    <row r="805" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A805" s="3" t="s">
         <v>60</v>
       </c>
@@ -20565,7 +20604,7 @@
         <v>187.71199999999999</v>
       </c>
     </row>
-    <row r="806" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A806" s="3" t="s">
         <v>60</v>
       </c>
@@ -20589,7 +20628,7 @@
         <v>350.75900000000001</v>
       </c>
     </row>
-    <row r="807" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A807" s="3" t="s">
         <v>60</v>
       </c>
@@ -20613,7 +20652,7 @@
         <v>117.5665</v>
       </c>
     </row>
-    <row r="808" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A808" s="3" t="s">
         <v>60</v>
       </c>
@@ -20637,7 +20676,7 @@
         <v>40.105000000000004</v>
       </c>
     </row>
-    <row r="809" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A809" s="3" t="s">
         <v>60</v>
       </c>
@@ -20661,7 +20700,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="810" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A810" s="3" t="s">
         <v>60</v>
       </c>
@@ -20685,7 +20724,7 @@
         <v>109.52500000000001</v>
       </c>
     </row>
-    <row r="811" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A811" s="3" t="s">
         <v>60</v>
       </c>
@@ -20709,7 +20748,7 @@
         <v>24.928000000000001</v>
       </c>
     </row>
-    <row r="812" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A812" s="3" t="s">
         <v>60</v>
       </c>
@@ -20733,7 +20772,7 @@
         <v>76.350999999999999</v>
       </c>
     </row>
-    <row r="813" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A813" s="3" t="s">
         <v>60</v>
       </c>
@@ -20757,7 +20796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A814" s="3" t="s">
         <v>60</v>
       </c>
@@ -20781,7 +20820,7 @@
         <v>426.91800000000006</v>
       </c>
     </row>
-    <row r="815" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A815" s="3" t="s">
         <v>60</v>
       </c>
@@ -20805,7 +20844,7 @@
         <v>21.12</v>
       </c>
     </row>
-    <row r="816" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A816" s="3" t="s">
         <v>60</v>
       </c>
@@ -20829,7 +20868,7 @@
         <v>42.912000000000006</v>
       </c>
     </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A817" s="3" t="s">
         <v>60</v>
       </c>
@@ -20853,7 +20892,7 @@
         <v>266.27199999999999</v>
       </c>
     </row>
-    <row r="818" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A818" s="3" t="s">
         <v>60</v>
       </c>
@@ -20877,7 +20916,7 @@
         <v>225.05600000000001</v>
       </c>
     </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A819" s="3" t="s">
         <v>60</v>
       </c>
@@ -20901,7 +20940,7 @@
         <v>296.55700000000002</v>
       </c>
     </row>
-    <row r="820" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A820" s="3" t="s">
         <v>99</v>
       </c>
@@ -20925,7 +20964,7 @@
         <v>432.81599999999997</v>
       </c>
     </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A821" s="3" t="s">
         <v>99</v>
       </c>
@@ -20949,7 +20988,7 @@
         <v>20.236800000000002</v>
       </c>
     </row>
-    <row r="822" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A822" s="3" t="s">
         <v>99</v>
       </c>
@@ -20973,7 +21012,7 @@
         <v>21.945599999999999</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A823" s="3" t="s">
         <v>99</v>
       </c>
@@ -20997,7 +21036,7 @@
         <v>113.1408</v>
       </c>
     </row>
-    <row r="824" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A824" s="3" t="s">
         <v>99</v>
       </c>
@@ -21021,7 +21060,7 @@
         <v>29.894400000000001</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A825" s="3" t="s">
         <v>99</v>
       </c>
@@ -21045,7 +21084,7 @@
         <v>86.745599999999996</v>
       </c>
     </row>
-    <row r="826" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A826" s="3" t="s">
         <v>99</v>
       </c>
@@ -21069,7 +21108,7 @@
         <v>70.118400000000008</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A827" s="3" t="s">
         <v>99</v>
       </c>
@@ -21093,7 +21132,7 @@
         <v>333.59039999999999</v>
       </c>
     </row>
-    <row r="828" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A828" s="3" t="s">
         <v>99</v>
       </c>
@@ -21117,7 +21156,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A829" s="3" t="s">
         <v>99</v>
       </c>
@@ -21141,7 +21180,7 @@
         <v>48.523199999999996</v>
       </c>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A830" s="3" t="s">
         <v>99</v>
       </c>
@@ -21165,7 +21204,7 @@
         <v>434.98080000000004</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A831" s="3" t="s">
         <v>99</v>
       </c>
@@ -21189,7 +21228,7 @@
         <v>976.43039999999996</v>
       </c>
     </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A832" s="3" t="s">
         <v>99</v>
       </c>
@@ -21213,7 +21252,7 @@
         <v>26.009600000000002</v>
       </c>
     </row>
-    <row r="833" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A833" s="3" t="s">
         <v>99</v>
       </c>
@@ -21237,7 +21276,7 @@
         <v>344.13599999999997</v>
       </c>
     </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A834" s="3" t="s">
         <v>99</v>
       </c>
@@ -21261,7 +21300,7 @@
         <v>218.50400000000002</v>
       </c>
     </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A835" s="3" t="s">
         <v>99</v>
       </c>
@@ -21285,7 +21324,7 @@
         <v>631.55200000000002</v>
       </c>
     </row>
-    <row r="836" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A836" s="3" t="s">
         <v>99</v>
       </c>
@@ -21309,7 +21348,7 @@
         <v>346.77760000000001</v>
       </c>
     </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A837" s="3" t="s">
         <v>99</v>
       </c>
@@ -21333,7 +21372,7 @@
         <v>245.56080000000003</v>
       </c>
     </row>
-    <row r="838" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A838" s="3" t="s">
         <v>99</v>
       </c>
@@ -21357,7 +21396,7 @@
         <v>351.80080000000004</v>
       </c>
     </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A839" s="3" t="s">
         <v>99</v>
       </c>
@@ -21381,7 +21420,7 @@
         <v>17.920000000000002</v>
       </c>
     </row>
-    <row r="840" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A840" s="3" t="s">
         <v>99</v>
       </c>
@@ -21405,7 +21444,7 @@
         <v>225.37439999999998</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A841" s="3" t="s">
         <v>99</v>
       </c>
@@ -21429,7 +21468,7 @@
         <v>482.15519999999998</v>
       </c>
     </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A842" s="3" t="s">
         <v>99</v>
       </c>
@@ -21453,7 +21492,7 @@
         <v>53.486400000000003</v>
       </c>
     </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A843" s="3" t="s">
         <v>99</v>
       </c>
@@ -21477,7 +21516,7 @@
         <v>294.7072</v>
       </c>
     </row>
-    <row r="844" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A844" s="3" t="s">
         <v>99</v>
       </c>
@@ -21501,7 +21540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A845" s="3" t="s">
         <v>129</v>
       </c>
@@ -21525,7 +21564,7 @@
         <v>16.847999999999999</v>
       </c>
     </row>
-    <row r="846" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A846" s="3" t="s">
         <v>129</v>
       </c>
@@ -21549,7 +21588,7 @@
         <v>399.33000000000004</v>
       </c>
     </row>
-    <row r="847" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A847" s="3" t="s">
         <v>129</v>
       </c>
@@ -21573,7 +21612,7 @@
         <v>350.78400000000005</v>
       </c>
     </row>
-    <row r="848" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A848" s="3" t="s">
         <v>129</v>
       </c>
@@ -21597,7 +21636,7 @@
         <v>356.88600000000002</v>
       </c>
     </row>
-    <row r="849" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A849" s="3" t="s">
         <v>129</v>
       </c>
@@ -21621,7 +21660,7 @@
         <v>146.934</v>
       </c>
     </row>
-    <row r="850" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A850" s="3" t="s">
         <v>129</v>
       </c>
@@ -21645,7 +21684,7 @@
         <v>291.54599999999999</v>
       </c>
     </row>
-    <row r="851" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A851" s="3" t="s">
         <v>129</v>
       </c>
@@ -21669,7 +21708,7 @@
         <v>20.484999999999999</v>
       </c>
     </row>
-    <row r="852" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A852" s="3" t="s">
         <v>129</v>
       </c>
@@ -21693,7 +21732,7 @@
         <v>274.11200000000002</v>
       </c>
     </row>
-    <row r="853" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A853" s="3" t="s">
         <v>129</v>
       </c>
@@ -21717,7 +21756,7 @@
         <v>611.91000000000008</v>
       </c>
     </row>
-    <row r="854" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A854" s="3" t="s">
         <v>129</v>
       </c>
@@ -21741,7 +21780,7 @@
         <v>68.415999999999997</v>
       </c>
     </row>
-    <row r="855" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A855" s="3" t="s">
         <v>129</v>
       </c>
@@ -21765,7 +21804,7 @@
         <v>68.864000000000004</v>
       </c>
     </row>
-    <row r="856" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A856" s="3" t="s">
         <v>129</v>
       </c>
@@ -21789,7 +21828,7 @@
         <v>171.45600000000002</v>
       </c>
     </row>
-    <row r="857" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A857" s="3" t="s">
         <v>129</v>
       </c>
@@ -21813,7 +21852,7 @@
         <v>150.976</v>
       </c>
     </row>
-    <row r="858" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A858" s="3" t="s">
         <v>129</v>
       </c>
@@ -21837,7 +21876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="859" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A859" s="3" t="s">
         <v>141</v>
       </c>
@@ -21861,7 +21900,7 @@
         <v>325.31400000000002</v>
       </c>
     </row>
-    <row r="860" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A860" s="3" t="s">
         <v>141</v>
       </c>
@@ -21885,7 +21924,7 @@
         <v>587.13599999999997</v>
       </c>
     </row>
-    <row r="861" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A861" s="3" t="s">
         <v>141</v>
       </c>
@@ -21909,7 +21948,7 @@
         <v>269.76</v>
       </c>
     </row>
-    <row r="862" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A862" s="3" t="s">
         <v>141</v>
       </c>
@@ -21933,7 +21972,7 @@
         <v>551.71199999999999</v>
       </c>
     </row>
-    <row r="863" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A863" s="3" t="s">
         <v>141</v>
       </c>
@@ -21957,7 +21996,7 @@
         <v>505.17200000000003</v>
       </c>
     </row>
-    <row r="864" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A864" s="3" t="s">
         <v>168</v>
       </c>
@@ -21981,7 +22020,7 @@
         <v>108.35899999999999</v>
       </c>
     </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A865" s="3" t="s">
         <v>168</v>
       </c>
@@ -22005,7 +22044,7 @@
         <v>138.845</v>
       </c>
     </row>
-    <row r="866" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A866" s="3" t="s">
         <v>168</v>
       </c>
@@ -22029,7 +22068,7 @@
         <v>138.845</v>
       </c>
     </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A867" s="3" t="s">
         <v>168</v>
       </c>
@@ -22053,7 +22092,7 @@
         <v>185.12700000000001</v>
       </c>
     </row>
-    <row r="868" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A868" s="3" t="s">
         <v>154</v>
       </c>
@@ -22077,7 +22116,7 @@
         <v>352.81400000000002</v>
       </c>
     </row>
-    <row r="869" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A869" s="3" t="s">
         <v>154</v>
       </c>
@@ -22101,7 +22140,7 @@
         <v>170.511</v>
       </c>
     </row>
-    <row r="870" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A870" s="3" t="s">
         <v>154</v>
       </c>
@@ -22125,7 +22164,7 @@
         <v>370.92</v>
       </c>
     </row>
-    <row r="871" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A871" s="3" t="s">
         <v>154</v>
       </c>
@@ -22149,7 +22188,7 @@
         <v>1078.9549999999999</v>
       </c>
     </row>
-    <row r="872" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A872" s="3" t="s">
         <v>154</v>
       </c>
@@ -22173,7 +22212,7 @@
         <v>223.67399999999998</v>
       </c>
     </row>
-    <row r="873" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A873" s="3" t="s">
         <v>154</v>
       </c>
@@ -22197,7 +22236,7 @@
         <v>35.136000000000003</v>
       </c>
     </row>
-    <row r="874" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A874" s="3" t="s">
         <v>169</v>
       </c>
@@ -22221,7 +22260,7 @@
         <v>12.727</v>
       </c>
     </row>
-    <row r="875" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A875" s="3" t="s">
         <v>169</v>
       </c>
@@ -22245,7 +22284,7 @@
         <v>293.59000000000003</v>
       </c>
     </row>
-    <row r="876" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A876" s="3" t="s">
         <v>176</v>
       </c>
@@ -22269,7 +22308,7 @@
         <v>308.55</v>
       </c>
     </row>
-    <row r="877" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A877" s="3" t="s">
         <v>176</v>
       </c>
@@ -22293,7 +22332,7 @@
         <v>487.24200000000002</v>
       </c>
     </row>
-    <row r="878" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A878" s="3" t="s">
         <v>176</v>
       </c>
@@ -22317,7 +22356,7 @@
         <v>57.472000000000008</v>
       </c>
     </row>
-    <row r="879" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A879" s="3" t="s">
         <v>176</v>
       </c>
@@ -22341,7 +22380,7 @@
         <v>148.928</v>
       </c>
     </row>
-    <row r="880" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A880" s="3" t="s">
         <v>176</v>
       </c>
@@ -22365,7 +22404,7 @@
         <v>30.912000000000003</v>
       </c>
     </row>
-    <row r="881" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A881" s="3" t="s">
         <v>176</v>
       </c>
@@ -22389,7 +22428,7 @@
         <v>207.55200000000002</v>
       </c>
     </row>
-    <row r="882" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A882" s="3" t="s">
         <v>179</v>
       </c>
@@ -22413,7 +22452,7 @@
         <v>195.52</v>
       </c>
     </row>
-    <row r="883" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A883" s="3" t="s">
         <v>227</v>
       </c>
@@ -22437,7 +22476,7 @@
         <v>59.768000000000001</v>
       </c>
     </row>
-    <row r="884" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A884" s="3" t="s">
         <v>227</v>
       </c>
@@ -22461,7 +22500,7 @@
         <v>42.966000000000008</v>
       </c>
     </row>
-    <row r="885" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A885" s="3" t="s">
         <v>227</v>
       </c>
@@ -22485,7 +22524,7 @@
         <v>32.67</v>
       </c>
     </row>
-    <row r="886" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A886" s="3" t="s">
         <v>227</v>
       </c>
@@ -22509,7 +22548,7 @@
         <v>436.35600000000005</v>
       </c>
     </row>
-    <row r="887" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A887" s="3" t="s">
         <v>186</v>
       </c>
@@ -22533,7 +22572,7 @@
         <v>28.072800000000001</v>
       </c>
     </row>
-    <row r="888" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A888" s="3" t="s">
         <v>186</v>
       </c>
@@ -22557,7 +22596,7 @@
         <v>269.51679999999999</v>
       </c>
     </row>
-    <row r="889" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A889" s="3" t="s">
         <v>186</v>
       </c>
@@ -22581,7 +22620,7 @@
         <v>127.3856</v>
       </c>
     </row>
-    <row r="890" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A890" s="3" t="s">
         <v>4</v>
       </c>
@@ -22605,7 +22644,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="891" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A891" s="3" t="s">
         <v>4</v>
       </c>
@@ -22629,7 +22668,7 @@
         <v>444.35200000000009</v>
       </c>
     </row>
-    <row r="892" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A892" s="3" t="s">
         <v>4</v>
       </c>
@@ -22653,7 +22692,7 @@
         <v>16.704000000000001</v>
       </c>
     </row>
-    <row r="893" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A893" s="3" t="s">
         <v>4</v>
       </c>
@@ -22677,7 +22716,7 @@
         <v>571.96800000000007</v>
       </c>
     </row>
-    <row r="894" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A894" s="3" t="s">
         <v>4</v>
       </c>
@@ -22701,7 +22740,7 @@
         <v>16.064</v>
       </c>
     </row>
-    <row r="895" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A895" s="3" t="s">
         <v>4</v>
       </c>
@@ -22725,7 +22764,7 @@
         <v>217.81399999999999</v>
       </c>
     </row>
-    <row r="896" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A896" s="3" t="s">
         <v>4</v>
       </c>
@@ -22749,7 +22788,7 @@
         <v>12.48</v>
       </c>
     </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A897" s="3" t="s">
         <v>4</v>
       </c>
@@ -22773,7 +22812,7 @@
         <v>92.50200000000001</v>
       </c>
     </row>
-    <row r="898" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A898" s="3" t="s">
         <v>4</v>
       </c>
@@ -22797,7 +22836,7 @@
         <v>124.67200000000001</v>
       </c>
     </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A899" s="3" t="s">
         <v>4</v>
       </c>
@@ -22821,7 +22860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="900" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A900" s="3" t="s">
         <v>4</v>
       </c>
@@ -22845,7 +22884,7 @@
         <v>66.088999999999999</v>
       </c>
     </row>
-    <row r="901" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A901" s="3" t="s">
         <v>27</v>
       </c>
@@ -22865,11 +22904,11 @@
         <v>0.1</v>
       </c>
       <c r="G901" s="2">
-        <f>E901*F901</f>
+        <f t="shared" ref="G901:G932" si="11">E901*F901</f>
         <v>1097.452</v>
       </c>
     </row>
-    <row r="902" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A902" s="3" t="s">
         <v>31</v>
       </c>
@@ -22889,11 +22928,11 @@
         <v>0.08</v>
       </c>
       <c r="G902" s="2">
-        <f>E902*F902</f>
+        <f t="shared" si="11"/>
         <v>535.55200000000002</v>
       </c>
     </row>
-    <row r="903" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A903" s="3" t="s">
         <v>31</v>
       </c>
@@ -22913,11 +22952,11 @@
         <v>0.08</v>
       </c>
       <c r="G903" s="2">
-        <f>E903*F903</f>
+        <f t="shared" si="11"/>
         <v>494.13120000000004</v>
       </c>
     </row>
-    <row r="904" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A904" s="3" t="s">
         <v>31</v>
       </c>
@@ -22937,11 +22976,11 @@
         <v>0.08</v>
       </c>
       <c r="G904" s="2">
-        <f>E904*F904</f>
+        <f t="shared" si="11"/>
         <v>201.88159999999999</v>
       </c>
     </row>
-    <row r="905" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A905" s="3" t="s">
         <v>31</v>
       </c>
@@ -22961,11 +23000,11 @@
         <v>0.08</v>
       </c>
       <c r="G905" s="2">
-        <f>E905*F905</f>
+        <f t="shared" si="11"/>
         <v>149.9136</v>
       </c>
     </row>
-    <row r="906" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A906" s="3" t="s">
         <v>31</v>
       </c>
@@ -22985,11 +23024,11 @@
         <v>0.08</v>
       </c>
       <c r="G906" s="2">
-        <f>E906*F906</f>
+        <f t="shared" si="11"/>
         <v>161.43360000000001</v>
       </c>
     </row>
-    <row r="907" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A907" s="3" t="s">
         <v>31</v>
       </c>
@@ -23009,11 +23048,11 @@
         <v>0.08</v>
       </c>
       <c r="G907" s="2">
-        <f>E907*F907</f>
+        <f t="shared" si="11"/>
         <v>129.2544</v>
       </c>
     </row>
-    <row r="908" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A908" s="3" t="s">
         <v>31</v>
       </c>
@@ -23033,11 +23072,11 @@
         <v>0.08</v>
       </c>
       <c r="G908" s="2">
-        <f>E908*F908</f>
+        <f t="shared" si="11"/>
         <v>186.03279999999998</v>
       </c>
     </row>
-    <row r="909" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A909" s="3" t="s">
         <v>31</v>
       </c>
@@ -23057,11 +23096,11 @@
         <v>0.08</v>
       </c>
       <c r="G909" s="2">
-        <f>E909*F909</f>
+        <f t="shared" si="11"/>
         <v>206.99200000000002</v>
       </c>
     </row>
-    <row r="910" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A910" s="3" t="s">
         <v>31</v>
       </c>
@@ -23081,11 +23120,11 @@
         <v>0.08</v>
       </c>
       <c r="G910" s="2">
-        <f>E910*F910</f>
+        <f t="shared" si="11"/>
         <v>397.71839999999997</v>
       </c>
     </row>
-    <row r="911" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A911" s="3" t="s">
         <v>31</v>
       </c>
@@ -23105,11 +23144,11 @@
         <v>0.08</v>
       </c>
       <c r="G911" s="2">
-        <f>E911*F911</f>
+        <f t="shared" si="11"/>
         <v>164.00479999999999</v>
       </c>
     </row>
-    <row r="912" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A912" s="3" t="s">
         <v>31</v>
       </c>
@@ -23129,11 +23168,11 @@
         <v>0.08</v>
       </c>
       <c r="G912" s="2">
-        <f>E912*F912</f>
+        <f t="shared" si="11"/>
         <v>56.601599999999998</v>
       </c>
     </row>
-    <row r="913" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A913" s="3" t="s">
         <v>31</v>
       </c>
@@ -23153,11 +23192,11 @@
         <v>0.08</v>
       </c>
       <c r="G913" s="2">
-        <f>E913*F913</f>
+        <f t="shared" si="11"/>
         <v>23.073600000000003</v>
       </c>
     </row>
-    <row r="914" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A914" s="3" t="s">
         <v>31</v>
       </c>
@@ -23177,11 +23216,11 @@
         <v>0.08</v>
       </c>
       <c r="G914" s="2">
-        <f>E914*F914</f>
+        <f t="shared" si="11"/>
         <v>103.23360000000001</v>
       </c>
     </row>
-    <row r="915" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A915" s="3" t="s">
         <v>31</v>
       </c>
@@ -23201,11 +23240,11 @@
         <v>0.08</v>
       </c>
       <c r="G915" s="2">
-        <f>E915*F915</f>
+        <f t="shared" si="11"/>
         <v>32.155200000000001</v>
       </c>
     </row>
-    <row r="916" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A916" s="3" t="s">
         <v>31</v>
       </c>
@@ -23225,11 +23264,11 @@
         <v>0.08</v>
       </c>
       <c r="G916" s="2">
-        <f>E916*F916</f>
+        <f t="shared" si="11"/>
         <v>144.9248</v>
       </c>
     </row>
-    <row r="917" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A917" s="3" t="s">
         <v>31</v>
       </c>
@@ -23249,11 +23288,11 @@
         <v>0.08</v>
       </c>
       <c r="G917" s="2">
-        <f>E917*F917</f>
+        <f t="shared" si="11"/>
         <v>103.27680000000001</v>
       </c>
     </row>
-    <row r="918" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A918" s="3" t="s">
         <v>31</v>
       </c>
@@ -23273,11 +23312,11 @@
         <v>0.08</v>
       </c>
       <c r="G918" s="2">
-        <f>E918*F918</f>
+        <f t="shared" si="11"/>
         <v>19.876799999999999</v>
       </c>
     </row>
-    <row r="919" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A919" s="3" t="s">
         <v>31</v>
       </c>
@@ -23297,11 +23336,11 @@
         <v>0.08</v>
       </c>
       <c r="G919" s="2">
-        <f>E919*F919</f>
+        <f t="shared" si="11"/>
         <v>9.7552000000000003</v>
       </c>
     </row>
-    <row r="920" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A920" s="3" t="s">
         <v>31</v>
       </c>
@@ -23321,11 +23360,11 @@
         <v>0.08</v>
       </c>
       <c r="G920" s="2">
-        <f>E920*F920</f>
+        <f t="shared" si="11"/>
         <v>32.976799999999997</v>
       </c>
     </row>
-    <row r="921" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A921" s="3" t="s">
         <v>31</v>
       </c>
@@ -23345,11 +23384,11 @@
         <v>0.08</v>
       </c>
       <c r="G921" s="2">
-        <f>E921*F921</f>
+        <f t="shared" si="11"/>
         <v>27.441599999999998</v>
       </c>
     </row>
-    <row r="922" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A922" s="3" t="s">
         <v>31</v>
       </c>
@@ -23369,11 +23408,11 @@
         <v>0.08</v>
       </c>
       <c r="G922" s="2">
-        <f>E922*F922</f>
+        <f t="shared" si="11"/>
         <v>21.386399999999998</v>
       </c>
     </row>
-    <row r="923" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A923" s="3" t="s">
         <v>31</v>
       </c>
@@ -23393,11 +23432,11 @@
         <v>0.08</v>
       </c>
       <c r="G923" s="2">
-        <f>E923*F923</f>
+        <f t="shared" si="11"/>
         <v>37.895200000000003</v>
       </c>
     </row>
-    <row r="924" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A924" s="3" t="s">
         <v>31</v>
       </c>
@@ -23417,11 +23456,11 @@
         <v>0.08</v>
       </c>
       <c r="G924" s="2">
-        <f>E924*F924</f>
+        <f t="shared" si="11"/>
         <v>63.087200000000003</v>
       </c>
     </row>
-    <row r="925" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A925" s="3" t="s">
         <v>31</v>
       </c>
@@ -23441,11 +23480,11 @@
         <v>0.08</v>
       </c>
       <c r="G925" s="2">
-        <f>E925*F925</f>
+        <f t="shared" si="11"/>
         <v>48.883199999999995</v>
       </c>
     </row>
-    <row r="926" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A926" s="3" t="s">
         <v>31</v>
       </c>
@@ -23465,11 +23504,11 @@
         <v>0.08</v>
       </c>
       <c r="G926" s="2">
-        <f>E926*F926</f>
+        <f t="shared" si="11"/>
         <v>110.616</v>
       </c>
     </row>
-    <row r="927" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A927" s="3" t="s">
         <v>31</v>
       </c>
@@ -23489,11 +23528,11 @@
         <v>0.08</v>
       </c>
       <c r="G927" s="2">
-        <f>E927*F927</f>
+        <f t="shared" si="11"/>
         <v>85.0608</v>
       </c>
     </row>
-    <row r="928" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A928" s="3" t="s">
         <v>60</v>
       </c>
@@ -23513,11 +23552,11 @@
         <v>0.05</v>
       </c>
       <c r="G928" s="2">
-        <f>E928*F928</f>
+        <f t="shared" si="11"/>
         <v>231.39200000000002</v>
       </c>
     </row>
-    <row r="929" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A929" s="3" t="s">
         <v>60</v>
       </c>
@@ -23537,11 +23576,11 @@
         <v>0.05</v>
       </c>
       <c r="G929" s="2">
-        <f>E929*F929</f>
+        <f t="shared" si="11"/>
         <v>233.40800000000002</v>
       </c>
     </row>
-    <row r="930" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A930" s="3" t="s">
         <v>60</v>
       </c>
@@ -23561,11 +23600,11 @@
         <v>0.05</v>
       </c>
       <c r="G930" s="2">
-        <f>E930*F930</f>
+        <f t="shared" si="11"/>
         <v>134.1925</v>
       </c>
     </row>
-    <row r="931" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A931" s="3" t="s">
         <v>60</v>
       </c>
@@ -23585,11 +23624,11 @@
         <v>0.05</v>
       </c>
       <c r="G931" s="2">
-        <f>E931*F931</f>
+        <f t="shared" si="11"/>
         <v>185.21550000000002</v>
       </c>
     </row>
-    <row r="932" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A932" s="3" t="s">
         <v>60</v>
       </c>
@@ -23609,11 +23648,11 @@
         <v>0.05</v>
       </c>
       <c r="G932" s="2">
-        <f>E932*F932</f>
+        <f t="shared" si="11"/>
         <v>571.42399999999998</v>
       </c>
     </row>
-    <row r="933" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A933" s="3" t="s">
         <v>60</v>
       </c>
@@ -23633,11 +23672,11 @@
         <v>0.05</v>
       </c>
       <c r="G933" s="2">
-        <f>E933*F933</f>
+        <f t="shared" ref="G933:G964" si="12">E933*F933</f>
         <v>85.632000000000005</v>
       </c>
     </row>
-    <row r="934" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A934" s="3" t="s">
         <v>60</v>
       </c>
@@ -23657,11 +23696,11 @@
         <v>0.05</v>
       </c>
       <c r="G934" s="2">
-        <f>E934*F934</f>
+        <f t="shared" si="12"/>
         <v>117.95250000000001</v>
       </c>
     </row>
-    <row r="935" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A935" s="3" t="s">
         <v>60</v>
       </c>
@@ -23681,11 +23720,11 @@
         <v>0.05</v>
       </c>
       <c r="G935" s="2">
-        <f>E935*F935</f>
+        <f t="shared" si="12"/>
         <v>154.976</v>
       </c>
     </row>
-    <row r="936" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A936" s="3" t="s">
         <v>60</v>
       </c>
@@ -23705,11 +23744,11 @@
         <v>0.05</v>
       </c>
       <c r="G936" s="2">
-        <f>E936*F936</f>
+        <f t="shared" si="12"/>
         <v>134.29000000000002</v>
       </c>
     </row>
-    <row r="937" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A937" s="3" t="s">
         <v>60</v>
       </c>
@@ -23729,11 +23768,11 @@
         <v>0.05</v>
       </c>
       <c r="G937" s="2">
-        <f>E937*F937</f>
+        <f t="shared" si="12"/>
         <v>220.24200000000002</v>
       </c>
     </row>
-    <row r="938" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A938" s="3" t="s">
         <v>60</v>
       </c>
@@ -23753,11 +23792,11 @@
         <v>0.05</v>
       </c>
       <c r="G938" s="2">
-        <f>E938*F938</f>
+        <f t="shared" si="12"/>
         <v>162.6695</v>
       </c>
     </row>
-    <row r="939" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A939" s="3" t="s">
         <v>60</v>
       </c>
@@ -23777,11 +23816,11 @@
         <v>0.05</v>
       </c>
       <c r="G939" s="2">
-        <f>E939*F939</f>
+        <f t="shared" si="12"/>
         <v>504.83199999999999</v>
       </c>
     </row>
-    <row r="940" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A940" s="3" t="s">
         <v>60</v>
       </c>
@@ -23801,11 +23840,11 @@
         <v>0.05</v>
       </c>
       <c r="G940" s="2">
-        <f>E940*F940</f>
+        <f t="shared" si="12"/>
         <v>164.352</v>
       </c>
     </row>
-    <row r="941" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A941" s="3" t="s">
         <v>60</v>
       </c>
@@ -23825,11 +23864,11 @@
         <v>0.05</v>
       </c>
       <c r="G941" s="2">
-        <f>E941*F941</f>
+        <f t="shared" si="12"/>
         <v>403.71500000000003</v>
       </c>
     </row>
-    <row r="942" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A942" s="3" t="s">
         <v>60</v>
       </c>
@@ -23849,11 +23888,11 @@
         <v>0.05</v>
       </c>
       <c r="G942" s="2">
-        <f>E942*F942</f>
+        <f t="shared" si="12"/>
         <v>143.494</v>
       </c>
     </row>
-    <row r="943" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A943" s="3" t="s">
         <v>60</v>
       </c>
@@ -23873,11 +23912,11 @@
         <v>0.05</v>
       </c>
       <c r="G943" s="2">
-        <f>E943*F943</f>
+        <f t="shared" si="12"/>
         <v>47.287500000000001</v>
       </c>
     </row>
-    <row r="944" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A944" s="3" t="s">
         <v>60</v>
       </c>
@@ -23897,11 +23936,11 @@
         <v>0.05</v>
       </c>
       <c r="G944" s="2">
-        <f>E944*F944</f>
+        <f t="shared" si="12"/>
         <v>29.632000000000001</v>
       </c>
     </row>
-    <row r="945" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A945" s="3" t="s">
         <v>60</v>
       </c>
@@ -23921,11 +23960,11 @@
         <v>0.05</v>
       </c>
       <c r="G945" s="2">
-        <f>E945*F945</f>
+        <f t="shared" si="12"/>
         <v>268.25500000000005</v>
       </c>
     </row>
-    <row r="946" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A946" s="3" t="s">
         <v>60</v>
       </c>
@@ -23945,11 +23984,11 @@
         <v>0.05</v>
       </c>
       <c r="G946" s="2">
-        <f>E946*F946</f>
+        <f t="shared" si="12"/>
         <v>18.880000000000003</v>
       </c>
     </row>
-    <row r="947" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A947" s="3" t="s">
         <v>60</v>
       </c>
@@ -23969,11 +24008,11 @@
         <v>0.05</v>
       </c>
       <c r="G947" s="2">
-        <f>E947*F947</f>
+        <f t="shared" si="12"/>
         <v>247.20000000000002</v>
       </c>
     </row>
-    <row r="948" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A948" s="3" t="s">
         <v>60</v>
       </c>
@@ -23993,11 +24032,11 @@
         <v>0.05</v>
       </c>
       <c r="G948" s="2">
-        <f>E948*F948</f>
+        <f t="shared" si="12"/>
         <v>352.26600000000002</v>
       </c>
     </row>
-    <row r="949" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A949" s="3" t="s">
         <v>60</v>
       </c>
@@ -24017,11 +24056,11 @@
         <v>0.05</v>
       </c>
       <c r="G949" s="2">
-        <f>E949*F949</f>
+        <f t="shared" si="12"/>
         <v>10.88</v>
       </c>
     </row>
-    <row r="950" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A950" s="3" t="s">
         <v>60</v>
       </c>
@@ -24041,11 +24080,11 @@
         <v>0.05</v>
       </c>
       <c r="G950" s="2">
-        <f>E950*F950</f>
+        <f t="shared" si="12"/>
         <v>48.384</v>
       </c>
     </row>
-    <row r="951" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A951" s="3" t="s">
         <v>60</v>
       </c>
@@ -24065,11 +24104,11 @@
         <v>0.05</v>
       </c>
       <c r="G951" s="2">
-        <f>E951*F951</f>
+        <f t="shared" si="12"/>
         <v>258.17950000000002</v>
       </c>
     </row>
-    <row r="952" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A952" s="3" t="s">
         <v>60</v>
       </c>
@@ -24089,11 +24128,11 @@
         <v>0.05</v>
       </c>
       <c r="G952" s="2">
-        <f>E952*F952</f>
+        <f t="shared" si="12"/>
         <v>246.56</v>
       </c>
     </row>
-    <row r="953" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A953" s="3" t="s">
         <v>60</v>
       </c>
@@ -24113,11 +24152,11 @@
         <v>0.05</v>
       </c>
       <c r="G953" s="2">
-        <f>E953*F953</f>
+        <f t="shared" si="12"/>
         <v>345.024</v>
       </c>
     </row>
-    <row r="954" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A954" s="3" t="s">
         <v>60</v>
       </c>
@@ -24137,11 +24176,11 @@
         <v>0.05</v>
       </c>
       <c r="G954" s="2">
-        <f>E954*F954</f>
+        <f t="shared" si="12"/>
         <v>337.935</v>
       </c>
     </row>
-    <row r="955" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A955" s="3" t="s">
         <v>99</v>
       </c>
@@ -24161,11 +24200,11 @@
         <v>0.08</v>
       </c>
       <c r="G955" s="2">
-        <f>E955*F955</f>
+        <f t="shared" si="12"/>
         <v>417.23040000000003</v>
       </c>
     </row>
-    <row r="956" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A956" s="3" t="s">
         <v>99</v>
       </c>
@@ -24185,11 +24224,11 @@
         <v>0.08</v>
       </c>
       <c r="G956" s="2">
-        <f>E956*F956</f>
+        <f t="shared" si="12"/>
         <v>20.2912</v>
       </c>
     </row>
-    <row r="957" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A957" s="3" t="s">
         <v>99</v>
       </c>
@@ -24209,11 +24248,11 @@
         <v>0.08</v>
       </c>
       <c r="G957" s="2">
-        <f>E957*F957</f>
+        <f t="shared" si="12"/>
         <v>23.630400000000002</v>
       </c>
     </row>
-    <row r="958" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A958" s="3" t="s">
         <v>99</v>
       </c>
@@ -24233,11 +24272,11 @@
         <v>0.08</v>
       </c>
       <c r="G958" s="2">
-        <f>E958*F958</f>
+        <f t="shared" si="12"/>
         <v>85.75200000000001</v>
       </c>
     </row>
-    <row r="959" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A959" s="3" t="s">
         <v>99</v>
       </c>
@@ -24257,11 +24296,11 @@
         <v>0.08</v>
       </c>
       <c r="G959" s="2">
-        <f>E959*F959</f>
+        <f t="shared" si="12"/>
         <v>31.017600000000002</v>
       </c>
     </row>
-    <row r="960" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A960" s="3" t="s">
         <v>99</v>
       </c>
@@ -24281,11 +24320,11 @@
         <v>0.08</v>
       </c>
       <c r="G960" s="2">
-        <f>E960*F960</f>
+        <f t="shared" si="12"/>
         <v>96.983999999999995</v>
       </c>
     </row>
-    <row r="961" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A961" s="3" t="s">
         <v>99</v>
       </c>
@@ -24305,11 +24344,11 @@
         <v>0.08</v>
       </c>
       <c r="G961" s="2">
-        <f>E961*F961</f>
+        <f t="shared" si="12"/>
         <v>79.728000000000009</v>
       </c>
     </row>
-    <row r="962" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A962" s="3" t="s">
         <v>99</v>
       </c>
@@ -24329,11 +24368,11 @@
         <v>0.08</v>
       </c>
       <c r="G962" s="2">
-        <f>E962*F962</f>
+        <f t="shared" si="12"/>
         <v>341.66879999999998</v>
       </c>
     </row>
-    <row r="963" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A963" s="3" t="s">
         <v>99</v>
       </c>
@@ -24353,11 +24392,11 @@
         <v>0.08</v>
       </c>
       <c r="G963" s="2">
-        <f>E963*F963</f>
+        <f t="shared" si="12"/>
         <v>75.303200000000004</v>
       </c>
     </row>
-    <row r="964" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A964" s="3" t="s">
         <v>99</v>
       </c>
@@ -24377,11 +24416,11 @@
         <v>0.08</v>
       </c>
       <c r="G964" s="2">
-        <f>E964*F964</f>
+        <f t="shared" si="12"/>
         <v>55.968000000000004</v>
       </c>
     </row>
-    <row r="965" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A965" s="3" t="s">
         <v>99</v>
       </c>
@@ -24401,11 +24440,11 @@
         <v>0.08</v>
       </c>
       <c r="G965" s="2">
-        <f>E965*F965</f>
+        <f t="shared" ref="G965:G996" si="13">E965*F965</f>
         <v>443.10239999999999</v>
       </c>
     </row>
-    <row r="966" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A966" s="3" t="s">
         <v>99</v>
       </c>
@@ -24425,11 +24464,11 @@
         <v>0.08</v>
       </c>
       <c r="G966" s="2">
-        <f>E966*F966</f>
+        <f t="shared" si="13"/>
         <v>610.90559999999994</v>
       </c>
     </row>
-    <row r="967" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A967" s="3" t="s">
         <v>99</v>
       </c>
@@ -24449,11 +24488,11 @@
         <v>0.08</v>
       </c>
       <c r="G967" s="2">
-        <f>E967*F967</f>
+        <f t="shared" si="13"/>
         <v>15.9232</v>
       </c>
     </row>
-    <row r="968" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A968" s="3" t="s">
         <v>99</v>
       </c>
@@ -24473,11 +24512,11 @@
         <v>0.08</v>
       </c>
       <c r="G968" s="2">
-        <f>E968*F968</f>
+        <f t="shared" si="13"/>
         <v>288.60000000000002</v>
       </c>
     </row>
-    <row r="969" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A969" s="3" t="s">
         <v>99</v>
       </c>
@@ -24497,11 +24536,11 @@
         <v>0.08</v>
       </c>
       <c r="G969" s="2">
-        <f>E969*F969</f>
+        <f t="shared" si="13"/>
         <v>122.97920000000001</v>
       </c>
     </row>
-    <row r="970" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A970" s="3" t="s">
         <v>99</v>
       </c>
@@ -24521,11 +24560,11 @@
         <v>0.08</v>
       </c>
       <c r="G970" s="2">
-        <f>E970*F970</f>
+        <f t="shared" si="13"/>
         <v>561.86879999999996</v>
       </c>
     </row>
-    <row r="971" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A971" s="3" t="s">
         <v>99</v>
       </c>
@@ -24545,11 +24584,11 @@
         <v>0.08</v>
       </c>
       <c r="G971" s="2">
-        <f>E971*F971</f>
+        <f t="shared" si="13"/>
         <v>263.68</v>
       </c>
     </row>
-    <row r="972" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A972" s="3" t="s">
         <v>99</v>
       </c>
@@ -24569,11 +24608,11 @@
         <v>0.08</v>
       </c>
       <c r="G972" s="2">
-        <f>E972*F972</f>
+        <f t="shared" si="13"/>
         <v>235.46080000000003</v>
       </c>
     </row>
-    <row r="973" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A973" s="3" t="s">
         <v>99</v>
       </c>
@@ -24593,11 +24632,11 @@
         <v>0.08</v>
       </c>
       <c r="G973" s="2">
-        <f>E973*F973</f>
+        <f t="shared" si="13"/>
         <v>126.256</v>
       </c>
     </row>
-    <row r="974" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A974" s="3" t="s">
         <v>99</v>
       </c>
@@ -24617,11 +24656,11 @@
         <v>0.08</v>
       </c>
       <c r="G974" s="2">
-        <f>E974*F974</f>
+        <f t="shared" si="13"/>
         <v>11.366400000000001</v>
       </c>
     </row>
-    <row r="975" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A975" s="3" t="s">
         <v>99</v>
       </c>
@@ -24641,11 +24680,11 @@
         <v>0.08</v>
       </c>
       <c r="G975" s="2">
-        <f>E975*F975</f>
+        <f t="shared" si="13"/>
         <v>80.913600000000002</v>
       </c>
     </row>
-    <row r="976" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A976" s="3" t="s">
         <v>99</v>
       </c>
@@ -24665,11 +24704,11 @@
         <v>0.08</v>
       </c>
       <c r="G976" s="2">
-        <f>E976*F976</f>
+        <f t="shared" si="13"/>
         <v>135.82079999999999</v>
       </c>
     </row>
-    <row r="977" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A977" s="3" t="s">
         <v>99</v>
       </c>
@@ -24689,11 +24728,11 @@
         <v>0.08</v>
       </c>
       <c r="G977" s="2">
-        <f>E977*F977</f>
+        <f t="shared" si="13"/>
         <v>55.862400000000001</v>
       </c>
     </row>
-    <row r="978" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A978" s="3" t="s">
         <v>99</v>
       </c>
@@ -24713,11 +24752,11 @@
         <v>0.08</v>
       </c>
       <c r="G978" s="2">
-        <f>E978*F978</f>
+        <f t="shared" si="13"/>
         <v>358.7072</v>
       </c>
     </row>
-    <row r="979" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A979" s="3" t="s">
         <v>99</v>
       </c>
@@ -24737,11 +24776,11 @@
         <v>0.08</v>
       </c>
       <c r="G979" s="2">
-        <f>E979*F979</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="980" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A980" s="3" t="s">
         <v>99</v>
       </c>
@@ -24761,11 +24800,11 @@
         <v>0.08</v>
       </c>
       <c r="G980" s="2">
-        <f>E980*F980</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="981" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A981" s="3" t="s">
         <v>99</v>
       </c>
@@ -24785,11 +24824,11 @@
         <v>0.08</v>
       </c>
       <c r="G981" s="2">
-        <f>E981*F981</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="982" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A982" s="3" t="s">
         <v>99</v>
       </c>
@@ -24809,11 +24848,11 @@
         <v>0.08</v>
       </c>
       <c r="G982" s="2">
-        <f>E982*F982</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="983" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A983" s="3" t="s">
         <v>129</v>
       </c>
@@ -24833,11 +24872,11 @@
         <v>0.1</v>
       </c>
       <c r="G983" s="2">
-        <f>E983*F983</f>
+        <f t="shared" si="13"/>
         <v>109.512</v>
       </c>
     </row>
-    <row r="984" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A984" s="3" t="s">
         <v>129</v>
       </c>
@@ -24857,11 +24896,11 @@
         <v>0.1</v>
       </c>
       <c r="G984" s="2">
-        <f>E984*F984</f>
+        <f t="shared" si="13"/>
         <v>431.08199999999999</v>
       </c>
     </row>
-    <row r="985" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A985" s="3" t="s">
         <v>129</v>
       </c>
@@ -24881,11 +24920,11 @@
         <v>0.1</v>
       </c>
       <c r="G985" s="2">
-        <f>E985*F985</f>
+        <f t="shared" si="13"/>
         <v>605.76599999999996</v>
       </c>
     </row>
-    <row r="986" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A986" s="3" t="s">
         <v>129</v>
       </c>
@@ -24905,11 +24944,11 @@
         <v>0.1</v>
       </c>
       <c r="G986" s="2">
-        <f>E986*F986</f>
+        <f t="shared" si="13"/>
         <v>189.86400000000003</v>
       </c>
     </row>
-    <row r="987" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A987" s="3" t="s">
         <v>129</v>
       </c>
@@ -24929,11 +24968,11 @@
         <v>0.1</v>
       </c>
       <c r="G987" s="2">
-        <f>E987*F987</f>
+        <f t="shared" si="13"/>
         <v>466.45200000000006</v>
       </c>
     </row>
-    <row r="988" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A988" s="3" t="s">
         <v>129</v>
       </c>
@@ -24953,11 +24992,11 @@
         <v>0.1</v>
       </c>
       <c r="G988" s="2">
-        <f>E988*F988</f>
+        <f t="shared" si="13"/>
         <v>15.062000000000001</v>
       </c>
     </row>
-    <row r="989" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A989" s="3" t="s">
         <v>129</v>
       </c>
@@ -24977,11 +25016,11 @@
         <v>0.1</v>
       </c>
       <c r="G989" s="2">
-        <f>E989*F989</f>
+        <f t="shared" si="13"/>
         <v>186.50200000000001</v>
       </c>
     </row>
-    <row r="990" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A990" s="3" t="s">
         <v>129</v>
       </c>
@@ -25001,11 +25040,11 @@
         <v>0.1</v>
       </c>
       <c r="G990" s="2">
-        <f>E990*F990</f>
+        <f t="shared" si="13"/>
         <v>708.69500000000005</v>
       </c>
     </row>
-    <row r="991" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A991" s="3" t="s">
         <v>129</v>
       </c>
@@ -25025,11 +25064,11 @@
         <v>0.1</v>
       </c>
       <c r="G991" s="2">
-        <f>E991*F991</f>
+        <f t="shared" si="13"/>
         <v>79.616</v>
       </c>
     </row>
-    <row r="992" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A992" s="3" t="s">
         <v>129</v>
       </c>
@@ -25049,11 +25088,11 @@
         <v>0.1</v>
       </c>
       <c r="G992" s="2">
-        <f>E992*F992</f>
+        <f t="shared" si="13"/>
         <v>87.68</v>
       </c>
     </row>
-    <row r="993" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A993" s="3" t="s">
         <v>129</v>
       </c>
@@ -25073,11 +25112,11 @@
         <v>0.1</v>
       </c>
       <c r="G993" s="2">
-        <f>E993*F993</f>
+        <f t="shared" si="13"/>
         <v>179.96800000000002</v>
       </c>
     </row>
-    <row r="994" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A994" s="3" t="s">
         <v>129</v>
       </c>
@@ -25097,11 +25136,11 @@
         <v>0.1</v>
       </c>
       <c r="G994" s="2">
-        <f>E994*F994</f>
+        <f t="shared" si="13"/>
         <v>150.01600000000002</v>
       </c>
     </row>
-    <row r="995" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A995" s="3" t="s">
         <v>129</v>
       </c>
@@ -25121,11 +25160,11 @@
         <v>0.1</v>
       </c>
       <c r="G995" s="2">
-        <f>E995*F995</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="996" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A996" s="3" t="s">
         <v>141</v>
       </c>
@@ -25145,11 +25184,11 @@
         <v>0.1</v>
       </c>
       <c r="G996" s="2">
-        <f>E996*F996</f>
+        <f t="shared" si="13"/>
         <v>315.87600000000003</v>
       </c>
     </row>
-    <row r="997" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A997" s="3" t="s">
         <v>141</v>
       </c>
@@ -25169,11 +25208,11 @@
         <v>0.1</v>
       </c>
       <c r="G997" s="2">
-        <f>E997*F997</f>
+        <f t="shared" ref="G997:G1028" si="14">E997*F997</f>
         <v>630.14400000000001</v>
       </c>
     </row>
-    <row r="998" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A998" s="3" t="s">
         <v>141</v>
       </c>
@@ -25193,11 +25232,11 @@
         <v>0.1</v>
       </c>
       <c r="G998" s="2">
-        <f>E998*F998</f>
+        <f t="shared" si="14"/>
         <v>284.99200000000002</v>
       </c>
     </row>
-    <row r="999" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A999" s="3" t="s">
         <v>141</v>
       </c>
@@ -25217,11 +25256,11 @@
         <v>0.1</v>
       </c>
       <c r="G999" s="2">
-        <f>E999*F999</f>
+        <f t="shared" si="14"/>
         <v>730.46400000000006</v>
       </c>
     </row>
-    <row r="1000" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1000" s="3" t="s">
         <v>141</v>
       </c>
@@ -25241,11 +25280,11 @@
         <v>0.1</v>
       </c>
       <c r="G1000" s="2">
-        <f>E1000*F1000</f>
+        <f t="shared" si="14"/>
         <v>530.87600000000009</v>
       </c>
     </row>
-    <row r="1001" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1001" s="3" t="s">
         <v>168</v>
       </c>
@@ -25265,11 +25304,11 @@
         <v>0.1</v>
       </c>
       <c r="G1001" s="2">
-        <f>E1001*F1001</f>
+        <f t="shared" si="14"/>
         <v>128.76600000000002</v>
       </c>
     </row>
-    <row r="1002" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1002" s="3" t="s">
         <v>168</v>
       </c>
@@ -25289,11 +25328,11 @@
         <v>0.1</v>
       </c>
       <c r="G1002" s="2">
-        <f>E1002*F1002</f>
+        <f t="shared" si="14"/>
         <v>122.15</v>
       </c>
     </row>
-    <row r="1003" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1003" s="3" t="s">
         <v>168</v>
       </c>
@@ -25313,11 +25352,11 @@
         <v>0.1</v>
       </c>
       <c r="G1003" s="2">
-        <f>E1003*F1003</f>
+        <f t="shared" si="14"/>
         <v>122.15</v>
       </c>
     </row>
-    <row r="1004" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1004" s="3" t="s">
         <v>168</v>
       </c>
@@ -25337,11 +25376,11 @@
         <v>0.1</v>
       </c>
       <c r="G1004" s="2">
-        <f>E1004*F1004</f>
+        <f t="shared" si="14"/>
         <v>162.86700000000002</v>
       </c>
     </row>
-    <row r="1005" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1005" s="3" t="s">
         <v>154</v>
       </c>
@@ -25361,11 +25400,11 @@
         <v>0.1</v>
       </c>
       <c r="G1005" s="2">
-        <f>E1005*F1005</f>
+        <f t="shared" si="14"/>
         <v>394.72399999999999</v>
       </c>
     </row>
-    <row r="1006" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1006" s="3" t="s">
         <v>154</v>
       </c>
@@ -25385,11 +25424,11 @@
         <v>0.1</v>
       </c>
       <c r="G1006" s="2">
-        <f>E1006*F1006</f>
+        <f t="shared" si="14"/>
         <v>220.53899999999999</v>
       </c>
     </row>
-    <row r="1007" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1007" s="3" t="s">
         <v>154</v>
       </c>
@@ -25409,11 +25448,11 @@
         <v>0.1</v>
       </c>
       <c r="G1007" s="2">
-        <f>E1007*F1007</f>
+        <f t="shared" si="14"/>
         <v>406.29600000000005</v>
       </c>
     </row>
-    <row r="1008" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1008" s="3" t="s">
         <v>154</v>
       </c>
@@ -25433,11 +25472,11 @@
         <v>0.1</v>
       </c>
       <c r="G1008" s="2">
-        <f>E1008*F1008</f>
+        <f t="shared" si="14"/>
         <v>168.96</v>
       </c>
     </row>
-    <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1009" s="3" t="s">
         <v>154</v>
       </c>
@@ -25457,11 +25496,11 @@
         <v>0.1</v>
       </c>
       <c r="G1009" s="2">
-        <f>E1009*F1009</f>
+        <f t="shared" si="14"/>
         <v>96.03</v>
       </c>
     </row>
-    <row r="1010" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1010" s="3" t="s">
         <v>154</v>
       </c>
@@ -25481,11 +25520,11 @@
         <v>0.1</v>
       </c>
       <c r="G1010" s="2">
-        <f>E1010*F1010</f>
+        <f t="shared" si="14"/>
         <v>1470.576</v>
       </c>
     </row>
-    <row r="1011" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1011" s="3" t="s">
         <v>154</v>
       </c>
@@ -25505,11 +25544,11 @@
         <v>0.1</v>
       </c>
       <c r="G1011" s="2">
-        <f>E1011*F1011</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1012" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1012" s="3" t="s">
         <v>169</v>
       </c>
@@ -25529,11 +25568,11 @@
         <v>0.1</v>
       </c>
       <c r="G1012" s="2">
-        <f>E1012*F1012</f>
+        <f t="shared" si="14"/>
         <v>62.772000000000006</v>
       </c>
     </row>
-    <row r="1013" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1013" s="3" t="s">
         <v>169</v>
       </c>
@@ -25553,11 +25592,11 @@
         <v>0.1</v>
       </c>
       <c r="G1013" s="2">
-        <f>E1013*F1013</f>
+        <f t="shared" si="14"/>
         <v>411.62</v>
       </c>
     </row>
-    <row r="1014" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1014" s="3" t="s">
         <v>245</v>
       </c>
@@ -25577,11 +25616,11 @@
         <v>0.1</v>
       </c>
       <c r="G1014" s="2">
-        <f>E1014*F1014</f>
+        <f t="shared" si="14"/>
         <v>336.53400000000005</v>
       </c>
     </row>
-    <row r="1015" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1015" s="3" t="s">
         <v>245</v>
       </c>
@@ -25601,11 +25640,11 @@
         <v>0.1</v>
       </c>
       <c r="G1015" s="2">
-        <f>E1015*F1015</f>
+        <f t="shared" si="14"/>
         <v>557.37400000000002</v>
       </c>
     </row>
-    <row r="1016" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1016" s="3" t="s">
         <v>245</v>
       </c>
@@ -25625,11 +25664,11 @@
         <v>0.1</v>
       </c>
       <c r="G1016" s="2">
-        <f>E1016*F1016</f>
+        <f t="shared" si="14"/>
         <v>56.448000000000008</v>
       </c>
     </row>
-    <row r="1017" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1017" s="3" t="s">
         <v>245</v>
       </c>
@@ -25649,11 +25688,11 @@
         <v>0.1</v>
       </c>
       <c r="G1017" s="2">
-        <f>E1017*F1017</f>
+        <f t="shared" si="14"/>
         <v>58.879999999999995</v>
       </c>
     </row>
-    <row r="1018" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1018" s="3" t="s">
         <v>245</v>
       </c>
@@ -25673,11 +25712,11 @@
         <v>0.1</v>
       </c>
       <c r="G1018" s="2">
-        <f>E1018*F1018</f>
+        <f t="shared" si="14"/>
         <v>180.41600000000003</v>
       </c>
     </row>
-    <row r="1019" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1019" s="3" t="s">
         <v>245</v>
       </c>
@@ -25697,11 +25736,11 @@
         <v>0.1</v>
       </c>
       <c r="G1019" s="2">
-        <f>E1019*F1019</f>
+        <f t="shared" si="14"/>
         <v>192.96</v>
       </c>
     </row>
-    <row r="1020" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1020" s="3" t="s">
         <v>179</v>
       </c>
@@ -25721,11 +25760,11 @@
         <v>0.1</v>
       </c>
       <c r="G1020" s="2">
-        <f>E1020*F1020</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1021" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1021" s="3" t="s">
         <v>179</v>
       </c>
@@ -25745,11 +25784,11 @@
         <v>0.1</v>
       </c>
       <c r="G1021" s="2">
-        <f>E1021*F1021</f>
+        <f t="shared" si="14"/>
         <v>166.59500000000003</v>
       </c>
     </row>
-    <row r="1022" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1022" s="3" t="s">
         <v>181</v>
       </c>
@@ -25769,11 +25808,11 @@
         <v>0.1</v>
       </c>
       <c r="G1022" s="2">
-        <f>E1022*F1022</f>
+        <f t="shared" si="14"/>
         <v>86.117999999999995</v>
       </c>
     </row>
-    <row r="1023" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1023" s="3" t="s">
         <v>181</v>
       </c>
@@ -25793,11 +25832,11 @@
         <v>0.1</v>
       </c>
       <c r="G1023" s="2">
-        <f>E1023*F1023</f>
+        <f t="shared" si="14"/>
         <v>47.616000000000007</v>
       </c>
     </row>
-    <row r="1024" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1024" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1024" s="3" t="s">
         <v>181</v>
       </c>
@@ -25817,11 +25856,11 @@
         <v>0.1</v>
       </c>
       <c r="G1024" s="2">
-        <f>E1024*F1024</f>
+        <f t="shared" si="14"/>
         <v>36.036000000000001</v>
       </c>
     </row>
-    <row r="1025" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1025" s="3" t="s">
         <v>181</v>
       </c>
@@ -25841,18 +25880,18 @@
         <v>0.1</v>
       </c>
       <c r="G1025" s="2">
-        <f>E1025*F1025</f>
+        <f t="shared" si="14"/>
         <v>493.27200000000005</v>
       </c>
     </row>
-    <row r="1026" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1026" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1026" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1026" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1026" s="4" t="s">
+      <c r="C1026" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D1026" s="9">
@@ -25865,18 +25904,18 @@
         <v>0.08</v>
       </c>
       <c r="G1026" s="2">
-        <f>E1026*F1026</f>
+        <f t="shared" si="14"/>
         <v>34.06</v>
       </c>
     </row>
-    <row r="1027" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1027" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1027" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1027" s="4" t="s">
+      <c r="C1027" s="3" t="s">
         <v>252</v>
       </c>
       <c r="D1027" s="9">
@@ -25889,18 +25928,18 @@
         <v>0.08</v>
       </c>
       <c r="G1027" s="2">
-        <f>E1027*F1027</f>
+        <f t="shared" si="14"/>
         <v>43.188800000000001</v>
       </c>
     </row>
-    <row r="1028" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1028" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1028" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1028" s="4" t="s">
+      <c r="C1028" s="3" t="s">
         <v>253</v>
       </c>
       <c r="D1028" s="9">
@@ -25913,18 +25952,18 @@
         <v>0.08</v>
       </c>
       <c r="G1028" s="2">
-        <f>E1028*F1028</f>
+        <f t="shared" si="14"/>
         <v>22.568000000000001</v>
       </c>
     </row>
-    <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1029" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1029" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1029" s="4" t="s">
+      <c r="C1029" s="3" t="s">
         <v>254</v>
       </c>
       <c r="D1029" s="9">
@@ -25937,18 +25976,18 @@
         <v>0.08</v>
       </c>
       <c r="G1029" s="2">
-        <f>E1029*F1029</f>
+        <f t="shared" ref="G1029:G1195" si="15">E1029*F1029</f>
         <v>43.188800000000001</v>
       </c>
     </row>
-    <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1030" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1030" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1030" s="4" t="s">
+      <c r="C1030" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D1030" s="9">
@@ -25961,18 +26000,18 @@
         <v>0.08</v>
       </c>
       <c r="G1030" s="2">
-        <f>E1030*F1030</f>
+        <f t="shared" si="15"/>
         <v>281.85599999999999</v>
       </c>
     </row>
-    <row r="1031" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1031" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1031" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1031" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1031" s="4" t="s">
+      <c r="C1031" s="3" t="s">
         <v>226</v>
       </c>
       <c r="D1031" s="9">
@@ -25985,18 +26024,18 @@
         <v>0.08</v>
       </c>
       <c r="G1031" s="2">
-        <f>E1031*F1031</f>
+        <f t="shared" si="15"/>
         <v>63.692799999999998</v>
       </c>
     </row>
-    <row r="1032" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1032" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B1032" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C1032" s="4" t="s">
+      <c r="C1032" s="3" t="s">
         <v>255</v>
       </c>
       <c r="D1032" s="9">
@@ -26009,18 +26048,18 @@
         <v>0.08</v>
       </c>
       <c r="G1032" s="2">
-        <f>E1032*F1032</f>
+        <f t="shared" si="15"/>
         <v>54.732799999999997</v>
       </c>
     </row>
-    <row r="1033" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1033" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1033" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1033" s="4" t="s">
+      <c r="C1033" s="3" t="s">
         <v>257</v>
       </c>
       <c r="D1033" s="9">
@@ -26033,18 +26072,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1033" s="2">
-        <f>E1033*F1033</f>
+        <f t="shared" si="15"/>
         <v>410.74040000000008</v>
       </c>
     </row>
-    <row r="1034" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1034" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1034" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1034" s="4" t="s">
+      <c r="C1034" s="3" t="s">
         <v>258</v>
       </c>
       <c r="D1034" s="9">
@@ -26057,18 +26096,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1034" s="2">
-        <f>E1034*F1034</f>
+        <f t="shared" si="15"/>
         <v>119.87570000000001</v>
       </c>
     </row>
-    <row r="1035" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1035" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1035" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1035" s="4" t="s">
+      <c r="C1035" s="3" t="s">
         <v>259</v>
       </c>
       <c r="D1035" s="9">
@@ -26081,18 +26120,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1035" s="2">
-        <f>E1035*F1035</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1036" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1036" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1036" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1036" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1036" s="4" t="s">
+      <c r="C1036" s="3" t="s">
         <v>260</v>
       </c>
       <c r="D1036" s="9">
@@ -26105,18 +26144,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1036" s="2">
-        <f>E1036*F1036</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1037" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1037" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1037" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1037" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1037" s="4" t="s">
+      <c r="C1037" s="3" t="s">
         <v>261</v>
       </c>
       <c r="D1037" s="9">
@@ -26129,18 +26168,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1037" s="2">
-        <f>E1037*F1037</f>
+        <f t="shared" si="15"/>
         <v>142.27640000000002</v>
       </c>
     </row>
-    <row r="1038" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1038" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1038" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1038" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1038" s="4" t="s">
+      <c r="C1038" s="3" t="s">
         <v>262</v>
       </c>
       <c r="D1038" s="9">
@@ -26153,18 +26192,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1038" s="2">
-        <f>E1038*F1038</f>
+        <f t="shared" si="15"/>
         <v>218.67440000000002</v>
       </c>
     </row>
-    <row r="1039" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1039" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1039" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1039" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1039" s="4" t="s">
+      <c r="C1039" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D1039" s="9">
@@ -26177,18 +26216,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1039" s="2">
-        <f>E1039*F1039</f>
+        <f t="shared" si="15"/>
         <v>209.03400000000002</v>
       </c>
     </row>
-    <row r="1040" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1040" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1040" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1040" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1040" s="4" t="s">
+      <c r="C1040" s="3" t="s">
         <v>264</v>
       </c>
       <c r="D1040" s="9">
@@ -26201,18 +26240,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1040" s="2">
-        <f>E1040*F1040</f>
+        <f t="shared" si="15"/>
         <v>285.15340000000003</v>
       </c>
     </row>
-    <row r="1041" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1041" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1041" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1041" s="4" t="s">
+      <c r="C1041" s="3" t="s">
         <v>265</v>
       </c>
       <c r="D1041" s="9">
@@ -26225,18 +26264,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1041" s="2">
-        <f>E1041*F1041</f>
+        <f t="shared" si="15"/>
         <v>287.98</v>
       </c>
     </row>
-    <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1042" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1042" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1042" s="4" t="s">
+      <c r="C1042" s="3" t="s">
         <v>266</v>
       </c>
       <c r="D1042" s="9">
@@ -26249,18 +26288,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1042" s="2">
-        <f>E1042*F1042</f>
+        <f t="shared" si="15"/>
         <v>360.07650000000001</v>
       </c>
     </row>
-    <row r="1043" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1043" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B1043" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1043" s="4" t="s">
+      <c r="C1043" s="3" t="s">
         <v>267</v>
       </c>
       <c r="D1043" s="9">
@@ -26273,12 +26312,3666 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G1043" s="2">
-        <f>E1043*F1043</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
+    <row r="1044" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1044" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1044" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1044" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1044" s="13">
+        <v>683.15</v>
+      </c>
+      <c r="F1044" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1044" s="2">
+        <f t="shared" si="15"/>
+        <v>68.314999999999998</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1045" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1045" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1045" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1045" s="13">
+        <v>3415.68</v>
+      </c>
+      <c r="F1045" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1045" s="2">
+        <f t="shared" si="15"/>
+        <v>341.56799999999998</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1046" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1046" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1046" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1046" s="13">
+        <v>166.4</v>
+      </c>
+      <c r="F1046" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1046" s="2">
+        <f t="shared" si="15"/>
+        <v>16.64</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1047" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1047" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1047" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1047" s="13">
+        <v>6138.24</v>
+      </c>
+      <c r="F1047" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1047" s="2">
+        <f t="shared" si="15"/>
+        <v>613.82399999999996</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1048" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1048" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1048" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1048" s="13">
+        <v>125.44</v>
+      </c>
+      <c r="F1048" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1048" s="2">
+        <f t="shared" si="15"/>
+        <v>12.544</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1049" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1049" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1049" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1049" s="13">
+        <v>1717.89</v>
+      </c>
+      <c r="F1049" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1049" s="2">
+        <f t="shared" si="15"/>
+        <v>171.78900000000002</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1050" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1050" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1050" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1050" s="13">
+        <v>291.83999999999997</v>
+      </c>
+      <c r="F1050" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1050" s="2">
+        <f t="shared" si="15"/>
+        <v>29.183999999999997</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1051" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1051" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1051" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1051" s="13">
+        <v>1381.15</v>
+      </c>
+      <c r="F1051" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1051" s="2">
+        <f t="shared" si="15"/>
+        <v>138.11500000000001</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1052" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1052" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1052" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1052" s="13">
+        <v>11198.72</v>
+      </c>
+      <c r="F1052" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1052" s="2">
+        <f t="shared" si="15"/>
+        <v>1119.8720000000001</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1053" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1053" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1053" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1053" s="13">
+        <v>369.27</v>
+      </c>
+      <c r="F1053" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1053" s="2">
+        <f t="shared" si="15"/>
+        <v>36.927</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1054" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1054" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1054" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1054" s="13">
+        <v>559.1</v>
+      </c>
+      <c r="F1054" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1054" s="2">
+        <f t="shared" si="15"/>
+        <v>55.910000000000004</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1055" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1055" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1055" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1055" s="14">
+        <v>11661.32</v>
+      </c>
+      <c r="F1055" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1055" s="2">
+        <f t="shared" si="15"/>
+        <v>1166.1320000000001</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1056" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1056" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1056" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1056" s="14">
+        <v>6789.76</v>
+      </c>
+      <c r="F1056" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1056" s="2">
+        <f t="shared" si="15"/>
+        <v>543.18079999999998</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1057" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1057" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1057" s="14">
+        <v>6286.72</v>
+      </c>
+      <c r="F1057" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1057" s="2">
+        <f t="shared" si="15"/>
+        <v>502.93760000000003</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1058" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1058" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1058" s="14">
+        <v>2650.88</v>
+      </c>
+      <c r="F1058" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1058" s="2">
+        <f t="shared" si="15"/>
+        <v>212.07040000000001</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1059" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1059" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1059" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1059" s="14">
+        <v>1660.16</v>
+      </c>
+      <c r="F1059" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1059" s="2">
+        <f t="shared" si="15"/>
+        <v>132.81280000000001</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1060" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1060" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1060" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1060" s="14">
+        <v>2101.12</v>
+      </c>
+      <c r="F1060" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1060" s="2">
+        <f t="shared" si="15"/>
+        <v>168.08959999999999</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1061" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1061" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1061" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1061" s="14">
+        <v>1854.72</v>
+      </c>
+      <c r="F1061" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1061" s="2">
+        <f t="shared" si="15"/>
+        <v>148.3776</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1062" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1062" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1062" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1062" s="14">
+        <v>2394.2800000000002</v>
+      </c>
+      <c r="F1062" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1062" s="2">
+        <f t="shared" si="15"/>
+        <v>191.54240000000001</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1063" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1063" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1063" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1063" s="14">
+        <v>2738.36</v>
+      </c>
+      <c r="F1063" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1063" s="2">
+        <f t="shared" si="15"/>
+        <v>219.06880000000001</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1064" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1064" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1064" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1064" s="14">
+        <v>4755.24</v>
+      </c>
+      <c r="F1064" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1064" s="2">
+        <f t="shared" si="15"/>
+        <v>380.41919999999999</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1065" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1065" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1065" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1065" s="14">
+        <v>2403</v>
+      </c>
+      <c r="F1065" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1065" s="2">
+        <f t="shared" si="15"/>
+        <v>192.24</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1066" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1066" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1066" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1066" s="14">
+        <v>707.52</v>
+      </c>
+      <c r="F1066" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1066" s="2">
+        <f t="shared" si="15"/>
+        <v>56.601599999999998</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1067" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1067" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1067" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1067" s="14">
+        <v>513.48</v>
+      </c>
+      <c r="F1067" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1067" s="2">
+        <f t="shared" si="15"/>
+        <v>41.078400000000002</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1068" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1068" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1068" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1068" s="14">
+        <v>1335.69</v>
+      </c>
+      <c r="F1068" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1068" s="2">
+        <f t="shared" si="15"/>
+        <v>106.85520000000001</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1069" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1069" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1069" s="14">
+        <v>393.36</v>
+      </c>
+      <c r="F1069" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1069" s="2">
+        <f t="shared" si="15"/>
+        <v>31.468800000000002</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1070" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1070" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1070" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1070" s="14">
+        <v>1272.3399999999999</v>
+      </c>
+      <c r="F1070" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1070" s="2">
+        <f t="shared" si="15"/>
+        <v>101.7872</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1071" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1071" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1071" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1071" s="14">
+        <v>1329.9</v>
+      </c>
+      <c r="F1071" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1071" s="2">
+        <f t="shared" si="15"/>
+        <v>106.39200000000001</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1072" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1072" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1072" s="14">
+        <v>282.74</v>
+      </c>
+      <c r="F1072" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1072" s="2">
+        <f t="shared" si="15"/>
+        <v>22.619200000000003</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1073" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1073" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1073" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1073" s="14">
+        <v>146.06</v>
+      </c>
+      <c r="F1073" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1073" s="2">
+        <f t="shared" si="15"/>
+        <v>11.684800000000001</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1074" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1074" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1074" s="14">
+        <v>469.09</v>
+      </c>
+      <c r="F1074" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1074" s="2">
+        <f t="shared" si="15"/>
+        <v>37.527200000000001</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1075" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1075" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1075" s="14">
+        <v>314.87</v>
+      </c>
+      <c r="F1075" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1075" s="2">
+        <f t="shared" si="15"/>
+        <v>25.189600000000002</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1076" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1076" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1076" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1076" s="14">
+        <v>297.01</v>
+      </c>
+      <c r="F1076" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1076" s="2">
+        <f t="shared" si="15"/>
+        <v>23.7608</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1077" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1077" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1077" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1077" s="14">
+        <v>300.83</v>
+      </c>
+      <c r="F1077" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1077" s="2">
+        <f t="shared" si="15"/>
+        <v>24.066399999999998</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1078" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1078" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1078" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1078" s="14">
+        <v>820.08</v>
+      </c>
+      <c r="F1078" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1078" s="2">
+        <f t="shared" si="15"/>
+        <v>65.606400000000008</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1079" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1079" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1079" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1079" s="14">
+        <v>600.32000000000005</v>
+      </c>
+      <c r="F1079" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1079" s="2">
+        <f t="shared" si="15"/>
+        <v>48.025600000000004</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1080" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1080" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1080" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1080" s="14">
+        <v>1434.84</v>
+      </c>
+      <c r="F1080" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1080" s="2">
+        <f t="shared" si="15"/>
+        <v>114.7872</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1081" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1081" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1081" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1081" s="14">
+        <v>1183.3800000000001</v>
+      </c>
+      <c r="F1081" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1081" s="2">
+        <f t="shared" si="15"/>
+        <v>94.670400000000015</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1082" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1082" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1082" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1082" s="14">
+        <v>4504.8999999999996</v>
+      </c>
+      <c r="F1082" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1082" s="2">
+        <f t="shared" si="15"/>
+        <v>225.245</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1083" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1083" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1083" s="14">
+        <v>2744.3</v>
+      </c>
+      <c r="F1083" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1083" s="2">
+        <f t="shared" si="15"/>
+        <v>137.215</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1084" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1084" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1084" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1084" s="14">
+        <v>3323.32</v>
+      </c>
+      <c r="F1084" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1084" s="2">
+        <f t="shared" si="15"/>
+        <v>166.16600000000003</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1085" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1085" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1085" s="14">
+        <v>2888.96</v>
+      </c>
+      <c r="F1085" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1085" s="2">
+        <f t="shared" si="15"/>
+        <v>144.44800000000001</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1086" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1086" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1086" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1086" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1086" s="14">
+        <v>2286.7199999999998</v>
+      </c>
+      <c r="F1086" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1086" s="2">
+        <f t="shared" si="15"/>
+        <v>114.336</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1087" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1087" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1087" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1087" s="14">
+        <v>2632.01</v>
+      </c>
+      <c r="F1087" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1087" s="2">
+        <f t="shared" si="15"/>
+        <v>131.60050000000001</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1088" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1088" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1088" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1088" s="14">
+        <v>2039.04</v>
+      </c>
+      <c r="F1088" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1088" s="2">
+        <f t="shared" si="15"/>
+        <v>101.952</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1089" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1089" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1089" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1089" s="14">
+        <v>1964.3</v>
+      </c>
+      <c r="F1089" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1089" s="2">
+        <f t="shared" si="15"/>
+        <v>98.215000000000003</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1090" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1090" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1090" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1090" s="14">
+        <v>4315.74</v>
+      </c>
+      <c r="F1090" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1090" s="2">
+        <f t="shared" si="15"/>
+        <v>215.78700000000001</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1091" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1091" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1091" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1091" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1091" s="14">
+        <v>9716.9599999999991</v>
+      </c>
+      <c r="F1091" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1091" s="2">
+        <f t="shared" si="15"/>
+        <v>485.84799999999996</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1092" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1092" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1092" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1092" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1092" s="14">
+        <v>12242.56</v>
+      </c>
+      <c r="F1092" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1092" s="2">
+        <f t="shared" si="15"/>
+        <v>612.12800000000004</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1093" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1093" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1093" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1093" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1093" s="14">
+        <v>4918.3999999999996</v>
+      </c>
+      <c r="F1093" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1093" s="2">
+        <f t="shared" si="15"/>
+        <v>245.92</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1094" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1094" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1094" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1094" s="14">
+        <v>9003.7999999999993</v>
+      </c>
+      <c r="F1094" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1094" s="2">
+        <f t="shared" si="15"/>
+        <v>450.19</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1095" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1095" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1095" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1095" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1095" s="14">
+        <v>3050.95</v>
+      </c>
+      <c r="F1095" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1095" s="2">
+        <f t="shared" si="15"/>
+        <v>152.54749999999999</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1096" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1096" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1096" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1096" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1096" s="14">
+        <v>862.55</v>
+      </c>
+      <c r="F1096" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1096" s="2">
+        <f t="shared" si="15"/>
+        <v>43.127499999999998</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1097" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1097" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1097" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1097" s="14">
+        <v>5253.28</v>
+      </c>
+      <c r="F1097" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1097" s="2">
+        <f t="shared" si="15"/>
+        <v>262.66399999999999</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1098" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1098" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1098" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1098" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1098" s="14">
+        <v>3935.1</v>
+      </c>
+      <c r="F1098" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1098" s="2">
+        <f t="shared" si="15"/>
+        <v>196.755</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1099" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1099" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1099" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1099" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1099" s="14">
+        <v>594.55999999999995</v>
+      </c>
+      <c r="F1099" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1099" s="2">
+        <f t="shared" si="15"/>
+        <v>29.727999999999998</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1100" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1100" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1100" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1100" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1100" s="14">
+        <v>5455.36</v>
+      </c>
+      <c r="F1100" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1100" s="2">
+        <f t="shared" si="15"/>
+        <v>272.76799999999997</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1101" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1101" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1101" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1101" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1101" s="14">
+        <v>9571.84</v>
+      </c>
+      <c r="F1101" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1101" s="2">
+        <f t="shared" si="15"/>
+        <v>478.59200000000004</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1102" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1102" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1102" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1102" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1102" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1102" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1102" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1103" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1103" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1103" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1103" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1103" s="14">
+        <v>61.44</v>
+      </c>
+      <c r="F1103" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1103" s="2">
+        <f t="shared" si="15"/>
+        <v>3.0720000000000001</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1104" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1104" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1104" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1104" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1104" s="14">
+        <v>956.8</v>
+      </c>
+      <c r="F1104" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1104" s="2">
+        <f t="shared" si="15"/>
+        <v>47.84</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1105" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1105" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1105" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1105" s="14">
+        <v>4974.9399999999996</v>
+      </c>
+      <c r="F1105" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1105" s="2">
+        <f t="shared" si="15"/>
+        <v>248.74699999999999</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1106" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1106" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1106" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1106" s="14">
+        <v>5052.16</v>
+      </c>
+      <c r="F1106" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1106" s="2">
+        <f t="shared" si="15"/>
+        <v>252.608</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1107" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1107" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1107" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1107" s="14">
+        <v>7214.72</v>
+      </c>
+      <c r="F1107" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1107" s="2">
+        <f t="shared" si="15"/>
+        <v>360.73600000000005</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1108" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1108" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1108" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1108" s="14">
+        <v>7229.3</v>
+      </c>
+      <c r="F1108" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1108" s="2">
+        <f t="shared" si="15"/>
+        <v>361.46500000000003</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1109" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1109" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1109" s="14">
+        <v>7229.3</v>
+      </c>
+      <c r="F1109" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1109" s="2">
+        <f t="shared" si="15"/>
+        <v>361.46500000000003</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1110" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1110" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1110" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1110" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1110" s="14">
+        <v>5358.51</v>
+      </c>
+      <c r="F1110" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1110" s="2">
+        <f t="shared" si="15"/>
+        <v>428.68080000000003</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1111" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1111" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1111" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1111" s="14">
+        <v>325.04000000000002</v>
+      </c>
+      <c r="F1111" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1111" s="2">
+        <f t="shared" si="15"/>
+        <v>26.003200000000003</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1112" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1112" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1112" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1112" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1112" s="14">
+        <v>290.52</v>
+      </c>
+      <c r="F1112" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1112" s="2">
+        <f t="shared" si="15"/>
+        <v>23.241599999999998</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1113" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1113" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1113" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1113" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1113" s="14">
+        <v>577.26</v>
+      </c>
+      <c r="F1113" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1113" s="2">
+        <f t="shared" si="15"/>
+        <v>46.180799999999998</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1114" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1114" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1114" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1114" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1114" s="14">
+        <v>225.18</v>
+      </c>
+      <c r="F1114" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1114" s="2">
+        <f t="shared" si="15"/>
+        <v>18.014400000000002</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1115" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1115" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1115" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1115" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1115" s="14">
+        <v>1469.98</v>
+      </c>
+      <c r="F1115" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1115" s="2">
+        <f t="shared" si="15"/>
+        <v>117.5984</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1116" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1116" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1116" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1116" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1116" s="14">
+        <v>1122</v>
+      </c>
+      <c r="F1116" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1116" s="2">
+        <f t="shared" si="15"/>
+        <v>89.76</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1117" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1117" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1117" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1117" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1117" s="14">
+        <v>4268.16</v>
+      </c>
+      <c r="F1117" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1117" s="2">
+        <f t="shared" si="15"/>
+        <v>341.45279999999997</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1118" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1118" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1118" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1118" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1118" s="14">
+        <v>1263.9000000000001</v>
+      </c>
+      <c r="F1118" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1118" s="2">
+        <f t="shared" si="15"/>
+        <v>101.11200000000001</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1119" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1119" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1119" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1119" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1119" s="14">
+        <v>664.62</v>
+      </c>
+      <c r="F1119" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1119" s="2">
+        <f t="shared" si="15"/>
+        <v>53.169600000000003</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1120" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1120" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1120" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1120" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1120" s="14">
+        <v>6810.48</v>
+      </c>
+      <c r="F1120" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1120" s="2">
+        <f t="shared" si="15"/>
+        <v>544.83839999999998</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1121" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1121" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1121" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1121" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1121" s="14">
+        <v>10057.219999999999</v>
+      </c>
+      <c r="F1121" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1121" s="2">
+        <f t="shared" si="15"/>
+        <v>804.57759999999996</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1122" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1122" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1122" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1122" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1122" s="14">
+        <v>330.24</v>
+      </c>
+      <c r="F1122" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1122" s="2">
+        <f t="shared" si="15"/>
+        <v>26.4192</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1123" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1123" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1123" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1123" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1123" s="14">
+        <v>5333.25</v>
+      </c>
+      <c r="F1123" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1123" s="2">
+        <f t="shared" si="15"/>
+        <v>426.66</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1124" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1124" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1124" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1124" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1124" s="14">
+        <v>2618.85</v>
+      </c>
+      <c r="F1124" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1124" s="2">
+        <f t="shared" si="15"/>
+        <v>209.50800000000001</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1125" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1125" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1125" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1125" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1125" s="14">
+        <v>5594.98</v>
+      </c>
+      <c r="F1125" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1125" s="2">
+        <f t="shared" si="15"/>
+        <v>447.59839999999997</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1126" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1126" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1126" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1126" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1126" s="14">
+        <v>4387.84</v>
+      </c>
+      <c r="F1126" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1126" s="2">
+        <f t="shared" si="15"/>
+        <v>351.02719999999999</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1127" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1127" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1127" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1127" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1127" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1127" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1127" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1128" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1128" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1128" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1128" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1128" s="14">
+        <v>2770.69</v>
+      </c>
+      <c r="F1128" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1128" s="2">
+        <f t="shared" si="15"/>
+        <v>221.65520000000001</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1129" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1129" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1129" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1129" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1129" s="14">
+        <v>216.32</v>
+      </c>
+      <c r="F1129" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1129" s="2">
+        <f t="shared" si="15"/>
+        <v>17.305599999999998</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1130" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1130" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1130" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1130" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1130" s="14">
+        <v>2572.56</v>
+      </c>
+      <c r="F1130" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1130" s="2">
+        <f t="shared" si="15"/>
+        <v>205.8048</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1131" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1131" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1131" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1131" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1131" s="14">
+        <v>6382.8</v>
+      </c>
+      <c r="F1131" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1131" s="2">
+        <f t="shared" si="15"/>
+        <v>510.62400000000002</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1132" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1132" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1132" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1132" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1132" s="14">
+        <v>665.28</v>
+      </c>
+      <c r="F1132" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1132" s="2">
+        <f t="shared" si="15"/>
+        <v>53.2224</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1133" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1133" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1133" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1133" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1133" s="14">
+        <v>5653.76</v>
+      </c>
+      <c r="F1133" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1133" s="2">
+        <f t="shared" si="15"/>
+        <v>452.30080000000004</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1134" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1134" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1134" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1134" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1134" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1134" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1134" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1135" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1135" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1135" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1135" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1135" s="14">
+        <v>1584.4</v>
+      </c>
+      <c r="F1135" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1135" s="2">
+        <f t="shared" si="15"/>
+        <v>126.75200000000001</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1136" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1136" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1136" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1136" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1136" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1136" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1136" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1137" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1137" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1137" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1137" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1137" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1137" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1137" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1138" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1138" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1138" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1138" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1138" s="14">
+        <v>1737.72</v>
+      </c>
+      <c r="F1138" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1138" s="2">
+        <f t="shared" si="15"/>
+        <v>173.77200000000002</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1139" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1139" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1139" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1139" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1139" s="14">
+        <v>1226.43</v>
+      </c>
+      <c r="F1139" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1139" s="2">
+        <f t="shared" si="15"/>
+        <v>122.64300000000001</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1140" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1140" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1140" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1140" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1140" s="14">
+        <v>5040.8999999999996</v>
+      </c>
+      <c r="F1140" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1140" s="2">
+        <f t="shared" si="15"/>
+        <v>504.09</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1141" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1141" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1141" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1141" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1141" s="14">
+        <v>106.38</v>
+      </c>
+      <c r="F1141" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1141" s="2">
+        <f t="shared" si="15"/>
+        <v>10.638</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1142" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1142" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1142" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1142" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1142" s="14">
+        <v>3202.56</v>
+      </c>
+      <c r="F1142" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1142" s="2">
+        <f t="shared" si="15"/>
+        <v>320.25600000000003</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1143" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1143" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1143" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1143" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1143" s="14">
+        <v>6805.5</v>
+      </c>
+      <c r="F1143" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1143" s="2">
+        <f t="shared" si="15"/>
+        <v>680.55000000000007</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1144" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1144" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1144" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1144" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1144" s="14">
+        <v>613.76</v>
+      </c>
+      <c r="F1144" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1144" s="2">
+        <f t="shared" si="15"/>
+        <v>61.376000000000005</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1145" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1145" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1145" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1145" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1145" s="14">
+        <v>935.68</v>
+      </c>
+      <c r="F1145" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1145" s="2">
+        <f t="shared" si="15"/>
+        <v>93.567999999999998</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1146" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1146" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1146" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1146" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1146" s="14">
+        <v>1500.8</v>
+      </c>
+      <c r="F1146" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1146" s="2">
+        <f t="shared" si="15"/>
+        <v>150.08000000000001</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1147" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1147" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1147" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1147" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1147" s="14">
+        <v>1427.84</v>
+      </c>
+      <c r="F1147" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1147" s="2">
+        <f t="shared" si="15"/>
+        <v>142.78399999999999</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1148" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1148" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1148" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1148" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1148" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1148" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1148" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1149" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1149" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1149" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1149" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1149" s="14">
+        <v>3125.1</v>
+      </c>
+      <c r="F1149" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1149" s="2">
+        <f t="shared" si="15"/>
+        <v>312.51</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1150" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1150" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1150" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1150" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1150" s="14">
+        <v>6624</v>
+      </c>
+      <c r="F1150" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1150" s="2">
+        <f t="shared" si="15"/>
+        <v>662.40000000000009</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1151" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1151" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1151" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1151" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1151" s="14">
+        <v>2934</v>
+      </c>
+      <c r="F1151" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1151" s="2">
+        <f t="shared" si="15"/>
+        <v>293.40000000000003</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1152" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1152" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1152" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1152" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1152" s="14">
+        <v>9561.2199999999993</v>
+      </c>
+      <c r="F1152" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1152" s="2">
+        <f t="shared" si="15"/>
+        <v>956.12199999999996</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1153" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1153" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1153" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1153" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1153" s="14">
+        <v>6443</v>
+      </c>
+      <c r="F1153" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1153" s="2">
+        <f t="shared" si="15"/>
+        <v>644.30000000000007</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1154" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1154" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1154" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1154" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1154" s="14">
+        <v>1269.18</v>
+      </c>
+      <c r="F1154" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1154" s="2">
+        <f t="shared" si="15"/>
+        <v>126.91800000000001</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1155" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1155" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1155" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1155" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1155" s="14">
+        <v>1411.74</v>
+      </c>
+      <c r="F1155" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1155" s="2">
+        <f t="shared" si="15"/>
+        <v>141.17400000000001</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1156" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1156" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1156" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1156" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1156" s="14">
+        <v>2166.9</v>
+      </c>
+      <c r="F1156" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1156" s="2">
+        <f t="shared" si="15"/>
+        <v>216.69000000000003</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1157" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1157" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1157" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1157" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1157" s="14">
+        <v>2654.22</v>
+      </c>
+      <c r="F1157" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1157" s="2">
+        <f t="shared" si="15"/>
+        <v>265.42199999999997</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1158" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1158" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1158" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1158" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1158" s="14">
+        <v>4081.77</v>
+      </c>
+      <c r="F1158" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1158" s="2">
+        <f t="shared" si="15"/>
+        <v>408.17700000000002</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1159" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1159" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1159" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1159" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1159" s="14">
+        <v>2490.84</v>
+      </c>
+      <c r="F1159" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1159" s="2">
+        <f t="shared" si="15"/>
+        <v>249.08400000000003</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1160" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1160" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1160" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1160" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1160" s="14">
+        <v>4449.0600000000004</v>
+      </c>
+      <c r="F1160" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1160" s="2">
+        <f t="shared" si="15"/>
+        <v>444.90600000000006</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1161" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1161" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1161" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1161" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1161" s="14">
+        <v>3475.84</v>
+      </c>
+      <c r="F1161" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1161" s="2">
+        <f t="shared" si="15"/>
+        <v>347.58400000000006</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1162" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1162" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1162" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1162" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1162" s="14">
+        <v>208.56</v>
+      </c>
+      <c r="F1162" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1162" s="2">
+        <f t="shared" si="15"/>
+        <v>20.856000000000002</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1163" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1163" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1163" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1163" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1163" s="14">
+        <v>6753.37</v>
+      </c>
+      <c r="F1163" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1163" s="2">
+        <f t="shared" si="15"/>
+        <v>675.33699999999999</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1164" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1164" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1164" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1164" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1164" s="14">
+        <v>12955.14</v>
+      </c>
+      <c r="F1164" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1164" s="2">
+        <f t="shared" si="15"/>
+        <v>1295.5140000000001</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1165" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1165" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1165" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1165" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1165" s="14">
+        <v>0</v>
+      </c>
+      <c r="F1165" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1165" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1166" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1166" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1166" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1166" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1166" s="14">
+        <v>1285.3499999999999</v>
+      </c>
+      <c r="F1166" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1166" s="2">
+        <f t="shared" si="15"/>
+        <v>128.535</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1167" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1167" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1167" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1167" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1167" s="14">
+        <v>3700.4</v>
+      </c>
+      <c r="F1167" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1167" s="2">
+        <f t="shared" si="15"/>
+        <v>370.04</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1168" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1168" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1168" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1168" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1168" s="14">
+        <v>2961.42</v>
+      </c>
+      <c r="F1168" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1168" s="2">
+        <f t="shared" si="15"/>
+        <v>296.142</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1169" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1169" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1169" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1169" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1169" s="14">
+        <v>6204.2</v>
+      </c>
+      <c r="F1169" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1169" s="2">
+        <f t="shared" si="15"/>
+        <v>620.42000000000007</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1170" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1170" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1170" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1170" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1170" s="14">
+        <v>1264</v>
+      </c>
+      <c r="F1170" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1170" s="2">
+        <f t="shared" si="15"/>
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1171" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1171" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1171" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1171" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1171" s="14">
+        <v>3433.6</v>
+      </c>
+      <c r="F1171" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1171" s="2">
+        <f t="shared" si="15"/>
+        <v>343.36</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1172" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1172" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1172" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1172" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1172" s="14">
+        <v>2128.64</v>
+      </c>
+      <c r="F1172" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1172" s="2">
+        <f>E1172*F1172</f>
+        <v>212.864</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1173" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1173" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1173" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1173" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1173" s="14">
+        <v>874.9</v>
+      </c>
+      <c r="F1173" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1173" s="2">
+        <f>E1173*F1173</f>
+        <v>87.490000000000009</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1174" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1174" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1174" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1174" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1174" s="14">
+        <v>666.5</v>
+      </c>
+      <c r="F1174" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1174" s="2">
+        <f t="shared" si="15"/>
+        <v>66.650000000000006</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1175" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1175" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1175" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1175" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1175" s="14">
+        <v>504.68</v>
+      </c>
+      <c r="F1175" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1175" s="2">
+        <f t="shared" si="15"/>
+        <v>50.468000000000004</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1176" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1176" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1176" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1176" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1176" s="14">
+        <v>382.14</v>
+      </c>
+      <c r="F1176" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1176" s="2">
+        <f t="shared" si="15"/>
+        <v>38.213999999999999</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1177" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1177" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1177" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1177" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1177" s="14">
+        <v>4835.38</v>
+      </c>
+      <c r="F1177" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1177" s="2">
+        <f t="shared" si="15"/>
+        <v>483.53800000000001</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1178" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1178" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1178" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1178" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1178" s="14">
+        <v>372.45</v>
+      </c>
+      <c r="F1178" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1178" s="2">
+        <f t="shared" si="15"/>
+        <v>29.795999999999999</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1179" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1179" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1179" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1179" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1179" s="14">
+        <v>1017.25</v>
+      </c>
+      <c r="F1179" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1179" s="2">
+        <f t="shared" si="15"/>
+        <v>81.38</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1180" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1180" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1180" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1180" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1180" s="14">
+        <v>247</v>
+      </c>
+      <c r="F1180" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1180" s="2">
+        <f t="shared" si="15"/>
+        <v>19.760000000000002</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1181" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1181" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1181" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1181" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1181" s="14">
+        <v>889.2</v>
+      </c>
+      <c r="F1181" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1181" s="2">
+        <f t="shared" si="15"/>
+        <v>71.13600000000001</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1182" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1182" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1182" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1182" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1182" s="14">
+        <v>3033.6</v>
+      </c>
+      <c r="F1182" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1182" s="2">
+        <f t="shared" si="15"/>
+        <v>242.68799999999999</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1183" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1183" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1183" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1183" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1183" s="14">
+        <v>6113.28</v>
+      </c>
+      <c r="F1183" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1183" s="2">
+        <f t="shared" si="15"/>
+        <v>489.06239999999997</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1184" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1184" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1184" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1184" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1184" s="14">
+        <v>1429.12</v>
+      </c>
+      <c r="F1184" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1184" s="2">
+        <f t="shared" si="15"/>
+        <v>114.3296</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1185" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1185" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1185" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1185" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1185" s="14">
+        <v>7775.12</v>
+      </c>
+      <c r="F1185" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1185" s="2">
+        <f t="shared" si="15"/>
+        <v>544.25840000000005</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1186" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1186" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1186" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1186" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1186" s="14">
+        <v>2951.88</v>
+      </c>
+      <c r="F1186" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1186" s="2">
+        <f t="shared" si="15"/>
+        <v>206.63160000000002</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1187" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1187" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1187" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1187" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1187" s="14">
+        <v>724.88</v>
+      </c>
+      <c r="F1187" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1187" s="2">
+        <f t="shared" si="15"/>
+        <v>50.741600000000005</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1188" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1188" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1188" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1188" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1188" s="14">
+        <v>1906.58</v>
+      </c>
+      <c r="F1188" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1188" s="2">
+        <f t="shared" si="15"/>
+        <v>133.4606</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1189" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1189" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1189" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1189" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1189" s="14">
+        <v>2732.77</v>
+      </c>
+      <c r="F1189" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1189" s="2">
+        <f t="shared" si="15"/>
+        <v>191.29390000000001</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1190" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1190" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1190" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1190" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1190" s="14">
+        <v>3241.56</v>
+      </c>
+      <c r="F1190" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1190" s="2">
+        <f t="shared" si="15"/>
+        <v>226.90920000000003</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1191" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1191" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1191" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1191" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1191" s="14">
+        <v>2979.2</v>
+      </c>
+      <c r="F1191" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1191" s="2">
+        <f t="shared" si="15"/>
+        <v>208.54400000000001</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1192" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1192" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1192" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1192" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1192" s="14">
+        <v>4421.6899999999996</v>
+      </c>
+      <c r="F1192" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1192" s="2">
+        <f t="shared" si="15"/>
+        <v>309.51830000000001</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1193" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1193" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1193" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1193" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1193" s="14">
+        <v>4322.76</v>
+      </c>
+      <c r="F1193" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1193" s="2">
+        <f t="shared" si="15"/>
+        <v>302.59320000000002</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1194" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1194" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1194" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1194" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1194" s="14">
+        <v>5728.28</v>
+      </c>
+      <c r="F1194" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1194" s="2">
+        <f t="shared" si="15"/>
+        <v>400.9796</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1195" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1195" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1195" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1195" s="9">
+        <v>46204</v>
+      </c>
+      <c r="E1195" s="14">
+        <v>3080.7</v>
+      </c>
+      <c r="F1195" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1195" s="2">
+        <f t="shared" si="15"/>
+        <v>215.649</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G363" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G1195" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <ignoredErrors>
